--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/3) Planning BOM/1) Shopify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{3DAB9BDB-8833-4CFF-ACEA-4394D2550275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012C0654-48D5-4A09-A2DC-1ACEFABA829F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA863C65-E04D-40BB-AD90-C4169AB2BA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -346,8 +346,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,7 +370,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls driveId="b!HTnOnJwPMEWf4Qc1OT0tJzUXtA3JA_dFmeLcrifvRQA3dGqF56dSRIF8RuQ19ZxM" itemId="01FHB6EQ4WFPYOBAHH6NC22UE5IJXHENMZ">
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -3164,7 +3163,7 @@
             <v>LL-16-3337</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Premium #4 - Seniros #1</v>
+            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
           </cell>
         </row>
         <row r="348">
@@ -3172,7 +3171,7 @@
             <v>LL-16-3388</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Premium #5 - Seniros #2</v>
+            <v>FlowArt: Premium #5 - Large Dot - Cozy</v>
           </cell>
         </row>
         <row r="349">
@@ -3273,2126 +3272,2214 @@
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Cross-Stitch: [Floral - name TBD]</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Cross-Stitch: [Cheeky Sayings - name TBD]</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Embroidery: [Landscapes - name TBD]</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
+            <v>LL-30-3359</v>
+          </cell>
+          <cell r="G405" t="str">
+            <v>FlowArt Mini EXPRESS, #12</v>
+          </cell>
+        </row>
+        <row r="406">
+          <cell r="F406" t="str">
+            <v>LL-30-3360</v>
+          </cell>
+          <cell r="G406" t="str">
+            <v>FlowArt Mini EXPRESS, #13</v>
+          </cell>
+        </row>
+        <row r="407">
+          <cell r="F407" t="str">
+            <v>LL-30-3361</v>
+          </cell>
+          <cell r="G407" t="str">
+            <v>FlowArt Mini EXPRESS, #14</v>
+          </cell>
+        </row>
+        <row r="408">
+          <cell r="F408" t="str">
             <v>LL-30-3362</v>
           </cell>
-          <cell r="G405" t="str">
+          <cell r="G408" t="str">
             <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
-        <row r="406">
-          <cell r="F406">
+        <row r="409">
+          <cell r="F409" t="str">
+            <v>LL-30-3405</v>
+          </cell>
+          <cell r="G409" t="str">
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+          </cell>
+        </row>
+        <row r="410">
+          <cell r="F410" t="str">
+            <v>LL-30-3406</v>
+          </cell>
+          <cell r="G410" t="str">
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+          </cell>
+        </row>
+        <row r="411">
+          <cell r="F411">
             <v>167001</v>
           </cell>
-          <cell r="G406" t="str">
+          <cell r="G411" t="str">
             <v>FlowCrafts: Paper Flower Bouquet</v>
           </cell>
         </row>
-        <row r="407">
-          <cell r="F407">
+        <row r="412">
+          <cell r="F412">
             <v>167002</v>
           </cell>
-          <cell r="G407" t="str">
+          <cell r="G412" t="str">
             <v>FlowCrafts: Collage Art</v>
           </cell>
         </row>
-        <row r="408">
-          <cell r="F408">
+        <row r="413">
+          <cell r="F413">
             <v>167004</v>
           </cell>
-          <cell r="G408" t="str">
+          <cell r="G413" t="str">
             <v>FlowCrafts: Layered Wooden Wall Art</v>
           </cell>
         </row>
-        <row r="409">
-          <cell r="F409">
+        <row r="414">
+          <cell r="F414">
             <v>167005</v>
           </cell>
-          <cell r="G409" t="str">
+          <cell r="G414" t="str">
             <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
-        <row r="410">
-          <cell r="F410">
+        <row r="415">
+          <cell r="F415">
             <v>167006</v>
           </cell>
-          <cell r="G410" t="str">
+          <cell r="G415" t="str">
             <v>FlowCrafts: Decorative Tile Lamp</v>
-          </cell>
-        </row>
-        <row r="411">
-          <cell r="F411" t="str">
-            <v>LL-98-3188</v>
-          </cell>
-          <cell r="G411" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="412">
-          <cell r="F412" t="str">
-            <v>LL-98-3189</v>
-          </cell>
-          <cell r="G412" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="413">
-          <cell r="F413" t="str">
-            <v>LL-98-3190</v>
-          </cell>
-          <cell r="G413" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="414">
-          <cell r="F414" t="str">
-            <v>LL-98-3191</v>
-          </cell>
-          <cell r="G414" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="415">
-          <cell r="F415" t="str">
-            <v>LL-98-3025</v>
-          </cell>
-          <cell r="G415" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-98-3026</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-98-3027</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-98-3028</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-98-3091</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-98-3168</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="421">
           <cell r="F421" t="str">
-            <v>LL-98-3169</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="422">
           <cell r="F422" t="str">
-            <v>LL-98-3170</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="423">
           <cell r="F423" t="str">
-            <v>LL-98-3307</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="424">
           <cell r="F424" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="425">
           <cell r="F425" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="434">
           <cell r="F434" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G437" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G438" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="439">
           <cell r="F439" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G439" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="440">
           <cell r="F440" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G440" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="441">
           <cell r="F441" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G441" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="442">
           <cell r="F442" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G442" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="443">
           <cell r="F443" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="444">
           <cell r="F444" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="445">
           <cell r="F445" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="446">
           <cell r="F446" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-11-2522</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G450" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-11-2523</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G451" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G452" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G453" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="454">
-          <cell r="F454">
-            <v>989514</v>
+          <cell r="F454" t="str">
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G454" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="455">
-          <cell r="F455">
-            <v>989525</v>
+          <cell r="F455" t="str">
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G455" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="456">
           <cell r="F456" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G456" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="457">
           <cell r="F457" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G457" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="458">
           <cell r="F458" t="str">
-            <v>11-2506-CP12</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G458" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="459">
           <cell r="F459" t="str">
-            <v>LL-99-3076</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G459" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="460">
           <cell r="F460" t="str">
-            <v>LL-99-3077</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G460" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-99-3089</v>
+            <v>LL-11-2522</v>
           </cell>
           <cell r="G461" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-99-3090</v>
+            <v>LL-11-2523</v>
           </cell>
           <cell r="G462" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G463" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-12-3161</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G464" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="465">
-          <cell r="F465" t="str">
-            <v>LL-12-3172</v>
+          <cell r="F465">
+            <v>989514</v>
           </cell>
           <cell r="G465" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="466">
-          <cell r="F466" t="str">
-            <v>LL-12-3196</v>
+          <cell r="F466">
+            <v>989525</v>
           </cell>
           <cell r="G466" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-12-3197</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G467" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-12-3215</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G468" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>LL-12-3216</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G469" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-12-3330</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G470" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-12-3331</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G471" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-12-3332</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G472" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G473" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G474" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="475">
           <cell r="F475" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G475" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="476">
           <cell r="F476" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G476" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G477" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G478" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G479" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G480" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G481" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G482" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G483" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G484" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G485" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v>Lifelines Analog Bag 2026</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G486" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G487" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G488" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G489" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G490" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G491" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G492" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="493">
           <cell r="F493" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="494">
           <cell r="F494" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G494" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G495" t="str">
-            <v>FlowArt Home for the Holidays Scented Hidden Pattern - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G496" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="497">
           <cell r="F497" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G497" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbred Shop - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="498">
           <cell r="F498" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G498" t="str">
-            <v>FlowArt Dot-By-Letter: Frosty Fun - WMT</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G499" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G500" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G501" t="str">
-            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G502" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G503" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G504" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G505" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt Home for the Holidays Scented Hidden Pattern - WMT</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G506" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G507" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbred Shop - WMT</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G508" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G509" t="str">
-            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
+            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G510" t="str">
-            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="511">
           <cell r="F511" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G511" t="str">
-            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="512">
           <cell r="F512" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G512" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G514" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G515" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G516" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G517" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G518" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G519" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G520" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G521" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G522" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G524" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G525" t="str">
-            <v>Candle - XX - WALMART PKG</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G526" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G528" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>99-8501</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G529" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>99-9002</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G530" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="531">
-          <cell r="F531">
-            <v>999003</v>
+          <cell r="F531" t="str">
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G531" t="str">
-            <v>BNC Floor Display</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="532">
-          <cell r="F532">
-            <v>999004</v>
+          <cell r="F532" t="str">
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G532" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-00-0001</v>
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G533" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-00-0002</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G534" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-00-0003</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G535" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-00-0005</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G536" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G537" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-00-0007</v>
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G538" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-00-0008</v>
+            <v>99-8302</v>
           </cell>
           <cell r="G539" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-00-0035</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G540" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-99-0035</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G541" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="542">
-          <cell r="F542" t="str">
-            <v>LL-00-0009</v>
+          <cell r="F542">
+            <v>999003</v>
           </cell>
           <cell r="G542" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="543">
-          <cell r="F543" t="str">
-            <v>LL-00-0010</v>
+          <cell r="F543">
+            <v>999004</v>
           </cell>
           <cell r="G543" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G544" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G545" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G546" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G547" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G548" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G549" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G550" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G551" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="552">
           <cell r="F552" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-99-0035</v>
           </cell>
           <cell r="G552" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="553">
           <cell r="F553" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G553" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G554" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G555" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G556" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G557" t="str">
-            <v>FA Mini - CVS Display - Full - 6</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G558" t="str">
-            <v>FA Mini - CVS Display - Empty</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G559" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G560" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G561" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G562" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G563" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G564" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G565" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G566" t="str">
-            <v>FlowArt Grocery Display #1 - 24</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G567" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G568" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G569" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="570">
           <cell r="F570" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G570" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="571">
           <cell r="F571" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G571" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G572" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G573" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="574">
           <cell r="F574" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G574" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="575">
           <cell r="F575" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G575" t="str">
-            <v>FlowArt Valentine Display - 32</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G576" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G577" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Grocery Display #1 - 24</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G578" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G579" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G580" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G581" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G582" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G583" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G584" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G585" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G586" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>FlowArt Valentine Display - 32</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G587" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G588" t="str">
-            <v>Lifelines Tote</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>99-9101</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G589" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>99-9500</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G590" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>99-9505</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G591" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>DS01-1001</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G592" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>DS01-1002</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G593" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>DS01-1003</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G594" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>DS01-1004</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G595" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>DS01-1005</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G596" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>DS01-1006</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G597" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>DS01-1007</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G598" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>DS01-1008</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G599" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>LL-16-3143</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G600" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>LL-12-3131</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G601" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>LL-16-3142</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G602" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>LL-12-3135</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G603" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>LL-12-3134</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G604" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>LL-14-3145</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G605" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>LL-14-3147</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G606" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>LL-98-3171</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G607" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>LL-11-3087</v>
+            <v>DS01-1006</v>
           </cell>
           <cell r="G608" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>LL-11-3088</v>
+            <v>DS01-1007</v>
           </cell>
           <cell r="G609" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>LL-11-3089</v>
+            <v>DS01-1008</v>
           </cell>
           <cell r="G610" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="611">
-          <cell r="F611">
-            <v>165002</v>
+          <cell r="F611" t="str">
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G611" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="612">
-          <cell r="F612">
-            <v>165003</v>
+          <cell r="F612" t="str">
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G612" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="613">
-          <cell r="F613">
-            <v>165004</v>
+          <cell r="F613" t="str">
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G613" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="614">
-          <cell r="F614">
-            <v>165010</v>
+          <cell r="F614" t="str">
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G614" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="615">
-          <cell r="F615">
-            <v>165011</v>
+          <cell r="F615" t="str">
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G615" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="616">
-          <cell r="F616">
-            <v>165013</v>
+          <cell r="F616" t="str">
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G616" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="617">
-          <cell r="F617">
-            <v>167003</v>
+          <cell r="F617" t="str">
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G617" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>11-1613</v>
+            <v>LL-98-3171</v>
           </cell>
           <cell r="G618" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>11-1614</v>
+            <v>LL-11-3087</v>
           </cell>
           <cell r="G619" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+            <v>Clickwick 2PK - SKU 5</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>11-1615</v>
+            <v>LL-11-3088</v>
           </cell>
           <cell r="G620" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
+            <v>Clickwick 2PK - SKU 6</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
+            <v>LL-11-3089</v>
+          </cell>
+          <cell r="G621" t="str">
+            <v>Clickwick 2PK - SKU 7</v>
+          </cell>
+        </row>
+        <row r="622">
+          <cell r="F622">
+            <v>165002</v>
+          </cell>
+          <cell r="G622" t="str">
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+          </cell>
+        </row>
+        <row r="623">
+          <cell r="F623">
+            <v>165003</v>
+          </cell>
+          <cell r="G623" t="str">
+            <v>FlowArt - Multiline art - Land</v>
+          </cell>
+        </row>
+        <row r="624">
+          <cell r="F624">
+            <v>165004</v>
+          </cell>
+          <cell r="G624" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="625">
+          <cell r="F625">
+            <v>165010</v>
+          </cell>
+          <cell r="G625" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="626">
+          <cell r="F626">
+            <v>165011</v>
+          </cell>
+          <cell r="G626" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="627">
+          <cell r="F627">
+            <v>165013</v>
+          </cell>
+          <cell r="G627" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="628">
+          <cell r="F628">
+            <v>167003</v>
+          </cell>
+          <cell r="G628" t="str">
+            <v>Decor Art - Stencil Stationery</v>
+          </cell>
+        </row>
+        <row r="629">
+          <cell r="F629" t="str">
+            <v>11-1613</v>
+          </cell>
+          <cell r="G629" t="str">
+            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+          </cell>
+        </row>
+        <row r="630">
+          <cell r="F630" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G630" t="str">
+            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="631">
+          <cell r="F631" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G631" t="str">
+            <v>Flameless Candle Diffuser -  Two Tone</v>
+          </cell>
+        </row>
+        <row r="632">
+          <cell r="F632" t="str">
             <v>11-1610</v>
           </cell>
-          <cell r="G621" t="str">
+          <cell r="G632" t="str">
             <v>Planter Diffuser -  Octagon (Cream)</v>
           </cell>
         </row>
-        <row r="622">
-          <cell r="F622" t="str">
+        <row r="633">
+          <cell r="F633" t="str">
             <v>16-0107</v>
           </cell>
-          <cell r="G622" t="str">
+          <cell r="G633" t="str">
             <v>Finger Maze Sensory Journal</v>
           </cell>
         </row>
-        <row r="623">
-          <cell r="F623" t="str">
+        <row r="634">
+          <cell r="F634" t="str">
             <v>11-0451</v>
           </cell>
-          <cell r="G623" t="str">
+          <cell r="G634" t="str">
             <v>Clickwick Replacement Bloom, Citrus</v>
           </cell>
         </row>
-        <row r="624">
-          <cell r="F624" t="str">
+        <row r="635">
+          <cell r="F635" t="str">
             <v>11-0452</v>
           </cell>
-          <cell r="G624" t="str">
+          <cell r="G635" t="str">
             <v>Clickwick Replacement Woods, Mountain</v>
           </cell>
         </row>
-        <row r="625">
-          <cell r="F625" t="str">
+        <row r="636">
+          <cell r="F636" t="str">
             <v>112522</v>
           </cell>
         </row>
-        <row r="626">
-          <cell r="F626" t="str">
+        <row r="637">
+          <cell r="F637" t="str">
             <v>99-9501</v>
           </cell>
-          <cell r="G626" t="str">
+          <cell r="G637" t="str">
             <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
           </cell>
         </row>
@@ -5574,24 +5661,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -5739,24 +5826,24 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" s="1" customFormat="1">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="2" t="str">
+      <c r="D11" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v/>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5865,24 +5952,24 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:6" s="1" customFormat="1">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>6</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="2" t="str">
+      <c r="D17" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C17), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>3.5</v>
       </c>
     </row>
@@ -5949,24 +6036,24 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="2" customFormat="1">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:6" s="1" customFormat="1">
+      <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="2">
-        <v>4</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="1">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="2" t="str">
+      <c r="D21" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FA Holiday Mini - Counter Display - Empty</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6117,24 +6204,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="2" customFormat="1">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:6" s="1" customFormat="1">
+      <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="1">
         <v>8</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="2" t="str">
+      <c r="D29" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
-      <c r="E29" s="2">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="E29" s="1">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6201,24 +6288,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="2" customFormat="1">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:6" s="1" customFormat="1">
+      <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="2">
-        <v>4</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="2" t="str">
+      <c r="D33" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="1">
         <v>8</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6285,24 +6372,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="2" customFormat="1">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:6" s="1" customFormat="1">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="2">
-        <v>4</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="2" t="str">
+      <c r="D37" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
-      <c r="E37" s="2">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6453,24 +6540,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="2" customFormat="1">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:6" s="1" customFormat="1">
+      <c r="A45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="1">
         <v>8</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="2" t="str">
+      <c r="D45" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6726,24 +6813,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="2" customFormat="1">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:6" s="1" customFormat="1">
+      <c r="A58" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>13</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="2" t="str">
+      <c r="D58" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6957,24 +7044,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="2" customFormat="1">
-      <c r="A69" s="2" t="s">
+    <row r="69" spans="1:6" s="1" customFormat="1">
+      <c r="A69" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>11</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D69" s="2" t="str">
+      <c r="D69" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7083,24 +7170,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" s="2" customFormat="1">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:6" s="1" customFormat="1">
+      <c r="A75" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>6</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D75" s="2" t="str">
+      <c r="D75" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7543,25 +7630,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" s="2" customFormat="1">
-      <c r="A96" s="2" t="s">
+    <row r="96" spans="1:6" s="1" customFormat="1">
+      <c r="A96" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D96" s="2" t="str">
+      <c r="D96" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>1</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7754,24 +7841,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" s="2" customFormat="1">
-      <c r="A106" s="2" t="s">
+    <row r="106" spans="1:6" s="1" customFormat="1">
+      <c r="A106" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="1">
         <v>10</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="2" t="str">
+      <c r="D106" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
-      <c r="E106" s="2">
-        <v>4</v>
-      </c>
-      <c r="F106" s="2">
+      <c r="E106" s="1">
+        <v>4</v>
+      </c>
+      <c r="F106" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -7901,24 +7988,24 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
+    <row r="113" spans="1:6" s="1" customFormat="1">
+      <c r="A113" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="1">
         <v>7</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D113" t="str">
+      <c r="D113" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v/>
       </c>
-      <c r="E113">
+      <c r="E113" s="1">
         <v>2</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7985,24 +8072,24 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" s="2" customFormat="1">
-      <c r="A117" s="2" t="s">
+    <row r="117" spans="1:6" s="1" customFormat="1">
+      <c r="A117" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B117" s="2">
-        <v>4</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="B117" s="1">
+        <v>4</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D117" s="2" t="str">
+      <c r="D117" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FA Holiday Mini - Counter Display - Empty</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="1">
         <v>1</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8153,24 +8240,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
+    <row r="125" spans="1:6" s="1" customFormat="1">
+      <c r="A125" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="1">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D125" t="str">
+      <c r="D125" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
-      <c r="E125">
-        <v>4</v>
-      </c>
-      <c r="F125">
+      <c r="E125" s="1">
+        <v>4</v>
+      </c>
+      <c r="F125" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8237,24 +8324,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="129" spans="1:6" s="2" customFormat="1">
-      <c r="A129" s="2" t="s">
+    <row r="129" spans="1:6" s="1" customFormat="1">
+      <c r="A129" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B129" s="2">
-        <v>4</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="B129" s="1">
+        <v>4</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D129" s="2" t="str">
+      <c r="D129" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>8</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8321,24 +8408,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" spans="1:6" s="2" customFormat="1">
-      <c r="A133" s="2" t="s">
+    <row r="133" spans="1:6" s="1" customFormat="1">
+      <c r="A133" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B133" s="2">
-        <v>4</v>
-      </c>
-      <c r="C133" s="2" t="s">
+      <c r="B133" s="1">
+        <v>4</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D133" s="2" t="str">
+      <c r="D133" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
-      <c r="E133" s="2">
-        <v>4</v>
-      </c>
-      <c r="F133" s="2">
+      <c r="E133" s="1">
+        <v>4</v>
+      </c>
+      <c r="F133" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8762,24 +8849,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" s="2" customFormat="1">
-      <c r="A154" s="2" t="s">
+    <row r="154" spans="1:6" s="1" customFormat="1">
+      <c r="A154" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="1">
         <v>13</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D154" s="2" t="str">
+      <c r="D154" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>1</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8993,24 +9080,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" s="2" customFormat="1">
-      <c r="A165" s="2" t="s">
+    <row r="165" spans="1:6" s="1" customFormat="1">
+      <c r="A165" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="1">
         <v>11</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D165" s="2" t="str">
+      <c r="D165" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>1</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9119,24 +9206,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
+    <row r="171" spans="1:6" s="1" customFormat="1">
+      <c r="A171" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="1">
         <v>6</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D171" t="str">
+      <c r="D171" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
-      <c r="E171">
+      <c r="E171" s="1">
         <v>1</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9602,24 +9689,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
+    <row r="194" spans="1:6" s="1" customFormat="1">
+      <c r="A194" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="1">
         <v>23</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D194" t="str">
+      <c r="D194" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="1">
         <v>1</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="1">
         <v>0</v>
       </c>
     </row>

--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA863C65-E04D-40BB-AD90-C4169AB2BA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73617F0-9821-4871-BF20-CE8831BE36F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="88">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>LL-20-3232</t>
-  </si>
-  <si>
-    <t>99-9502</t>
   </si>
   <si>
     <t>LL-Mini-RO</t>
@@ -227,9 +224,6 @@
     <t>LL-12-3018</t>
   </si>
   <si>
-    <t>99-9504</t>
-  </si>
-  <si>
     <t>00-LL-DISP-WR2</t>
   </si>
   <si>
@@ -303,6 +297,9 @@
   </si>
   <si>
     <t>LL-16-3224</t>
+  </si>
+  <si>
+    <t>LL-99-0014</t>
   </si>
 </sst>
 </file>
@@ -378,8 +375,8 @@
       <sheetName val="SBOM"/>
       <sheetName val="LL SKU CREATION"/>
       <sheetName val="LL SKU"/>
+      <sheetName val="UPC List"/>
       <sheetName val="ASSORTMENT CREATION"/>
-      <sheetName val="UPC List"/>
       <sheetName val="FINAL BOM"/>
       <sheetName val="NEW COMPONENT"/>
       <sheetName val="MASTER COMP #"/>
@@ -822,7 +819,7 @@
             <v>11-4001</v>
           </cell>
           <cell r="G54" t="str">
-            <v>Discovery Set - Be Transported (5 oils) - 3ml</v>
+            <v>Grounding Stones - Tactile Set - "Classic"</v>
           </cell>
         </row>
         <row r="55">
@@ -2747,7 +2744,7 @@
             <v>LL-16-3151</v>
           </cell>
           <cell r="G295" t="str">
-            <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
           </cell>
         </row>
         <row r="296">
@@ -2875,7 +2872,7 @@
             <v>LL-16-3367</v>
           </cell>
           <cell r="G311" t="str">
-            <v>FlowArt: Trace-by-Line, Gingerbred Delights</v>
+            <v>FlowArt: Trace-by-Line, Gingerbread Delights</v>
           </cell>
         </row>
         <row r="312">
@@ -3080,2406 +3077,2518 @@
         </row>
         <row r="337">
           <cell r="F337" t="str">
-            <v>LL-16-3202</v>
+            <v>LL-16-3411</v>
           </cell>
           <cell r="G337" t="str">
-            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
           </cell>
         </row>
         <row r="338">
           <cell r="F338" t="str">
-            <v>LL-16-3203</v>
+            <v>LL-16-3418</v>
           </cell>
           <cell r="G338" t="str">
-            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+            <v>FlowArt: Trace-By-Line, Pets</v>
           </cell>
         </row>
         <row r="339">
           <cell r="F339" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3202</v>
           </cell>
           <cell r="G339" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
           </cell>
         </row>
         <row r="340">
           <cell r="F340" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3203</v>
           </cell>
           <cell r="G340" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
           </cell>
         </row>
         <row r="341">
           <cell r="F341" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G341" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
           </cell>
         </row>
         <row r="342">
           <cell r="F342" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G342" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
         </row>
         <row r="343">
           <cell r="F343" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G343" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
         </row>
         <row r="344">
           <cell r="F344" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G344" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
         </row>
         <row r="345">
           <cell r="F345" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G345" t="str">
-            <v>FlowArt: Premium #2 - Masterworks</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="346">
           <cell r="F346" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G346" t="str">
-            <v>FlowArt: Premium #3 - Nature</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="347">
           <cell r="F347" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="348">
           <cell r="F348" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Cozy</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="349">
           <cell r="F349" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G349" t="str">
-            <v>FlowArt: DbL, Lovestruck</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="350">
           <cell r="F350" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G350" t="str">
-            <v>FlowArt: DbL, Spooky Season</v>
+            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
           </cell>
         </row>
         <row r="351">
           <cell r="F351" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Premium #5 - Large Dot - Cozy</v>
           </cell>
         </row>
         <row r="352">
           <cell r="F352" t="str">
-            <v>LL-16-3385</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G352" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="353">
           <cell r="F353" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G353" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="354">
           <cell r="F354" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G354" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="355">
           <cell r="F355" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3385</v>
           </cell>
           <cell r="G355" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
           </cell>
         </row>
         <row r="356">
           <cell r="F356" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G356" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="357">
           <cell r="F357" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G357" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="358">
           <cell r="F358" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G358" t="str">
-            <v>FlowArt: Cozy Companions - TGT</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Corner Cafe - TGT</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Cabin Getaway - TGT</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Cross-Stitch: [Floral - name TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Cross-Stitch: [Cheeky Sayings - name TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Corner Cafe - TGT</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Embroidery: [Landscapes - name TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Cross-Stitch: [Floral - name TBD]</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Cross-Stitch: [Cheeky Sayings - name TBD]</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Embroidery: [Landscapes - name TBD]</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt: Mini Single - Coastal Calm</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt: Mini Single - Sweet Summer</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt: Mini Single - Under the Sea</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-30-3406</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="411">
-          <cell r="F411">
-            <v>167001</v>
+          <cell r="F411" t="str">
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="412">
-          <cell r="F412">
-            <v>167002</v>
+          <cell r="F412" t="str">
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowCrafts: Collage Art</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="413">
-          <cell r="F413">
-            <v>167004</v>
+          <cell r="F413" t="str">
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="414">
-          <cell r="F414">
-            <v>167005</v>
+          <cell r="F414" t="str">
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="415">
-          <cell r="F415">
-            <v>167006</v>
+          <cell r="F415" t="str">
+            <v>LL-30-3359</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowCrafts: Decorative Tile Lamp</v>
+            <v>FlowArt Mini EXPRESS, #12</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-98-3188</v>
+            <v>LL-30-3360</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, #13</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-98-3189</v>
+            <v>LL-30-3361</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, #14</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-98-3190</v>
+            <v>LL-30-3362</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-98-3191</v>
+            <v>LL-30-3405</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-98-3025</v>
+            <v>LL-30-3406</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
           </cell>
         </row>
         <row r="421">
-          <cell r="F421" t="str">
-            <v>LL-98-3026</v>
+          <cell r="F421">
+            <v>167001</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowCrafts: Paper Flower Bouquet</v>
           </cell>
         </row>
         <row r="422">
-          <cell r="F422" t="str">
-            <v>LL-98-3027</v>
+          <cell r="F422">
+            <v>167002</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowCrafts: Collage Art</v>
           </cell>
         </row>
         <row r="423">
-          <cell r="F423" t="str">
-            <v>LL-98-3028</v>
+          <cell r="F423">
+            <v>167004</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
           </cell>
         </row>
         <row r="424">
-          <cell r="F424" t="str">
-            <v>LL-98-3091</v>
+          <cell r="F424">
+            <v>167005</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="425">
-          <cell r="F425" t="str">
-            <v>LL-98-3168</v>
+          <cell r="F425">
+            <v>167006</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowCrafts: Decorative Tile Lamp</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-98-3169</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-98-3170</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-98-3307</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="434">
           <cell r="F434" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G437" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G438" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="439">
           <cell r="F439" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G439" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="440">
           <cell r="F440" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G440" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="441">
           <cell r="F441" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G441" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="442">
           <cell r="F442" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G442" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="443">
           <cell r="F443" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="444">
           <cell r="F444" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="445">
           <cell r="F445" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="446">
           <cell r="F446" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="456">
           <cell r="F456" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="457">
           <cell r="F457" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="458">
           <cell r="F458" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="459">
           <cell r="F459" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="460">
           <cell r="F460" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-11-2522</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G461" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-11-2523</v>
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G462" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G463" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G464" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="465">
-          <cell r="F465">
-            <v>989514</v>
+          <cell r="F465" t="str">
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G465" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="466">
-          <cell r="F466">
-            <v>989525</v>
+          <cell r="F466" t="str">
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G466" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G467" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G468" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>11-2506-CP12</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G469" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-99-3076</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G470" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-99-3077</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G471" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>Scented Squishy Plush - #1</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-99-3089</v>
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G472" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v>Scented Squishy Non-Plush - #2</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-99-3090</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G473" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G474" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="475">
-          <cell r="F475" t="str">
-            <v>LL-12-3161</v>
+          <cell r="F475">
+            <v>989514</v>
           </cell>
           <cell r="G475" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="476">
-          <cell r="F476" t="str">
-            <v>LL-12-3172</v>
+          <cell r="F476">
+            <v>989525</v>
           </cell>
           <cell r="G476" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-12-3196</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G477" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-12-3197</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G478" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-12-3215</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G479" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-12-3216</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G480" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-12-3330</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G481" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-12-3331</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G482" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-12-3332</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G483" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G484" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G485" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G486" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G487" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G488" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G489" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G490" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G491" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G492" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="493">
           <cell r="F493" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="494">
           <cell r="F494" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G494" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G495" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Lifelines Analog Bag 2026</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G496" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="497">
           <cell r="F497" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G497" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="498">
           <cell r="F498" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G498" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G499" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G500" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G501" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G502" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G503" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G504" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G505" t="str">
-            <v>FlowArt Home for the Holidays Scented Hidden Pattern - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G506" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G507" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbred Shop - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G508" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G509" t="str">
-            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G510" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="511">
           <cell r="F511" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G511" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="512">
           <cell r="F512" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G512" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G513" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G514" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G515" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G516" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G517" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G518" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G519" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G520" t="str">
-            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G521" t="str">
-            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G522" t="str">
-            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G524" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G525" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G526" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G528" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G529" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G530" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G531" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G532" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G533" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G534" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G535" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G536" t="str">
-            <v>Candle - XX - WALMART PKG</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G537" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G538" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G539" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>99-8501</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G540" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>99-9002</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G541" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="542">
-          <cell r="F542">
-            <v>999003</v>
+          <cell r="F542" t="str">
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G542" t="str">
-            <v>BNC Floor Display</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="543">
-          <cell r="F543">
-            <v>999004</v>
+          <cell r="F543" t="str">
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G543" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-00-0001</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G544" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-00-0002</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G545" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-00-0003</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G546" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-00-0005</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G547" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G548" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-00-0007</v>
+            <v>99-8302</v>
           </cell>
           <cell r="G549" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-00-0008</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G550" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-00-0035</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G551" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="552">
-          <cell r="F552" t="str">
-            <v>LL-99-0035</v>
+          <cell r="F552">
+            <v>999003</v>
           </cell>
           <cell r="G552" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="553">
-          <cell r="F553" t="str">
-            <v>LL-00-0009</v>
+          <cell r="F553">
+            <v>999004</v>
           </cell>
           <cell r="G553" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-00-0010</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G554" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G555" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G556" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G557" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G558" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G559" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G560" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-99-0035</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G563" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G564" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G565" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G566" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G567" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G568" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G569" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="570">
           <cell r="F570" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G570" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="571">
           <cell r="F571" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G571" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G572" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G573" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="574">
           <cell r="F574" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G574" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="575">
           <cell r="F575" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G575" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G576" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G577" t="str">
-            <v>FlowArt Grocery Display #1 - 24</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G578" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G579" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G580" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G581" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G582" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G583" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G584" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G585" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G586" t="str">
-            <v>FlowArt Valentine Display - 32</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G587" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt Grocery Display #1 - 24</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G588" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G589" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G590" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G591" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G592" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G593" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G594" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G595" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G596" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>FlowArt Valentine Display - 32</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G597" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G598" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G599" t="str">
-            <v>Lifelines Tote</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>99-9101</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G600" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>99-9500</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G601" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>99-9505</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G602" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>DS01-1001</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G603" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>DS01-1002</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G604" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>DS01-1003</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G605" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>DS01-1004</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G606" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>DS01-1005</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G607" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>DS01-1006</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G608" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>DS01-1007</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G609" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>DS01-1008</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G610" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="611">
           <cell r="F611" t="str">
-            <v>LL-16-3143</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G611" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="612">
           <cell r="F612" t="str">
-            <v>LL-12-3131</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G612" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="613">
           <cell r="F613" t="str">
-            <v>LL-16-3142</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G613" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="614">
           <cell r="F614" t="str">
-            <v>LL-12-3135</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G614" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="615">
           <cell r="F615" t="str">
-            <v>LL-12-3134</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G615" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>LL-14-3145</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G616" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>LL-14-3147</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G617" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>LL-98-3171</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G618" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>LL-11-3087</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G619" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>LL-11-3088</v>
+            <v>DS01-1006</v>
           </cell>
           <cell r="G620" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>LL-11-3089</v>
+            <v>DS01-1007</v>
           </cell>
           <cell r="G621" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="622">
-          <cell r="F622">
-            <v>165002</v>
+          <cell r="F622" t="str">
+            <v>DS01-1008</v>
           </cell>
           <cell r="G622" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="623">
-          <cell r="F623">
-            <v>165003</v>
+          <cell r="F623" t="str">
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G623" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="624">
-          <cell r="F624">
-            <v>165004</v>
+          <cell r="F624" t="str">
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G624" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="625">
-          <cell r="F625">
-            <v>165010</v>
+          <cell r="F625" t="str">
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G625" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="626">
-          <cell r="F626">
-            <v>165011</v>
+          <cell r="F626" t="str">
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G626" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="627">
-          <cell r="F627">
-            <v>165013</v>
+          <cell r="F627" t="str">
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G627" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="628">
-          <cell r="F628">
-            <v>167003</v>
+          <cell r="F628" t="str">
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G628" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>11-1613</v>
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G629" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>11-1614</v>
+            <v>LL-98-3171</v>
           </cell>
           <cell r="G630" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>11-1615</v>
+            <v>LL-11-3087</v>
           </cell>
           <cell r="G631" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
+            <v>Clickwick 2PK - SKU 5</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>11-1610</v>
+            <v>LL-11-3088</v>
           </cell>
           <cell r="G632" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>Clickwick 2PK - SKU 6</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
+            <v>LL-11-3089</v>
+          </cell>
+          <cell r="G633" t="str">
+            <v>Clickwick 2PK - SKU 7</v>
+          </cell>
+        </row>
+        <row r="634">
+          <cell r="F634">
+            <v>165002</v>
+          </cell>
+          <cell r="G634" t="str">
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+          </cell>
+        </row>
+        <row r="635">
+          <cell r="F635">
+            <v>165003</v>
+          </cell>
+          <cell r="G635" t="str">
+            <v>FlowArt - Multiline art - Land</v>
+          </cell>
+        </row>
+        <row r="636">
+          <cell r="F636">
+            <v>165004</v>
+          </cell>
+          <cell r="G636" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="637">
+          <cell r="F637">
+            <v>165010</v>
+          </cell>
+          <cell r="G637" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="638">
+          <cell r="F638">
+            <v>165011</v>
+          </cell>
+          <cell r="G638" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="639">
+          <cell r="F639">
+            <v>165013</v>
+          </cell>
+          <cell r="G639" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="640">
+          <cell r="F640">
+            <v>167003</v>
+          </cell>
+          <cell r="G640" t="str">
+            <v>Decor Art - Stencil Stationery</v>
+          </cell>
+        </row>
+        <row r="641">
+          <cell r="F641" t="str">
+            <v>11-1613</v>
+          </cell>
+          <cell r="G641" t="str">
+            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+          </cell>
+        </row>
+        <row r="642">
+          <cell r="F642" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G642" t="str">
+            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="643">
+          <cell r="F643" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G643" t="str">
+            <v>Flameless Candle Diffuser -  Two Tone</v>
+          </cell>
+        </row>
+        <row r="644">
+          <cell r="F644" t="str">
+            <v>11-1610</v>
+          </cell>
+          <cell r="G644" t="str">
+            <v>Planter Diffuser -  Octagon (Cream)</v>
+          </cell>
+        </row>
+        <row r="645">
+          <cell r="F645" t="str">
             <v>16-0107</v>
           </cell>
-          <cell r="G633" t="str">
+          <cell r="G645" t="str">
             <v>Finger Maze Sensory Journal</v>
           </cell>
         </row>
-        <row r="634">
-          <cell r="F634" t="str">
+        <row r="646">
+          <cell r="F646" t="str">
+            <v>LL-11-2522</v>
+          </cell>
+          <cell r="G646" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="647">
+          <cell r="F647" t="str">
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G647" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="648">
+          <cell r="F648" t="str">
             <v>11-0451</v>
           </cell>
-          <cell r="G634" t="str">
+          <cell r="G648" t="str">
             <v>Clickwick Replacement Bloom, Citrus</v>
           </cell>
         </row>
-        <row r="635">
-          <cell r="F635" t="str">
+        <row r="649">
+          <cell r="F649" t="str">
             <v>11-0452</v>
           </cell>
-          <cell r="G635" t="str">
+          <cell r="G649" t="str">
             <v>Clickwick Replacement Woods, Mountain</v>
           </cell>
         </row>
-        <row r="636">
-          <cell r="F636" t="str">
+        <row r="650">
+          <cell r="F650" t="str">
             <v>112522</v>
           </cell>
         </row>
-        <row r="637">
-          <cell r="F637" t="str">
+        <row r="651">
+          <cell r="F651" t="str">
             <v>99-9501</v>
           </cell>
-          <cell r="G637" t="str">
+          <cell r="G651" t="str">
             <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
           </cell>
         </row>
@@ -5691,7 +5800,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5715,7 +5824,7 @@
         <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>3.5</v>
@@ -5799,7 +5908,7 @@
         <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>3.5</v>
@@ -5834,14 +5943,14 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D11" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v/>
+        <v>FA Mini - Counter Display - Empty</v>
       </c>
       <c r="E11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -5849,7 +5958,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -5870,7 +5979,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -5891,7 +6000,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -5912,7 +6021,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -5933,7 +6042,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -5954,7 +6063,7 @@
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1">
         <v>6</v>
@@ -5975,13 +6084,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C18), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -5996,13 +6105,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C19), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6017,13 +6126,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C20), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6038,13 +6147,13 @@
     </row>
     <row r="21" spans="1:6" s="1" customFormat="1">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="1">
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6059,13 +6168,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C22), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6080,17 +6189,17 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C23), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -6101,13 +6210,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6122,13 +6231,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6143,13 +6252,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6164,13 +6273,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6185,13 +6294,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6206,17 +6315,17 @@
     </row>
     <row r="29" spans="1:6" s="1" customFormat="1">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" s="1">
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -6227,13 +6336,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6248,13 +6357,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6269,13 +6378,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6290,13 +6399,13 @@
     </row>
     <row r="33" spans="1:6" s="1" customFormat="1">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6311,13 +6420,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6332,13 +6441,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D35" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6353,13 +6462,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6374,13 +6483,13 @@
     </row>
     <row r="37" spans="1:6" s="1" customFormat="1">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="1">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6395,13 +6504,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6416,13 +6525,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6437,13 +6546,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6458,13 +6567,13 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6479,13 +6588,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6500,13 +6609,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6521,13 +6630,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D44" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6542,13 +6651,13 @@
     </row>
     <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1">
         <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6563,13 +6672,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6584,13 +6693,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6605,13 +6714,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6626,13 +6735,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6647,13 +6756,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6668,13 +6777,13 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6689,13 +6798,13 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52">
         <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6710,13 +6819,13 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6731,17 +6840,17 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D54" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -6752,13 +6861,13 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55">
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6773,13 +6882,13 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56">
         <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6794,13 +6903,13 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57">
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6815,13 +6924,13 @@
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1">
       <c r="A58" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B58" s="1">
         <v>13</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6836,13 +6945,13 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D59" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6857,13 +6966,13 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6878,13 +6987,13 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6899,13 +7008,13 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62">
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6920,13 +7029,13 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63">
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6941,13 +7050,13 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6962,13 +7071,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B65">
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -6983,13 +7092,13 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7004,13 +7113,13 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B67">
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7025,13 +7134,13 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68">
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7046,17 +7155,17 @@
     </row>
     <row r="69" spans="1:6" s="1" customFormat="1">
       <c r="A69" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B69" s="1">
         <v>11</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D69" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7067,13 +7176,13 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7088,13 +7197,13 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7109,13 +7218,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7130,13 +7239,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B73">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7151,13 +7260,13 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74">
         <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7172,17 +7281,17 @@
     </row>
     <row r="75" spans="1:6" s="1" customFormat="1">
       <c r="A75" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B75" s="1">
         <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D75" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7193,13 +7302,13 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7214,14 +7323,14 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B77">
         <f>B76+1</f>
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7236,14 +7345,14 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B78">
         <f t="shared" ref="B78:B96" si="0">B77+1</f>
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D78" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7258,14 +7367,14 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B79">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7280,14 +7389,14 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B80">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7302,14 +7411,14 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B81">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7324,14 +7433,14 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B82">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7346,18 +7455,18 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B83">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E83">
         <v>8</v>
@@ -7368,14 +7477,14 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B84">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7390,14 +7499,14 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B85">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7412,14 +7521,14 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B86">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7434,14 +7543,14 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B87">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7456,14 +7565,14 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B88">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7478,14 +7587,14 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B89">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7500,14 +7609,14 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B90">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7522,14 +7631,14 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B91">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7544,14 +7653,14 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B92">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7566,14 +7675,14 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B93">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7588,14 +7697,14 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B94">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7610,14 +7719,14 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B95">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7632,14 +7741,14 @@
     </row>
     <row r="96" spans="1:6" s="1" customFormat="1">
       <c r="A96" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B96" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7654,13 +7763,13 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7675,13 +7784,13 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7696,13 +7805,13 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B99">
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7717,13 +7826,13 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B100">
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7738,13 +7847,13 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B101">
         <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7759,13 +7868,13 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7780,13 +7889,13 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B103">
         <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7801,13 +7910,13 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B104">
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7822,13 +7931,13 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B105">
         <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7843,13 +7952,13 @@
     </row>
     <row r="106" spans="1:6" s="1" customFormat="1">
       <c r="A106" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B106" s="1">
         <v>10</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D106" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -7864,7 +7973,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -7885,7 +7994,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -7906,7 +8015,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -7927,7 +8036,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B110">
         <v>4</v>
@@ -7948,7 +8057,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -7969,7 +8078,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B112">
         <v>6</v>
@@ -7990,17 +8099,17 @@
     </row>
     <row r="113" spans="1:6" s="1" customFormat="1">
       <c r="A113" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B113" s="1">
         <v>7</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v/>
+        <v>FA Mini - Counter Display - Empty</v>
       </c>
       <c r="E113" s="1">
         <v>2</v>
@@ -8011,13 +8120,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8032,13 +8141,13 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8053,13 +8162,13 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8074,13 +8183,13 @@
     </row>
     <row r="117" spans="1:6" s="1" customFormat="1">
       <c r="A117" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B117" s="1">
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D117" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8095,13 +8204,13 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8116,17 +8225,17 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E119">
         <v>4</v>
@@ -8137,13 +8246,13 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8158,13 +8267,13 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8179,13 +8288,13 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B122">
         <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8200,13 +8309,13 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B123">
         <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8221,13 +8330,13 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B124">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8242,13 +8351,13 @@
     </row>
     <row r="125" spans="1:6" s="1" customFormat="1">
       <c r="A125" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B125" s="1">
         <v>8</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D125" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8263,13 +8372,13 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8284,13 +8393,13 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8305,13 +8414,13 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D128" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8326,13 +8435,13 @@
     </row>
     <row r="129" spans="1:6" s="1" customFormat="1">
       <c r="A129" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B129" s="1">
         <v>4</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D129" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8347,13 +8456,13 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8368,13 +8477,13 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8389,13 +8498,13 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8410,13 +8519,13 @@
     </row>
     <row r="133" spans="1:6" s="1" customFormat="1">
       <c r="A133" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B133" s="1">
         <v>4</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D133" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8431,13 +8540,13 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D134" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8452,13 +8561,13 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8473,13 +8582,13 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8494,13 +8603,13 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8515,13 +8624,13 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B138">
         <v>5</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D138" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8536,13 +8645,13 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B139">
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D139" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8557,13 +8666,13 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B140">
         <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8578,13 +8687,13 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B141">
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8599,13 +8708,13 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8620,13 +8729,13 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B143">
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8641,13 +8750,13 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B144">
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8662,13 +8771,13 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8683,13 +8792,13 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B146">
         <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8704,13 +8813,13 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B147">
         <v>6</v>
       </c>
       <c r="C147" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8725,13 +8834,13 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B148">
         <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8746,13 +8855,13 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B149">
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8767,17 +8876,17 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B150">
         <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D150" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E150">
         <v>4</v>
@@ -8788,13 +8897,13 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B151">
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8809,13 +8918,13 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B152">
         <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8830,13 +8939,13 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B153">
         <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8851,13 +8960,13 @@
     </row>
     <row r="154" spans="1:6" s="1" customFormat="1">
       <c r="A154" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B154" s="1">
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D154" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8872,13 +8981,13 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B155">
         <v>1</v>
       </c>
       <c r="C155" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8893,13 +9002,13 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B156">
         <v>2</v>
       </c>
       <c r="C156" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8914,13 +9023,13 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B157">
         <v>3</v>
       </c>
       <c r="C157" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8935,13 +9044,13 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B158">
         <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8956,13 +9065,13 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B159">
         <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D159" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8977,13 +9086,13 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B160">
         <v>6</v>
       </c>
       <c r="C160" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D160" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -8998,13 +9107,13 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B161">
         <v>7</v>
       </c>
       <c r="C161" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D161" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9019,13 +9128,13 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B162">
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9040,13 +9149,13 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B163">
         <v>9</v>
       </c>
       <c r="C163" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9061,13 +9170,13 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B164">
         <v>10</v>
       </c>
       <c r="C164" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9082,17 +9191,17 @@
     </row>
     <row r="165" spans="1:6" s="1" customFormat="1">
       <c r="A165" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B165" s="1">
         <v>11</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D165" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E165" s="1">
         <v>1</v>
@@ -9103,13 +9212,13 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9124,13 +9233,13 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B167">
         <v>2</v>
       </c>
       <c r="C167" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D167" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9145,13 +9254,13 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B168">
         <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9166,13 +9275,13 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D169" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9187,13 +9296,13 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B170">
         <v>5</v>
       </c>
       <c r="C170" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D170" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9208,17 +9317,17 @@
     </row>
     <row r="171" spans="1:6" s="1" customFormat="1">
       <c r="A171" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B171" s="1">
         <v>6</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D171" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -9229,13 +9338,13 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9250,13 +9359,13 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B173">
         <v>2</v>
       </c>
       <c r="C173" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9271,13 +9380,13 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B174">
         <v>3</v>
       </c>
       <c r="C174" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D174" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9292,13 +9401,13 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B175">
         <v>4</v>
       </c>
       <c r="C175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D175" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9313,13 +9422,13 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B176">
         <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D176" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9334,13 +9443,13 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B177">
         <v>6</v>
       </c>
       <c r="C177" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D177" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9355,13 +9464,13 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B178">
         <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D178" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C178, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C178), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9376,13 +9485,13 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B179">
         <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D179" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C179, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C179), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9397,13 +9506,13 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B180">
         <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D180" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C180, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C180), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9418,17 +9527,17 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B181">
         <v>10</v>
       </c>
       <c r="C181" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D181" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C181, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C181), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E181">
         <v>8</v>
@@ -9439,13 +9548,13 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B182">
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D182" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C182, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C182), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9460,13 +9569,13 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B183">
         <v>12</v>
       </c>
       <c r="C183" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D183" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C183, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C183), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9481,13 +9590,13 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B184">
         <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D184" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C184, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C184), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9502,13 +9611,13 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B185">
         <v>14</v>
       </c>
       <c r="C185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D185" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C185, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C185), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9523,13 +9632,13 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B186">
         <v>15</v>
       </c>
       <c r="C186" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D186" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C186, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C186), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9544,13 +9653,13 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B187">
         <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D187" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C187, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C187), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9565,13 +9674,13 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B188">
         <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D188" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C188, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C188), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9586,13 +9695,13 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B189">
         <v>18</v>
       </c>
       <c r="C189" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D189" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C189, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C189), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9607,13 +9716,13 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B190">
         <v>19</v>
       </c>
       <c r="C190" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D190" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C190, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C190), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9628,13 +9737,13 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B191">
         <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D191" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C191, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C191), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9649,13 +9758,13 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B192">
         <v>21</v>
       </c>
       <c r="C192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D192" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C192, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C192), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9670,13 +9779,13 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B193">
         <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D193" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C193, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C193), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9691,13 +9800,13 @@
     </row>
     <row r="194" spans="1:6" s="1" customFormat="1">
       <c r="A194" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B194" s="1">
         <v>23</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D194" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9712,13 +9821,13 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B195">
         <v>1</v>
       </c>
       <c r="C195" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D195" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C195, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C195), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9733,13 +9842,13 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B196">
         <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D196" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C196, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C196), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9754,13 +9863,13 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B197">
         <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D197" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C197, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C197), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9775,13 +9884,13 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B198">
         <v>4</v>
       </c>
       <c r="C198" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D198" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C198, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C198), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9796,13 +9905,13 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B199">
         <v>5</v>
       </c>
       <c r="C199" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D199" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9817,13 +9926,13 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B200">
         <v>6</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D200" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9838,17 +9947,17 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B201">
         <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D201" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C201, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C201), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Hidden Patterns, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E201">
         <v>4</v>
@@ -9859,13 +9968,13 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B202">
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D202" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C202, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C202), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9880,13 +9989,13 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B203">
         <v>9</v>
       </c>
       <c r="C203" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D203" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C203, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C203), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -9901,13 +10010,13 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B204">
         <v>10</v>
       </c>
       <c r="C204" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D204" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C204, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C204), [1]SBOM!$F:$G, 2, FALSE)), "")</f>

--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73617F0-9821-4871-BF20-CE8831BE36F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1AB7652-949F-4993-94E9-BDB212782097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$200</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="88">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -2856,7 +2859,7 @@
             <v>LL-16-3366</v>
           </cell>
           <cell r="G309" t="str">
-            <v>FlowArt: Color-To-Reveal, Snowy Village</v>
+            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
           </cell>
         </row>
         <row r="310">
@@ -2936,7 +2939,7 @@
             <v>LL-16-3390</v>
           </cell>
           <cell r="G319" t="str">
-            <v>FlowArt: Cross-Stitch, Cheery Pop - TGT</v>
+            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
           </cell>
         </row>
         <row r="320">
@@ -3000,7 +3003,7 @@
             <v>LL-16-3394</v>
           </cell>
           <cell r="G327" t="str">
-            <v>FlowArt: Cross-Stitch, Cheery Pop</v>
+            <v>FlowArt: Trace-By-Line, Coquette</v>
           </cell>
         </row>
         <row r="328">
@@ -3093,2502 +3096,2646 @@
         </row>
         <row r="339">
           <cell r="F339" t="str">
-            <v>LL-16-3202</v>
+            <v>LL-16-3420</v>
           </cell>
           <cell r="G339" t="str">
-            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
           </cell>
         </row>
         <row r="340">
           <cell r="F340" t="str">
-            <v>LL-16-3203</v>
+            <v>LL-16-3202</v>
           </cell>
           <cell r="G340" t="str">
-            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
           </cell>
         </row>
         <row r="341">
           <cell r="F341" t="str">
-            <v>LL-16-3407</v>
+            <v>LL-16-3203</v>
           </cell>
           <cell r="G341" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
+            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
           </cell>
         </row>
         <row r="342">
           <cell r="F342" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G342" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
           </cell>
         </row>
         <row r="343">
           <cell r="F343" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G343" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
         </row>
         <row r="344">
           <cell r="F344" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G344" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
         </row>
         <row r="345">
           <cell r="F345" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G345" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
         </row>
         <row r="346">
           <cell r="F346" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G346" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="347">
           <cell r="F347" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="348">
           <cell r="F348" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="349">
           <cell r="F349" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G349" t="str">
-            <v>FlowArt: Premium #3 - The Great Outdoors</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="350">
           <cell r="F350" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G350" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="351">
           <cell r="F351" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Cozy</v>
+            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
           </cell>
         </row>
         <row r="352">
           <cell r="F352" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G352" t="str">
-            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
+            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
           </cell>
         </row>
         <row r="353">
           <cell r="F353" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G353" t="str">
-            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="354">
           <cell r="F354" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G354" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="355">
           <cell r="F355" t="str">
-            <v>LL-16-3385</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G355" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="356">
           <cell r="F356" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3385</v>
           </cell>
           <cell r="G356" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
           </cell>
         </row>
         <row r="357">
           <cell r="F357" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G357" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="358">
           <cell r="F358" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G358" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Dot-By-Letter, Corner Cafe - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
+            <v>FlowArt: Dot-By-Letter, Corner Café</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Cross-Stitch: [Floral - name TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Cross-Stitch: [Cheeky Sayings - name TBD]</v>
+            <v>FlowArt: Stitch-By-Cross: [Floral - name TBD]</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Embroidery: [Landscapes - name TBD]</v>
+            <v>FlowArt: Stich-By-Cross: Cheeky Sayings</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3419</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Stitch-By-Cross: [TBD]</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Stitch-By-Needlepoint: [Cottage]</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3422</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-16-3423</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Stitch-To-Embroider: #1</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-16-3424</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Stitch-To-Quilt: #1</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-20-3408</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt: Mini Single - Berry Bliss</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-20-3409</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt: Mini Single - Hummingbird Haven</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-20-3410</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt: Mini Single - Wildflower Woods</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-20-3412</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt: Mini Single - Coastal Calm</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-20-3413</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt: Mini Single - Sweet Summer</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-20-3414</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt: Mini Single - Under the Sea</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-20-3415</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="411">
           <cell r="F411" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt: Mini Single - Coastal Calm</v>
           </cell>
         </row>
         <row r="412">
           <cell r="F412" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt: Mini Single - Sweet Summer</v>
           </cell>
         </row>
         <row r="413">
           <cell r="F413" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt: Mini Single - Under the Sea</v>
           </cell>
         </row>
         <row r="414">
           <cell r="F414" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="415">
           <cell r="F415" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
+            <v>LL-30-3359</v>
+          </cell>
+          <cell r="G420" t="str">
+            <v>FlowArt Mini EXPRESS, #12</v>
+          </cell>
+        </row>
+        <row r="421">
+          <cell r="F421" t="str">
+            <v>LL-30-3360</v>
+          </cell>
+          <cell r="G421" t="str">
+            <v>FlowArt Mini EXPRESS, #13</v>
+          </cell>
+        </row>
+        <row r="422">
+          <cell r="F422" t="str">
+            <v>LL-30-3361</v>
+          </cell>
+          <cell r="G422" t="str">
+            <v>FlowArt Mini EXPRESS, #14</v>
+          </cell>
+        </row>
+        <row r="423">
+          <cell r="F423" t="str">
+            <v>LL-30-3362</v>
+          </cell>
+          <cell r="G423" t="str">
+            <v>FlowArt Mini EXPRESS, #15</v>
+          </cell>
+        </row>
+        <row r="424">
+          <cell r="F424" t="str">
+            <v>LL-30-3405</v>
+          </cell>
+          <cell r="G424" t="str">
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+          </cell>
+        </row>
+        <row r="425">
+          <cell r="F425" t="str">
             <v>LL-30-3406</v>
           </cell>
-          <cell r="G420" t="str">
+          <cell r="G425" t="str">
             <v>FlowArt Mini EXPRESS, Pretty Petals</v>
-          </cell>
-        </row>
-        <row r="421">
-          <cell r="F421">
-            <v>167001</v>
-          </cell>
-          <cell r="G421" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
-          </cell>
-        </row>
-        <row r="422">
-          <cell r="F422">
-            <v>167002</v>
-          </cell>
-          <cell r="G422" t="str">
-            <v>FlowCrafts: Collage Art</v>
-          </cell>
-        </row>
-        <row r="423">
-          <cell r="F423">
-            <v>167004</v>
-          </cell>
-          <cell r="G423" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
-          </cell>
-        </row>
-        <row r="424">
-          <cell r="F424">
-            <v>167005</v>
-          </cell>
-          <cell r="G424" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
-          </cell>
-        </row>
-        <row r="425">
-          <cell r="F425">
-            <v>167006</v>
-          </cell>
-          <cell r="G425" t="str">
-            <v>FlowCrafts: Decorative Tile Lamp</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-98-3188</v>
+            <v>LL-30-3425</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-98-3189</v>
+            <v>LL-30-3426</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-98-3190</v>
+            <v>LL-30-3427</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-98-3191</v>
+            <v>LL-30-3428</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Fruity Tutti</v>
           </cell>
         </row>
         <row r="430">
-          <cell r="F430" t="str">
-            <v>LL-98-3025</v>
+          <cell r="F430">
+            <v>167001</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowCrafts: Paper Flower Bouquet</v>
           </cell>
         </row>
         <row r="431">
-          <cell r="F431" t="str">
-            <v>LL-98-3026</v>
+          <cell r="F431">
+            <v>167002</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowCrafts: Collage Art</v>
           </cell>
         </row>
         <row r="432">
-          <cell r="F432" t="str">
-            <v>LL-98-3027</v>
+          <cell r="F432">
+            <v>167004</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
           </cell>
         </row>
         <row r="433">
-          <cell r="F433" t="str">
-            <v>LL-98-3028</v>
+          <cell r="F433">
+            <v>167005</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="434">
-          <cell r="F434" t="str">
-            <v>LL-98-3091</v>
+          <cell r="F434">
+            <v>167006</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowCrafts: Decorative Tile Lamp</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-98-3168</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-98-3169</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
-            <v>LL-98-3170</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G437" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438" t="str">
-            <v>LL-98-3307</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G438" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="439">
           <cell r="F439" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G439" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="440">
           <cell r="F440" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G440" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="441">
           <cell r="F441" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G441" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="442">
           <cell r="F442" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G442" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="443">
           <cell r="F443" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="444">
           <cell r="F444" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="445">
           <cell r="F445" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="446">
           <cell r="F446" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="456">
           <cell r="F456" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="457">
           <cell r="F457" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="458">
           <cell r="F458" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="459">
           <cell r="F459" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="460">
           <cell r="F460" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G461" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G462" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G463" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G464" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="465">
           <cell r="F465" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G465" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="466">
           <cell r="F466" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G466" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G467" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G468" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G469" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G470" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-25-3416</v>
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G471" t="str">
-            <v>Scented Squishy Plush - #1</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-25-3417</v>
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G472" t="str">
-            <v>Scented Squishy Non-Plush - #2</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G473" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G474" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="475">
-          <cell r="F475">
-            <v>989514</v>
+          <cell r="F475" t="str">
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G475" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="476">
-          <cell r="F476">
-            <v>989525</v>
+          <cell r="F476" t="str">
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G476" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G477" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G478" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>11-2506-CP12</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G479" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-99-3076</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G480" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>Scented Squishy Plush - Nightime</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-99-3077</v>
+            <v>LL-25-3421</v>
           </cell>
           <cell r="G481" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>Scented Squishy Plush - Woodland</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-99-3089</v>
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G482" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v>Scented Squishy Non-Plush - #2</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-99-3090</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G483" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G484" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="485">
-          <cell r="F485" t="str">
-            <v>LL-12-3161</v>
+          <cell r="F485">
+            <v>989514</v>
           </cell>
           <cell r="G485" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="486">
-          <cell r="F486" t="str">
-            <v>LL-12-3172</v>
+          <cell r="F486">
+            <v>989525</v>
           </cell>
           <cell r="G486" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-12-3196</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G487" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-12-3197</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G488" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-12-3215</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G489" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-12-3216</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G490" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-12-3330</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G491" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-12-3331</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G492" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="493">
           <cell r="F493" t="str">
-            <v>LL-12-3332</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="494">
           <cell r="F494" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G494" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G495" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G496" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="497">
           <cell r="F497" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G497" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="498">
           <cell r="F498" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G498" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G499" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G500" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G501" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G502" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G503" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G504" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G505" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Lifelines Analog Bag 2026</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G506" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G507" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G508" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G509" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G510" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="511">
           <cell r="F511" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G511" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="512">
           <cell r="F512" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G512" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G514" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G515" t="str">
-            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G516" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G517" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G518" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G519" t="str">
-            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G520" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G521" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G522" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G523" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G524" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G525" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G526" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G527" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G528" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G529" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter: Fluffy Favorites - WMT</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G530" t="str">
-            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G531" t="str">
-            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G532" t="str">
-            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G533" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G534" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G535" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G536" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G537" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G538" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G539" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G540" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G541" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="542">
           <cell r="F542" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G542" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="543">
           <cell r="F543" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G543" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G544" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G545" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G546" t="str">
-            <v>Candle - XX - WALMART PKG</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G547" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G548" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G549" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>99-8501</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G550" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>99-9002</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G551" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="552">
-          <cell r="F552">
-            <v>999003</v>
+          <cell r="F552" t="str">
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G552" t="str">
-            <v>BNC Floor Display</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="553">
-          <cell r="F553">
-            <v>999004</v>
+          <cell r="F553" t="str">
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G553" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-00-0001</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G554" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-00-0002</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G555" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-00-0003</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G556" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-00-0005</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G557" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G558" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-00-0007</v>
+            <v>99-8302</v>
           </cell>
           <cell r="G559" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-00-0008</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G560" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-00-0035</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="562">
-          <cell r="F562" t="str">
-            <v>LL-99-0035</v>
+          <cell r="F562">
+            <v>999003</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="563">
-          <cell r="F563" t="str">
-            <v>LL-00-0009</v>
+          <cell r="F563">
+            <v>999004</v>
           </cell>
           <cell r="G563" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-00-0010</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G564" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G565" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G566" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G567" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G568" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G569" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="570">
           <cell r="F570" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G570" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="571">
           <cell r="F571" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G571" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-99-0035</v>
           </cell>
           <cell r="G572" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G573" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="574">
           <cell r="F574" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G574" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="575">
           <cell r="F575" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G575" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G576" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G577" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G578" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G579" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G580" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G581" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G582" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G583" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G584" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G585" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G586" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G587" t="str">
-            <v>FlowArt Grocery Display #1 - 24</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G588" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G589" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G590" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G591" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G592" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G593" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G594" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G595" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G596" t="str">
-            <v>FlowArt Valentine Display - 32</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G597" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt Grocery Display Evergreen - 24</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-99-0024</v>
           </cell>
           <cell r="G598" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Grocery Display Evergreen - Empty</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G599" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-99-0025</v>
           </cell>
           <cell r="G600" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G601" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-99-0026</v>
           </cell>
           <cell r="G602" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FlowArt Fall Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G603" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G604" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G605" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G606" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G607" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G608" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G609" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 36</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G610" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 36</v>
           </cell>
         </row>
         <row r="611">
           <cell r="F611" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G611" t="str">
-            <v>Lifelines Tote</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="612">
           <cell r="F612" t="str">
-            <v>99-9101</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G612" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="613">
           <cell r="F613" t="str">
-            <v>99-9500</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G613" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="614">
           <cell r="F614" t="str">
-            <v>99-9505</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G614" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FlowArt Valentine Display - 32</v>
           </cell>
         </row>
         <row r="615">
           <cell r="F615" t="str">
-            <v>DS01-1001</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G615" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>DS01-1002</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G616" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>DS01-1003</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G617" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>DS01-1004</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G618" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>DS01-1005</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G619" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>DS01-1006</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G620" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>DS01-1007</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G621" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="622">
           <cell r="F622" t="str">
-            <v>DS01-1008</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G622" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="623">
           <cell r="F623" t="str">
-            <v>LL-16-3143</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G623" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="624">
           <cell r="F624" t="str">
-            <v>LL-12-3131</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G624" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="625">
           <cell r="F625" t="str">
-            <v>LL-16-3142</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G625" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="626">
           <cell r="F626" t="str">
-            <v>LL-12-3135</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G626" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="627">
           <cell r="F627" t="str">
-            <v>LL-12-3134</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G627" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="628">
           <cell r="F628" t="str">
-            <v>LL-14-3145</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G628" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>LL-14-3147</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G629" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>LL-98-3171</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G630" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>LL-11-3087</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G631" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>LL-11-3088</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G632" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
-            <v>LL-11-3089</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G633" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="634">
-          <cell r="F634">
-            <v>165002</v>
+          <cell r="F634" t="str">
+            <v>DS01-1002</v>
           </cell>
           <cell r="G634" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="635">
-          <cell r="F635">
-            <v>165003</v>
+          <cell r="F635" t="str">
+            <v>DS01-1003</v>
           </cell>
           <cell r="G635" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="636">
-          <cell r="F636">
-            <v>165004</v>
+          <cell r="F636" t="str">
+            <v>DS01-1004</v>
           </cell>
           <cell r="G636" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="637">
-          <cell r="F637">
-            <v>165010</v>
+          <cell r="F637" t="str">
+            <v>DS01-1005</v>
           </cell>
           <cell r="G637" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="638">
-          <cell r="F638">
-            <v>165011</v>
+          <cell r="F638" t="str">
+            <v>DS01-1006</v>
           </cell>
           <cell r="G638" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="639">
-          <cell r="F639">
-            <v>165013</v>
+          <cell r="F639" t="str">
+            <v>DS01-1007</v>
           </cell>
           <cell r="G639" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="640">
-          <cell r="F640">
-            <v>167003</v>
+          <cell r="F640" t="str">
+            <v>DS01-1008</v>
           </cell>
           <cell r="G640" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>11-1613</v>
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G641" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>11-1614</v>
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G642" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>11-1615</v>
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G643" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>11-1610</v>
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G644" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>16-0107</v>
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G645" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>LL-11-2522</v>
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G646" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>LL-11-2523</v>
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G647" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>11-0451</v>
+            <v>LL-98-3171</v>
           </cell>
           <cell r="G648" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>11-0452</v>
+            <v>LL-11-3087</v>
           </cell>
           <cell r="G649" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>Clickwick 2PK - SKU 5</v>
           </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>112522</v>
+            <v>LL-11-3088</v>
+          </cell>
+          <cell r="G650" t="str">
+            <v>Clickwick 2PK - SKU 6</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
+            <v>LL-11-3089</v>
+          </cell>
+          <cell r="G651" t="str">
+            <v>Clickwick 2PK - SKU 7</v>
+          </cell>
+        </row>
+        <row r="652">
+          <cell r="F652">
+            <v>165002</v>
+          </cell>
+          <cell r="G652" t="str">
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+          </cell>
+        </row>
+        <row r="653">
+          <cell r="F653">
+            <v>165003</v>
+          </cell>
+          <cell r="G653" t="str">
+            <v>FlowArt - Multiline art - Land</v>
+          </cell>
+        </row>
+        <row r="654">
+          <cell r="F654">
+            <v>165004</v>
+          </cell>
+          <cell r="G654" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="655">
+          <cell r="F655">
+            <v>165010</v>
+          </cell>
+          <cell r="G655" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="656">
+          <cell r="F656">
+            <v>165011</v>
+          </cell>
+          <cell r="G656" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="657">
+          <cell r="F657">
+            <v>165013</v>
+          </cell>
+          <cell r="G657" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="658">
+          <cell r="F658">
+            <v>167003</v>
+          </cell>
+          <cell r="G658" t="str">
+            <v>Decor Art - Stencil Stationery</v>
+          </cell>
+        </row>
+        <row r="659">
+          <cell r="F659" t="str">
+            <v>11-1613</v>
+          </cell>
+          <cell r="G659" t="str">
+            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+          </cell>
+        </row>
+        <row r="660">
+          <cell r="F660" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G660" t="str">
+            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="661">
+          <cell r="F661" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G661" t="str">
+            <v>Flameless Candle Diffuser -  Two Tone</v>
+          </cell>
+        </row>
+        <row r="662">
+          <cell r="F662" t="str">
+            <v>11-1610</v>
+          </cell>
+          <cell r="G662" t="str">
+            <v>Planter Diffuser -  Octagon (Cream)</v>
+          </cell>
+        </row>
+        <row r="663">
+          <cell r="F663" t="str">
+            <v>16-0107</v>
+          </cell>
+          <cell r="G663" t="str">
+            <v>Finger Maze Sensory Journal</v>
+          </cell>
+        </row>
+        <row r="664">
+          <cell r="F664" t="str">
+            <v>LL-11-2522</v>
+          </cell>
+          <cell r="G664" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="665">
+          <cell r="F665" t="str">
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G665" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="666">
+          <cell r="F666" t="str">
+            <v>11-0451</v>
+          </cell>
+          <cell r="G666" t="str">
+            <v>Clickwick Replacement Bloom, Citrus</v>
+          </cell>
+        </row>
+        <row r="667">
+          <cell r="F667" t="str">
+            <v>11-0452</v>
+          </cell>
+          <cell r="G667" t="str">
+            <v>Clickwick Replacement Woods, Mountain</v>
+          </cell>
+        </row>
+        <row r="668">
+          <cell r="F668" t="str">
+            <v>112522</v>
+          </cell>
+        </row>
+        <row r="669">
+          <cell r="F669" t="str">
             <v>99-9501</v>
           </cell>
-          <cell r="G651" t="str">
+          <cell r="G669" t="str">
             <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
           </cell>
         </row>
@@ -5758,7 +5905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -5814,17 +5961,17 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C5), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>3.5</v>
@@ -5835,14 +5982,14 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C6), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -5856,17 +6003,17 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C7), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>3.5</v>
@@ -5877,56 +6024,56 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C8), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" s="1" customFormat="1">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="str">
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C9), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
-      </c>
-      <c r="E9">
+        <v>FA Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>0</v>
-      </c>
-      <c r="F9">
-        <v>3.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C10), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -5935,25 +6082,25 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="1" customFormat="1">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="1" t="str">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>3.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5961,59 +6108,59 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C12), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="str">
+      <c r="B13" s="1">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C13), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
+        <v>FlowArt: Mini Single - Furry Friends</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1">
         <v>3.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C14), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <v>3.5</v>
@@ -6021,20 +6168,20 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D15" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C15), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F15">
         <v>3.5</v>
@@ -6042,20 +6189,20 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D16" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C16), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16">
         <v>3.5</v>
@@ -6063,107 +6210,107 @@
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D17" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C17), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FA Holiday Mini - Counter Display - Empty</v>
       </c>
       <c r="E17" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D18" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C18), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C19), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D20" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C20), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="1" customFormat="1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>6.5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -6171,17 +6318,17 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D22" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C22), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22">
         <v>6.5</v>
@@ -6192,14 +6339,14 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D23" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C23), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -6213,14 +6360,14 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D24" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -6229,40 +6376,40 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+    <row r="25" spans="1:6" s="1" customFormat="1">
+      <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" t="str">
+      <c r="B25" s="1">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25">
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1">
         <v>6.5</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D26" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -6273,20 +6420,20 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D27" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F27">
         <v>6.5</v>
@@ -6294,17 +6441,17 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D28" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -6315,20 +6462,20 @@
     </row>
     <row r="29" spans="1:6" s="1" customFormat="1">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E29" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1">
         <v>6.5</v>
@@ -6336,20 +6483,20 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D30" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>6.5</v>
@@ -6357,17 +6504,17 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D31" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -6378,17 +6525,17 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D32" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
       </c>
       <c r="E32">
         <v>4</v>
@@ -6399,20 +6546,20 @@
     </row>
     <row r="33" spans="1:6" s="1" customFormat="1">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
       <c r="E33" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1">
         <v>6.5</v>
@@ -6420,20 +6567,20 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D34" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34">
         <v>6.5</v>
@@ -6441,20 +6588,20 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D35" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35">
         <v>6.5</v>
@@ -6462,43 +6609,43 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D36" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F36">
         <v>6.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="1" customFormat="1">
-      <c r="A37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1">
-        <v>4</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="1" t="str">
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
-      </c>
-      <c r="E37" s="1">
-        <v>4</v>
-      </c>
-      <c r="F37" s="1">
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
         <v>6.5</v>
       </c>
     </row>
@@ -6507,17 +6654,17 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>6.5</v>
@@ -6528,14 +6675,14 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -6549,56 +6696,56 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
         <v>8</v>
       </c>
-      <c r="F40">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" t="str">
+      <c r="C41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E41">
-        <v>4</v>
-      </c>
-      <c r="F41">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -6609,20 +6756,20 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43">
         <v>6.5</v>
@@ -6630,44 +6777,44 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D44" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>6.5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="1" customFormat="1">
-      <c r="A45" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="1">
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E45">
         <v>8</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1">
-        <v>0</v>
+      <c r="F45">
+        <v>6.5</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -6675,14 +6822,14 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E46">
         <v>8</v>
@@ -6696,14 +6843,14 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -6717,14 +6864,14 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -6738,17 +6885,17 @@
         <v>46</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F49">
         <v>6.5</v>
@@ -6759,17 +6906,17 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F50">
         <v>6.5</v>
@@ -6780,14 +6927,14 @@
         <v>46</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E51">
         <v>8</v>
@@ -6801,17 +6948,17 @@
         <v>46</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E52">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52">
         <v>6.5</v>
@@ -6822,14 +6969,14 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -6838,43 +6985,43 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+    <row r="54" spans="1:6" s="1" customFormat="1">
+      <c r="A54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="str">
+      <c r="B54" s="1">
+        <v>13</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
-      </c>
-      <c r="E54">
-        <v>4</v>
-      </c>
-      <c r="F54">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B55">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E55">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F55">
         <v>6.5</v>
@@ -6882,20 +7029,20 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B56">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56">
         <v>6.5</v>
@@ -6903,17 +7050,17 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B57">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E57">
         <v>4</v>
@@ -6922,25 +7069,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="1" customFormat="1">
-      <c r="A58" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="1">
-        <v>13</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="1" t="str">
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="1">
-        <v>0</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -6948,17 +7095,17 @@
         <v>51</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D59" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59">
         <v>6.5</v>
@@ -6969,17 +7116,17 @@
         <v>51</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60">
         <v>6.5</v>
@@ -6990,20 +7137,20 @@
         <v>51</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E61">
         <v>4</v>
       </c>
       <c r="F61">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -7011,20 +7158,20 @@
         <v>51</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7032,14 +7179,14 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E63">
         <v>4</v>
@@ -7053,14 +7200,14 @@
         <v>51</v>
       </c>
       <c r="B64">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E64">
         <v>4</v>
@@ -7069,43 +7216,43 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+    <row r="65" spans="1:6" s="1" customFormat="1">
+      <c r="A65" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B65">
-        <v>7</v>
-      </c>
-      <c r="C65" t="s">
-        <v>58</v>
-      </c>
-      <c r="D65" t="str">
+      <c r="B65" s="1">
+        <v>11</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
-      </c>
-      <c r="E65">
-        <v>4</v>
-      </c>
-      <c r="F65">
-        <v>10</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F66">
         <v>6.5</v>
@@ -7113,20 +7260,20 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67">
         <v>6.5</v>
@@ -7134,17 +7281,17 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E68">
         <v>4</v>
@@ -7153,25 +7300,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="1" customFormat="1">
-      <c r="A69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="1">
-        <v>11</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="1" t="str">
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+      </c>
+      <c r="E69">
+        <v>8</v>
+      </c>
+      <c r="F69">
+        <v>6.5</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -7179,125 +7326,128 @@
         <v>62</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E70">
+        <v>8</v>
+      </c>
+      <c r="F70">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" s="1" customFormat="1">
+      <c r="A71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="1">
         <v>6</v>
       </c>
-      <c r="F70">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71" t="s">
-        <v>63</v>
-      </c>
-      <c r="D71" t="str">
+      <c r="C71" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
-      </c>
-      <c r="E71">
-        <v>6</v>
-      </c>
-      <c r="F71">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F72">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <f>B72+1</f>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F73">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B74">
-        <v>5</v>
+        <f t="shared" ref="B74:B92" si="0">B73+1</f>
+        <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" s="1" customFormat="1">
-      <c r="A75" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="1">
-        <v>6</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="1" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>42</v>
+      </c>
+      <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+      </c>
+      <c r="E75">
+        <v>12</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -7305,17 +7455,18 @@
         <v>65</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F76">
         <v>5</v>
@@ -7326,15 +7477,15 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <f>B76+1</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E77">
         <v>12</v>
@@ -7348,15 +7499,15 @@
         <v>65</v>
       </c>
       <c r="B78">
-        <f t="shared" ref="B78:B96" si="0">B77+1</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D78" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E78">
         <v>8</v>
@@ -7371,17 +7522,17 @@
       </c>
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E79">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79">
         <v>5</v>
@@ -7393,17 +7544,17 @@
       </c>
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E80">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80">
         <v>5</v>
@@ -7415,17 +7566,17 @@
       </c>
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E81">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F81">
         <v>5</v>
@@ -7437,14 +7588,14 @@
       </c>
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E82">
         <v>8</v>
@@ -7459,14 +7610,14 @@
       </c>
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E83">
         <v>8</v>
@@ -7481,14 +7632,14 @@
       </c>
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E84">
         <v>8</v>
@@ -7503,14 +7654,14 @@
       </c>
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E85">
         <v>8</v>
@@ -7525,17 +7676,17 @@
       </c>
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E86">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86">
         <v>5</v>
@@ -7547,17 +7698,17 @@
       </c>
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E87">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87">
         <v>5</v>
@@ -7569,14 +7720,14 @@
       </c>
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E88">
         <v>8</v>
@@ -7591,14 +7742,14 @@
       </c>
       <c r="B89">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E89">
         <v>8</v>
@@ -7613,14 +7764,14 @@
       </c>
       <c r="B90">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E90">
         <v>4</v>
@@ -7635,14 +7786,14 @@
       </c>
       <c r="B91">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E91">
         <v>4</v>
@@ -7651,114 +7802,110 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="A92" t="s">
+    <row r="92" spans="1:6" s="1" customFormat="1">
+      <c r="A92" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" t="str">
+        <v>21</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D92" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
-      </c>
-      <c r="E92">
-        <v>8</v>
-      </c>
-      <c r="F92">
-        <v>5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B93">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E93">
         <v>8</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B94">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B95">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="F95">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" s="1" customFormat="1">
-      <c r="A96" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B96" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D96" s="1" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-      <c r="F96" s="1">
-        <v>0</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>6.5</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -7766,17 +7913,17 @@
         <v>73</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E97">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97">
         <v>6.5</v>
@@ -7787,17 +7934,17 @@
         <v>73</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E98">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98">
         <v>6.5</v>
@@ -7808,14 +7955,14 @@
         <v>73</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D99" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E99">
         <v>4</v>
@@ -7829,14 +7976,14 @@
         <v>73</v>
       </c>
       <c r="B100">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E100">
         <v>4</v>
@@ -7850,14 +7997,14 @@
         <v>73</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -7866,109 +8013,109 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
+    <row r="102" spans="1:6" s="1" customFormat="1">
+      <c r="A102" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B102">
-        <v>6</v>
-      </c>
-      <c r="C102" t="s">
-        <v>86</v>
-      </c>
-      <c r="D102" t="str">
+      <c r="B102" s="1">
+        <v>10</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D102" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
-      </c>
-      <c r="E102">
-        <v>4</v>
-      </c>
-      <c r="F102">
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+      <c r="F102" s="1">
         <v>6.5</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B103">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C103" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E103">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F103">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B104">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F104">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B105">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F105">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" s="1" customFormat="1">
-      <c r="A106" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B106" s="1">
-        <v>10</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D106" s="1" t="str">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>74</v>
+      </c>
+      <c r="B106">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
-      </c>
-      <c r="E106" s="1">
-        <v>4</v>
-      </c>
-      <c r="F106" s="1">
-        <v>6.5</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
+      </c>
+      <c r="E106">
+        <v>6</v>
+      </c>
+      <c r="F106">
+        <v>3.5</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -7976,14 +8123,14 @@
         <v>74</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E107">
         <v>6</v>
@@ -7997,14 +8144,14 @@
         <v>74</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C108" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E108">
         <v>6</v>
@@ -8013,43 +8160,43 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="A109" t="s">
+    <row r="109" spans="1:6" s="1" customFormat="1">
+      <c r="A109" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B109">
-        <v>3</v>
-      </c>
-      <c r="C109" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" t="str">
+      <c r="B109" s="1">
+        <v>7</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D109" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
-      </c>
-      <c r="E109">
-        <v>6</v>
-      </c>
-      <c r="F109">
-        <v>3.5</v>
+        <v>FA Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E109" s="1">
+        <v>2</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B110">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D110" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E110">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F110">
         <v>3.5</v>
@@ -8057,20 +8204,20 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D111" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
       <c r="E111">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F111">
         <v>3.5</v>
@@ -8078,20 +8225,20 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E112">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F112">
         <v>3.5</v>
@@ -8099,20 +8246,20 @@
     </row>
     <row r="113" spans="1:6" s="1" customFormat="1">
       <c r="A113" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B113" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Mini - Counter Display - Empty</v>
+        <v>FA Holiday Mini - Counter Display - Empty</v>
       </c>
       <c r="E113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -8120,86 +8267,86 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F114">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E115">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F115">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E116">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F116">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" s="1" customFormat="1">
-      <c r="A117" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B117" s="1">
-        <v>4</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D117" s="1" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>24</v>
+      </c>
+      <c r="D117" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E117" s="1">
-        <v>1</v>
-      </c>
-      <c r="F117" s="1">
-        <v>0</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+      </c>
+      <c r="E117">
+        <v>4</v>
+      </c>
+      <c r="F117">
+        <v>6.5</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -8207,17 +8354,17 @@
         <v>76</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E118">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118">
         <v>6.5</v>
@@ -8228,14 +8375,14 @@
         <v>76</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E119">
         <v>4</v>
@@ -8249,14 +8396,14 @@
         <v>76</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E120">
         <v>4</v>
@@ -8265,40 +8412,40 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
+    <row r="121" spans="1:6" s="1" customFormat="1">
+      <c r="A121" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B121">
-        <v>4</v>
-      </c>
-      <c r="C121" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" t="str">
+      <c r="B121" s="1">
+        <v>8</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D121" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
-      </c>
-      <c r="E121">
-        <v>4</v>
-      </c>
-      <c r="F121">
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+      </c>
+      <c r="E121" s="1">
+        <v>4</v>
+      </c>
+      <c r="F121" s="1">
         <v>6.5</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E122">
         <v>4</v>
@@ -8309,20 +8456,20 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B123">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F123">
         <v>6.5</v>
@@ -8330,17 +8477,17 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B124">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E124">
         <v>4</v>
@@ -8351,20 +8498,20 @@
     </row>
     <row r="125" spans="1:6" s="1" customFormat="1">
       <c r="A125" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B125" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D125" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E125" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1">
         <v>6.5</v>
@@ -8372,20 +8519,20 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F126">
         <v>6.5</v>
@@ -8393,17 +8540,17 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E127">
         <v>8</v>
@@ -8414,17 +8561,17 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D128" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
       </c>
       <c r="E128">
         <v>4</v>
@@ -8435,20 +8582,20 @@
     </row>
     <row r="129" spans="1:6" s="1" customFormat="1">
       <c r="A129" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B129" s="1">
         <v>4</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D129" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
       <c r="E129" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1">
         <v>6.5</v>
@@ -8456,20 +8603,20 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130">
         <v>6.5</v>
@@ -8477,20 +8624,20 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131">
         <v>6.5</v>
@@ -8498,43 +8645,43 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E132">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132">
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" spans="1:6" s="1" customFormat="1">
-      <c r="A133" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B133" s="1">
-        <v>4</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D133" s="1" t="str">
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>79</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
-      </c>
-      <c r="E133" s="1">
-        <v>4</v>
-      </c>
-      <c r="F133" s="1">
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E133">
+        <v>4</v>
+      </c>
+      <c r="F133">
         <v>6.5</v>
       </c>
     </row>
@@ -8543,17 +8690,17 @@
         <v>79</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D134" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E134">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F134">
         <v>6.5</v>
@@ -8564,14 +8711,14 @@
         <v>79</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C135" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -8585,17 +8732,17 @@
         <v>79</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E136">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F136">
         <v>6.5</v>
@@ -8606,35 +8753,35 @@
         <v>79</v>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F137">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D138" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E138">
         <v>8</v>
@@ -8645,20 +8792,20 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B139">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C139" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D139" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F139">
         <v>6.5</v>
@@ -8666,20 +8813,20 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140">
         <v>6.5</v>
@@ -8687,23 +8834,23 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B141">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v>FlowArt: Stamp by Shape, Mediterranean</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -8711,14 +8858,14 @@
         <v>80</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E142">
         <v>8</v>
@@ -8732,14 +8879,14 @@
         <v>80</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C143" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E143">
         <v>8</v>
@@ -8753,14 +8900,14 @@
         <v>80</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E144">
         <v>8</v>
@@ -8774,17 +8921,17 @@
         <v>80</v>
       </c>
       <c r="B145">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Mediterranean</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F145">
         <v>6.5</v>
@@ -8795,17 +8942,17 @@
         <v>80</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E146">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F146">
         <v>6.5</v>
@@ -8816,14 +8963,14 @@
         <v>80</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E147">
         <v>8</v>
@@ -8837,17 +8984,17 @@
         <v>80</v>
       </c>
       <c r="B148">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E148">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148">
         <v>6.5</v>
@@ -8858,59 +9005,59 @@
         <v>80</v>
       </c>
       <c r="B149">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E149">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149">
         <v>6.5</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+    <row r="150" spans="1:6" s="1" customFormat="1">
+      <c r="A150" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B150">
-        <v>9</v>
-      </c>
-      <c r="C150" t="s">
-        <v>22</v>
-      </c>
-      <c r="D150" t="str">
+      <c r="B150" s="1">
+        <v>13</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D150" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
-      </c>
-      <c r="E150">
-        <v>4</v>
-      </c>
-      <c r="F150">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B151">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C151" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F151">
         <v>6.5</v>
@@ -8918,20 +9065,20 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B152">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C152" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F152">
         <v>6.5</v>
@@ -8939,17 +9086,17 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B153">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C153" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E153">
         <v>4</v>
@@ -8958,25 +9105,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" s="1" customFormat="1">
-      <c r="A154" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B154" s="1">
-        <v>13</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D154" s="1" t="str">
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>81</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154" t="s">
+        <v>55</v>
+      </c>
+      <c r="D154" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E154" s="1">
-        <v>1</v>
-      </c>
-      <c r="F154" s="1">
-        <v>0</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+      </c>
+      <c r="E154">
+        <v>4</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -8984,17 +9131,17 @@
         <v>81</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F155">
         <v>6.5</v>
@@ -9005,17 +9152,17 @@
         <v>81</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C156" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E156">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F156">
         <v>6.5</v>
@@ -9026,20 +9173,20 @@
         <v>81</v>
       </c>
       <c r="B157">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C157" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E157">
         <v>4</v>
       </c>
       <c r="F157">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -9047,20 +9194,20 @@
         <v>81</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E158">
         <v>4</v>
       </c>
       <c r="F158">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -9068,14 +9215,14 @@
         <v>81</v>
       </c>
       <c r="B159">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C159" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D159" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E159">
         <v>4</v>
@@ -9089,14 +9236,14 @@
         <v>81</v>
       </c>
       <c r="B160">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D160" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E160">
         <v>4</v>
@@ -9105,43 +9252,43 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
+    <row r="161" spans="1:6" s="1" customFormat="1">
+      <c r="A161" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B161">
-        <v>7</v>
-      </c>
-      <c r="C161" t="s">
-        <v>58</v>
-      </c>
-      <c r="D161" t="str">
+      <c r="B161" s="1">
+        <v>11</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D161" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
-      </c>
-      <c r="E161">
-        <v>4</v>
-      </c>
-      <c r="F161">
-        <v>10</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E161" s="1">
+        <v>1</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B162">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F162">
         <v>6.5</v>
@@ -9149,20 +9296,20 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B163">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F163">
         <v>6.5</v>
@@ -9170,17 +9317,17 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B164">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E164">
         <v>4</v>
@@ -9189,25 +9336,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" s="1" customFormat="1">
-      <c r="A165" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B165" s="1">
-        <v>11</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D165" s="1" t="str">
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>82</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>59</v>
+      </c>
+      <c r="D165" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E165" s="1">
-        <v>1</v>
-      </c>
-      <c r="F165" s="1">
-        <v>0</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+      </c>
+      <c r="E165">
+        <v>8</v>
+      </c>
+      <c r="F165">
+        <v>6.5</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -9215,125 +9362,125 @@
         <v>82</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E166">
+        <v>8</v>
+      </c>
+      <c r="F166">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" s="1" customFormat="1">
+      <c r="A167" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B167" s="1">
         <v>6</v>
       </c>
-      <c r="F166">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" t="s">
-        <v>82</v>
-      </c>
-      <c r="B167">
-        <v>2</v>
-      </c>
-      <c r="C167" t="s">
-        <v>63</v>
-      </c>
-      <c r="D167" t="str">
+      <c r="C167" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D167" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
-      </c>
-      <c r="E167">
-        <v>6</v>
-      </c>
-      <c r="F167">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E167" s="1">
+        <v>1</v>
+      </c>
+      <c r="F167" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B168">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E168">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B169">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C169" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D169" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F169">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B170">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C170" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D170" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>FlowArt: Pogo-Dot, Nature</v>
       </c>
       <c r="E170">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" s="1" customFormat="1">
-      <c r="A171" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B171" s="1">
-        <v>6</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D171" s="1" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>83</v>
+      </c>
+      <c r="B171">
+        <v>4</v>
+      </c>
+      <c r="C171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D171" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E171" s="1">
-        <v>1</v>
-      </c>
-      <c r="F171" s="1">
-        <v>0</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+      </c>
+      <c r="E171">
+        <v>12</v>
+      </c>
+      <c r="F171">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -9341,17 +9488,17 @@
         <v>83</v>
       </c>
       <c r="B172">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C172" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E172">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F172">
         <v>5</v>
@@ -9362,17 +9509,17 @@
         <v>83</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C173" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F173">
         <v>5</v>
@@ -9383,17 +9530,17 @@
         <v>83</v>
       </c>
       <c r="B174">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D174" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Pogo-Dot, Nature</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F174">
         <v>5</v>
@@ -9404,14 +9551,14 @@
         <v>83</v>
       </c>
       <c r="B175">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C175" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D175" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E175">
         <v>12</v>
@@ -9425,17 +9572,17 @@
         <v>83</v>
       </c>
       <c r="B176">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D176" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E176">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F176">
         <v>5</v>
@@ -9446,17 +9593,17 @@
         <v>83</v>
       </c>
       <c r="B177">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C177" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D177" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E177">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F177">
         <v>5</v>
@@ -9467,14 +9614,14 @@
         <v>83</v>
       </c>
       <c r="B178">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D178" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C178, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C178), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E178">
         <v>12</v>
@@ -9488,14 +9635,14 @@
         <v>83</v>
       </c>
       <c r="B179">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C179" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D179" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C179, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C179), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E179">
         <v>12</v>
@@ -9509,14 +9656,14 @@
         <v>83</v>
       </c>
       <c r="B180">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="D180" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C180, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C180), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E180">
         <v>8</v>
@@ -9530,14 +9677,14 @@
         <v>83</v>
       </c>
       <c r="B181">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C181" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D181" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C181, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C181), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E181">
         <v>8</v>
@@ -9551,17 +9698,17 @@
         <v>83</v>
       </c>
       <c r="B182">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C182" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D182" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C182, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C182), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E182">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F182">
         <v>5</v>
@@ -9572,17 +9719,17 @@
         <v>83</v>
       </c>
       <c r="B183">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D183" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C183, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C183), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E183">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F183">
         <v>5</v>
@@ -9593,17 +9740,17 @@
         <v>83</v>
       </c>
       <c r="B184">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D184" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C184, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C184), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E184">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184">
         <v>5</v>
@@ -9614,17 +9761,17 @@
         <v>83</v>
       </c>
       <c r="B185">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C185" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D185" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C185, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C185), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E185">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F185">
         <v>5</v>
@@ -9635,17 +9782,17 @@
         <v>83</v>
       </c>
       <c r="B186">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C186" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D186" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C186, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C186), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E186">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F186">
         <v>5</v>
@@ -9656,17 +9803,17 @@
         <v>83</v>
       </c>
       <c r="B187">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D187" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C187, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C187), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E187">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F187">
         <v>5</v>
@@ -9677,17 +9824,17 @@
         <v>83</v>
       </c>
       <c r="B188">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C188" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D188" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C188, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C188), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F188">
         <v>5</v>
@@ -9698,14 +9845,14 @@
         <v>83</v>
       </c>
       <c r="B189">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D189" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C189, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C189), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E189">
         <v>4</v>
@@ -9714,109 +9861,109 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
-      <c r="A190" t="s">
+    <row r="190" spans="1:6" s="1" customFormat="1">
+      <c r="A190" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B190">
-        <v>19</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="B190" s="1">
         <v>23</v>
       </c>
-      <c r="D190" t="str">
+      <c r="C190" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D190" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C190, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C190), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
-      </c>
-      <c r="E190">
-        <v>4</v>
-      </c>
-      <c r="F190">
-        <v>5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E190" s="1">
+        <v>1</v>
+      </c>
+      <c r="F190" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B191">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C191" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D191" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C191, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C191), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E191">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F191">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B192">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C192" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D192" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C192, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C192), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E192">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F192">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B193">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D193" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C193, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C193), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E193">
         <v>4</v>
       </c>
       <c r="F193">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" s="1" customFormat="1">
-      <c r="A194" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B194" s="1">
-        <v>23</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D194" s="1" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>84</v>
+      </c>
+      <c r="B194">
+        <v>4</v>
+      </c>
+      <c r="C194" t="s">
+        <v>40</v>
+      </c>
+      <c r="D194" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E194" s="1">
-        <v>1</v>
-      </c>
-      <c r="F194" s="1">
-        <v>0</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E194">
+        <v>4</v>
+      </c>
+      <c r="F194">
+        <v>6.5</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -9824,17 +9971,17 @@
         <v>84</v>
       </c>
       <c r="B195">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C195" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D195" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C195, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C195), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E195">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195">
         <v>6.5</v>
@@ -9845,17 +9992,17 @@
         <v>84</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C196" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D196" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C196, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C196), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E196">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196">
         <v>6.5</v>
@@ -9866,14 +10013,14 @@
         <v>84</v>
       </c>
       <c r="B197">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D197" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C197, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C197), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -9887,14 +10034,14 @@
         <v>84</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D198" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C198, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C198), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E198">
         <v>4</v>
@@ -9908,14 +10055,14 @@
         <v>84</v>
       </c>
       <c r="B199">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D199" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E199">
         <v>4</v>
@@ -9929,14 +10076,14 @@
         <v>84</v>
       </c>
       <c r="B200">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C200" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D200" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E200">
         <v>4</v>
@@ -9945,91 +10092,8 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
-      <c r="A201" t="s">
-        <v>84</v>
-      </c>
-      <c r="B201">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s">
-        <v>22</v>
-      </c>
-      <c r="D201" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C201, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C201), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
-      </c>
-      <c r="E201">
-        <v>4</v>
-      </c>
-      <c r="F201">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" t="s">
-        <v>84</v>
-      </c>
-      <c r="B202">
-        <v>8</v>
-      </c>
-      <c r="C202" t="s">
-        <v>47</v>
-      </c>
-      <c r="D202" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C202, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C202), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
-      </c>
-      <c r="E202">
-        <v>4</v>
-      </c>
-      <c r="F202">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" t="s">
-        <v>84</v>
-      </c>
-      <c r="B203">
-        <v>9</v>
-      </c>
-      <c r="C203" t="s">
-        <v>26</v>
-      </c>
-      <c r="D203" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C203, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C203), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
-      </c>
-      <c r="E203">
-        <v>4</v>
-      </c>
-      <c r="F203">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
-        <v>84</v>
-      </c>
-      <c r="B204">
-        <v>10</v>
-      </c>
-      <c r="C204" t="s">
-        <v>49</v>
-      </c>
-      <c r="D204" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C204, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C204), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
-      </c>
-      <c r="E204">
-        <v>4</v>
-      </c>
-      <c r="F204">
-        <v>6.5</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A4:F200" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>

--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/4) Demand/10) Shopify Orders/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/4) Demand/17) Scripts/mt-shopify-sync/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{443DA277-78C9-4C95-8C0A-D8566ACC877D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E250D84-EE5E-4EF3-A31D-3AD4BC6671E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$204</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="88">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -2738,3039 +2738,3135 @@
         </row>
         <row r="294">
           <cell r="F294" t="str">
-            <v>LL-16-3148</v>
+            <v>LL-16-3433</v>
           </cell>
           <cell r="G294" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Birds Song in Bloom [Metallic]</v>
           </cell>
         </row>
         <row r="295">
           <cell r="F295" t="str">
-            <v>LL-16-3153</v>
+            <v>LL-16-3148</v>
           </cell>
           <cell r="G295" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="296">
           <cell r="F296" t="str">
-            <v>LL-16-3148-V3</v>
+            <v>LL-16-3153</v>
           </cell>
           <cell r="G296" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="297">
           <cell r="F297" t="str">
-            <v>LL-16-3153-V3</v>
+            <v>LL-16-3148-V3</v>
           </cell>
           <cell r="G297" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="298">
           <cell r="F298" t="str">
-            <v>LL-16-3149</v>
+            <v>LL-16-3153-V3</v>
           </cell>
           <cell r="G298" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="299">
           <cell r="F299" t="str">
-            <v>LL-16-3150</v>
+            <v>LL-16-3149</v>
           </cell>
           <cell r="G299" t="str">
-            <v>FlowArt: Stamp by Shape, Secret Garden</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
           </cell>
         </row>
         <row r="300">
           <cell r="F300" t="str">
-            <v>LL-16-3151</v>
+            <v>LL-16-3150</v>
           </cell>
           <cell r="G300" t="str">
-            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+            <v>FlowArt: Stamp by Shape, Secret Garden</v>
           </cell>
         </row>
         <row r="301">
           <cell r="F301" t="str">
-            <v>LL-16-3152</v>
+            <v>LL-16-3151</v>
           </cell>
           <cell r="G301" t="str">
-            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
+            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
           </cell>
         </row>
         <row r="302">
           <cell r="F302" t="str">
-            <v>LL-16-3157</v>
+            <v>LL-16-3152</v>
           </cell>
           <cell r="G302" t="str">
-            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
           </cell>
         </row>
         <row r="303">
           <cell r="F303" t="str">
-            <v>LL-16-3158</v>
+            <v>LL-16-3157</v>
           </cell>
           <cell r="G303" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
           </cell>
         </row>
         <row r="304">
           <cell r="F304" t="str">
-            <v>LL-16-3323</v>
+            <v>LL-16-3158</v>
           </cell>
           <cell r="G304" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
           </cell>
         </row>
         <row r="305">
           <cell r="F305" t="str">
-            <v>LL-16-3159</v>
+            <v>LL-16-3323</v>
           </cell>
           <cell r="G305" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
           </cell>
         </row>
         <row r="306">
           <cell r="F306" t="str">
-            <v>LL-16-3160</v>
+            <v>LL-16-3159</v>
           </cell>
           <cell r="G306" t="str">
-            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
+            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
           </cell>
         </row>
         <row r="307">
           <cell r="F307" t="str">
-            <v>LL-16-3290</v>
+            <v>LL-16-3160</v>
           </cell>
           <cell r="G307" t="str">
-            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
           </cell>
         </row>
         <row r="308">
           <cell r="F308" t="str">
-            <v>LL-16-3247</v>
+            <v>LL-16-3290</v>
           </cell>
           <cell r="G308" t="str">
-            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
           </cell>
         </row>
         <row r="309">
           <cell r="F309" t="str">
-            <v>LL-16-3248</v>
+            <v>LL-16-3247</v>
           </cell>
           <cell r="G309" t="str">
-            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
           </cell>
         </row>
         <row r="310">
           <cell r="F310" t="str">
-            <v>LL-16-3162</v>
+            <v>LL-16-3248</v>
           </cell>
           <cell r="G310" t="str">
-            <v>FlowArt: Dot-By-Letter, Snowed In</v>
+            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
           </cell>
         </row>
         <row r="311">
           <cell r="F311" t="str">
-            <v>LL-16-3244</v>
+            <v>LL-16-3162</v>
           </cell>
           <cell r="G311" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Snowed In</v>
           </cell>
         </row>
         <row r="312">
           <cell r="F312" t="str">
-            <v>LL-16-3245</v>
+            <v>LL-16-3244</v>
           </cell>
           <cell r="G312" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
           </cell>
         </row>
         <row r="313">
           <cell r="F313" t="str">
-            <v>LL-16-3246</v>
+            <v>LL-16-3245</v>
           </cell>
           <cell r="G313" t="str">
-            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
           </cell>
         </row>
         <row r="314">
           <cell r="F314" t="str">
-            <v>LL-16-3366</v>
+            <v>LL-16-3246</v>
           </cell>
           <cell r="G314" t="str">
-            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
+            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
           </cell>
         </row>
         <row r="315">
           <cell r="F315" t="str">
-            <v>LL-16-3163</v>
+            <v>LL-16-3366</v>
           </cell>
           <cell r="G315" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
+            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
           </cell>
         </row>
         <row r="316">
           <cell r="F316" t="str">
-            <v>LL-16-3367</v>
+            <v>LL-16-3163</v>
           </cell>
           <cell r="G316" t="str">
-            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
           </cell>
         </row>
         <row r="317">
           <cell r="F317" t="str">
-            <v>LL-16-3368</v>
+            <v>LL-16-3367</v>
           </cell>
           <cell r="G317" t="str">
-            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
+            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
           </cell>
         </row>
         <row r="318">
           <cell r="F318" t="str">
-            <v>LL-16-3369</v>
+            <v>LL-16-3368</v>
           </cell>
           <cell r="G318" t="str">
-            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
+            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
           </cell>
         </row>
         <row r="319">
           <cell r="F319" t="str">
-            <v>LL-16-3371</v>
+            <v>LL-16-3369</v>
           </cell>
           <cell r="G319" t="str">
-            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
           </cell>
         </row>
         <row r="320">
           <cell r="F320" t="str">
-            <v>LL-16-3372</v>
+            <v>LL-16-3371</v>
           </cell>
           <cell r="G320" t="str">
-            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
           </cell>
         </row>
         <row r="321">
           <cell r="F321" t="str">
-            <v>LL-16-3373</v>
+            <v>LL-16-3372</v>
           </cell>
           <cell r="G321" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
           </cell>
         </row>
         <row r="322">
           <cell r="F322" t="str">
-            <v>LL-16-3374</v>
+            <v>LL-16-3373</v>
           </cell>
           <cell r="G322" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sweets - TGT</v>
           </cell>
         </row>
         <row r="323">
           <cell r="F323" t="str">
-            <v>LL-16-3352</v>
+            <v>LL-16-3374</v>
           </cell>
           <cell r="G323" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
           </cell>
         </row>
         <row r="324">
           <cell r="F324" t="str">
-            <v>LL-16-3390</v>
+            <v>LL-16-3352</v>
           </cell>
           <cell r="G324" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
           </cell>
         </row>
         <row r="325">
           <cell r="F325" t="str">
-            <v>LL-16-3375</v>
+            <v>LL-16-3390</v>
           </cell>
           <cell r="G325" t="str">
-            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
+            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
           </cell>
         </row>
         <row r="326">
           <cell r="F326" t="str">
-            <v>LL-16-3391</v>
+            <v>LL-16-3375</v>
           </cell>
           <cell r="G326" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club - TGT</v>
+            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
           </cell>
         </row>
         <row r="327">
           <cell r="F327" t="str">
-            <v>LL-16-3376</v>
+            <v>LL-16-3391</v>
           </cell>
           <cell r="G327" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance - TGT</v>
+            <v>FlowArt: Trace-By-Line, Self Care Club - TGT</v>
           </cell>
         </row>
         <row r="328">
           <cell r="F328" t="str">
-            <v>LL-16-3389</v>
+            <v>LL-16-3376</v>
           </cell>
           <cell r="G328" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance</v>
+            <v>FlowArt: Trace-By-Line, Book Romance - TGT</v>
           </cell>
         </row>
         <row r="329">
           <cell r="F329" t="str">
-            <v>LL-16-3395</v>
+            <v>LL-16-3389</v>
           </cell>
           <cell r="G329" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club</v>
+            <v>FlowArt: Trace-By-Line, Book Romance</v>
           </cell>
         </row>
         <row r="330">
           <cell r="F330" t="str">
-            <v>LL-16-3392</v>
+            <v>LL-16-3395</v>
           </cell>
           <cell r="G330" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets</v>
+            <v>FlowArt: Trace-By-Line, Self Care Club</v>
           </cell>
         </row>
         <row r="331">
           <cell r="F331" t="str">
-            <v>LL-16-3393</v>
+            <v>LL-16-3392</v>
           </cell>
           <cell r="G331" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
+            <v>FlowArt: Dot-By-Letter, Sweets</v>
           </cell>
         </row>
         <row r="332">
           <cell r="F332" t="str">
-            <v>LL-16-3394</v>
+            <v>LL-16-3393</v>
           </cell>
           <cell r="G332" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
           </cell>
         </row>
         <row r="333">
           <cell r="F333" t="str">
-            <v>LL-16-3200</v>
+            <v>LL-16-3394</v>
           </cell>
           <cell r="G333" t="str">
-            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+            <v>FlowArt: Trace-By-Line, Coquette</v>
           </cell>
         </row>
         <row r="334">
           <cell r="F334" t="str">
-            <v>LL-16-3201</v>
+            <v>LL-16-3200</v>
           </cell>
           <cell r="G334" t="str">
-            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
+            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
           </cell>
         </row>
         <row r="335">
           <cell r="F335" t="str">
-            <v>LL-16-3204</v>
+            <v>LL-16-3201</v>
           </cell>
           <cell r="G335" t="str">
-            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
+            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
           </cell>
         </row>
         <row r="336">
           <cell r="F336" t="str">
-            <v>LL-16-3205</v>
+            <v>LL-16-3204</v>
           </cell>
           <cell r="G336" t="str">
-            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
           </cell>
         </row>
         <row r="337">
           <cell r="F337" t="str">
-            <v>LL-16-3206</v>
+            <v>LL-16-3205</v>
           </cell>
           <cell r="G337" t="str">
-            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
           </cell>
         </row>
         <row r="338">
           <cell r="F338" t="str">
-            <v>LL-16-3207</v>
+            <v>LL-16-3206</v>
           </cell>
           <cell r="G338" t="str">
-            <v>FlowArt: Trace Within, Peaceful Pause</v>
+            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
           </cell>
         </row>
         <row r="339">
           <cell r="F339" t="str">
-            <v>LL-16-3249</v>
+            <v>LL-16-3207</v>
           </cell>
           <cell r="G339" t="str">
-            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+            <v>FlowArt: Trace Within, Peaceful Pause</v>
           </cell>
         </row>
         <row r="340">
           <cell r="F340" t="str">
-            <v>LL-16-3222</v>
+            <v>LL-16-3249</v>
           </cell>
           <cell r="G340" t="str">
-            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
           </cell>
         </row>
         <row r="341">
           <cell r="F341" t="str">
-            <v>LL-16-3223</v>
+            <v>LL-16-3222</v>
           </cell>
           <cell r="G341" t="str">
-            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
           </cell>
         </row>
         <row r="342">
           <cell r="F342" t="str">
-            <v>LL-16-3411</v>
+            <v>LL-16-3223</v>
           </cell>
           <cell r="G342" t="str">
-            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
+            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
           </cell>
         </row>
         <row r="343">
           <cell r="F343" t="str">
-            <v>LL-16-3418</v>
+            <v>LL-16-3411</v>
           </cell>
           <cell r="G343" t="str">
-            <v>FlowArt: Trace-By-Line, Pets</v>
+            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
           </cell>
         </row>
         <row r="344">
           <cell r="F344" t="str">
-            <v>LL-16-3420</v>
+            <v>LL-16-3418</v>
           </cell>
           <cell r="G344" t="str">
-            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
+            <v>FlowArt: Trace-By-Line, Pets</v>
           </cell>
         </row>
         <row r="345">
           <cell r="F345" t="str">
-            <v>LL-16-3202</v>
+            <v>LL-16-3420</v>
           </cell>
           <cell r="G345" t="str">
-            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
           </cell>
         </row>
         <row r="346">
           <cell r="F346" t="str">
-            <v>LL-16-3203</v>
+            <v>LL-16-3202</v>
           </cell>
           <cell r="G346" t="str">
-            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
           </cell>
         </row>
         <row r="347">
           <cell r="F347" t="str">
-            <v>LL-16-3407</v>
+            <v>LL-16-3203</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
+            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
           </cell>
         </row>
         <row r="348">
           <cell r="F348" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
           </cell>
         </row>
         <row r="349">
           <cell r="F349" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G349" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
         </row>
         <row r="350">
           <cell r="F350" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G350" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
         </row>
         <row r="351">
           <cell r="F351" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
         </row>
         <row r="352">
           <cell r="F352" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G352" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="353">
           <cell r="F353" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G353" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="354">
           <cell r="F354" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G354" t="str">
-            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="355">
           <cell r="F355" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G355" t="str">
-            <v>FlowArt: Premium #3 - The Great Outdoors</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="356">
           <cell r="F356" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G356" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="357">
           <cell r="F357" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G357" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
+            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
           </cell>
         </row>
         <row r="358">
           <cell r="F358" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G358" t="str">
-            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
+            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
           </cell>
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Dot-By-Letter, Corner Café</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
+            <v>FlowArt: Dot-By-Letter, Corner Café</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Stitch-By-Cross: [Floral - name TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Stich-By-Cross: Cheeky Sayings</v>
+            <v>FlowArt: Stitch-By-Cross: [Floral - name TBD]</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-16-3419</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Stitch-By-Cross: [TBD]</v>
+            <v>FlowArt: Stich-By-Cross: Cheeky Sayings</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3419</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: [Cottage]</v>
+            <v>FlowArt: Stitch-By-Cross: [TBD]</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-16-3422</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
+            <v>FlowArt: Stitch-By-Needlepoint: [Cottage]</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-16-3423</v>
+            <v>LL-16-3422</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Stitch-To-Embroider: #1</v>
+            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-16-3424</v>
+            <v>LL-16-3423</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Stitch-To-Quilt: #1</v>
+            <v>FlowArt: Stitch-To-Embroider: #1</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3424</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Stitch-To-Quilt: #1</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt: Mini Single - Coastal Calm</v>
           </cell>
         </row>
         <row r="411">
           <cell r="F411" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt: Mini Single - Sweet Summer</v>
           </cell>
         </row>
         <row r="412">
           <cell r="F412" t="str">
-            <v>LL-20-3408</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowArt: Mini Single - Berry Bliss</v>
+            <v>FlowArt: Mini Single - Under the Sea</v>
           </cell>
         </row>
         <row r="413">
           <cell r="F413" t="str">
-            <v>LL-20-3409</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowArt: Mini Single - Hummingbird Haven</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="414">
           <cell r="F414" t="str">
-            <v>LL-20-3410</v>
+            <v>LL-20-3434</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowArt: Mini Single - Wildflower Woods</v>
+            <v>FlowArt: Mini Single - Cross-Stitch #1</v>
           </cell>
         </row>
         <row r="415">
           <cell r="F415" t="str">
-            <v>LL-20-3412</v>
+            <v>LL-20-3435</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowArt: Mini Single - Coastal Calm</v>
+            <v>FlowArt: Mini Single - Cross-Stitch #2</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-20-3413</v>
+            <v>LL-20-3436</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt: Mini Single - Sweet Summer</v>
+            <v>FlowArt: Mini Single - Cross-Stitch #3</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-20-3414</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt: Mini Single - Under the Sea</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-20-3415</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="421">
           <cell r="F421" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="422">
           <cell r="F422" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="423">
           <cell r="F423" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="424">
           <cell r="F424" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="425">
           <cell r="F425" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-30-3359</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt Mini EXPRESS, #12</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-30-3406</v>
+            <v>LL-30-3360</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+            <v>FlowArt Mini EXPRESS, #13</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-30-3425</v>
+            <v>LL-30-3361</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
+            <v>FlowArt Mini EXPRESS, #14</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-30-3426</v>
+            <v>LL-30-3362</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
+            <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-30-3427</v>
+            <v>LL-30-3405</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
+            <v>LL-30-3406</v>
+          </cell>
+          <cell r="G433" t="str">
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+          </cell>
+        </row>
+        <row r="434">
+          <cell r="F434" t="str">
+            <v>LL-30-3425</v>
+          </cell>
+          <cell r="G434" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
+          </cell>
+        </row>
+        <row r="435">
+          <cell r="F435" t="str">
+            <v>LL-30-3426</v>
+          </cell>
+          <cell r="G435" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
+          </cell>
+        </row>
+        <row r="436">
+          <cell r="F436" t="str">
+            <v>LL-30-3427</v>
+          </cell>
+          <cell r="G436" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
+          </cell>
+        </row>
+        <row r="437">
+          <cell r="F437" t="str">
             <v>LL-30-3428</v>
           </cell>
-          <cell r="G433" t="str">
+          <cell r="G437" t="str">
             <v>FlowArt Mini EXPRESS, Tween Collection - Fruity Tutti</v>
-          </cell>
-        </row>
-        <row r="434">
-          <cell r="F434">
-            <v>167001</v>
-          </cell>
-          <cell r="G434" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
-          </cell>
-        </row>
-        <row r="435">
-          <cell r="F435">
-            <v>167002</v>
-          </cell>
-          <cell r="G435" t="str">
-            <v>FlowCrafts: Collage Art</v>
-          </cell>
-        </row>
-        <row r="436">
-          <cell r="F436">
-            <v>167004</v>
-          </cell>
-          <cell r="G436" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
-          </cell>
-        </row>
-        <row r="437">
-          <cell r="F437">
-            <v>167005</v>
-          </cell>
-          <cell r="G437" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438">
+            <v>167001</v>
+          </cell>
+          <cell r="G438" t="str">
+            <v>FlowCrafts: Paper Flower Bouquet</v>
+          </cell>
+        </row>
+        <row r="439">
+          <cell r="F439">
+            <v>167002</v>
+          </cell>
+          <cell r="G439" t="str">
+            <v>FlowCrafts: Collage Art</v>
+          </cell>
+        </row>
+        <row r="440">
+          <cell r="F440">
+            <v>167004</v>
+          </cell>
+          <cell r="G440" t="str">
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
+          </cell>
+        </row>
+        <row r="441">
+          <cell r="F441">
+            <v>167005</v>
+          </cell>
+          <cell r="G441" t="str">
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
+          </cell>
+        </row>
+        <row r="442">
+          <cell r="F442">
             <v>167006</v>
           </cell>
-          <cell r="G438" t="str">
+          <cell r="G442" t="str">
             <v>FlowCrafts: Decorative Tile Lamp</v>
-          </cell>
-        </row>
-        <row r="439">
-          <cell r="F439" t="str">
-            <v>LL-98-3188</v>
-          </cell>
-          <cell r="G439" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="440">
-          <cell r="F440" t="str">
-            <v>LL-98-3189</v>
-          </cell>
-          <cell r="G440" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="441">
-          <cell r="F441" t="str">
-            <v>LL-98-3190</v>
-          </cell>
-          <cell r="G441" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="442">
-          <cell r="F442" t="str">
-            <v>LL-98-3191</v>
-          </cell>
-          <cell r="G442" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="443">
           <cell r="F443" t="str">
-            <v>LL-98-3025</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="444">
           <cell r="F444" t="str">
-            <v>LL-98-3026</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="445">
           <cell r="F445" t="str">
-            <v>LL-98-3027</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="446">
           <cell r="F446" t="str">
-            <v>LL-98-3028</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3091</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3168</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3169</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-98-3170</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-98-3307</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="456">
           <cell r="F456" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="457">
           <cell r="F457" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="458">
           <cell r="F458" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="459">
           <cell r="F459" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="460">
           <cell r="F460" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G461" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G462" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G463" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G464" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="465">
           <cell r="F465" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G465" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="466">
           <cell r="F466" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G466" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G467" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G468" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G469" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G470" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G471" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G472" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G473" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G474" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="475">
           <cell r="F475" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G475" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="476">
           <cell r="F476" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G476" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G477" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G478" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G479" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G480" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G481" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G482" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G483" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-25-3416</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G484" t="str">
-            <v>Scented Squishy Plush - Nightime</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-25-3421</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G485" t="str">
-            <v>Scented Squishy Plush - Woodland</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-25-3417</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G486" t="str">
-            <v>Scented Squishy Non-Plush - #2</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G487" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G488" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>Scented Squishy Plush - Nightime</v>
           </cell>
         </row>
         <row r="489">
-          <cell r="F489">
-            <v>989514</v>
+          <cell r="F489" t="str">
+            <v>LL-25-3421</v>
           </cell>
           <cell r="G489" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>Scented Squishy Plush - Woodland</v>
           </cell>
         </row>
         <row r="490">
-          <cell r="F490">
-            <v>989525</v>
+          <cell r="F490" t="str">
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G490" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>Scented Squishy Non-Plush - #2</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G491" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G492" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="493">
-          <cell r="F493" t="str">
-            <v>11-2506-CP12</v>
+          <cell r="F493">
+            <v>989514</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="494">
-          <cell r="F494" t="str">
-            <v>LL-99-3076</v>
+          <cell r="F494">
+            <v>989525</v>
           </cell>
           <cell r="G494" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-99-3077</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G495" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-99-3089</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G496" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="497">
           <cell r="F497" t="str">
-            <v>LL-99-3090</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G497" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="498">
           <cell r="F498" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G498" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-12-3161</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G499" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-12-3172</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G500" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-12-3196</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G501" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-12-3197</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G502" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-12-3215</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G503" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-12-3216</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G504" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-12-3330</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G505" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-12-3331</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G506" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-12-3332</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G507" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G508" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G509" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G510" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="511">
           <cell r="F511" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G511" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="512">
           <cell r="F512" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G512" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Lifelines Analog Bag 2026</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G514" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G515" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G516" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G517" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G518" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G519" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G520" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G521" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G522" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G524" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G525" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G526" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G528" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G529" t="str">
-            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G530" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G531" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G532" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G533" t="str">
-            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G534" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G535" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G536" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G537" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G538" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G539" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G540" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G541" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="542">
           <cell r="F542" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G542" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="543">
           <cell r="F543" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G543" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G544" t="str">
-            <v>FlowArt Minis EXPRESS: Nature's Wonder - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G545" t="str">
-            <v>FlowArt Minis EXPRESS: Furry Friends - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G546" t="str">
-            <v>FlowArt Minis EXPRESS: Pretty Petals - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G547" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G548" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G549" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G550" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G551" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="552">
           <cell r="F552" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G552" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="553">
           <cell r="F553" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G553" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G554" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G555" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G556" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G557" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G558" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G559" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G560" t="str">
-            <v>Candle - Iridescent - WALMART PKG</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G563" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>99-8501</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G564" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Candle - Iridescent - WALMART PKG</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>99-9002</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G565" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="566">
-          <cell r="F566">
-            <v>999003</v>
+          <cell r="F566" t="str">
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G566" t="str">
-            <v>BNC Floor Display</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="567">
-          <cell r="F567">
-            <v>999004</v>
+          <cell r="F567" t="str">
+            <v>99-8302</v>
           </cell>
           <cell r="G567" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-00-0001</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G568" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-00-0002</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G569" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="570">
-          <cell r="F570" t="str">
-            <v>LL-00-0003</v>
+          <cell r="F570">
+            <v>999003</v>
           </cell>
           <cell r="G570" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="571">
-          <cell r="F571" t="str">
-            <v>LL-00-0005</v>
+          <cell r="F571">
+            <v>999004</v>
           </cell>
           <cell r="G571" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G572" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-00-0007</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G573" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="574">
           <cell r="F574" t="str">
-            <v>LL-00-0008</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G574" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="575">
           <cell r="F575" t="str">
-            <v>LL-00-0035</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G575" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-99-0035</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G576" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-00-0009</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G577" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-00-0010</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G578" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G579" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-99-0035</v>
           </cell>
           <cell r="G580" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G581" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G582" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G583" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G584" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G585" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G586" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G587" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G588" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G589" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G590" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G591" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G592" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G593" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G594" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G595" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G596" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G597" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G598" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G599" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G600" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G601" t="str">
-            <v>FlowArt Grocery Display Evergreen - 24</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>LL-99-0024</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G602" t="str">
-            <v>FlowArt Grocery Display Evergreen - Empty</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G603" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>LL-99-0025</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G604" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G605" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>FlowArt Grocery Display Evergreen - 24</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>LL-99-0026</v>
+            <v>LL-99-0024</v>
           </cell>
           <cell r="G606" t="str">
-            <v>FlowArt Fall Grocery Display - Empty</v>
+            <v>FlowArt Grocery Display Evergreen - Empty</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G607" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>LL-99-0027</v>
+            <v>LL-99-0025</v>
           </cell>
           <cell r="G608" t="str">
-            <v>FlowArt Holiday Grocery Display - Empty</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G609" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>LL-99-0028</v>
+            <v>LL-99-0026</v>
           </cell>
           <cell r="G610" t="str">
-            <v>FlowArt Mini Grocery Display - Empty</v>
+            <v>FlowArt Fall Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="611">
           <cell r="F611" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G611" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="612">
           <cell r="F612" t="str">
-            <v>LL-99-0029</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G612" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="613">
           <cell r="F613" t="str">
-            <v>LL-00-0037</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G613" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 36</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="614">
           <cell r="F614" t="str">
-            <v>LL-99-0037</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G614" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 36</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="615">
           <cell r="F615" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G615" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G616" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G617" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G618" t="str">
-            <v>FlowArt Valentine Display - 32</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G619" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G620" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G621" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="622">
           <cell r="F622" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-99-0039</v>
           </cell>
           <cell r="G622" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt MINI Spring Display - Empty</v>
           </cell>
         </row>
         <row r="623">
           <cell r="F623" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0039</v>
           </cell>
           <cell r="G623" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt MINI Spring Display - 36</v>
           </cell>
         </row>
         <row r="624">
           <cell r="F624" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-99-0038</v>
           </cell>
           <cell r="G624" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FlowArt Spring Display - Empty</v>
           </cell>
         </row>
         <row r="625">
           <cell r="F625" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-00-0038</v>
           </cell>
           <cell r="G625" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>FlowArt Spring Display - 24</v>
           </cell>
         </row>
         <row r="626">
           <cell r="F626" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-99-0033</v>
           </cell>
           <cell r="G626" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>FlowArt Valentine Display - Empty</v>
           </cell>
         </row>
         <row r="627">
           <cell r="F627" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G627" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>FlowArt Valentine Display - 24</v>
           </cell>
         </row>
         <row r="628">
           <cell r="F628" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G628" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G629" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G630" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G631" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G632" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G633" t="str">
-            <v>Lifelines Tote</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="634">
           <cell r="F634" t="str">
-            <v>99-9101</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G634" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="635">
           <cell r="F635" t="str">
-            <v>99-9500</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G635" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="636">
           <cell r="F636" t="str">
-            <v>99-9505</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G636" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="637">
           <cell r="F637" t="str">
-            <v>DS01-1001</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G637" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="638">
           <cell r="F638" t="str">
-            <v>DS01-1002</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G638" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="639">
           <cell r="F639" t="str">
-            <v>DS01-1003</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G639" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="640">
           <cell r="F640" t="str">
-            <v>DS01-1004</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G640" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>DS01-1005</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G641" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>DS01-1006</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G642" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>DS01-1007</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G643" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>DS01-1008</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G644" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>LL-16-3143</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G645" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>LL-12-3131</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G646" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>LL-16-3142</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G647" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>LL-12-3135</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G648" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>LL-12-3134</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G649" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>LL-14-3145</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G650" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
-            <v>LL-14-3147</v>
+            <v>DS01-1006</v>
           </cell>
           <cell r="G651" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="652">
           <cell r="F652" t="str">
-            <v>LL-98-3171</v>
+            <v>DS01-1007</v>
           </cell>
           <cell r="G652" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="653">
           <cell r="F653" t="str">
-            <v>LL-11-3087</v>
+            <v>DS01-1008</v>
           </cell>
           <cell r="G653" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="654">
           <cell r="F654" t="str">
-            <v>LL-11-3088</v>
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G654" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="655">
           <cell r="F655" t="str">
-            <v>LL-11-3089</v>
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G655" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="656">
-          <cell r="F656">
-            <v>165002</v>
+          <cell r="F656" t="str">
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G656" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="657">
-          <cell r="F657">
-            <v>165003</v>
+          <cell r="F657" t="str">
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G657" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="658">
-          <cell r="F658">
-            <v>165004</v>
+          <cell r="F658" t="str">
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G658" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="659">
-          <cell r="F659">
-            <v>165010</v>
+          <cell r="F659" t="str">
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G659" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="660">
-          <cell r="F660">
-            <v>165011</v>
+          <cell r="F660" t="str">
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G660" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
         </row>
         <row r="661">
-          <cell r="F661">
-            <v>165013</v>
+          <cell r="F661" t="str">
+            <v>LL-98-3171</v>
           </cell>
           <cell r="G661" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
           </cell>
         </row>
         <row r="662">
-          <cell r="F662">
-            <v>167003</v>
+          <cell r="F662" t="str">
+            <v>LL-11-3087</v>
           </cell>
           <cell r="G662" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>Clickwick 2PK - SKU 5</v>
           </cell>
         </row>
         <row r="663">
           <cell r="F663" t="str">
-            <v>11-1613</v>
+            <v>LL-11-3088</v>
           </cell>
           <cell r="G663" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+            <v>Clickwick 2PK - SKU 6</v>
           </cell>
         </row>
         <row r="664">
           <cell r="F664" t="str">
-            <v>11-1614</v>
+            <v>LL-11-3089</v>
           </cell>
           <cell r="G664" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+            <v>Clickwick 2PK - SKU 7</v>
           </cell>
         </row>
         <row r="665">
-          <cell r="F665" t="str">
-            <v>11-1615</v>
+          <cell r="F665">
+            <v>165002</v>
           </cell>
           <cell r="G665" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
           </cell>
         </row>
         <row r="666">
-          <cell r="F666" t="str">
-            <v>11-1610</v>
+          <cell r="F666">
+            <v>165003</v>
           </cell>
           <cell r="G666" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>FlowArt - Multiline art - Land</v>
           </cell>
         </row>
         <row r="667">
-          <cell r="F667" t="str">
-            <v>16-0107</v>
+          <cell r="F667">
+            <v>165004</v>
           </cell>
           <cell r="G667" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
           </cell>
         </row>
         <row r="668">
-          <cell r="F668" t="str">
-            <v>LL-11-2522</v>
+          <cell r="F668">
+            <v>165010</v>
           </cell>
           <cell r="G668" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>FlowArt - Pogo-dot - In the Garden</v>
           </cell>
         </row>
         <row r="669">
-          <cell r="F669" t="str">
-            <v>LL-11-2523</v>
+          <cell r="F669">
+            <v>165011</v>
           </cell>
           <cell r="G669" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>FlowArt - Dot-pop - Sea</v>
           </cell>
         </row>
         <row r="670">
-          <cell r="F670" t="str">
-            <v>11-0451</v>
+          <cell r="F670">
+            <v>165013</v>
           </cell>
           <cell r="G670" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>FlowArt - Multiline art - Sea</v>
           </cell>
         </row>
         <row r="671">
-          <cell r="F671" t="str">
-            <v>11-0452</v>
+          <cell r="F671">
+            <v>167003</v>
           </cell>
           <cell r="G671" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>Decor Art - Stencil Stationery</v>
           </cell>
         </row>
         <row r="672">
           <cell r="F672" t="str">
-            <v>112522</v>
+            <v>11-1613</v>
+          </cell>
+          <cell r="G672" t="str">
+            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
           </cell>
         </row>
         <row r="673">
           <cell r="F673" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G673" t="str">
+            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="674">
+          <cell r="F674" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G674" t="str">
+            <v>Flameless Candle Diffuser -  Two Tone</v>
+          </cell>
+        </row>
+        <row r="675">
+          <cell r="F675" t="str">
+            <v>11-1610</v>
+          </cell>
+          <cell r="G675" t="str">
+            <v>Planter Diffuser -  Octagon (Cream)</v>
+          </cell>
+        </row>
+        <row r="676">
+          <cell r="F676" t="str">
+            <v>16-0107</v>
+          </cell>
+          <cell r="G676" t="str">
+            <v>Finger Maze Sensory Journal</v>
+          </cell>
+        </row>
+        <row r="677">
+          <cell r="F677" t="str">
+            <v>LL-11-2522</v>
+          </cell>
+          <cell r="G677" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="678">
+          <cell r="F678" t="str">
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G678" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="679">
+          <cell r="F679" t="str">
+            <v>11-0451</v>
+          </cell>
+          <cell r="G679" t="str">
+            <v>Clickwick Replacement Bloom, Citrus</v>
+          </cell>
+        </row>
+        <row r="680">
+          <cell r="F680" t="str">
+            <v>99-9502</v>
+          </cell>
+          <cell r="G680" t="str">
+            <v>Pen Display - Empty</v>
+          </cell>
+        </row>
+        <row r="681">
+          <cell r="F681" t="str">
+            <v>11-0452</v>
+          </cell>
+          <cell r="G681" t="str">
+            <v>Clickwick Replacement Woods, Mountain</v>
+          </cell>
+        </row>
+        <row r="682">
+          <cell r="F682" t="str">
+            <v>112522</v>
+          </cell>
+        </row>
+        <row r="683">
+          <cell r="F683" t="str">
             <v>99-9501</v>
           </cell>
-          <cell r="G673" t="str">
+          <cell r="G683" t="str">
             <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+          </cell>
+        </row>
+        <row r="684">
+          <cell r="F684" t="str">
+            <v>11-1618</v>
+          </cell>
+          <cell r="G684" t="str">
+            <v>Flameless Candle Diffuser - Winter Edition (Frosted Green)</v>
+          </cell>
+        </row>
+        <row r="685">
+          <cell r="F685" t="str">
+            <v>98-9220</v>
+          </cell>
+          <cell r="G685" t="str">
+            <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
         </row>
       </sheetData>
@@ -5940,7 +6036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -6069,7 +6165,7 @@
         <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>3.5</v>
@@ -6080,14 +6176,14 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C9), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -6096,46 +6192,46 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C10), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Mini Single - Furry Friends</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C10), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D11" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FA Mini - Counter Display - Empty</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>3.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6143,14 +6239,14 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C12), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -6164,14 +6260,14 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C13), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -6185,82 +6281,82 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C14), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>3.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="1" customFormat="1">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C15), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
+      </c>
+      <c r="E15">
         <v>6</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C15), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
-      </c>
-      <c r="E15" s="1">
-        <v>6</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>3.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D16" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C16), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>3.5</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="str">
+    <row r="17" spans="1:6" s="1" customFormat="1">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C17), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
-      </c>
-      <c r="E17">
-        <v>12</v>
-      </c>
-      <c r="F17">
+        <v>FlowArt: Mini Single - Furry Friends</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1">
         <v>3.5</v>
       </c>
     </row>
@@ -6269,14 +6365,14 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C18), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E18">
         <v>12</v>
@@ -6285,67 +6381,67 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1" t="str">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C19), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>3.5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D20" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C20), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="str">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>6.5</v>
+        <v>FA Holiday Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -6353,17 +6449,17 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C22), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>6.5</v>
@@ -6374,14 +6470,14 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C23), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -6395,14 +6491,14 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -6416,14 +6512,14 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -6437,14 +6533,14 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -6453,40 +6549,40 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="1" customFormat="1">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="1">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="1" t="str">
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
-      </c>
-      <c r="E27" s="1">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1">
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
         <v>6.5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -6495,24 +6591,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" t="str">
+    <row r="29" spans="1:6" s="1" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="1">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
-      </c>
-      <c r="E29">
-        <v>8</v>
-      </c>
-      <c r="F29">
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E29" s="1">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6521,14 +6617,14 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D30" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -6537,66 +6633,66 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1">
-        <v>4</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="1" t="str">
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
-      </c>
-      <c r="E31" s="1">
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+      </c>
+      <c r="E31">
         <v>8</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>6.5</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D32" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="1" customFormat="1">
+      <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E33" s="1">
         <v>8</v>
       </c>
-      <c r="F32">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
-      </c>
-      <c r="E33">
-        <v>8</v>
-      </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6605,56 +6701,56 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D34" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F34">
         <v>6.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="1" customFormat="1">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="1">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="1" t="str">
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
-      </c>
-      <c r="E35" s="1">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1">
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
         <v>6.5</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D36" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -6663,24 +6759,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" t="str">
+    <row r="37" spans="1:6" s="1" customFormat="1">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
-      <c r="F37">
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -6689,17 +6785,17 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38">
         <v>6.5</v>
@@ -6710,14 +6806,14 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -6731,14 +6827,14 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E40">
         <v>8</v>
@@ -6752,14 +6848,14 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -6773,83 +6869,83 @@
         <v>39</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F42">
         <v>6.5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="1" customFormat="1">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="1">
-        <v>8</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="1" t="str">
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="1">
-        <v>0</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>6.5</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D44" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1">
+      <c r="A45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="1">
         <v>8</v>
       </c>
-      <c r="F44">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
-      </c>
-      <c r="C45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="str">
+      <c r="C45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E45">
-        <v>8</v>
-      </c>
-      <c r="F45">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -6857,14 +6953,14 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E46">
         <v>8</v>
@@ -6878,14 +6974,14 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -6899,14 +6995,14 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -6920,14 +7016,14 @@
         <v>46</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E49">
         <v>8</v>
@@ -6941,14 +7037,14 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E50">
         <v>8</v>
@@ -6962,17 +7058,17 @@
         <v>46</v>
       </c>
       <c r="B51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51">
         <v>6.5</v>
@@ -6983,17 +7079,17 @@
         <v>46</v>
       </c>
       <c r="B52">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52">
         <v>6.5</v>
@@ -7004,17 +7100,17 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53">
         <v>6.5</v>
@@ -7025,14 +7121,14 @@
         <v>46</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D54" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -7046,83 +7142,83 @@
         <v>46</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F55">
         <v>6.5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" s="1" customFormat="1">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
         <v>46</v>
       </c>
-      <c r="B56" s="1">
-        <v>13</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" s="1" t="str">
+      <c r="B56">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="F56" s="1">
-        <v>0</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+      </c>
+      <c r="E56">
+        <v>4</v>
+      </c>
+      <c r="F56">
+        <v>6.5</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57">
         <v>6.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" t="str">
+    <row r="58" spans="1:6" s="1" customFormat="1">
+      <c r="A58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="1">
+        <v>13</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
-      </c>
-      <c r="E58">
-        <v>6</v>
-      </c>
-      <c r="F58">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -7130,17 +7226,17 @@
         <v>51</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D59" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F59">
         <v>6.5</v>
@@ -7151,20 +7247,20 @@
         <v>51</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -7172,14 +7268,14 @@
         <v>51</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E61">
         <v>4</v>
@@ -7193,20 +7289,20 @@
         <v>51</v>
       </c>
       <c r="B62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7214,20 +7310,20 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E63">
         <v>4</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -7235,14 +7331,14 @@
         <v>51</v>
       </c>
       <c r="B64">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E64">
         <v>4</v>
@@ -7256,20 +7352,20 @@
         <v>51</v>
       </c>
       <c r="B65">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E65">
         <v>4</v>
       </c>
       <c r="F65">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -7277,14 +7373,14 @@
         <v>51</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -7293,67 +7389,67 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="1" customFormat="1">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
         <v>51</v>
       </c>
-      <c r="B67" s="1">
-        <v>11</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="1" t="str">
+      <c r="B67">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>6.5</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F68">
         <v>6.5</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69" t="s">
-        <v>63</v>
-      </c>
-      <c r="D69" t="str">
+    <row r="69" spans="1:6" s="1" customFormat="1">
+      <c r="A69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69" s="1">
+        <v>11</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
-      </c>
-      <c r="E69">
-        <v>6</v>
-      </c>
-      <c r="F69">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -7361,17 +7457,17 @@
         <v>62</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F70">
         <v>6.5</v>
@@ -7382,17 +7478,17 @@
         <v>62</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71">
         <v>6.5</v>
@@ -7403,84 +7499,83 @@
         <v>62</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+      </c>
+      <c r="E73">
         <v>8</v>
       </c>
-      <c r="F72">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" s="1" customFormat="1">
-      <c r="A73" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="1">
-        <v>6</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
+      <c r="F73">
+        <v>6.5</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <f>B74+1</f>
-        <v>2</v>
-      </c>
-      <c r="C75" t="s">
-        <v>41</v>
-      </c>
-      <c r="D75" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="1" customFormat="1">
+      <c r="A75" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D75" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E75">
-        <v>12</v>
-      </c>
-      <c r="F75">
-        <v>5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -7488,15 +7583,14 @@
         <v>65</v>
       </c>
       <c r="B76">
-        <f t="shared" ref="B76:B94" si="0">B75+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E76">
         <v>8</v>
@@ -7510,15 +7604,15 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>B76+1</f>
+        <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E77">
         <v>12</v>
@@ -7532,18 +7626,18 @@
         <v>65</v>
       </c>
       <c r="B78">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="B78:B96" si="0">B77+1</f>
+        <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D78" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E78">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F78">
         <v>5</v>
@@ -7555,14 +7649,14 @@
       </c>
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E79">
         <v>12</v>
@@ -7577,17 +7671,17 @@
       </c>
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E80">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F80">
         <v>5</v>
@@ -7599,17 +7693,17 @@
       </c>
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F81">
         <v>5</v>
@@ -7621,14 +7715,14 @@
       </c>
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E82">
         <v>8</v>
@@ -7643,14 +7737,14 @@
       </c>
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E83">
         <v>8</v>
@@ -7665,14 +7759,14 @@
       </c>
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E84">
         <v>8</v>
@@ -7687,14 +7781,14 @@
       </c>
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E85">
         <v>8</v>
@@ -7709,14 +7803,14 @@
       </c>
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E86">
         <v>8</v>
@@ -7731,14 +7825,14 @@
       </c>
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E87">
         <v>8</v>
@@ -7753,17 +7847,17 @@
       </c>
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F88">
         <v>5</v>
@@ -7775,17 +7869,17 @@
       </c>
       <c r="B89">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E89">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89">
         <v>5</v>
@@ -7797,17 +7891,17 @@
       </c>
       <c r="B90">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E90">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90">
         <v>5</v>
@@ -7819,17 +7913,17 @@
       </c>
       <c r="B91">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E91">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91">
         <v>5</v>
@@ -7841,17 +7935,17 @@
       </c>
       <c r="B92">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E92">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92">
         <v>5</v>
@@ -7863,84 +7957,86 @@
       </c>
       <c r="B93">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E93">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" s="1" customFormat="1">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
         <v>65</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>72</v>
+      </c>
+      <c r="D94" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
+      </c>
+      <c r="E94">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>65</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" s="1" customFormat="1">
+      <c r="A96" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D94" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D96" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E96" s="1">
         <v>1</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F96" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" t="s">
-        <v>73</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="C95" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E95">
-        <v>8</v>
-      </c>
-      <c r="F95">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
-        <v>73</v>
-      </c>
-      <c r="B96">
-        <v>2</v>
-      </c>
-      <c r="C96" t="s">
-        <v>43</v>
-      </c>
-      <c r="D96" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E96">
-        <v>8</v>
-      </c>
-      <c r="F96">
-        <v>6.5</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -7948,17 +8044,17 @@
         <v>73</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E97">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97">
         <v>6.5</v>
@@ -7969,17 +8065,17 @@
         <v>73</v>
       </c>
       <c r="B98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98">
         <v>6.5</v>
@@ -7990,14 +8086,14 @@
         <v>73</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D99" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E99">
         <v>4</v>
@@ -8011,14 +8107,14 @@
         <v>73</v>
       </c>
       <c r="B100">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E100">
         <v>4</v>
@@ -8032,14 +8128,14 @@
         <v>73</v>
       </c>
       <c r="B101">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -8053,14 +8149,14 @@
         <v>73</v>
       </c>
       <c r="B102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E102">
         <v>4</v>
@@ -8074,14 +8170,14 @@
         <v>73</v>
       </c>
       <c r="B103">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -8090,67 +8186,67 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" s="1" customFormat="1">
-      <c r="A104" s="1" t="s">
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
         <v>73</v>
       </c>
-      <c r="B104" s="1">
-        <v>10</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D104" s="1" t="str">
+      <c r="B104">
+        <v>8</v>
+      </c>
+      <c r="C104" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
-      </c>
-      <c r="E104" s="1">
-        <v>4</v>
-      </c>
-      <c r="F104" s="1">
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+      <c r="F104">
         <v>6.5</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E105">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F105">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
-        <v>74</v>
-      </c>
-      <c r="B106">
-        <v>2</v>
-      </c>
-      <c r="C106" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="1" customFormat="1">
+      <c r="A106" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106" s="1">
+        <v>10</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D106" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
-      </c>
-      <c r="E106">
-        <v>6</v>
-      </c>
-      <c r="F106">
-        <v>3.5</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+      </c>
+      <c r="E106" s="1">
+        <v>4</v>
+      </c>
+      <c r="F106" s="1">
+        <v>6.5</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -8158,14 +8254,14 @@
         <v>74</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E107">
         <v>6</v>
@@ -8179,14 +8275,14 @@
         <v>74</v>
       </c>
       <c r="B108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C108" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E108">
         <v>6</v>
@@ -8200,14 +8296,14 @@
         <v>74</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D109" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E109">
         <v>6</v>
@@ -8221,14 +8317,14 @@
         <v>74</v>
       </c>
       <c r="B110">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D110" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E110">
         <v>6</v>
@@ -8237,67 +8333,67 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" s="1" customFormat="1">
-      <c r="A111" s="1" t="s">
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
         <v>74</v>
       </c>
-      <c r="B111" s="1">
-        <v>7</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D111" s="1" t="str">
+      <c r="B111">
+        <v>5</v>
+      </c>
+      <c r="C111" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E111" s="1">
-        <v>2</v>
-      </c>
-      <c r="F111" s="1">
-        <v>0</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
+      </c>
+      <c r="E111">
+        <v>6</v>
+      </c>
+      <c r="F111">
+        <v>3.5</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E112">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F112">
         <v>3.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
-        <v>75</v>
-      </c>
-      <c r="B113">
+    <row r="113" spans="1:6" s="1" customFormat="1">
+      <c r="A113" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B113" s="1">
+        <v>7</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FA Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E113" s="1">
         <v>2</v>
       </c>
-      <c r="C113" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
-      </c>
-      <c r="E113">
-        <v>12</v>
-      </c>
-      <c r="F113">
-        <v>3.5</v>
+      <c r="F113" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -8305,14 +8401,14 @@
         <v>75</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E114">
         <v>12</v>
@@ -8321,67 +8417,67 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" s="1" customFormat="1">
-      <c r="A115" s="1" t="s">
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
         <v>75</v>
       </c>
-      <c r="B115" s="1">
-        <v>4</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D115" s="1" t="str">
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E115" s="1">
-        <v>1</v>
-      </c>
-      <c r="F115" s="1">
-        <v>0</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+      </c>
+      <c r="E115">
+        <v>12</v>
+      </c>
+      <c r="F115">
+        <v>3.5</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E116">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F116">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
-        <v>76</v>
-      </c>
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117" t="s">
-        <v>22</v>
-      </c>
-      <c r="D117" t="str">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="1" customFormat="1">
+      <c r="A117" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
-      </c>
-      <c r="E117">
-        <v>4</v>
-      </c>
-      <c r="F117">
-        <v>6.5</v>
+        <v>FA Holiday Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -8389,17 +8485,17 @@
         <v>76</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118">
         <v>6.5</v>
@@ -8410,14 +8506,14 @@
         <v>76</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E119">
         <v>4</v>
@@ -8431,14 +8527,14 @@
         <v>76</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E120">
         <v>4</v>
@@ -8452,14 +8548,14 @@
         <v>76</v>
       </c>
       <c r="B121">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D121" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E121">
         <v>4</v>
@@ -8473,14 +8569,14 @@
         <v>76</v>
       </c>
       <c r="B122">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E122">
         <v>4</v>
@@ -8489,40 +8585,40 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="123" spans="1:6" s="1" customFormat="1">
-      <c r="A123" s="1" t="s">
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
         <v>76</v>
       </c>
-      <c r="B123" s="1">
-        <v>8</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D123" s="1" t="str">
+      <c r="B123">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>26</v>
+      </c>
+      <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
-      </c>
-      <c r="E123" s="1">
-        <v>4</v>
-      </c>
-      <c r="F123" s="1">
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123">
         <v>6.5</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E124">
         <v>4</v>
@@ -8531,24 +8627,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
-        <v>77</v>
-      </c>
-      <c r="B125">
-        <v>2</v>
-      </c>
-      <c r="C125" t="s">
-        <v>31</v>
-      </c>
-      <c r="D125" t="str">
+    <row r="125" spans="1:6" s="1" customFormat="1">
+      <c r="A125" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125" s="1">
+        <v>8</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
-      </c>
-      <c r="E125">
-        <v>8</v>
-      </c>
-      <c r="F125">
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+      </c>
+      <c r="E125" s="1">
+        <v>4</v>
+      </c>
+      <c r="F125" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8557,14 +8653,14 @@
         <v>77</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -8573,66 +8669,66 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="127" spans="1:6" s="1" customFormat="1">
-      <c r="A127" s="1" t="s">
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
         <v>77</v>
       </c>
-      <c r="B127" s="1">
-        <v>4</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D127" s="1" t="str">
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>31</v>
+      </c>
+      <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
-      </c>
-      <c r="E127" s="1">
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+      </c>
+      <c r="E127">
         <v>8</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127">
         <v>6.5</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D128" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="1" customFormat="1">
+      <c r="A129" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B129" s="1">
+        <v>4</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D129" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E129" s="1">
         <v>8</v>
       </c>
-      <c r="F128">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
-        <v>78</v>
-      </c>
-      <c r="B129">
-        <v>2</v>
-      </c>
-      <c r="C129" t="s">
-        <v>36</v>
-      </c>
-      <c r="D129" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
-      </c>
-      <c r="E129">
-        <v>8</v>
-      </c>
-      <c r="F129">
+      <c r="F129" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8641,56 +8737,56 @@
         <v>78</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E130">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F130">
         <v>6.5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" s="1" customFormat="1">
-      <c r="A131" s="1" t="s">
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
         <v>78</v>
       </c>
-      <c r="B131" s="1">
-        <v>4</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D131" s="1" t="str">
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
-      </c>
-      <c r="E131" s="1">
-        <v>4</v>
-      </c>
-      <c r="F131" s="1">
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+      </c>
+      <c r="E131">
+        <v>8</v>
+      </c>
+      <c r="F131">
         <v>6.5</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
       </c>
       <c r="E132">
         <v>4</v>
@@ -8699,24 +8795,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
-        <v>79</v>
-      </c>
-      <c r="B133">
-        <v>2</v>
-      </c>
-      <c r="C133" t="s">
-        <v>41</v>
-      </c>
-      <c r="D133" t="str">
+    <row r="133" spans="1:6" s="1" customFormat="1">
+      <c r="A133" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B133" s="1">
+        <v>4</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E133">
-        <v>4</v>
-      </c>
-      <c r="F133">
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+      </c>
+      <c r="E133" s="1">
+        <v>4</v>
+      </c>
+      <c r="F133" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8725,17 +8821,17 @@
         <v>79</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D134" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E134">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F134">
         <v>6.5</v>
@@ -8746,14 +8842,14 @@
         <v>79</v>
       </c>
       <c r="B135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -8767,14 +8863,14 @@
         <v>79</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E136">
         <v>8</v>
@@ -8788,14 +8884,14 @@
         <v>79</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E137">
         <v>4</v>
@@ -8809,17 +8905,17 @@
         <v>79</v>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C138" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D138" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F138">
         <v>6.5</v>
@@ -8830,38 +8926,38 @@
         <v>79</v>
       </c>
       <c r="B139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D139" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E140">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140">
         <v>6.5</v>
@@ -8869,23 +8965,23 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E141">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F141">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -8893,14 +8989,14 @@
         <v>80</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E142">
         <v>8</v>
@@ -8914,17 +9010,17 @@
         <v>80</v>
       </c>
       <c r="B143">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Mediterranean</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F143">
         <v>6.5</v>
@@ -8935,14 +9031,14 @@
         <v>80</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E144">
         <v>8</v>
@@ -8956,17 +9052,17 @@
         <v>80</v>
       </c>
       <c r="B145">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Stamp by Shape, Mediterranean</v>
       </c>
       <c r="E145">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F145">
         <v>6.5</v>
@@ -8977,14 +9073,14 @@
         <v>80</v>
       </c>
       <c r="B146">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E146">
         <v>8</v>
@@ -8998,14 +9094,14 @@
         <v>80</v>
       </c>
       <c r="B147">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C147" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E147">
         <v>8</v>
@@ -9019,17 +9115,17 @@
         <v>80</v>
       </c>
       <c r="B148">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148">
         <v>6.5</v>
@@ -9040,14 +9136,14 @@
         <v>80</v>
       </c>
       <c r="B149">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E149">
         <v>8</v>
@@ -9061,14 +9157,14 @@
         <v>80</v>
       </c>
       <c r="B150">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D150" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E150">
         <v>4</v>
@@ -9082,83 +9178,83 @@
         <v>80</v>
       </c>
       <c r="B151">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151">
         <v>6.5</v>
       </c>
     </row>
-    <row r="152" spans="1:6" s="1" customFormat="1">
-      <c r="A152" s="1" t="s">
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
         <v>80</v>
       </c>
-      <c r="B152" s="1">
-        <v>13</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D152" s="1" t="str">
+      <c r="B152">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>49</v>
+      </c>
+      <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E152" s="1">
-        <v>1</v>
-      </c>
-      <c r="F152" s="1">
-        <v>0</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+      </c>
+      <c r="E152">
+        <v>4</v>
+      </c>
+      <c r="F152">
+        <v>6.5</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F153">
         <v>6.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
-        <v>81</v>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154" t="s">
-        <v>53</v>
-      </c>
-      <c r="D154" t="str">
+    <row r="154" spans="1:6" s="1" customFormat="1">
+      <c r="A154" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B154" s="1">
+        <v>13</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D154" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
-      </c>
-      <c r="E154">
-        <v>6</v>
-      </c>
-      <c r="F154">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E154" s="1">
+        <v>1</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -9166,17 +9262,17 @@
         <v>81</v>
       </c>
       <c r="B155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C155" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F155">
         <v>6.5</v>
@@ -9187,20 +9283,20 @@
         <v>81</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C156" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E156">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F156">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -9208,14 +9304,14 @@
         <v>81</v>
       </c>
       <c r="B157">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C157" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E157">
         <v>4</v>
@@ -9229,20 +9325,20 @@
         <v>81</v>
       </c>
       <c r="B158">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E158">
         <v>4</v>
       </c>
       <c r="F158">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -9250,20 +9346,20 @@
         <v>81</v>
       </c>
       <c r="B159">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D159" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E159">
         <v>4</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -9271,14 +9367,14 @@
         <v>81</v>
       </c>
       <c r="B160">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C160" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D160" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E160">
         <v>4</v>
@@ -9292,20 +9388,20 @@
         <v>81</v>
       </c>
       <c r="B161">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C161" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D161" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E161">
         <v>4</v>
       </c>
       <c r="F161">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -9313,14 +9409,14 @@
         <v>81</v>
       </c>
       <c r="B162">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E162">
         <v>4</v>
@@ -9329,67 +9425,67 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="163" spans="1:6" s="1" customFormat="1">
-      <c r="A163" s="1" t="s">
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
         <v>81</v>
       </c>
-      <c r="B163" s="1">
-        <v>11</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D163" s="1" t="str">
+      <c r="B163">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s">
+        <v>60</v>
+      </c>
+      <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E163" s="1">
-        <v>1</v>
-      </c>
-      <c r="F163" s="1">
-        <v>0</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+      </c>
+      <c r="E163">
+        <v>4</v>
+      </c>
+      <c r="F163">
+        <v>6.5</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B164">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C164" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F164">
         <v>6.5</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
-        <v>82</v>
-      </c>
-      <c r="B165">
-        <v>2</v>
-      </c>
-      <c r="C165" t="s">
-        <v>63</v>
-      </c>
-      <c r="D165" t="str">
+    <row r="165" spans="1:6" s="1" customFormat="1">
+      <c r="A165" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B165" s="1">
+        <v>11</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D165" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
-      </c>
-      <c r="E165">
-        <v>6</v>
-      </c>
-      <c r="F165">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E165" s="1">
+        <v>1</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -9397,17 +9493,17 @@
         <v>82</v>
       </c>
       <c r="B166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E166">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F166">
         <v>6.5</v>
@@ -9418,17 +9514,17 @@
         <v>82</v>
       </c>
       <c r="B167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C167" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D167" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E167">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F167">
         <v>6.5</v>
@@ -9439,83 +9535,83 @@
         <v>82</v>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E168">
+        <v>4</v>
+      </c>
+      <c r="F168">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>82</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>59</v>
+      </c>
+      <c r="D169" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+      </c>
+      <c r="E169">
         <v>8</v>
       </c>
-      <c r="F168">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" s="1" customFormat="1">
-      <c r="A169" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B169" s="1">
-        <v>6</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D169" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E169" s="1">
-        <v>1</v>
-      </c>
-      <c r="F169" s="1">
-        <v>0</v>
+      <c r="F169">
+        <v>6.5</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C170" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D170" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E170">
         <v>8</v>
       </c>
       <c r="F170">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
-        <v>83</v>
-      </c>
-      <c r="B171">
-        <v>2</v>
-      </c>
-      <c r="C171" t="s">
-        <v>66</v>
-      </c>
-      <c r="D171" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" s="1" customFormat="1">
+      <c r="A171" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B171" s="1">
+        <v>6</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D171" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
-      </c>
-      <c r="E171">
-        <v>4</v>
-      </c>
-      <c r="F171">
-        <v>5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E171" s="1">
+        <v>1</v>
+      </c>
+      <c r="F171" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -9523,17 +9619,17 @@
         <v>83</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Pogo-Dot, Nature</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172">
         <v>5</v>
@@ -9544,17 +9640,17 @@
         <v>83</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
       </c>
       <c r="E173">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F173">
         <v>5</v>
@@ -9565,17 +9661,17 @@
         <v>83</v>
       </c>
       <c r="B174">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C174" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D174" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Pogo-Dot, Nature</v>
       </c>
       <c r="E174">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F174">
         <v>5</v>
@@ -9586,14 +9682,14 @@
         <v>83</v>
       </c>
       <c r="B175">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D175" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E175">
         <v>12</v>
@@ -9607,14 +9703,14 @@
         <v>83</v>
       </c>
       <c r="B176">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D176" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E176">
         <v>12</v>
@@ -9628,14 +9724,14 @@
         <v>83</v>
       </c>
       <c r="B177">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D177" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E177">
         <v>12</v>
@@ -9649,17 +9745,17 @@
         <v>83</v>
       </c>
       <c r="B178">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D178" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C178, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C178), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E178">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F178">
         <v>5</v>
@@ -9670,17 +9766,17 @@
         <v>83</v>
       </c>
       <c r="B179">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D179" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C179, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C179), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E179">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F179">
         <v>5</v>
@@ -9691,17 +9787,17 @@
         <v>83</v>
       </c>
       <c r="B180">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D180" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C180, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C180), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E180">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F180">
         <v>5</v>
@@ -9712,17 +9808,17 @@
         <v>83</v>
       </c>
       <c r="B181">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C181" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D181" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C181, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C181), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E181">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F181">
         <v>5</v>
@@ -9733,17 +9829,17 @@
         <v>83</v>
       </c>
       <c r="B182">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D182" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C182, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C182), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E182">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F182">
         <v>5</v>
@@ -9754,17 +9850,17 @@
         <v>83</v>
       </c>
       <c r="B183">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D183" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C183, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C183), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E183">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F183">
         <v>5</v>
@@ -9775,14 +9871,14 @@
         <v>83</v>
       </c>
       <c r="B184">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="D184" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C184, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C184), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E184">
         <v>8</v>
@@ -9796,14 +9892,14 @@
         <v>83</v>
       </c>
       <c r="B185">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D185" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C185, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C185), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E185">
         <v>8</v>
@@ -9817,17 +9913,17 @@
         <v>83</v>
       </c>
       <c r="B186">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C186" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D186" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C186, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C186), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E186">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F186">
         <v>5</v>
@@ -9838,17 +9934,17 @@
         <v>83</v>
       </c>
       <c r="B187">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D187" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C187, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C187), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E187">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F187">
         <v>5</v>
@@ -9859,14 +9955,14 @@
         <v>83</v>
       </c>
       <c r="B188">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D188" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C188, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C188), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E188">
         <v>4</v>
@@ -9880,14 +9976,14 @@
         <v>83</v>
       </c>
       <c r="B189">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C189" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D189" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C189, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C189), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E189">
         <v>4</v>
@@ -9901,17 +9997,17 @@
         <v>83</v>
       </c>
       <c r="B190">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C190" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D190" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C190, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C190), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E190">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -9922,14 +10018,14 @@
         <v>83</v>
       </c>
       <c r="B191">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D191" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C191, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C191), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E191">
         <v>4</v>
@@ -9938,67 +10034,67 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" s="1" customFormat="1">
-      <c r="A192" s="1" t="s">
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
         <v>83</v>
       </c>
-      <c r="B192" s="1">
-        <v>23</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D192" s="1" t="str">
+      <c r="B192">
+        <v>21</v>
+      </c>
+      <c r="C192" t="s">
+        <v>72</v>
+      </c>
+      <c r="D192" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C192, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C192), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E192" s="1">
-        <v>1</v>
-      </c>
-      <c r="F192" s="1">
-        <v>0</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
+      </c>
+      <c r="E192">
+        <v>12</v>
+      </c>
+      <c r="F192">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D193" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C193, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C193), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E193">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F193">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
-        <v>84</v>
-      </c>
-      <c r="B194">
-        <v>2</v>
-      </c>
-      <c r="C194" t="s">
-        <v>43</v>
-      </c>
-      <c r="D194" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" s="1" customFormat="1">
+      <c r="A194" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B194" s="1">
+        <v>23</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D194" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E194">
-        <v>8</v>
-      </c>
-      <c r="F194">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E194" s="1">
+        <v>1</v>
+      </c>
+      <c r="F194" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -10006,17 +10102,17 @@
         <v>84</v>
       </c>
       <c r="B195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D195" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C195, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C195), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E195">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195">
         <v>6.5</v>
@@ -10027,17 +10123,17 @@
         <v>84</v>
       </c>
       <c r="B196">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D196" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C196, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C196), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E196">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F196">
         <v>6.5</v>
@@ -10048,14 +10144,14 @@
         <v>84</v>
       </c>
       <c r="B197">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D197" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C197, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C197), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -10069,14 +10165,14 @@
         <v>84</v>
       </c>
       <c r="B198">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D198" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C198, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C198), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E198">
         <v>4</v>
@@ -10090,14 +10186,14 @@
         <v>84</v>
       </c>
       <c r="B199">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C199" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D199" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E199">
         <v>4</v>
@@ -10111,14 +10207,14 @@
         <v>84</v>
       </c>
       <c r="B200">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C200" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D200" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E200">
         <v>4</v>
@@ -10132,14 +10228,14 @@
         <v>84</v>
       </c>
       <c r="B201">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D201" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C201, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C201), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E201">
         <v>4</v>
@@ -10153,28 +10249,343 @@
         <v>84</v>
       </c>
       <c r="B202">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D202" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C202, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C202), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
+      </c>
+      <c r="E202">
+        <v>4</v>
+      </c>
+      <c r="F202">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>84</v>
+      </c>
+      <c r="B203">
+        <v>9</v>
+      </c>
+      <c r="C203" t="s">
+        <v>26</v>
+      </c>
+      <c r="D203" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C203, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C203), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E203">
+        <v>4</v>
+      </c>
+      <c r="F203">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>84</v>
+      </c>
+      <c r="B204">
+        <v>10</v>
+      </c>
+      <c r="C204" t="s">
+        <v>49</v>
+      </c>
+      <c r="D204" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C204, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C204), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
-      <c r="E202">
-        <v>4</v>
-      </c>
-      <c r="F202">
+      <c r="E204">
+        <v>4</v>
+      </c>
+      <c r="F204">
         <v>6.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F202" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:F204" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
+    <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+    <xsd:import namespace="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="856a7437-a7e7-4452-817c-46e435f59c4c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2f7773e7-c09a-4624-9b47-1ae33f44799c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0db41735-03c9-45f7-99e2-dcae27ef4500" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{31fd351d-a755-486a-a08e-1b724b18a896}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0db41735-03c9-45f7-99e2-dcae27ef4500">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}"/>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/4) Demand/17) Scripts/mt-shopify-sync/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E250D84-EE5E-4EF3-A31D-3AD4BC6671E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC4D6B3-20AB-4BFB-A44B-52B0EBDDD4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$209</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="93">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -304,6 +304,21 @@
   <si>
     <t>LL-99-0014</t>
   </si>
+  <si>
+    <t>LL-16-3290</t>
+  </si>
+  <si>
+    <t>LL-16-3366</t>
+  </si>
+  <si>
+    <t>LL-16-3367</t>
+  </si>
+  <si>
+    <t>LL-12-3213</t>
+  </si>
+  <si>
+    <t>LL-12-3214</t>
+  </si>
 </sst>
 </file>
 
@@ -344,10 +359,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,7 +391,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls driveId="b!HTnOnJwPMEWf4Qc1OT0tJzUXtA3JA_dFmeLcrifvRQA3dGqF56dSRIF8RuQ19ZxM" itemId="01FHB6EQ4WFPYOBAHH6NC22UE5IJXHENMZ">
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -396,6 +416,9 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
+          <cell r="C1" t="str">
+            <v>Report Format2</v>
+          </cell>
           <cell r="F1" t="str">
             <v>SBOM SKU</v>
           </cell>
@@ -1580,6 +1603,7 @@
           </cell>
         </row>
         <row r="149">
+          <cell r="F149"/>
           <cell r="G149" t="str">
             <v>Lifelines Bath &amp; Shower Spa Bundle</v>
           </cell>
@@ -2498,3374 +2522,3406 @@
         </row>
         <row r="264">
           <cell r="F264" t="str">
-            <v>LL-11-3198</v>
+            <v>LL-11-3440</v>
           </cell>
           <cell r="G264" t="str">
-            <v>ClickWick: Walk-in-the-Woods 3PK</v>
+            <v>Clickwick 7.5ml Single - Autumn's Glow [Bubble Bag]</v>
           </cell>
         </row>
         <row r="265">
           <cell r="F265" t="str">
-            <v>LL-11-3199</v>
+            <v>LL-11-3441</v>
           </cell>
           <cell r="G265" t="str">
-            <v>ClickWick: Herbal 3PK</v>
+            <v>Clickwick 7.5ml Single - Vanilla Plum Bliss [Bubble Bag]</v>
           </cell>
         </row>
         <row r="266">
           <cell r="F266" t="str">
-            <v>LL-11-3194</v>
+            <v>LL-11-3442</v>
           </cell>
           <cell r="G266" t="str">
-            <v>ClickWick: In Bloom 3PK</v>
+            <v>Clickwick 7.5ml Single - Pumpkin Spiced Latte [Bubble Bag]</v>
           </cell>
         </row>
         <row r="267">
           <cell r="F267" t="str">
-            <v>LL-11-3195</v>
+            <v>LL-11-3443</v>
           </cell>
           <cell r="G267" t="str">
-            <v>ClickWick: Citrus Grove 3PK</v>
+            <v>Clickwick 7.5ml Single - Fresh Picked Apples [Bubble Bag]</v>
           </cell>
         </row>
         <row r="268">
           <cell r="F268" t="str">
-            <v>LL-11-3234</v>
+            <v>LL-11-3198</v>
           </cell>
           <cell r="G268" t="str">
-            <v>ClickWick: Very Vanilla: 3PK</v>
+            <v>ClickWick: Walk-in-the-Woods 3PK</v>
           </cell>
         </row>
         <row r="269">
           <cell r="F269" t="str">
-            <v>LL-11-3235</v>
+            <v>LL-11-3199</v>
           </cell>
           <cell r="G269" t="str">
-            <v>ClickWick: Salted Coconut: 3PK</v>
+            <v>ClickWick: Herbal 3PK</v>
           </cell>
         </row>
         <row r="270">
           <cell r="F270" t="str">
-            <v>LL-11-3236</v>
+            <v>LL-11-3194</v>
           </cell>
           <cell r="G270" t="str">
-            <v>ClickWick: Peach Velvet: 3PK</v>
+            <v>ClickWick: In Bloom 3PK</v>
           </cell>
         </row>
         <row r="271">
           <cell r="F271" t="str">
-            <v>LL-11-3237</v>
+            <v>LL-11-3195</v>
           </cell>
           <cell r="G271" t="str">
-            <v>ClickWick: Spiced Rose: 3PK</v>
+            <v>ClickWick: Citrus Grove 3PK</v>
           </cell>
         </row>
         <row r="272">
           <cell r="F272" t="str">
-            <v>LL-11-3240</v>
+            <v>LL-11-3234</v>
           </cell>
           <cell r="G272" t="str">
-            <v>ClickWick: Frosted Fir: 3PK</v>
+            <v>ClickWick: Very Vanilla: 3PK</v>
           </cell>
         </row>
         <row r="273">
           <cell r="F273" t="str">
-            <v>LL-11-3241</v>
+            <v>LL-11-3235</v>
           </cell>
           <cell r="G273" t="str">
-            <v>ClickWick: Warm Mahogany: 3PK</v>
+            <v>ClickWick: Salted Coconut: 3PK</v>
           </cell>
         </row>
         <row r="274">
           <cell r="F274" t="str">
-            <v>LL-11-3306</v>
+            <v>LL-11-3236</v>
           </cell>
           <cell r="G274" t="str">
-            <v>ClickWick: Vanilla Cashmere: 3PK</v>
+            <v>ClickWick: Peach Velvet: 3PK</v>
           </cell>
         </row>
         <row r="275">
           <cell r="F275" t="str">
-            <v>LL-11-3006</v>
+            <v>LL-11-3237</v>
           </cell>
           <cell r="G275" t="str">
-            <v>Clickwick 2 Pack - Desert Canyon Air &amp; Salted Coconut (Target)</v>
+            <v>ClickWick: Spiced Rose: 3PK</v>
           </cell>
         </row>
         <row r="276">
           <cell r="F276" t="str">
-            <v>LL-11-3007</v>
+            <v>LL-11-3240</v>
           </cell>
           <cell r="G276" t="str">
-            <v>Clickwick 2 Pack - Vanilla Tangerine &amp; Peach Linen (Target)</v>
+            <v>ClickWick: Frosted Fir: 3PK</v>
           </cell>
         </row>
         <row r="277">
           <cell r="F277" t="str">
-            <v>LL-11-3008</v>
+            <v>LL-11-3241</v>
           </cell>
           <cell r="G277" t="str">
-            <v>Clickwick 4 PK - Sun-Kissed Escape ClickWick Collection</v>
+            <v>ClickWick: Warm Mahogany: 3PK</v>
           </cell>
         </row>
         <row r="278">
           <cell r="F278" t="str">
-            <v>LL-11-3064</v>
+            <v>LL-11-3306</v>
           </cell>
           <cell r="G278" t="str">
-            <v>Clickwick 4 PK - Lush Earth ClickWick Collection</v>
+            <v>ClickWick: Vanilla Cashmere: 3PK</v>
           </cell>
         </row>
         <row r="279">
           <cell r="F279" t="str">
-            <v>LL-11-3292</v>
+            <v>LL-11-3006</v>
           </cell>
           <cell r="G279" t="str">
-            <v>Fall Clickwick 4PK</v>
+            <v>Clickwick 2 Pack - Desert Canyon Air &amp; Salted Coconut (Target)</v>
           </cell>
         </row>
         <row r="280">
           <cell r="F280" t="str">
+            <v>LL-11-3007</v>
+          </cell>
+          <cell r="G280" t="str">
+            <v>Clickwick 2 Pack - Vanilla Tangerine &amp; Peach Linen (Target)</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="F281" t="str">
+            <v>LL-11-3008</v>
+          </cell>
+          <cell r="G281" t="str">
+            <v>Clickwick 4 PK - Sun-Kissed Escape ClickWick Collection</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="F282" t="str">
+            <v>LL-11-3064</v>
+          </cell>
+          <cell r="G282" t="str">
+            <v>Clickwick 4 PK - Lush Earth ClickWick Collection</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="F283" t="str">
+            <v>LL-11-3292</v>
+          </cell>
+          <cell r="G283" t="str">
+            <v>Fall Clickwick 4PK</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="F284" t="str">
             <v>LL-11-3103</v>
           </cell>
-          <cell r="G280" t="str">
+          <cell r="G284" t="str">
             <v>Winter Clickwick 4PK</v>
-          </cell>
-        </row>
-        <row r="281">
-          <cell r="F281">
-            <v>993014</v>
-          </cell>
-          <cell r="G281" t="str">
-            <v>BNC FlowArt Assorted Shipper Display (Spring 2025)</v>
-          </cell>
-        </row>
-        <row r="282">
-          <cell r="F282">
-            <v>165001</v>
-          </cell>
-          <cell r="G282" t="str">
-            <v>FlowArt: Dot-Pop, Natural Flow</v>
-          </cell>
-        </row>
-        <row r="283">
-          <cell r="F283">
-            <v>165005</v>
-          </cell>
-          <cell r="G283" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals</v>
-          </cell>
-        </row>
-        <row r="284">
-          <cell r="F284">
-            <v>165006</v>
-          </cell>
-          <cell r="G284" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
           </cell>
         </row>
         <row r="285">
           <cell r="F285">
-            <v>165007</v>
+            <v>993014</v>
           </cell>
           <cell r="G285" t="str">
-            <v>FlowArt: Pogo-Dot, Nature</v>
+            <v>BNC FlowArt Assorted Shipper Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="286">
           <cell r="F286">
-            <v>165008</v>
+            <v>165001</v>
           </cell>
           <cell r="G286" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes</v>
+            <v>FlowArt: Dot-Pop, Natural Flow</v>
           </cell>
         </row>
         <row r="287">
           <cell r="F287">
-            <v>165009</v>
+            <v>165005</v>
           </cell>
           <cell r="G287" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals</v>
           </cell>
         </row>
         <row r="288">
           <cell r="F288">
-            <v>165012</v>
+            <v>165006</v>
           </cell>
           <cell r="G288" t="str">
-            <v>FlowArt: Color-to-Reveal, Animals</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
           </cell>
         </row>
         <row r="289">
           <cell r="F289">
+            <v>165007</v>
+          </cell>
+          <cell r="G289" t="str">
+            <v>FlowArt: Pogo-Dot, Nature</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="F290">
+            <v>165008</v>
+          </cell>
+          <cell r="G290" t="str">
+            <v>FlowArt: Dot-By-Letter, Landscapes</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="F291">
+            <v>165009</v>
+          </cell>
+          <cell r="G291" t="str">
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="F292">
+            <v>165012</v>
+          </cell>
+          <cell r="G292" t="str">
+            <v>FlowArt: Color-to-Reveal, Animals</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="F293">
             <v>165014</v>
           </cell>
-          <cell r="G289" t="str">
+          <cell r="G293" t="str">
             <v>FlowArt: Stamp by Shape, Mediterranean</v>
-          </cell>
-        </row>
-        <row r="290">
-          <cell r="F290" t="str">
-            <v>LL-16-3429</v>
-          </cell>
-          <cell r="G290" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - D03</v>
-          </cell>
-        </row>
-        <row r="291">
-          <cell r="F291" t="str">
-            <v>LL-16-3430</v>
-          </cell>
-          <cell r="G291" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - D03</v>
-          </cell>
-        </row>
-        <row r="292">
-          <cell r="F292" t="str">
-            <v>LL-16-3385</v>
-          </cell>
-          <cell r="G292" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
-          </cell>
-        </row>
-        <row r="293">
-          <cell r="F293" t="str">
-            <v>LL-16-3384</v>
-          </cell>
-          <cell r="G293" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink] - D03</v>
           </cell>
         </row>
         <row r="294">
           <cell r="F294" t="str">
-            <v>LL-16-3433</v>
+            <v>LL-16-3429</v>
           </cell>
           <cell r="G294" t="str">
-            <v>FlowArt: Dot-By-Letter, Birds Song in Bloom [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - D03</v>
           </cell>
         </row>
         <row r="295">
           <cell r="F295" t="str">
-            <v>LL-16-3148</v>
+            <v>LL-16-3430</v>
           </cell>
           <cell r="G295" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - D03</v>
           </cell>
         </row>
         <row r="296">
           <cell r="F296" t="str">
-            <v>LL-16-3153</v>
+            <v>LL-16-3385</v>
           </cell>
           <cell r="G296" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
           </cell>
         </row>
         <row r="297">
           <cell r="F297" t="str">
-            <v>LL-16-3148-V3</v>
+            <v>LL-16-3384</v>
           </cell>
           <cell r="G297" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink] - D03</v>
           </cell>
         </row>
         <row r="298">
           <cell r="F298" t="str">
-            <v>LL-16-3153-V3</v>
+            <v>LL-16-3433</v>
           </cell>
           <cell r="G298" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Birds Song in Bloom [Metallic]</v>
           </cell>
         </row>
         <row r="299">
           <cell r="F299" t="str">
-            <v>LL-16-3149</v>
+            <v>LL-16-3148</v>
           </cell>
           <cell r="G299" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="300">
           <cell r="F300" t="str">
-            <v>LL-16-3150</v>
+            <v>LL-16-3153</v>
           </cell>
           <cell r="G300" t="str">
-            <v>FlowArt: Stamp by Shape, Secret Garden</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="301">
           <cell r="F301" t="str">
-            <v>LL-16-3151</v>
+            <v>LL-16-3148-V3</v>
           </cell>
           <cell r="G301" t="str">
-            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="302">
           <cell r="F302" t="str">
-            <v>LL-16-3152</v>
+            <v>LL-16-3153-V3</v>
           </cell>
           <cell r="G302" t="str">
-            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="303">
           <cell r="F303" t="str">
-            <v>LL-16-3157</v>
+            <v>LL-16-3149</v>
           </cell>
           <cell r="G303" t="str">
-            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
           </cell>
         </row>
         <row r="304">
           <cell r="F304" t="str">
-            <v>LL-16-3158</v>
+            <v>LL-16-3150</v>
           </cell>
           <cell r="G304" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+            <v>FlowArt: Stamp by Shape, Secret Garden</v>
           </cell>
         </row>
         <row r="305">
           <cell r="F305" t="str">
-            <v>LL-16-3323</v>
+            <v>LL-16-3151</v>
           </cell>
           <cell r="G305" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
+            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
           </cell>
         </row>
         <row r="306">
           <cell r="F306" t="str">
-            <v>LL-16-3159</v>
+            <v>LL-16-3152</v>
           </cell>
           <cell r="G306" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
+            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
           </cell>
         </row>
         <row r="307">
           <cell r="F307" t="str">
-            <v>LL-16-3160</v>
+            <v>LL-16-3157</v>
           </cell>
           <cell r="G307" t="str">
-            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
+            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
           </cell>
         </row>
         <row r="308">
           <cell r="F308" t="str">
-            <v>LL-16-3290</v>
+            <v>LL-16-3158</v>
           </cell>
           <cell r="G308" t="str">
-            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
           </cell>
         </row>
         <row r="309">
           <cell r="F309" t="str">
-            <v>LL-16-3247</v>
+            <v>LL-16-3323</v>
           </cell>
           <cell r="G309" t="str">
-            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
           </cell>
         </row>
         <row r="310">
           <cell r="F310" t="str">
-            <v>LL-16-3248</v>
+            <v>LL-16-3159</v>
           </cell>
           <cell r="G310" t="str">
-            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
           </cell>
         </row>
         <row r="311">
           <cell r="F311" t="str">
-            <v>LL-16-3162</v>
+            <v>LL-16-3160</v>
           </cell>
           <cell r="G311" t="str">
-            <v>FlowArt: Dot-By-Letter, Snowed In</v>
+            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
           </cell>
         </row>
         <row r="312">
           <cell r="F312" t="str">
-            <v>LL-16-3244</v>
+            <v>LL-16-3290</v>
           </cell>
           <cell r="G312" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
           </cell>
         </row>
         <row r="313">
           <cell r="F313" t="str">
-            <v>LL-16-3245</v>
+            <v>LL-16-3247</v>
           </cell>
           <cell r="G313" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
           </cell>
         </row>
         <row r="314">
           <cell r="F314" t="str">
-            <v>LL-16-3246</v>
+            <v>LL-16-3248</v>
           </cell>
           <cell r="G314" t="str">
-            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
           </cell>
         </row>
         <row r="315">
           <cell r="F315" t="str">
-            <v>LL-16-3366</v>
+            <v>LL-16-3162</v>
           </cell>
           <cell r="G315" t="str">
-            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Snowed In</v>
           </cell>
         </row>
         <row r="316">
           <cell r="F316" t="str">
-            <v>LL-16-3163</v>
+            <v>LL-16-3244</v>
           </cell>
           <cell r="G316" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
+            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
           </cell>
         </row>
         <row r="317">
           <cell r="F317" t="str">
-            <v>LL-16-3367</v>
+            <v>LL-16-3245</v>
           </cell>
           <cell r="G317" t="str">
-            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
           </cell>
         </row>
         <row r="318">
           <cell r="F318" t="str">
-            <v>LL-16-3368</v>
+            <v>LL-16-3246</v>
           </cell>
           <cell r="G318" t="str">
-            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
+            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
           </cell>
         </row>
         <row r="319">
           <cell r="F319" t="str">
-            <v>LL-16-3369</v>
+            <v>LL-16-3366</v>
           </cell>
           <cell r="G319" t="str">
-            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
+            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
           </cell>
         </row>
         <row r="320">
           <cell r="F320" t="str">
-            <v>LL-16-3371</v>
+            <v>LL-16-3163</v>
           </cell>
           <cell r="G320" t="str">
-            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
+            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
           </cell>
         </row>
         <row r="321">
           <cell r="F321" t="str">
-            <v>LL-16-3372</v>
+            <v>LL-16-3367</v>
           </cell>
           <cell r="G321" t="str">
-            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
+            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
           </cell>
         </row>
         <row r="322">
           <cell r="F322" t="str">
-            <v>LL-16-3373</v>
+            <v>LL-16-3368</v>
           </cell>
           <cell r="G322" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
           </cell>
         </row>
         <row r="323">
           <cell r="F323" t="str">
-            <v>LL-16-3374</v>
+            <v>LL-16-3369</v>
           </cell>
           <cell r="G323" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
           </cell>
         </row>
         <row r="324">
           <cell r="F324" t="str">
-            <v>LL-16-3352</v>
+            <v>LL-16-3371</v>
           </cell>
           <cell r="G324" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
           </cell>
         </row>
         <row r="325">
           <cell r="F325" t="str">
-            <v>LL-16-3390</v>
+            <v>LL-16-3372</v>
           </cell>
           <cell r="G325" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
           </cell>
         </row>
         <row r="326">
           <cell r="F326" t="str">
-            <v>LL-16-3375</v>
+            <v>LL-16-3373</v>
           </cell>
           <cell r="G326" t="str">
-            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sweets - TGT</v>
           </cell>
         </row>
         <row r="327">
           <cell r="F327" t="str">
-            <v>LL-16-3391</v>
+            <v>LL-16-3374</v>
           </cell>
           <cell r="G327" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
           </cell>
         </row>
         <row r="328">
           <cell r="F328" t="str">
-            <v>LL-16-3376</v>
+            <v>LL-16-3352</v>
           </cell>
           <cell r="G328" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
           </cell>
         </row>
         <row r="329">
           <cell r="F329" t="str">
-            <v>LL-16-3389</v>
+            <v>LL-16-3390</v>
           </cell>
           <cell r="G329" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance</v>
+            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
           </cell>
         </row>
         <row r="330">
           <cell r="F330" t="str">
-            <v>LL-16-3395</v>
+            <v>LL-16-3375</v>
           </cell>
           <cell r="G330" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club</v>
+            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
           </cell>
         </row>
         <row r="331">
           <cell r="F331" t="str">
-            <v>LL-16-3392</v>
+            <v>LL-16-3391</v>
           </cell>
           <cell r="G331" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets</v>
+            <v>FlowArt: Trace-By-Line, Self Care Club - TGT</v>
           </cell>
         </row>
         <row r="332">
           <cell r="F332" t="str">
-            <v>LL-16-3393</v>
+            <v>LL-16-3376</v>
           </cell>
           <cell r="G332" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
+            <v>FlowArt: Trace-By-Line, Book Romance - TGT</v>
           </cell>
         </row>
         <row r="333">
           <cell r="F333" t="str">
-            <v>LL-16-3394</v>
+            <v>LL-16-3389</v>
           </cell>
           <cell r="G333" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette</v>
+            <v>FlowArt: Trace-By-Line, Book Romance</v>
           </cell>
         </row>
         <row r="334">
           <cell r="F334" t="str">
-            <v>LL-16-3200</v>
+            <v>LL-16-3395</v>
           </cell>
           <cell r="G334" t="str">
-            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+            <v>FlowArt: Trace-By-Line, Self Care Club</v>
           </cell>
         </row>
         <row r="335">
           <cell r="F335" t="str">
-            <v>LL-16-3201</v>
+            <v>LL-16-3392</v>
           </cell>
           <cell r="G335" t="str">
-            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
+            <v>FlowArt: Dot-By-Letter, Sweets</v>
           </cell>
         </row>
         <row r="336">
           <cell r="F336" t="str">
-            <v>LL-16-3204</v>
+            <v>LL-16-3393</v>
           </cell>
           <cell r="G336" t="str">
-            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
           </cell>
         </row>
         <row r="337">
           <cell r="F337" t="str">
-            <v>LL-16-3205</v>
+            <v>LL-16-3394</v>
           </cell>
           <cell r="G337" t="str">
-            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+            <v>FlowArt: Trace-By-Line, Coquette</v>
           </cell>
         </row>
         <row r="338">
           <cell r="F338" t="str">
-            <v>LL-16-3206</v>
+            <v>LL-16-3200</v>
           </cell>
           <cell r="G338" t="str">
-            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
           </cell>
         </row>
         <row r="339">
           <cell r="F339" t="str">
-            <v>LL-16-3207</v>
+            <v>LL-16-3201</v>
           </cell>
           <cell r="G339" t="str">
-            <v>FlowArt: Trace Within, Peaceful Pause</v>
+            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
           </cell>
         </row>
         <row r="340">
           <cell r="F340" t="str">
-            <v>LL-16-3249</v>
+            <v>LL-16-3204</v>
           </cell>
           <cell r="G340" t="str">
-            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
           </cell>
         </row>
         <row r="341">
           <cell r="F341" t="str">
-            <v>LL-16-3222</v>
+            <v>LL-16-3205</v>
           </cell>
           <cell r="G341" t="str">
-            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
           </cell>
         </row>
         <row r="342">
           <cell r="F342" t="str">
-            <v>LL-16-3223</v>
+            <v>LL-16-3206</v>
           </cell>
           <cell r="G342" t="str">
-            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
           </cell>
         </row>
         <row r="343">
           <cell r="F343" t="str">
-            <v>LL-16-3411</v>
+            <v>LL-16-3207</v>
           </cell>
           <cell r="G343" t="str">
-            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
+            <v>FlowArt: Trace Within, Peaceful Pause</v>
           </cell>
         </row>
         <row r="344">
           <cell r="F344" t="str">
-            <v>LL-16-3418</v>
+            <v>LL-16-3249</v>
           </cell>
           <cell r="G344" t="str">
-            <v>FlowArt: Trace-By-Line, Pets</v>
+            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
           </cell>
         </row>
         <row r="345">
           <cell r="F345" t="str">
-            <v>LL-16-3420</v>
+            <v>LL-16-3222</v>
           </cell>
           <cell r="G345" t="str">
-            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
+            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
           </cell>
         </row>
         <row r="346">
           <cell r="F346" t="str">
-            <v>LL-16-3202</v>
+            <v>LL-16-3223</v>
           </cell>
           <cell r="G346" t="str">
-            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
           </cell>
         </row>
         <row r="347">
           <cell r="F347" t="str">
-            <v>LL-16-3203</v>
+            <v>LL-16-3411</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
           </cell>
         </row>
         <row r="348">
           <cell r="F348" t="str">
-            <v>LL-16-3407</v>
+            <v>LL-16-3418</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
+            <v>FlowArt: Trace-By-Line, Pets</v>
           </cell>
         </row>
         <row r="349">
           <cell r="F349" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3420</v>
           </cell>
           <cell r="G349" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
           </cell>
         </row>
         <row r="350">
           <cell r="F350" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3202</v>
           </cell>
           <cell r="G350" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
           </cell>
         </row>
         <row r="351">
           <cell r="F351" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3203</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
           </cell>
         </row>
         <row r="352">
           <cell r="F352" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G352" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
           </cell>
         </row>
         <row r="353">
           <cell r="F353" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G353" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
         </row>
         <row r="354">
           <cell r="F354" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G354" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
         </row>
         <row r="355">
           <cell r="F355" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G355" t="str">
-            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
         </row>
         <row r="356">
           <cell r="F356" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G356" t="str">
-            <v>FlowArt: Premium #3 - The Great Outdoors</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="357">
           <cell r="F357" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G357" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="358">
           <cell r="F358" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G358" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Dot-By-Letter, Corner Café</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Stitch-By-Cross: [Floral - name TBD]</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Stich-By-Cross: Cheeky Sayings</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-16-3419</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Stitch-By-Cross: [TBD]</v>
+            <v>FlowArt: Dot-By-Letter, Corner Café</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: [Cottage]</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-16-3422</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
+            <v>FlowArt: Stitch-By-X, Homegrown Garden</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-16-3423</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Stitch-To-Embroider: #1</v>
+            <v>FlowArt: Stich-By-X, Cheeky Sayings</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-16-3424</v>
+            <v>LL-16-3419</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Stitch-To-Quilt: #1</v>
+            <v>FlowArt: Stitch-By-X, [Nature TBD]</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Stitch-By-Needlepoint: Home Sweet Home</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3422</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3423</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Stitch-To-Embroider: #1</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-16-3424</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Stitch-To-Quilt: #1</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-20-3408</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt: Mini Single - Berry Bliss</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-20-3409</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt: Mini Single - Hummingbird Haven</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-20-3410</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt: Mini Single - Wildflower Woods</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-20-3412</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt: Mini Single - Coastal Calm</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="411">
           <cell r="F411" t="str">
-            <v>LL-20-3413</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowArt: Mini Single - Sweet Summer</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="412">
           <cell r="F412" t="str">
-            <v>LL-20-3414</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowArt: Mini Single - Under the Sea</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="413">
           <cell r="F413" t="str">
-            <v>LL-20-3415</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="414">
           <cell r="F414" t="str">
-            <v>LL-20-3434</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowArt: Mini Single - Cross-Stitch #1</v>
+            <v>FlowArt: Mini Single - Coastal Calm</v>
           </cell>
         </row>
         <row r="415">
           <cell r="F415" t="str">
-            <v>LL-20-3435</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowArt: Mini Single - Cross-Stitch #2</v>
+            <v>FlowArt: Mini Single - Sweet Summer</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-20-3436</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt: Mini Single - Cross-Stitch #3</v>
+            <v>FlowArt: Mini Single - Under the Sea</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3434</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt Mini Stitch-by-X: [Botanical Bouquet]</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3435</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt Mini Stitch-by-X: [Birds &amp; Branches]</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-20-3436</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt Mini Stitch-by-X: [Spring Landscape]</v>
           </cell>
         </row>
         <row r="421">
           <cell r="F421" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="422">
           <cell r="F422" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="423">
           <cell r="F423" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="424">
           <cell r="F424" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="425">
           <cell r="F425" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-30-3359</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt Mini EXPRESS, #12</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
-            <v>LL-30-3406</v>
+            <v>LL-30-3360</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+            <v>FlowArt Mini EXPRESS, #13</v>
           </cell>
         </row>
         <row r="434">
           <cell r="F434" t="str">
-            <v>LL-30-3425</v>
+            <v>LL-30-3361</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
+            <v>FlowArt Mini EXPRESS, #14</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-30-3426</v>
+            <v>LL-30-3362</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
+            <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-30-3427</v>
+            <v>LL-30-3405</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
+            <v>LL-30-3406</v>
+          </cell>
+          <cell r="G437" t="str">
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+          </cell>
+        </row>
+        <row r="438">
+          <cell r="F438" t="str">
+            <v>LL-30-3425</v>
+          </cell>
+          <cell r="G438" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
+          </cell>
+        </row>
+        <row r="439">
+          <cell r="F439" t="str">
+            <v>LL-30-3426</v>
+          </cell>
+          <cell r="G439" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
+          </cell>
+        </row>
+        <row r="440">
+          <cell r="F440" t="str">
+            <v>LL-30-3427</v>
+          </cell>
+          <cell r="G440" t="str">
+            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
+          </cell>
+        </row>
+        <row r="441">
+          <cell r="F441" t="str">
             <v>LL-30-3428</v>
           </cell>
-          <cell r="G437" t="str">
+          <cell r="G441" t="str">
             <v>FlowArt Mini EXPRESS, Tween Collection - Fruity Tutti</v>
-          </cell>
-        </row>
-        <row r="438">
-          <cell r="F438">
-            <v>167001</v>
-          </cell>
-          <cell r="G438" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
-          </cell>
-        </row>
-        <row r="439">
-          <cell r="F439">
-            <v>167002</v>
-          </cell>
-          <cell r="G439" t="str">
-            <v>FlowCrafts: Collage Art</v>
-          </cell>
-        </row>
-        <row r="440">
-          <cell r="F440">
-            <v>167004</v>
-          </cell>
-          <cell r="G440" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
-          </cell>
-        </row>
-        <row r="441">
-          <cell r="F441">
-            <v>167005</v>
-          </cell>
-          <cell r="G441" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="442">
           <cell r="F442">
+            <v>167001</v>
+          </cell>
+          <cell r="G442" t="str">
+            <v>FlowCrafts: Paper Flower Bouquet</v>
+          </cell>
+        </row>
+        <row r="443">
+          <cell r="F443">
+            <v>167002</v>
+          </cell>
+          <cell r="G443" t="str">
+            <v>FlowCrafts: Collage Art</v>
+          </cell>
+        </row>
+        <row r="444">
+          <cell r="F444">
+            <v>167004</v>
+          </cell>
+          <cell r="G444" t="str">
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
+          </cell>
+        </row>
+        <row r="445">
+          <cell r="F445">
+            <v>167005</v>
+          </cell>
+          <cell r="G445" t="str">
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
+          </cell>
+        </row>
+        <row r="446">
+          <cell r="F446">
             <v>167006</v>
           </cell>
-          <cell r="G442" t="str">
+          <cell r="G446" t="str">
             <v>FlowCrafts: Decorative Tile Lamp</v>
-          </cell>
-        </row>
-        <row r="443">
-          <cell r="F443" t="str">
-            <v>LL-98-3188</v>
-          </cell>
-          <cell r="G443" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="444">
-          <cell r="F444" t="str">
-            <v>LL-98-3189</v>
-          </cell>
-          <cell r="G444" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="445">
-          <cell r="F445" t="str">
-            <v>LL-98-3190</v>
-          </cell>
-          <cell r="G445" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
-          </cell>
-        </row>
-        <row r="446">
-          <cell r="F446" t="str">
-            <v>LL-98-3191</v>
-          </cell>
-          <cell r="G446" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3025</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3026</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3027</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-98-3028</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-98-3091</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-98-3168</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-98-3169</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-98-3170</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-98-3307</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="456">
           <cell r="F456" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="457">
           <cell r="F457" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="458">
           <cell r="F458" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="459">
           <cell r="F459" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="460">
           <cell r="F460" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G461" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G462" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G463" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G464" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="465">
           <cell r="F465" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G465" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="466">
           <cell r="F466" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G466" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G467" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G468" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G469" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G470" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G471" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G472" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G473" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G474" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="475">
           <cell r="F475" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G475" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="476">
           <cell r="F476" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G476" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G477" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G478" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G479" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G480" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G481" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G482" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G483" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G484" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G485" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G486" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G487" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-25-3416</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G488" t="str">
-            <v>Scented Squishy Plush - Nightime</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-25-3421</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G489" t="str">
-            <v>Scented Squishy Plush - Woodland</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-25-3417</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G490" t="str">
-            <v>Scented Squishy Non-Plush - #2</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G491" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G492" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>Scented Squishy Plush - Nightime</v>
           </cell>
         </row>
         <row r="493">
-          <cell r="F493">
-            <v>989514</v>
+          <cell r="F493" t="str">
+            <v>LL-25-3421</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>Scented Squishy Plush - Woodland</v>
           </cell>
         </row>
         <row r="494">
-          <cell r="F494">
-            <v>989525</v>
+          <cell r="F494" t="str">
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G494" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>Scented Squishy Non-Plush - #2</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G495" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G496" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="497">
-          <cell r="F497" t="str">
-            <v>11-2506-CP12</v>
+          <cell r="F497">
+            <v>989514</v>
           </cell>
           <cell r="G497" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="498">
-          <cell r="F498" t="str">
-            <v>LL-99-3076</v>
+          <cell r="F498">
+            <v>989525</v>
           </cell>
           <cell r="G498" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-99-3077</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G499" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-99-3089</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G500" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-99-3090</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G501" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G502" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-12-3161</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G503" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-12-3172</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G504" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-12-3196</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G505" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-12-3197</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G506" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-12-3215</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G507" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-12-3216</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G508" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-12-3330</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G509" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-12-3331</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G510" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="511">
           <cell r="F511" t="str">
-            <v>LL-12-3332</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G511" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="512">
           <cell r="F512" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G512" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G514" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G515" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G516" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G517" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Lifelines Analog Bag 2026</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G518" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G519" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G520" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G521" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G522" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G524" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G525" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G526" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G528" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G529" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G530" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G531" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G532" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G533" t="str">
-            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G534" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G535" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G536" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G537" t="str">
-            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G538" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G539" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G540" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G541" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
           </cell>
         </row>
         <row r="542">
           <cell r="F542" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G542" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="543">
           <cell r="F543" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G543" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G544" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G545" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G546" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G547" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G548" t="str">
-            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G549" t="str">
-            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G550" t="str">
-            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G551" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="552">
           <cell r="F552" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G552" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
           </cell>
         </row>
         <row r="553">
           <cell r="F553" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G553" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G554" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G555" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G556" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G557" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G558" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G559" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G560" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G563" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G564" t="str">
-            <v>Candle - Iridescent - WALMART PKG</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G565" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G566" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G567" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>99-8501</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G568" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Candle - Iridescent - WALMART PKG</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>99-9002</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G569" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="570">
-          <cell r="F570">
-            <v>999003</v>
+          <cell r="F570" t="str">
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G570" t="str">
-            <v>BNC Floor Display</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="571">
-          <cell r="F571">
-            <v>999004</v>
+          <cell r="F571" t="str">
+            <v>99-8302</v>
           </cell>
           <cell r="G571" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-00-0001</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G572" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-00-0002</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G573" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="574">
-          <cell r="F574" t="str">
-            <v>LL-00-0003</v>
+          <cell r="F574">
+            <v>999003</v>
           </cell>
           <cell r="G574" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="575">
-          <cell r="F575" t="str">
-            <v>LL-00-0005</v>
+          <cell r="F575">
+            <v>999004</v>
           </cell>
           <cell r="G575" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G576" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-00-0007</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G577" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-00-0008</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G578" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-00-0035</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G579" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-99-0035</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G580" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-00-0009</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G581" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-00-0010</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G582" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G583" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-99-0035</v>
           </cell>
           <cell r="G584" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G585" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G586" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G587" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G588" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G589" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G590" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G591" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G592" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G593" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G594" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G595" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G596" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G597" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G598" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G599" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G600" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G601" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G602" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G603" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G604" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G605" t="str">
-            <v>FlowArt Grocery Display Evergreen - 24</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>LL-99-0024</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G606" t="str">
-            <v>FlowArt Grocery Display Evergreen - Empty</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G607" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>LL-99-0025</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G608" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G609" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>FlowArt Grocery Display Evergreen - 24</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>LL-99-0026</v>
+            <v>LL-99-0024</v>
           </cell>
           <cell r="G610" t="str">
-            <v>FlowArt Fall Grocery Display - Empty</v>
+            <v>FlowArt Grocery Display Evergreen - Empty</v>
           </cell>
         </row>
         <row r="611">
           <cell r="F611" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G611" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="612">
           <cell r="F612" t="str">
-            <v>LL-99-0027</v>
+            <v>LL-99-0025</v>
           </cell>
           <cell r="G612" t="str">
-            <v>FlowArt Holiday Grocery Display - Empty</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="613">
           <cell r="F613" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G613" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="614">
           <cell r="F614" t="str">
-            <v>LL-99-0028</v>
+            <v>LL-99-0026</v>
           </cell>
           <cell r="G614" t="str">
-            <v>FlowArt Mini Grocery Display - Empty</v>
+            <v>FlowArt Fall Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="615">
           <cell r="F615" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G615" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>LL-99-0029</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G616" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>LL-00-0037</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G617" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>LL-99-0037</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G618" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G619" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G620" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G621" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
           </cell>
         </row>
         <row r="622">
           <cell r="F622" t="str">
-            <v>LL-99-0039</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G622" t="str">
-            <v>FlowArt MINI Spring Display - Empty</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
           </cell>
         </row>
         <row r="623">
           <cell r="F623" t="str">
-            <v>LL-00-0039</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G623" t="str">
-            <v>FlowArt MINI Spring Display - 36</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="624">
           <cell r="F624" t="str">
-            <v>LL-99-0038</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G624" t="str">
-            <v>FlowArt Spring Display - Empty</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="625">
           <cell r="F625" t="str">
-            <v>LL-00-0038</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G625" t="str">
-            <v>FlowArt Spring Display - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="626">
           <cell r="F626" t="str">
-            <v>LL-99-0033</v>
+            <v>LL-99-0039</v>
           </cell>
           <cell r="G626" t="str">
-            <v>FlowArt Valentine Display - Empty</v>
+            <v>FlowArt MINI Spring Display - Empty</v>
           </cell>
         </row>
         <row r="627">
           <cell r="F627" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-00-0039</v>
           </cell>
           <cell r="G627" t="str">
-            <v>FlowArt Valentine Display - 24</v>
+            <v>FlowArt MINI Spring Display - 36</v>
           </cell>
         </row>
         <row r="628">
           <cell r="F628" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-99-0038</v>
           </cell>
           <cell r="G628" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt Spring Display - Empty</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-00-0038</v>
           </cell>
           <cell r="G629" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Spring Display - 24</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-99-0033</v>
           </cell>
           <cell r="G630" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Valentine Display - Empty</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G631" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Valentine Display - 24</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G632" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G633" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="634">
           <cell r="F634" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G634" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="635">
           <cell r="F635" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G635" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="636">
           <cell r="F636" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G636" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="637">
           <cell r="F637" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G637" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="638">
           <cell r="F638" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G638" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="639">
           <cell r="F639" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G639" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="640">
           <cell r="F640" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G640" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G641" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G642" t="str">
-            <v>Lifelines Tote</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>99-9101</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G643" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>99-9500</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G644" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>99-9505</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G645" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>DS01-1001</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G646" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>DS01-1002</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G647" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>DS01-1003</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G648" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>DS01-1004</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G649" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>DS01-1005</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G650" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
-            <v>DS01-1006</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G651" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="652">
           <cell r="F652" t="str">
-            <v>DS01-1007</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G652" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="653">
           <cell r="F653" t="str">
-            <v>DS01-1008</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G653" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="654">
           <cell r="F654" t="str">
-            <v>LL-16-3143</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G654" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="655">
           <cell r="F655" t="str">
-            <v>LL-12-3131</v>
+            <v>DS01-1006</v>
           </cell>
           <cell r="G655" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="656">
           <cell r="F656" t="str">
-            <v>LL-16-3142</v>
+            <v>DS01-1007</v>
           </cell>
           <cell r="G656" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="657">
           <cell r="F657" t="str">
-            <v>LL-12-3135</v>
+            <v>DS01-1008</v>
           </cell>
           <cell r="G657" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="658">
           <cell r="F658" t="str">
-            <v>LL-12-3134</v>
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G658" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="659">
           <cell r="F659" t="str">
-            <v>LL-14-3145</v>
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G659" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="660">
           <cell r="F660" t="str">
-            <v>LL-14-3147</v>
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G660" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="661">
           <cell r="F661" t="str">
-            <v>LL-98-3171</v>
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G661" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="662">
           <cell r="F662" t="str">
-            <v>LL-11-3087</v>
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G662" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="663">
           <cell r="F663" t="str">
-            <v>LL-11-3088</v>
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G663" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="664">
           <cell r="F664" t="str">
+            <v>LL-14-3147</v>
+          </cell>
+          <cell r="G664" t="str">
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="665">
+          <cell r="F665" t="str">
+            <v>LL-98-3171</v>
+          </cell>
+          <cell r="G665" t="str">
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="666">
+          <cell r="F666" t="str">
+            <v>LL-11-3087</v>
+          </cell>
+          <cell r="G666" t="str">
+            <v>Clickwick 2PK - SKU 5</v>
+          </cell>
+        </row>
+        <row r="667">
+          <cell r="F667" t="str">
+            <v>LL-11-3088</v>
+          </cell>
+          <cell r="G667" t="str">
+            <v>Clickwick 2PK - SKU 6</v>
+          </cell>
+        </row>
+        <row r="668">
+          <cell r="F668" t="str">
             <v>LL-11-3089</v>
           </cell>
-          <cell r="G664" t="str">
+          <cell r="G668" t="str">
             <v>Clickwick 2PK - SKU 7</v>
-          </cell>
-        </row>
-        <row r="665">
-          <cell r="F665">
-            <v>165002</v>
-          </cell>
-          <cell r="G665" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
-          </cell>
-        </row>
-        <row r="666">
-          <cell r="F666">
-            <v>165003</v>
-          </cell>
-          <cell r="G666" t="str">
-            <v>FlowArt - Multiline art - Land</v>
-          </cell>
-        </row>
-        <row r="667">
-          <cell r="F667">
-            <v>165004</v>
-          </cell>
-          <cell r="G667" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
-          </cell>
-        </row>
-        <row r="668">
-          <cell r="F668">
-            <v>165010</v>
-          </cell>
-          <cell r="G668" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
           </cell>
         </row>
         <row r="669">
           <cell r="F669">
-            <v>165011</v>
+            <v>165002</v>
           </cell>
           <cell r="G669" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
           </cell>
         </row>
         <row r="670">
           <cell r="F670">
-            <v>165013</v>
+            <v>165003</v>
           </cell>
           <cell r="G670" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>FlowArt - Multiline art - Land</v>
           </cell>
         </row>
         <row r="671">
           <cell r="F671">
+            <v>165004</v>
+          </cell>
+          <cell r="G671" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="672">
+          <cell r="F672">
+            <v>165010</v>
+          </cell>
+          <cell r="G672" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="673">
+          <cell r="F673">
+            <v>165011</v>
+          </cell>
+          <cell r="G673" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="674">
+          <cell r="F674">
+            <v>165013</v>
+          </cell>
+          <cell r="G674" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="675">
+          <cell r="F675">
             <v>167003</v>
           </cell>
-          <cell r="G671" t="str">
+          <cell r="G675" t="str">
             <v>Decor Art - Stencil Stationery</v>
-          </cell>
-        </row>
-        <row r="672">
-          <cell r="F672" t="str">
-            <v>11-1613</v>
-          </cell>
-          <cell r="G672" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
-          </cell>
-        </row>
-        <row r="673">
-          <cell r="F673" t="str">
-            <v>11-1614</v>
-          </cell>
-          <cell r="G673" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
-          </cell>
-        </row>
-        <row r="674">
-          <cell r="F674" t="str">
-            <v>11-1615</v>
-          </cell>
-          <cell r="G674" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
-          </cell>
-        </row>
-        <row r="675">
-          <cell r="F675" t="str">
-            <v>11-1610</v>
-          </cell>
-          <cell r="G675" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
           </cell>
         </row>
         <row r="676">
           <cell r="F676" t="str">
-            <v>16-0107</v>
+            <v>11-1613</v>
           </cell>
           <cell r="G676" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
           </cell>
         </row>
         <row r="677">
           <cell r="F677" t="str">
-            <v>LL-11-2522</v>
+            <v>11-1614</v>
           </cell>
           <cell r="G677" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
           </cell>
         </row>
         <row r="678">
           <cell r="F678" t="str">
-            <v>LL-11-2523</v>
+            <v>11-1615</v>
           </cell>
           <cell r="G678" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>Flameless Candle Diffuser -  Two Tone</v>
           </cell>
         </row>
         <row r="679">
           <cell r="F679" t="str">
-            <v>11-0451</v>
+            <v>11-1610</v>
           </cell>
           <cell r="G679" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>Planter Diffuser -  Octagon (Cream)</v>
           </cell>
         </row>
         <row r="680">
           <cell r="F680" t="str">
-            <v>99-9502</v>
+            <v>16-0107</v>
           </cell>
           <cell r="G680" t="str">
-            <v>Pen Display - Empty</v>
+            <v>Finger Maze Sensory Journal</v>
           </cell>
         </row>
         <row r="681">
           <cell r="F681" t="str">
-            <v>11-0452</v>
+            <v>LL-11-2522</v>
           </cell>
           <cell r="G681" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
           </cell>
         </row>
         <row r="682">
           <cell r="F682" t="str">
-            <v>112522</v>
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G682" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
           </cell>
         </row>
         <row r="683">
           <cell r="F683" t="str">
-            <v>99-9501</v>
+            <v>11-0451</v>
           </cell>
           <cell r="G683" t="str">
-            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+            <v>Clickwick Replacement Bloom, Citrus</v>
           </cell>
         </row>
         <row r="684">
           <cell r="F684" t="str">
-            <v>11-1618</v>
+            <v>99-9502</v>
           </cell>
           <cell r="G684" t="str">
-            <v>Flameless Candle Diffuser - Winter Edition (Frosted Green)</v>
+            <v>Pen Display - Empty</v>
           </cell>
         </row>
         <row r="685">
           <cell r="F685" t="str">
+            <v>11-0452</v>
+          </cell>
+          <cell r="G685" t="str">
+            <v>Clickwick Replacement Woods, Mountain</v>
+          </cell>
+        </row>
+        <row r="686">
+          <cell r="F686" t="str">
+            <v>112522</v>
+          </cell>
+        </row>
+        <row r="687">
+          <cell r="F687" t="str">
+            <v>99-9501</v>
+          </cell>
+          <cell r="G687" t="str">
+            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+          </cell>
+        </row>
+        <row r="688">
+          <cell r="F688" t="str">
+            <v>11-1618</v>
+          </cell>
+          <cell r="G688" t="str">
+            <v>Flameless Candle Diffuser - Winter Edition (Frosted Green)</v>
+          </cell>
+        </row>
+        <row r="689">
+          <cell r="F689" t="str">
             <v>98-9220</v>
           </cell>
-          <cell r="G685" t="str">
+          <cell r="G689" t="str">
             <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
         </row>
@@ -5875,7 +5931,13 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="9">
+        <row r="1">
+          <cell r="C1" t="str">
+            <v>LL PN (Final)</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -6036,12 +6098,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.6875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
@@ -6074,7 +6136,7 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
@@ -6094,7 +6156,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="str">
@@ -6115,7 +6177,7 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="str">
@@ -6136,7 +6198,7 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="str">
@@ -6157,7 +6219,7 @@
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="str">
@@ -6178,7 +6240,7 @@
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="str">
@@ -6199,7 +6261,7 @@
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="str">
@@ -6220,7 +6282,7 @@
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D11" s="1" t="str">
@@ -6241,7 +6303,7 @@
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="str">
@@ -6249,7 +6311,7 @@
         <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>3.5</v>
@@ -6262,7 +6324,7 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="str">
@@ -6283,7 +6345,7 @@
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D14" t="str">
@@ -6304,7 +6366,7 @@
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="str">
@@ -6312,7 +6374,7 @@
         <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F15">
         <v>3.5</v>
@@ -6325,7 +6387,7 @@
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="str">
@@ -6346,7 +6408,7 @@
       <c r="B17" s="1">
         <v>6</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="1" t="str">
@@ -6354,7 +6416,7 @@
         <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E17" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1">
         <v>3.5</v>
@@ -6367,7 +6429,7 @@
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D18" t="str">
@@ -6388,7 +6450,7 @@
       <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D19" t="str">
@@ -6409,7 +6471,7 @@
       <c r="B20">
         <v>3</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="str">
@@ -6430,7 +6492,7 @@
       <c r="B21" s="1">
         <v>4</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="1" t="str">
@@ -6451,7 +6513,7 @@
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="str">
@@ -6472,7 +6534,7 @@
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D23" t="str">
@@ -6493,7 +6555,7 @@
       <c r="B24">
         <v>3</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="str">
@@ -6514,7 +6576,7 @@
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D25" t="str">
@@ -6535,7 +6597,7 @@
       <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="str">
@@ -6556,7 +6618,7 @@
       <c r="B27">
         <v>6</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D27" t="str">
@@ -6577,7 +6639,7 @@
       <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="str">
@@ -6598,7 +6660,7 @@
       <c r="B29" s="1">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D29" s="1" t="str">
@@ -6619,7 +6681,7 @@
       <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D30" t="str">
@@ -6640,7 +6702,7 @@
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D31" t="str">
@@ -6661,7 +6723,7 @@
       <c r="B32">
         <v>3</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D32" t="str">
@@ -6682,7 +6744,7 @@
       <c r="B33" s="1">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D33" s="1" t="str">
@@ -6703,7 +6765,7 @@
       <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D34" t="str">
@@ -6724,7 +6786,7 @@
       <c r="B35">
         <v>2</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D35" t="str">
@@ -6745,7 +6807,7 @@
       <c r="B36">
         <v>3</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="str">
@@ -6766,7 +6828,7 @@
       <c r="B37" s="1">
         <v>4</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="1" t="str">
@@ -6787,15 +6849,15 @@
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" t="s">
-        <v>40</v>
+      <c r="C38" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D38" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>6.5</v>
@@ -6808,15 +6870,15 @@
       <c r="B39">
         <v>2</v>
       </c>
-      <c r="C39" t="s">
-        <v>41</v>
+      <c r="C39" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D39" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39">
         <v>6.5</v>
@@ -6829,15 +6891,15 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
-        <v>42</v>
+      <c r="C40" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D40" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F40">
         <v>6.5</v>
@@ -6850,15 +6912,15 @@
       <c r="B41">
         <v>4</v>
       </c>
-      <c r="C41" t="s">
-        <v>43</v>
+      <c r="C41" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D41" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41">
         <v>6.5</v>
@@ -6871,15 +6933,15 @@
       <c r="B42">
         <v>5</v>
       </c>
-      <c r="C42" t="s">
-        <v>21</v>
+      <c r="C42" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E42">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42">
         <v>6.5</v>
@@ -6892,12 +6954,12 @@
       <c r="B43">
         <v>6</v>
       </c>
-      <c r="C43" t="s">
-        <v>44</v>
+      <c r="C43" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E43">
         <v>4</v>
@@ -6906,46 +6968,46 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+    <row r="44" spans="1:6" s="1" customFormat="1">
+      <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D44" t="str">
+      <c r="B44" s="1">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
-      </c>
-      <c r="E44">
-        <v>4</v>
-      </c>
-      <c r="F44">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" s="1" customFormat="1">
-      <c r="A45" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="1">
-        <v>8</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="1" t="str">
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3">
+        <v>165005</v>
+      </c>
+      <c r="D45" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1">
-        <v>0</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>6.5</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -6953,17 +7015,17 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="C46" s="3">
+        <v>165008</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F46">
         <v>6.5</v>
@@ -6974,14 +7036,14 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>41</v>
+        <v>3</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -6995,14 +7057,14 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>23</v>
+        <v>4</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -7016,14 +7078,14 @@
         <v>46</v>
       </c>
       <c r="B49">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
-        <v>86</v>
+        <v>5</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E49">
         <v>8</v>
@@ -7037,14 +7099,14 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <v>5</v>
-      </c>
-      <c r="C50" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E50">
         <v>8</v>
@@ -7058,17 +7120,17 @@
         <v>46</v>
       </c>
       <c r="B51">
-        <v>6</v>
-      </c>
-      <c r="C51" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51">
         <v>6.5</v>
@@ -7079,17 +7141,17 @@
         <v>46</v>
       </c>
       <c r="B52">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E52">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52">
         <v>6.5</v>
@@ -7100,17 +7162,17 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>8</v>
-      </c>
-      <c r="C53" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F53">
         <v>6.5</v>
@@ -7121,14 +7183,14 @@
         <v>46</v>
       </c>
       <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D54" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -7142,9 +7204,9 @@
         <v>46</v>
       </c>
       <c r="B55">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D55" t="str">
@@ -7152,7 +7214,7 @@
         <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E55">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55">
         <v>6.5</v>
@@ -7163,14 +7225,14 @@
         <v>46</v>
       </c>
       <c r="B56">
-        <v>11</v>
-      </c>
-      <c r="C56" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E56">
         <v>4</v>
@@ -7184,9 +7246,10 @@
         <v>46</v>
       </c>
       <c r="B57">
-        <v>12</v>
-      </c>
-      <c r="C57" t="s">
+        <f>B56+1</f>
+        <v>13</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D57" t="str">
@@ -7200,46 +7263,47 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="1" customFormat="1">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
         <v>46</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58">
+        <f>B57+1</f>
+        <v>14</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+      </c>
+      <c r="E58">
+        <v>8</v>
+      </c>
+      <c r="F58">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="1" customFormat="1">
+      <c r="A59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="1">
         <v>13</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D59" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F59" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>52</v>
-      </c>
-      <c r="D59" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E59">
-        <v>6</v>
-      </c>
-      <c r="F59">
-        <v>6.5</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -7247,14 +7311,14 @@
         <v>51</v>
       </c>
       <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D60" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -7268,17 +7332,17 @@
         <v>51</v>
       </c>
       <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61" t="s">
-        <v>54</v>
+        <v>2</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61">
         <v>6.5</v>
@@ -7289,20 +7353,20 @@
         <v>51</v>
       </c>
       <c r="B62">
-        <v>4</v>
-      </c>
-      <c r="C62" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7310,20 +7374,20 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>5</v>
-      </c>
-      <c r="C63" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E63">
         <v>4</v>
       </c>
       <c r="F63">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -7331,14 +7395,14 @@
         <v>51</v>
       </c>
       <c r="B64">
-        <v>6</v>
-      </c>
-      <c r="C64" t="s">
-        <v>57</v>
+        <v>5</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E64">
         <v>4</v>
@@ -7352,20 +7416,20 @@
         <v>51</v>
       </c>
       <c r="B65">
-        <v>7</v>
-      </c>
-      <c r="C65" t="s">
-        <v>58</v>
+        <v>6</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E65">
         <v>4</v>
       </c>
       <c r="F65">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -7373,20 +7437,20 @@
         <v>51</v>
       </c>
       <c r="B66">
-        <v>8</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E66">
         <v>4</v>
       </c>
       <c r="F66">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -7394,14 +7458,14 @@
         <v>51</v>
       </c>
       <c r="B67">
-        <v>9</v>
-      </c>
-      <c r="C67" t="s">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -7415,59 +7479,59 @@
         <v>51</v>
       </c>
       <c r="B68">
-        <v>10</v>
-      </c>
-      <c r="C68" t="s">
-        <v>61</v>
+        <v>9</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>Scented Marker 10 Colors</v>
       </c>
-      <c r="E68">
-        <v>4</v>
-      </c>
-      <c r="F68">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" s="1" customFormat="1">
-      <c r="A69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B69" s="1">
-        <v>11</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>6.5</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Visual Symphony Pen, Glitter 5Pck</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F70">
         <v>6.5</v>
@@ -7475,44 +7539,44 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71" t="s">
-        <v>63</v>
+        <v>12</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Visual Symphony Pen, Swirl 5Pck</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71">
         <v>6.5</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72">
-        <v>3</v>
-      </c>
-      <c r="C72" t="s">
-        <v>57</v>
-      </c>
-      <c r="D72" t="str">
+    <row r="72" spans="1:6" s="1" customFormat="1">
+      <c r="A72" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" s="1">
+        <v>13</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
-      </c>
-      <c r="E72">
-        <v>4</v>
-      </c>
-      <c r="F72">
-        <v>6.5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -7520,17 +7584,17 @@
         <v>62</v>
       </c>
       <c r="B73">
-        <v>4</v>
-      </c>
-      <c r="C73" t="s">
-        <v>59</v>
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73">
         <v>6.5</v>
@@ -7541,106 +7605,104 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>5</v>
-      </c>
-      <c r="C74" t="s">
-        <v>64</v>
+        <v>2</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E74">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F74">
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" s="1" customFormat="1">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
         <v>62</v>
       </c>
-      <c r="B75" s="1">
-        <v>6</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="1" t="str">
+      <c r="B75">
+        <v>3</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>6.5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E76">
         <v>8</v>
       </c>
       <c r="F76">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B77">
-        <f>B76+1</f>
-        <v>2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E77">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B78">
-        <f t="shared" ref="B78:B96" si="0">B77+1</f>
-        <v>3</v>
-      </c>
-      <c r="C78" t="s">
-        <v>86</v>
-      </c>
-      <c r="D78" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" s="1" customFormat="1">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>6</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
-      </c>
-      <c r="E78">
-        <v>8</v>
-      </c>
-      <c r="F78">
-        <v>5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -7648,18 +7710,17 @@
         <v>65</v>
       </c>
       <c r="B79">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C79" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C79" s="3">
+        <v>165005</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E79">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79">
         <v>5</v>
@@ -7670,15 +7731,15 @@
         <v>65</v>
       </c>
       <c r="B80">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C80" t="s">
-        <v>43</v>
+        <f>B79+1</f>
+        <v>2</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E80">
         <v>12</v>
@@ -7692,18 +7753,18 @@
         <v>65</v>
       </c>
       <c r="B81">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C81" t="s">
-        <v>21</v>
+        <f t="shared" ref="B81:B99" si="0">B80+1</f>
+        <v>3</v>
+      </c>
+      <c r="C81" s="3">
+        <v>165008</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E81">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F81">
         <v>5</v>
@@ -7715,9 +7776,9 @@
       </c>
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D82" t="str">
@@ -7725,7 +7786,7 @@
         <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E82">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82">
         <v>5</v>
@@ -7737,17 +7798,17 @@
       </c>
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C83" t="s">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E83">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F83">
         <v>5</v>
@@ -7759,17 +7820,17 @@
       </c>
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>68</v>
+        <v>6</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E84">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F84">
         <v>5</v>
@@ -7781,17 +7842,17 @@
       </c>
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C85" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E85">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F85">
         <v>5</v>
@@ -7803,17 +7864,17 @@
       </c>
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C86" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E86">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F86">
         <v>5</v>
@@ -7825,9 +7886,9 @@
       </c>
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="str">
@@ -7847,17 +7908,17 @@
       </c>
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E88">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F88">
         <v>5</v>
@@ -7869,14 +7930,14 @@
       </c>
       <c r="B89">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C89" t="s">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E89">
         <v>8</v>
@@ -7891,17 +7952,17 @@
       </c>
       <c r="B90">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C90" t="s">
-        <v>70</v>
+        <v>12</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F90">
         <v>5</v>
@@ -7913,14 +7974,14 @@
       </c>
       <c r="B91">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C91" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E91">
         <v>4</v>
@@ -7935,17 +7996,17 @@
       </c>
       <c r="B92">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92">
         <v>5</v>
@@ -7957,17 +8018,17 @@
       </c>
       <c r="B93">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C93" t="s">
-        <v>71</v>
+        <v>15</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E93">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93">
         <v>5</v>
@@ -7979,17 +8040,17 @@
       </c>
       <c r="B94">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C94" t="s">
-        <v>72</v>
+        <v>16</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F94">
         <v>5</v>
@@ -8001,105 +8062,108 @@
       </c>
       <c r="B95">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C95" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E95">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" s="1" customFormat="1">
-      <c r="A96" s="1" t="s">
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
         <v>65</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D96" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E96">
+        <v>8</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+      </c>
+      <c r="E97">
+        <v>12</v>
+      </c>
+      <c r="F97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" s="1" customFormat="1">
+      <c r="A99" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B99" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C99" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D96" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D99" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E99" s="1">
         <v>1</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F99" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" t="s">
-        <v>73</v>
-      </c>
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="C97" t="s">
-        <v>42</v>
-      </c>
-      <c r="D97" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E97">
-        <v>8</v>
-      </c>
-      <c r="F97">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
-        <v>73</v>
-      </c>
-      <c r="B98">
-        <v>2</v>
-      </c>
-      <c r="C98" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E98">
-        <v>8</v>
-      </c>
-      <c r="F98">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" t="s">
-        <v>73</v>
-      </c>
-      <c r="B99">
-        <v>3</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E99">
-        <v>4</v>
-      </c>
-      <c r="F99">
-        <v>6.5</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -8107,17 +8171,17 @@
         <v>73</v>
       </c>
       <c r="B100">
-        <v>4</v>
-      </c>
-      <c r="C100" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E100">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100">
         <v>6.5</v>
@@ -8128,17 +8192,17 @@
         <v>73</v>
       </c>
       <c r="B101">
-        <v>5</v>
-      </c>
-      <c r="C101" t="s">
-        <v>41</v>
+        <v>2</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101">
         <v>6.5</v>
@@ -8149,14 +8213,14 @@
         <v>73</v>
       </c>
       <c r="B102">
-        <v>6</v>
-      </c>
-      <c r="C102" t="s">
-        <v>86</v>
+        <v>3</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E102">
         <v>4</v>
@@ -8170,14 +8234,14 @@
         <v>73</v>
       </c>
       <c r="B103">
-        <v>7</v>
-      </c>
-      <c r="C103" t="s">
-        <v>44</v>
+        <v>4</v>
+      </c>
+      <c r="C103" s="3">
+        <v>165005</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -8191,14 +8255,14 @@
         <v>73</v>
       </c>
       <c r="B104">
-        <v>8</v>
-      </c>
-      <c r="C104" t="s">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="C104" s="3">
+        <v>165008</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -8212,9 +8276,9 @@
         <v>73</v>
       </c>
       <c r="B105">
-        <v>9</v>
-      </c>
-      <c r="C105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D105" t="str">
@@ -8228,109 +8292,109 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" s="1" customFormat="1">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B106" s="1">
-        <v>10</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D106" s="1" t="str">
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D106" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
-      </c>
-      <c r="E106" s="1">
-        <v>4</v>
-      </c>
-      <c r="F106" s="1">
+        <v>FlowArt: Dot-By-Letter, Americana</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+      <c r="F106">
         <v>6.5</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107" t="s">
         <v>8</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E107">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F107">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B108">
-        <v>2</v>
-      </c>
-      <c r="C108" t="s">
         <v>9</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E108">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F108">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B109">
-        <v>3</v>
-      </c>
-      <c r="C109" t="s">
         <v>10</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D109" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F109">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
-        <v>74</v>
-      </c>
-      <c r="B110">
-        <v>4</v>
-      </c>
-      <c r="C110" t="s">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="1" customFormat="1">
+      <c r="A110" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B110" s="1">
         <v>11</v>
       </c>
-      <c r="D110" t="str">
+      <c r="C110" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
-      </c>
-      <c r="E110">
-        <v>6</v>
-      </c>
-      <c r="F110">
-        <v>3.5</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E110" s="1">
+        <v>4</v>
+      </c>
+      <c r="F110" s="1">
+        <v>6.5</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -8338,14 +8402,14 @@
         <v>74</v>
       </c>
       <c r="B111">
-        <v>5</v>
-      </c>
-      <c r="C111" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D111" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E111">
         <v>6</v>
@@ -8359,14 +8423,14 @@
         <v>74</v>
       </c>
       <c r="B112">
-        <v>6</v>
-      </c>
-      <c r="C112" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E112">
         <v>6</v>
@@ -8375,43 +8439,43 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" s="1" customFormat="1">
-      <c r="A113" s="1" t="s">
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
         <v>74</v>
       </c>
-      <c r="B113" s="1">
-        <v>7</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D113" s="1" t="str">
+      <c r="B113">
+        <v>3</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Mini - Counter Display - Empty</v>
-      </c>
-      <c r="E113" s="1">
-        <v>2</v>
-      </c>
-      <c r="F113" s="1">
-        <v>0</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
+      </c>
+      <c r="E113">
+        <v>6</v>
+      </c>
+      <c r="F113">
+        <v>3.5</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114" t="s">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F114">
         <v>3.5</v>
@@ -8419,20 +8483,20 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B115">
-        <v>2</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E115">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F115">
         <v>3.5</v>
@@ -8440,20 +8504,20 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E116">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F116">
         <v>3.5</v>
@@ -8461,20 +8525,20 @@
     </row>
     <row r="117" spans="1:6" s="1" customFormat="1">
       <c r="A117" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B117" s="1">
-        <v>4</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D117" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FA Holiday Mini - Counter Display - Empty</v>
+        <v>FA Mini - Counter Display - Empty</v>
       </c>
       <c r="E117" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -8482,86 +8546,86 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
-      <c r="C118" t="s">
-        <v>21</v>
+      <c r="C118" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E118">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F118">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
-      <c r="C119" t="s">
-        <v>22</v>
+      <c r="C119" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F119">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
-      <c r="C120" t="s">
-        <v>23</v>
+      <c r="C120" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F120">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
-        <v>76</v>
-      </c>
-      <c r="B121">
-        <v>4</v>
-      </c>
-      <c r="C121" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" t="str">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" s="1" customFormat="1">
+      <c r="A121" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
-      </c>
-      <c r="E121">
-        <v>4</v>
-      </c>
-      <c r="F121">
-        <v>6.5</v>
+        <v>FA Holiday Mini - Counter Display - Empty</v>
+      </c>
+      <c r="E121" s="1">
+        <v>1</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -8569,17 +8633,17 @@
         <v>76</v>
       </c>
       <c r="B122">
-        <v>5</v>
-      </c>
-      <c r="C122" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F122">
         <v>6.5</v>
@@ -8590,14 +8654,14 @@
         <v>76</v>
       </c>
       <c r="B123">
-        <v>6</v>
-      </c>
-      <c r="C123" t="s">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E123">
         <v>4</v>
@@ -8611,56 +8675,56 @@
         <v>76</v>
       </c>
       <c r="B124">
-        <v>7</v>
-      </c>
-      <c r="C124" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
+      </c>
+      <c r="E124">
+        <v>8</v>
+      </c>
+      <c r="F124">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D125" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
-      <c r="E124">
-        <v>4</v>
-      </c>
-      <c r="F124">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" s="1" customFormat="1">
-      <c r="A125" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B125" s="1">
-        <v>8</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
-      </c>
-      <c r="E125" s="1">
-        <v>4</v>
-      </c>
-      <c r="F125" s="1">
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125">
         <v>6.5</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B126">
-        <v>1</v>
-      </c>
-      <c r="C126" t="s">
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -8671,83 +8735,83 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B127">
-        <v>2</v>
-      </c>
-      <c r="C127" t="s">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E127">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127">
         <v>6.5</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
+    <row r="128" spans="1:6" s="1" customFormat="1">
+      <c r="A128" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B128" s="1">
+        <v>7</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D128" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+      </c>
+      <c r="E128" s="1">
+        <v>4</v>
+      </c>
+      <c r="F128" s="1">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
         <v>77</v>
       </c>
-      <c r="B128">
-        <v>3</v>
-      </c>
-      <c r="C128" t="s">
-        <v>32</v>
-      </c>
-      <c r="D128" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
-      </c>
-      <c r="E128">
-        <v>4</v>
-      </c>
-      <c r="F128">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" s="1" customFormat="1">
-      <c r="A129" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B129" s="1">
-        <v>4</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D129" s="1" t="str">
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
-      </c>
-      <c r="E129" s="1">
-        <v>8</v>
-      </c>
-      <c r="F129" s="1">
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+      </c>
+      <c r="E129">
+        <v>4</v>
+      </c>
+      <c r="F129">
         <v>6.5</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B130">
-        <v>1</v>
-      </c>
-      <c r="C130" t="s">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130">
         <v>6.5</v>
@@ -8755,17 +8819,17 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
-      <c r="C131" t="s">
-        <v>36</v>
+      <c r="C131" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E131">
         <v>8</v>
@@ -8776,17 +8840,17 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
-      <c r="C132" t="s">
-        <v>37</v>
+      <c r="C132" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E132">
         <v>4</v>
@@ -8797,17 +8861,17 @@
     </row>
     <row r="133" spans="1:6" s="1" customFormat="1">
       <c r="A133" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B133" s="1">
         <v>4</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>38</v>
+      <c r="C133" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="D133" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -8818,17 +8882,17 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
-      <c r="C134" t="s">
-        <v>40</v>
+      <c r="C134" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D134" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E134">
         <v>4</v>
@@ -8839,17 +8903,17 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
-      <c r="C135" t="s">
-        <v>41</v>
+      <c r="C135" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -8860,17 +8924,17 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
-      <c r="C136" t="s">
-        <v>42</v>
+      <c r="C136" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
       <c r="E136">
         <v>8</v>
@@ -8881,17 +8945,17 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
-      <c r="C137" t="s">
-        <v>43</v>
+      <c r="C137" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
       </c>
       <c r="E137">
         <v>4</v>
@@ -8900,24 +8964,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
-      <c r="A138" t="s">
-        <v>79</v>
-      </c>
-      <c r="B138">
+    <row r="138" spans="1:6" s="1" customFormat="1">
+      <c r="A138" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B138" s="1">
         <v>5</v>
       </c>
-      <c r="C138" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" t="str">
+      <c r="C138" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E138">
-        <v>8</v>
-      </c>
-      <c r="F138">
+        <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+      </c>
+      <c r="E138" s="1">
+        <v>4</v>
+      </c>
+      <c r="F138" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8926,14 +8990,14 @@
         <v>79</v>
       </c>
       <c r="B139">
-        <v>6</v>
-      </c>
-      <c r="C139" t="s">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D139" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E139">
         <v>4</v>
@@ -8947,14 +9011,14 @@
         <v>79</v>
       </c>
       <c r="B140">
-        <v>7</v>
-      </c>
-      <c r="C140" t="s">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E140">
         <v>4</v>
@@ -8968,38 +9032,38 @@
         <v>79</v>
       </c>
       <c r="B141">
-        <v>8</v>
-      </c>
-      <c r="C141" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B142">
-        <v>1</v>
-      </c>
-      <c r="C142" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E142">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F142">
         <v>6.5</v>
@@ -9007,17 +9071,17 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B143">
-        <v>2</v>
-      </c>
-      <c r="C143" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E143">
         <v>8</v>
@@ -9028,20 +9092,20 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B144">
-        <v>3</v>
-      </c>
-      <c r="C144" t="s">
-        <v>47</v>
+        <v>6</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144">
         <v>6.5</v>
@@ -9049,17 +9113,17 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B145">
-        <v>4</v>
-      </c>
-      <c r="C145" t="s">
-        <v>48</v>
+        <v>7</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Mediterranean</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E145">
         <v>4</v>
@@ -9070,23 +9134,23 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B146">
-        <v>5</v>
-      </c>
-      <c r="C146" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E146">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F146">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -9094,14 +9158,14 @@
         <v>80</v>
       </c>
       <c r="B147">
-        <v>6</v>
-      </c>
-      <c r="C147" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E147">
         <v>8</v>
@@ -9115,14 +9179,14 @@
         <v>80</v>
       </c>
       <c r="B148">
-        <v>7</v>
-      </c>
-      <c r="C148" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E148">
         <v>8</v>
@@ -9136,14 +9200,14 @@
         <v>80</v>
       </c>
       <c r="B149">
-        <v>8</v>
-      </c>
-      <c r="C149" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E149">
         <v>8</v>
@@ -9157,14 +9221,14 @@
         <v>80</v>
       </c>
       <c r="B150">
-        <v>9</v>
-      </c>
-      <c r="C150" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D150" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Stamp by Shape, Mediterranean</v>
       </c>
       <c r="E150">
         <v>4</v>
@@ -9178,14 +9242,14 @@
         <v>80</v>
       </c>
       <c r="B151">
-        <v>10</v>
-      </c>
-      <c r="C151" t="s">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E151">
         <v>8</v>
@@ -9199,17 +9263,17 @@
         <v>80</v>
       </c>
       <c r="B152">
-        <v>11</v>
-      </c>
-      <c r="C152" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F152">
         <v>6.5</v>
@@ -9220,59 +9284,59 @@
         <v>80</v>
       </c>
       <c r="B153">
-        <v>12</v>
-      </c>
-      <c r="C153" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F153">
         <v>6.5</v>
       </c>
     </row>
-    <row r="154" spans="1:6" s="1" customFormat="1">
-      <c r="A154" s="1" t="s">
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
         <v>80</v>
       </c>
-      <c r="B154" s="1">
-        <v>13</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D154" s="1" t="str">
+      <c r="B154">
+        <v>8</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D154" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E154" s="1">
-        <v>1</v>
-      </c>
-      <c r="F154" s="1">
-        <v>0</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+      </c>
+      <c r="E154">
+        <v>8</v>
+      </c>
+      <c r="F154">
+        <v>6.5</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B155">
-        <v>1</v>
-      </c>
-      <c r="C155" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F155">
         <v>6.5</v>
@@ -9280,20 +9344,20 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156" t="s">
-        <v>53</v>
+        <v>10</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E156">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F156">
         <v>6.5</v>
@@ -9301,17 +9365,17 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B157">
-        <v>3</v>
-      </c>
-      <c r="C157" t="s">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E157">
         <v>4</v>
@@ -9322,44 +9386,44 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B158">
-        <v>4</v>
-      </c>
-      <c r="C158" t="s">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E158">
         <v>4</v>
       </c>
       <c r="F158">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
-        <v>81</v>
-      </c>
-      <c r="B159">
-        <v>5</v>
-      </c>
-      <c r="C159" t="s">
-        <v>56</v>
-      </c>
-      <c r="D159" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" s="1" customFormat="1">
+      <c r="A159" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B159" s="1">
+        <v>13</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D159" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
-      </c>
-      <c r="E159">
-        <v>4</v>
-      </c>
-      <c r="F159">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E159" s="1">
+        <v>1</v>
+      </c>
+      <c r="F159" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -9367,17 +9431,17 @@
         <v>81</v>
       </c>
       <c r="B160">
-        <v>6</v>
-      </c>
-      <c r="C160" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D160" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F160">
         <v>6.5</v>
@@ -9388,20 +9452,20 @@
         <v>81</v>
       </c>
       <c r="B161">
-        <v>7</v>
-      </c>
-      <c r="C161" t="s">
-        <v>58</v>
+        <v>2</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D161" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F161">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -9409,14 +9473,14 @@
         <v>81</v>
       </c>
       <c r="B162">
-        <v>8</v>
-      </c>
-      <c r="C162" t="s">
-        <v>59</v>
+        <v>3</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E162">
         <v>4</v>
@@ -9430,20 +9494,20 @@
         <v>81</v>
       </c>
       <c r="B163">
-        <v>9</v>
-      </c>
-      <c r="C163" t="s">
-        <v>60</v>
+        <v>4</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E163">
         <v>4</v>
       </c>
       <c r="F163">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -9451,14 +9515,14 @@
         <v>81</v>
       </c>
       <c r="B164">
-        <v>10</v>
-      </c>
-      <c r="C164" t="s">
-        <v>61</v>
+        <v>5</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E164">
         <v>4</v>
@@ -9467,64 +9531,64 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="165" spans="1:6" s="1" customFormat="1">
-      <c r="A165" s="1" t="s">
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
         <v>81</v>
       </c>
-      <c r="B165" s="1">
-        <v>11</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D165" s="1" t="str">
+      <c r="B165">
+        <v>6</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D165" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E165" s="1">
-        <v>1</v>
-      </c>
-      <c r="F165" s="1">
-        <v>0</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+      </c>
+      <c r="E165">
+        <v>4</v>
+      </c>
+      <c r="F165">
+        <v>6.5</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B166">
-        <v>1</v>
-      </c>
-      <c r="C166" t="s">
-        <v>52</v>
+        <v>7</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F166">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B167">
-        <v>2</v>
-      </c>
-      <c r="C167" t="s">
-        <v>63</v>
+        <v>8</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D167" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E167">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F167">
         <v>6.5</v>
@@ -9532,17 +9596,17 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B168">
-        <v>3</v>
-      </c>
-      <c r="C168" t="s">
-        <v>57</v>
+        <v>9</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E168">
         <v>4</v>
@@ -9553,170 +9617,170 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B169">
-        <v>4</v>
-      </c>
-      <c r="C169" t="s">
-        <v>59</v>
+        <v>10</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D169" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F169">
         <v>6.5</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
-      <c r="A170" t="s">
+    <row r="170" spans="1:6" s="1" customFormat="1">
+      <c r="A170" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B170" s="1">
+        <v>11</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D170" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E170" s="1">
+        <v>1</v>
+      </c>
+      <c r="F170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
         <v>82</v>
       </c>
-      <c r="B170">
-        <v>5</v>
-      </c>
-      <c r="C170" t="s">
-        <v>64</v>
-      </c>
-      <c r="D170" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
-      </c>
-      <c r="E170">
-        <v>8</v>
-      </c>
-      <c r="F170">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" s="1" customFormat="1">
-      <c r="A171" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B171" s="1">
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D171" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+      </c>
+      <c r="E171">
         <v>6</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D171" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E171" s="1">
-        <v>1</v>
-      </c>
-      <c r="F171" s="1">
-        <v>0</v>
+      <c r="F171">
+        <v>6.5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B172">
-        <v>1</v>
-      </c>
-      <c r="C172" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E172">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B173">
-        <v>2</v>
-      </c>
-      <c r="C173" t="s">
-        <v>66</v>
+        <v>3</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E173">
         <v>4</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B174">
-        <v>3</v>
-      </c>
-      <c r="C174" t="s">
-        <v>67</v>
+        <v>4</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D174" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Pogo-Dot, Nature</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B175">
-        <v>4</v>
-      </c>
-      <c r="C175" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D175" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F175">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" t="s">
-        <v>83</v>
-      </c>
-      <c r="B176">
-        <v>5</v>
-      </c>
-      <c r="C176" t="s">
-        <v>47</v>
-      </c>
-      <c r="D176" t="str">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" s="1" customFormat="1">
+      <c r="A176" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B176" s="1">
+        <v>6</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D176" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
-      </c>
-      <c r="E176">
-        <v>12</v>
-      </c>
-      <c r="F176">
-        <v>5</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E176" s="1">
+        <v>1</v>
+      </c>
+      <c r="F176" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -9724,17 +9788,17 @@
         <v>83</v>
       </c>
       <c r="B177">
-        <v>6</v>
-      </c>
-      <c r="C177" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D177" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E177">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F177">
         <v>5</v>
@@ -9745,17 +9809,17 @@
         <v>83</v>
       </c>
       <c r="B178">
-        <v>7</v>
-      </c>
-      <c r="C178" t="s">
-        <v>43</v>
+        <v>2</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="D178" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C178, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C178), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
       </c>
       <c r="E178">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F178">
         <v>5</v>
@@ -9766,17 +9830,17 @@
         <v>83</v>
       </c>
       <c r="B179">
-        <v>8</v>
-      </c>
-      <c r="C179" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="D179" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C179, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C179), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Pogo-Dot, Nature</v>
       </c>
       <c r="E179">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F179">
         <v>5</v>
@@ -9787,17 +9851,17 @@
         <v>83</v>
       </c>
       <c r="B180">
-        <v>9</v>
-      </c>
-      <c r="C180" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D180" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C180, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C180), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E180">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F180">
         <v>5</v>
@@ -9808,17 +9872,17 @@
         <v>83</v>
       </c>
       <c r="B181">
-        <v>10</v>
-      </c>
-      <c r="C181" t="s">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D181" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C181, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C181), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E181">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F181">
         <v>5</v>
@@ -9829,14 +9893,14 @@
         <v>83</v>
       </c>
       <c r="B182">
-        <v>11</v>
-      </c>
-      <c r="C182" t="s">
-        <v>68</v>
+        <v>6</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D182" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C182, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C182), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E182">
         <v>12</v>
@@ -9850,14 +9914,14 @@
         <v>83</v>
       </c>
       <c r="B183">
-        <v>12</v>
-      </c>
-      <c r="C183" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D183" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C183, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C183), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E183">
         <v>12</v>
@@ -9871,17 +9935,17 @@
         <v>83</v>
       </c>
       <c r="B184">
-        <v>13</v>
-      </c>
-      <c r="C184" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D184" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C184, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C184), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E184">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F184">
         <v>5</v>
@@ -9892,14 +9956,14 @@
         <v>83</v>
       </c>
       <c r="B185">
-        <v>14</v>
-      </c>
-      <c r="C185" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D185" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C185, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C185), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E185">
         <v>8</v>
@@ -9913,14 +9977,14 @@
         <v>83</v>
       </c>
       <c r="B186">
-        <v>15</v>
-      </c>
-      <c r="C186" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D186" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C186, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C186), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E186">
         <v>8</v>
@@ -9934,17 +9998,17 @@
         <v>83</v>
       </c>
       <c r="B187">
-        <v>16</v>
-      </c>
-      <c r="C187" t="s">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="D187" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C187, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C187), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E187">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F187">
         <v>5</v>
@@ -9955,17 +10019,17 @@
         <v>83</v>
       </c>
       <c r="B188">
-        <v>17</v>
-      </c>
-      <c r="C188" t="s">
-        <v>70</v>
+        <v>12</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D188" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C188, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C188), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F188">
         <v>5</v>
@@ -9976,17 +10040,17 @@
         <v>83</v>
       </c>
       <c r="B189">
-        <v>18</v>
-      </c>
-      <c r="C189" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="D189" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C189, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C189), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E189">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F189">
         <v>5</v>
@@ -9997,17 +10061,17 @@
         <v>83</v>
       </c>
       <c r="B190">
-        <v>19</v>
-      </c>
-      <c r="C190" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D190" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C190, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C190), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E190">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -10018,17 +10082,17 @@
         <v>83</v>
       </c>
       <c r="B191">
-        <v>20</v>
-      </c>
-      <c r="C191" t="s">
-        <v>71</v>
+        <v>15</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D191" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C191, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C191), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E191">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F191">
         <v>5</v>
@@ -10039,17 +10103,17 @@
         <v>83</v>
       </c>
       <c r="B192">
-        <v>21</v>
-      </c>
-      <c r="C192" t="s">
-        <v>72</v>
+        <v>16</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D192" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C192, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C192), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E192">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F192">
         <v>5</v>
@@ -10060,14 +10124,14 @@
         <v>83</v>
       </c>
       <c r="B193">
-        <v>22</v>
-      </c>
-      <c r="C193" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D193" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C193, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C193), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E193">
         <v>4</v>
@@ -10076,130 +10140,130 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:6" s="1" customFormat="1">
-      <c r="A194" s="1" t="s">
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
         <v>83</v>
       </c>
-      <c r="B194" s="1">
-        <v>23</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D194" s="1" t="str">
+      <c r="B194">
+        <v>18</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D194" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E194" s="1">
-        <v>1</v>
-      </c>
-      <c r="F194" s="1">
-        <v>0</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E194">
+        <v>4</v>
+      </c>
+      <c r="F194">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B195">
-        <v>1</v>
-      </c>
-      <c r="C195" t="s">
-        <v>42</v>
+        <v>19</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D195" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C195, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C195), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E195">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B196">
-        <v>2</v>
-      </c>
-      <c r="C196" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="D196" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C196, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C196), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E196">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B197">
-        <v>3</v>
-      </c>
-      <c r="C197" t="s">
         <v>21</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="D197" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C197, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C197), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E197">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F197">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B198">
-        <v>4</v>
-      </c>
-      <c r="C198" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D198" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C198, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C198), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E198">
         <v>4</v>
       </c>
       <c r="F198">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" t="s">
-        <v>84</v>
-      </c>
-      <c r="B199">
         <v>5</v>
       </c>
-      <c r="C199" t="s">
-        <v>41</v>
-      </c>
-      <c r="D199" t="str">
+    </row>
+    <row r="199" spans="1:6" s="1" customFormat="1">
+      <c r="A199" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B199" s="1">
+        <v>23</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D199" s="1" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E199">
-        <v>4</v>
-      </c>
-      <c r="F199">
-        <v>6.5</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E199" s="1">
+        <v>1</v>
+      </c>
+      <c r="F199" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -10207,17 +10271,17 @@
         <v>84</v>
       </c>
       <c r="B200">
-        <v>6</v>
-      </c>
-      <c r="C200" t="s">
-        <v>24</v>
+        <v>1</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D200" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E200">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F200">
         <v>6.5</v>
@@ -10228,17 +10292,17 @@
         <v>84</v>
       </c>
       <c r="B201">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D201" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C201, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C201), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E201">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F201">
         <v>6.5</v>
@@ -10249,14 +10313,14 @@
         <v>84</v>
       </c>
       <c r="B202">
-        <v>8</v>
-      </c>
-      <c r="C202" t="s">
-        <v>47</v>
+        <v>3</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D202" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C202, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C202), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E202">
         <v>4</v>
@@ -10270,14 +10334,14 @@
         <v>84</v>
       </c>
       <c r="B203">
-        <v>9</v>
-      </c>
-      <c r="C203" t="s">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D203" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C203, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C203), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E203">
         <v>4</v>
@@ -10291,24 +10355,129 @@
         <v>84</v>
       </c>
       <c r="B204">
-        <v>10</v>
-      </c>
-      <c r="C204" t="s">
-        <v>49</v>
+        <v>5</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="D204" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C204, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C204), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+      </c>
+      <c r="E204">
+        <v>4</v>
+      </c>
+      <c r="F204">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>84</v>
+      </c>
+      <c r="B205">
+        <v>6</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D205" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C205, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C205), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+      </c>
+      <c r="E205">
+        <v>4</v>
+      </c>
+      <c r="F205">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>84</v>
+      </c>
+      <c r="B206">
+        <v>7</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D206" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C206, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C206), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+      </c>
+      <c r="E206">
+        <v>4</v>
+      </c>
+      <c r="F206">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>84</v>
+      </c>
+      <c r="B207">
+        <v>8</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D207" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C207, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C207), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
+      </c>
+      <c r="E207">
+        <v>4</v>
+      </c>
+      <c r="F207">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>84</v>
+      </c>
+      <c r="B208">
+        <v>9</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D208" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C208, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C208), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E208">
+        <v>4</v>
+      </c>
+      <c r="F208">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>84</v>
+      </c>
+      <c r="B209">
+        <v>10</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D209" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C209, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C209), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
-      <c r="E204">
-        <v>4</v>
-      </c>
-      <c r="F204">
+      <c r="E209">
+        <v>4</v>
+      </c>
+      <c r="F209">
         <v>6.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F204" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:F209" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -10318,6 +10487,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -10558,15 +10736,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10579,13 +10748,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/3) Planning BOM/Archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC4D6B3-20AB-4BFB-A44B-52B0EBDDD4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6CE46B8-8A67-4B67-8940-BC48F4305077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,13 +362,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,6 +391,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls driveId="b!HTnOnJwPMEWf4Qc1OT0tJzUXtA3JA_dFmeLcrifvRQA3dGqF56dSRIF8RuQ19ZxM" itemId="01FHB6EQ4WFPYOBAHH6NC22UE5IJXHENMZ">
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -416,9 +417,6 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
-          <cell r="C1" t="str">
-            <v>Report Format2</v>
-          </cell>
           <cell r="F1" t="str">
             <v>SBOM SKU</v>
           </cell>
@@ -1603,7 +1601,6 @@
           </cell>
         </row>
         <row r="149">
-          <cell r="F149"/>
           <cell r="G149" t="str">
             <v>Lifelines Bath &amp; Shower Spa Bundle</v>
           </cell>
@@ -1773,7 +1770,7 @@
             <v>LL-14-3305</v>
           </cell>
           <cell r="G170" t="str">
-            <v>Flameless Candle Diffuser -  Frosted Green - WINTER 2x ClickWicks</v>
+            <v>DIFFUSER, LED, Frosted Green - WINTER 2x ClickWicks</v>
           </cell>
         </row>
         <row r="171">
@@ -1813,7 +1810,7 @@
             <v>11-1603</v>
           </cell>
           <cell r="G175" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Cream)</v>
+            <v>DIFFUSER, LED,Frosted Glass (Cream)</v>
           </cell>
         </row>
         <row r="176">
@@ -1821,7 +1818,7 @@
             <v>11-1612</v>
           </cell>
           <cell r="G176" t="str">
-            <v>Flameless Candle Diffuser -  Frosted Glass (Charcoal)</v>
+            <v>DIFFUSER, LED, Frosted Glass (Charcoal)</v>
           </cell>
         </row>
         <row r="177">
@@ -1829,7 +1826,7 @@
             <v>11-1616</v>
           </cell>
           <cell r="G177" t="str">
-            <v>Flameless Candle Diffuser -  Marble</v>
+            <v>DIFFUSER, LED, Marble</v>
           </cell>
         </row>
         <row r="178">
@@ -1837,7 +1834,7 @@
             <v>11-1617</v>
           </cell>
           <cell r="G178" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream)</v>
+            <v>DIFFUSER, LED,Bubble (Cream)</v>
           </cell>
         </row>
         <row r="179">
@@ -1845,7 +1842,7 @@
             <v>11-1619</v>
           </cell>
           <cell r="G179" t="str">
-            <v>Flameless Candle Diffuser- Bubble (Green)</v>
+            <v>DIFFUSER, LED, Bubble (Green)</v>
           </cell>
         </row>
         <row r="180">
@@ -1853,7 +1850,7 @@
             <v>111618</v>
           </cell>
           <cell r="G180" t="str">
-            <v>Flameless Candle Diffuser - Winter Edition (Frosted Green)</v>
+            <v>DIFFUSER, LED, Winter Edition (Frosted Green)</v>
           </cell>
         </row>
         <row r="181">
@@ -1885,7 +1882,7 @@
             <v>LL-14-3338</v>
           </cell>
           <cell r="G184" t="str">
-            <v>Flameless Candle Diffuser- QVC Deal - Green [Fir + Fresia]</v>
+            <v>DIFFUSER, LED, QVC Deal - Green [Fir + Fresia]</v>
           </cell>
         </row>
         <row r="185">
@@ -1893,7 +1890,7 @@
             <v>LL-14-3339</v>
           </cell>
           <cell r="G185" t="str">
-            <v>Flameless Candle Diffuser- QVC Deal - Blue [Mahogany + Mango]</v>
+            <v>DIFFUSER, LED, QVC Deal - Blue [Mahogany + Mango]</v>
           </cell>
         </row>
         <row r="186">
@@ -1901,7 +1898,7 @@
             <v>LL-14-3340</v>
           </cell>
           <cell r="G186" t="str">
-            <v>Flameless Candle Diffuser- QVC Deal - Pink [Berry + Rose]</v>
+            <v>DIFFUSER, LED, QVC Deal - Pink [Berry + Rose]</v>
           </cell>
         </row>
         <row r="187">
@@ -1909,3111 +1906,3111 @@
             <v>LL-14-3431</v>
           </cell>
           <cell r="G187" t="str">
-            <v>Flameless Candle Diffuser- QVC Deal - White [Vanilla + Hibiscus]</v>
+            <v>DIFFUSER, LED, QVC Deal - White [Vanilla + Hibiscus]</v>
           </cell>
         </row>
         <row r="188">
           <cell r="F188" t="str">
-            <v>LL-14-3085</v>
+            <v>LL-14-3452</v>
           </cell>
           <cell r="G188" t="str">
-            <v>Flameless Candle Diffuser- Bubble (Blue)</v>
+            <v>DIFFUSER, LED, Ribbed Mauve [In Bloom + Coco Hibiscus]</v>
           </cell>
         </row>
         <row r="189">
           <cell r="F189" t="str">
-            <v>LL-14-3432</v>
+            <v>LL-14-3453</v>
           </cell>
           <cell r="G189" t="str">
-            <v>Flameless Candle Diffuser- Iridescent - Vanilla Cashmere</v>
+            <v>DIFFUSER, LED, Ribbed Amber [Citrus + Herbal]</v>
           </cell>
         </row>
         <row r="190">
           <cell r="F190" t="str">
+            <v>LL-14-3454</v>
+          </cell>
+          <cell r="G190" t="str">
+            <v>DIFFUSER, LED, Frosted Oatmeal [WITW + Desert Winds]</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="F191" t="str">
+            <v>LL-14-3455</v>
+          </cell>
+          <cell r="G191" t="str">
+            <v>DIFFUSER, LED, Frosted Blue [Coco Hibiscus + CMA]</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="F192" t="str">
+            <v>LL-14-3085</v>
+          </cell>
+          <cell r="G192" t="str">
+            <v>DIFFUSER, LED, Bubble (Blue)</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="F193" t="str">
+            <v>LL-14-3432</v>
+          </cell>
+          <cell r="G193" t="str">
+            <v>DIFFUSER, LED, Iridescent - Vanilla Cashmere</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="F194" t="str">
             <v>LL-14-3086</v>
           </cell>
-          <cell r="G190" t="str">
+          <cell r="G194" t="str">
             <v>Blue Bubble  Planter Diffuser - Desert Canyon Air</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="F191">
-            <v>110454</v>
-          </cell>
-          <cell r="G191" t="str">
-            <v>ClickWick™ Replacement Bloom, Citrus (Universal)</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="F192">
-            <v>110455</v>
-          </cell>
-          <cell r="G192" t="str">
-            <v>ClickWick™ Replacement Woodsy, Mountain (Universal)</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="F193">
-            <v>989521</v>
-          </cell>
-          <cell r="G193" t="str">
-            <v>Lifelines Scented Lava Pen, Highlighter &amp; Pencil (11-2508 &amp; 11-2509 &amp; 11-2507)</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="F194">
-            <v>989522</v>
-          </cell>
-          <cell r="G194" t="str">
-            <v>Lifelines Meadow Journal, Highlighter, Pen Diffuser &amp; Pencil  (16-0109 &amp; 11-2509 &amp; 11-2504 &amp; 11-2507)</v>
           </cell>
         </row>
         <row r="195">
           <cell r="F195">
-            <v>989523</v>
+            <v>110454</v>
           </cell>
           <cell r="G195" t="str">
-            <v xml:space="preserve">Lifelines Ocean Journal, Highlighter, Pen Diffuser &amp; Pencil (16-0103 &amp; 11-2509 &amp; 11-2504 &amp; 11-2507) </v>
+            <v>ClickWick™ Replacement Bloom, Citrus (Universal)</v>
           </cell>
         </row>
         <row r="196">
           <cell r="F196">
-            <v>110456</v>
+            <v>110455</v>
           </cell>
           <cell r="G196" t="str">
-            <v>ClickWick™ Replacement Woodsy, Herbal (Universal) - 2pk</v>
+            <v>ClickWick™ Replacement Woodsy, Mountain (Universal)</v>
           </cell>
         </row>
         <row r="197">
           <cell r="F197">
+            <v>989521</v>
+          </cell>
+          <cell r="G197" t="str">
+            <v>Lifelines Scented Lava Pen, Highlighter &amp; Pencil (11-2508 &amp; 11-2509 &amp; 11-2507)</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="F198">
+            <v>989522</v>
+          </cell>
+          <cell r="G198" t="str">
+            <v>Lifelines Meadow Journal, Highlighter, Pen Diffuser &amp; Pencil  (16-0109 &amp; 11-2509 &amp; 11-2504 &amp; 11-2507)</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="F199">
+            <v>989523</v>
+          </cell>
+          <cell r="G199" t="str">
+            <v xml:space="preserve">Lifelines Ocean Journal, Highlighter, Pen Diffuser &amp; Pencil (16-0103 &amp; 11-2509 &amp; 11-2504 &amp; 11-2507) </v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="F200">
+            <v>110456</v>
+          </cell>
+          <cell r="G200" t="str">
+            <v>ClickWick™ Replacement Woodsy, Herbal (Universal) - 2pk</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="F201">
             <v>110511</v>
           </cell>
-          <cell r="G197" t="str">
+          <cell r="G201" t="str">
             <v>Herbal Garden - 2pk oils (7.5ML)</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="F198" t="str">
-            <v>98-9221</v>
-          </cell>
-          <cell r="G198" t="str">
-            <v>Waves + Oil BOX  Set (5 oils)</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="F199" t="str">
-            <v>LL-12-3021</v>
-          </cell>
-          <cell r="G199" t="str">
-            <v>Scented Lava Pen Set- 10-pack</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="F200" t="str">
-            <v>LL-12-3102</v>
-          </cell>
-          <cell r="G200" t="str">
-            <v>Scented Lava Pen Set- 5-pack (Brights)</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="F201" t="str">
-            <v>11-2508</v>
-          </cell>
-          <cell r="G201" t="str">
-            <v>Scented Lava Pen Set- 5-pack</v>
           </cell>
         </row>
         <row r="202">
           <cell r="F202" t="str">
-            <v>LL-11-2508-V2</v>
+            <v>98-9221</v>
           </cell>
           <cell r="G202" t="str">
-            <v>Scented Lava Pen Set- 5-pack</v>
+            <v>Waves + Oil BOX  Set (5 oils)</v>
           </cell>
         </row>
         <row r="203">
           <cell r="F203" t="str">
-            <v>11-2508-V2</v>
+            <v>LL-12-3021</v>
           </cell>
           <cell r="G203" t="str">
-            <v>Scented Lava Pen Set- 5-pack</v>
+            <v>Scented Lava Pen Set- 10-pack</v>
           </cell>
         </row>
         <row r="204">
           <cell r="F204" t="str">
-            <v>LL-11-2508-CP12</v>
+            <v>LL-12-3102</v>
           </cell>
           <cell r="G204" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+            <v>Scented Lava Pen Set- 5-pack (Brights)</v>
           </cell>
         </row>
         <row r="205">
           <cell r="F205" t="str">
-            <v>LL-12-3104</v>
+            <v>11-2508</v>
           </cell>
           <cell r="G205" t="str">
-            <v>Scented Lava Pen Set- 5-pack (Winter)</v>
+            <v>Scented Lava Pen Set- 5-pack</v>
           </cell>
         </row>
         <row r="206">
           <cell r="F206" t="str">
-            <v>11-2509</v>
+            <v>LL-11-2508-V2</v>
           </cell>
           <cell r="G206" t="str">
-            <v>Scented Stacking Highlighters - 2-pack</v>
+            <v>Scented Lava Pen Set- 5-pack</v>
           </cell>
         </row>
         <row r="207">
           <cell r="F207" t="str">
-            <v>11-2509-CP12</v>
+            <v>11-2508-V2</v>
           </cell>
           <cell r="G207" t="str">
-            <v>Scented Stacking Highlighters - 2-pack</v>
+            <v>Scented Lava Pen Set- 5-pack</v>
           </cell>
         </row>
         <row r="208">
           <cell r="F208" t="str">
-            <v>LL-12-3365</v>
+            <v>LL-11-2508-CP12</v>
           </cell>
           <cell r="G208" t="str">
-            <v>DbL Marker Extension Tray - 8</v>
+            <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
           </cell>
         </row>
         <row r="209">
           <cell r="F209" t="str">
-            <v>LL-12-3379</v>
+            <v>LL-12-3104</v>
           </cell>
           <cell r="G209" t="str">
-            <v>DbL Marker Extension Tray - 4</v>
+            <v>Scented Lava Pen Set- 5-pack (Winter)</v>
           </cell>
         </row>
         <row r="210">
           <cell r="F210" t="str">
-            <v>LL-12-3018</v>
+            <v>11-2509</v>
           </cell>
           <cell r="G210" t="str">
-            <v>Scented Marker 10 Colors</v>
+            <v>Scented Stacking Highlighters - 2-pack</v>
           </cell>
         </row>
         <row r="211">
           <cell r="F211" t="str">
-            <v>LL-12-3019</v>
+            <v>11-2509-CP12</v>
           </cell>
           <cell r="G211" t="str">
-            <v>Scented Marker 20 Colors</v>
+            <v>Scented Stacking Highlighters - 2-pack</v>
           </cell>
         </row>
         <row r="212">
           <cell r="F212" t="str">
-            <v>LL-12-3082</v>
+            <v>LL-12-3365</v>
           </cell>
           <cell r="G212" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Purple / Orange) </v>
+            <v>DbL Marker Extension Tray - 8</v>
           </cell>
         </row>
         <row r="213">
           <cell r="F213" t="str">
-            <v>LL-12-3109</v>
+            <v>LL-12-3379</v>
           </cell>
           <cell r="G213" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+            <v>DbL Marker Extension Tray - 4</v>
           </cell>
         </row>
         <row r="214">
           <cell r="F214" t="str">
-            <v>LL-12-3110</v>
+            <v>LL-12-3018</v>
           </cell>
           <cell r="G214" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Lime Green / Violet) </v>
+            <v>Scented Marker 10 Colors</v>
           </cell>
         </row>
         <row r="215">
           <cell r="F215" t="str">
-            <v>11-2520</v>
+            <v>LL-12-3019</v>
           </cell>
           <cell r="G215" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Black / Red)</v>
+            <v>Scented Marker 20 Colors</v>
           </cell>
         </row>
         <row r="216">
           <cell r="F216" t="str">
-            <v>11-2521</v>
+            <v>LL-12-3082</v>
           </cell>
           <cell r="G216" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Purple / Orange) </v>
           </cell>
         </row>
         <row r="217">
           <cell r="F217" t="str">
-            <v>LL-12-3066</v>
+            <v>LL-12-3109</v>
           </cell>
           <cell r="G217" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
           </cell>
         </row>
         <row r="218">
           <cell r="F218" t="str">
-            <v>LL-12-3155</v>
+            <v>LL-12-3110</v>
           </cell>
           <cell r="G218" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Brown / Violet) </v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Lime Green / Violet) </v>
           </cell>
         </row>
         <row r="219">
           <cell r="F219" t="str">
-            <v>LL-12-3156</v>
+            <v>11-2520</v>
           </cell>
           <cell r="G219" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (TBD / TBD) </v>
+            <v>Scented Lava Pen Set - 2-pack (Black / Red)</v>
           </cell>
         </row>
         <row r="220">
           <cell r="F220" t="str">
-            <v>LL-12-3066-CP12</v>
+            <v>11-2521</v>
           </cell>
           <cell r="G220" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="221">
           <cell r="F221" t="str">
-            <v>LL-12-3082-CP12</v>
+            <v>LL-12-3066</v>
           </cell>
           <cell r="G221" t="str">
-            <v>Lava Pen 2 Pack - Purple/Orange</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
           </cell>
         </row>
         <row r="222">
           <cell r="F222" t="str">
-            <v>LL-11-2520-CP12</v>
+            <v>LL-12-3155</v>
           </cell>
           <cell r="G222" t="str">
-            <v>Lava Pen 2 Pack - Black/Red</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Brown / Violet) </v>
           </cell>
         </row>
         <row r="223">
           <cell r="F223" t="str">
-            <v>LL-12-3105</v>
+            <v>LL-12-3156</v>
           </cell>
           <cell r="G223" t="str">
-            <v>Lava Pen 2 PK - Holiday 2</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (TBD / TBD) </v>
           </cell>
         </row>
         <row r="224">
           <cell r="F224" t="str">
-            <v>LL-12-3106</v>
+            <v>LL-12-3066-CP12</v>
           </cell>
           <cell r="G224" t="str">
-            <v>Lava Pen 2 PK - Holiday 3</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
           </cell>
         </row>
         <row r="225">
           <cell r="F225" t="str">
-            <v>LL-12-3107</v>
+            <v>LL-12-3082-CP12</v>
           </cell>
           <cell r="G225" t="str">
-            <v>Lava Pen 2 PK - NPI #1</v>
+            <v>Lava Pen 2 Pack - Purple/Orange</v>
           </cell>
         </row>
         <row r="226">
           <cell r="F226" t="str">
-            <v>LL-12-3108</v>
+            <v>LL-11-2520-CP12</v>
           </cell>
           <cell r="G226" t="str">
-            <v>Lava Pen 2 PK - NPI #2</v>
+            <v>Lava Pen 2 Pack - Black/Red</v>
           </cell>
         </row>
         <row r="227">
           <cell r="F227" t="str">
-            <v>LL-12-3288</v>
+            <v>LL-12-3105</v>
           </cell>
           <cell r="G227" t="str">
-            <v>Pen Discovery Set - 6Pck</v>
+            <v>Lava Pen 2 PK - Holiday 2</v>
           </cell>
         </row>
         <row r="228">
           <cell r="F228" t="str">
-            <v>LL-12-3242</v>
+            <v>LL-12-3106</v>
           </cell>
           <cell r="G228" t="str">
-            <v>Visual Symphony Pen, Glitter 10Pck</v>
+            <v>Lava Pen 2 PK - Holiday 3</v>
           </cell>
         </row>
         <row r="229">
           <cell r="F229" t="str">
-            <v>LL-12-3213</v>
+            <v>LL-12-3107</v>
           </cell>
           <cell r="G229" t="str">
-            <v>Visual Symphony Pen, Glitter 5Pck</v>
+            <v>Lava Pen 2 PK - NPI #1</v>
           </cell>
         </row>
         <row r="230">
           <cell r="F230" t="str">
-            <v>LL-12-3233</v>
+            <v>LL-12-3108</v>
           </cell>
           <cell r="G230" t="str">
-            <v>Visual Symphony Pen, Glitter 2Pck (Teal / Purple)</v>
+            <v>Lava Pen 2 PK - NPI #2</v>
           </cell>
         </row>
         <row r="231">
           <cell r="F231" t="str">
-            <v>LL-12-3214</v>
+            <v>LL-12-3288</v>
           </cell>
           <cell r="G231" t="str">
-            <v>Visual Symphony Pen, Swirl 5Pck</v>
+            <v>Pen Discovery Set - 6Pck</v>
           </cell>
         </row>
         <row r="232">
           <cell r="F232" t="str">
+            <v>LL-12-3242</v>
+          </cell>
+          <cell r="G232" t="str">
+            <v>Visual Symphony Pen, Glitter 10Pck</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="F233" t="str">
+            <v>LL-12-3213</v>
+          </cell>
+          <cell r="G233" t="str">
+            <v>Visual Symphony Pen, Glitter 5Pck</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="F234" t="str">
+            <v>LL-12-3233</v>
+          </cell>
+          <cell r="G234" t="str">
+            <v>Visual Symphony Pen, Glitter 2Pck (Teal / Purple)</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="F235" t="str">
+            <v>LL-12-3214</v>
+          </cell>
+          <cell r="G235" t="str">
+            <v>Visual Symphony Pen, Swirl 5Pck</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="F236" t="str">
             <v>LL-12-3238</v>
           </cell>
-          <cell r="G232" t="str">
+          <cell r="G236" t="str">
             <v>Visual Symphony Pen, Swirl 2Pck (X / X)</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="F233">
-            <v>989518</v>
-          </cell>
-          <cell r="G233" t="str">
-            <v>Lifelines Frosted Cream Candle with Clickwick (11-1603 &amp; 110455 Woodsy)</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="F234">
-            <v>989519</v>
-          </cell>
-          <cell r="G234" t="str">
-            <v>Lifelines Frosted Charcoal Candle with Clickwick (11-1612 &amp; 110454 Citrus/Bloom)</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="F235">
-            <v>989520</v>
-          </cell>
-          <cell r="G235" t="str">
-            <v>Lifelines Grass Planter with Clickwick (11-1608 &amp; 110454 citrus)</v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="F236">
-            <v>119008</v>
-          </cell>
-          <cell r="G236" t="str">
-            <v>Essential Oil Blend Discovery Set - 5-pack (Winter)</v>
           </cell>
         </row>
         <row r="237">
           <cell r="F237">
-            <v>119010</v>
+            <v>989518</v>
           </cell>
           <cell r="G237" t="str">
-            <v>Sensory Immersion™ Gift Set (Winter)</v>
+            <v>Lifelines Frosted Cream Candle with Clickwick (11-1603 &amp; 110455 Woodsy)</v>
           </cell>
         </row>
         <row r="238">
           <cell r="F238">
-            <v>112513</v>
+            <v>989519</v>
           </cell>
           <cell r="G238" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Winter)</v>
+            <v>Lifelines Frosted Charcoal Candle with Clickwick (11-1612 &amp; 110454 Citrus/Bloom)</v>
           </cell>
         </row>
         <row r="239">
           <cell r="F239">
+            <v>989520</v>
+          </cell>
+          <cell r="G239" t="str">
+            <v>Lifelines Grass Planter with Clickwick (11-1608 &amp; 110454 citrus)</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="F240">
+            <v>119008</v>
+          </cell>
+          <cell r="G240" t="str">
+            <v>Essential Oil Blend Discovery Set - 5-pack (Winter)</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="F241">
+            <v>119010</v>
+          </cell>
+          <cell r="G241" t="str">
+            <v>Sensory Immersion™ Gift Set (Winter)</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="F242">
+            <v>112513</v>
+          </cell>
+          <cell r="G242" t="str">
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Winter)</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="F243">
             <v>112519</v>
           </cell>
-          <cell r="G239" t="str">
+          <cell r="G243" t="str">
             <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Scents of the Seasons)</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="F240" t="str">
-            <v>11-0450</v>
-          </cell>
-          <cell r="G240" t="str">
-            <v xml:space="preserve">Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set </v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="F241" t="str">
-            <v>11-0450-CP24</v>
-          </cell>
-          <cell r="G241" t="str">
-            <v xml:space="preserve">Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set </v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="F242" t="str">
-            <v>11-0450-A</v>
-          </cell>
-          <cell r="G242" t="str">
-            <v>Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set  - Non Retail Packaging</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="F243" t="str">
-            <v>LL-11-3077</v>
-          </cell>
-          <cell r="G243" t="str">
-            <v>Clickwick 7.5ml Single - In Bloom</v>
           </cell>
         </row>
         <row r="244">
           <cell r="F244" t="str">
-            <v>LL-11-3078</v>
+            <v>11-0450</v>
           </cell>
           <cell r="G244" t="str">
-            <v>Clickwick 7.5ml Single - Woods</v>
+            <v xml:space="preserve">Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set </v>
           </cell>
         </row>
         <row r="245">
           <cell r="F245" t="str">
-            <v>LL-11-3079</v>
+            <v>11-0450-CP24</v>
           </cell>
           <cell r="G245" t="str">
-            <v>Clickwick 7.5ml Single - Herbal</v>
+            <v xml:space="preserve">Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set </v>
           </cell>
         </row>
         <row r="246">
           <cell r="F246" t="str">
-            <v>LL-11-3080</v>
+            <v>11-0450-A</v>
           </cell>
           <cell r="G246" t="str">
-            <v>Clickwick 7.5ml Single - Citrus</v>
+            <v>Essential Oil Blends ClickWick™ Refills - 4-pack Discovery Set  - Non Retail Packaging</v>
           </cell>
         </row>
         <row r="247">
           <cell r="F247" t="str">
-            <v>LL-11-3081</v>
+            <v>LL-11-3077</v>
           </cell>
           <cell r="G247" t="str">
-            <v>Clickwick 7.5ml Single - CMA</v>
+            <v>Clickwick 7.5ml Single - In Bloom</v>
           </cell>
         </row>
         <row r="248">
           <cell r="F248" t="str">
-            <v>LL-11-3072</v>
+            <v>LL-11-3078</v>
           </cell>
           <cell r="G248" t="str">
-            <v>Clickwick 7.5ml Single - Vanilla Bean</v>
+            <v>Clickwick 7.5ml Single - Woods</v>
           </cell>
         </row>
         <row r="249">
           <cell r="F249" t="str">
-            <v>LL-11-3093</v>
+            <v>LL-11-3079</v>
           </cell>
           <cell r="G249" t="str">
-            <v>Clickwick 7.5ml Single - Salted Coconut</v>
+            <v>Clickwick 7.5ml Single - Herbal</v>
           </cell>
         </row>
         <row r="250">
           <cell r="F250" t="str">
-            <v>LL-11-3094</v>
+            <v>LL-11-3080</v>
           </cell>
           <cell r="G250" t="str">
-            <v>Clickwick 7.5ml Single - Desert Canyon Air [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Citrus</v>
           </cell>
         </row>
         <row r="251">
           <cell r="F251" t="str">
-            <v>LL-11-3095</v>
+            <v>LL-11-3081</v>
           </cell>
           <cell r="G251" t="str">
-            <v>Clickwick 7.5ml Single - Peach Velvet [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - CMA</v>
           </cell>
         </row>
         <row r="252">
           <cell r="F252" t="str">
-            <v>LL-11-3096</v>
+            <v>LL-11-3072</v>
           </cell>
           <cell r="G252" t="str">
-            <v>Clickwick 7.5ml Single - Vanilla Tangerine</v>
+            <v>Clickwick 7.5ml Single - Vanilla Bean</v>
           </cell>
         </row>
         <row r="253">
           <cell r="F253" t="str">
-            <v>LL-11-3097</v>
+            <v>LL-11-3093</v>
           </cell>
           <cell r="G253" t="str">
-            <v>Clickwick 7.5ml Single - Crisp Green Apple</v>
+            <v>Clickwick 7.5ml Single - Salted Coconut</v>
           </cell>
         </row>
         <row r="254">
           <cell r="F254" t="str">
-            <v>LL-11-3098</v>
+            <v>LL-11-3094</v>
           </cell>
           <cell r="G254" t="str">
-            <v>Clickwick 7.5ml Single - Rose &amp; Pink Pepper [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Desert Canyon Air [Bubble Bag]</v>
           </cell>
         </row>
         <row r="255">
           <cell r="F255" t="str">
-            <v>LL-11-3099</v>
+            <v>LL-11-3095</v>
           </cell>
           <cell r="G255" t="str">
-            <v>Clickwick 7.5ml Single - Spiced Orange</v>
+            <v>Clickwick 7.5ml Single - Peach Velvet [Bubble Bag]</v>
           </cell>
         </row>
         <row r="256">
           <cell r="F256" t="str">
-            <v>LL-11-3100</v>
+            <v>LL-11-3096</v>
           </cell>
           <cell r="G256" t="str">
-            <v>Clickwick 7.5ml Single - Freesia Fields [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Vanilla Tangerine</v>
           </cell>
         </row>
         <row r="257">
           <cell r="F257" t="str">
-            <v>LL-11-3101</v>
+            <v>LL-11-3097</v>
           </cell>
           <cell r="G257" t="str">
-            <v>Clickwick 7.5ml Single - Aspen Breeze</v>
+            <v>Clickwick 7.5ml Single - Crisp Green Apple</v>
           </cell>
         </row>
         <row r="258">
           <cell r="F258" t="str">
-            <v>LL-11-3345</v>
+            <v>LL-11-3098</v>
           </cell>
           <cell r="G258" t="str">
-            <v>Clickwick 7.5ml Single - Warm Mahogony [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Rose &amp; Pink Pepper [Bubble Bag]</v>
           </cell>
         </row>
         <row r="259">
           <cell r="F259" t="str">
-            <v>LL-11-3346</v>
+            <v>LL-11-3099</v>
           </cell>
           <cell r="G259" t="str">
-            <v>Clickwick 7.5ml Single - Frosted Fir [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Spiced Orange</v>
           </cell>
         </row>
         <row r="260">
           <cell r="F260" t="str">
-            <v>LL-11-3347</v>
+            <v>LL-11-3100</v>
           </cell>
           <cell r="G260" t="str">
-            <v>Clickwick 7.5ml Single - Midnight Berry [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Freesia Fields [Bubble Bag]</v>
           </cell>
         </row>
         <row r="261">
           <cell r="F261" t="str">
-            <v>LL-11-3348</v>
+            <v>LL-11-3101</v>
           </cell>
           <cell r="G261" t="str">
-            <v>Clickwick 7.5ml Single - Coconut Hibiscus [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Aspen Breeze</v>
           </cell>
         </row>
         <row r="262">
           <cell r="F262" t="str">
-            <v>LL-11-3349</v>
+            <v>LL-11-3345</v>
           </cell>
           <cell r="G262" t="str">
-            <v>Clickwick 7.5ml Single - Earthy Mango [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Warm Mahogony [Bubble Bag]</v>
           </cell>
         </row>
         <row r="263">
           <cell r="F263" t="str">
-            <v>LL-11-3291</v>
+            <v>LL-11-3346</v>
           </cell>
           <cell r="G263" t="str">
-            <v>Clickwick 7.5ml Single - Vanilla Cashmere [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Frosted Fir [Bubble Bag]</v>
           </cell>
         </row>
         <row r="264">
           <cell r="F264" t="str">
-            <v>LL-11-3440</v>
+            <v>LL-11-3347</v>
           </cell>
           <cell r="G264" t="str">
-            <v>Clickwick 7.5ml Single - Autumn's Glow [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Midnight Berry [Bubble Bag]</v>
           </cell>
         </row>
         <row r="265">
           <cell r="F265" t="str">
-            <v>LL-11-3441</v>
+            <v>LL-11-3348</v>
           </cell>
           <cell r="G265" t="str">
-            <v>Clickwick 7.5ml Single - Vanilla Plum Bliss [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Coconut Hibiscus [Bubble Bag]</v>
           </cell>
         </row>
         <row r="266">
           <cell r="F266" t="str">
-            <v>LL-11-3442</v>
+            <v>LL-11-3349</v>
           </cell>
           <cell r="G266" t="str">
-            <v>Clickwick 7.5ml Single - Pumpkin Spiced Latte [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Earthy Mango [Bubble Bag]</v>
           </cell>
         </row>
         <row r="267">
           <cell r="F267" t="str">
-            <v>LL-11-3443</v>
+            <v>LL-11-3291</v>
           </cell>
           <cell r="G267" t="str">
-            <v>Clickwick 7.5ml Single - Fresh Picked Apples [Bubble Bag]</v>
+            <v>Clickwick 7.5ml Single - Vanilla Cashmere [Bubble Bag]</v>
           </cell>
         </row>
         <row r="268">
           <cell r="F268" t="str">
-            <v>LL-11-3198</v>
+            <v>LL-11-3440</v>
           </cell>
           <cell r="G268" t="str">
-            <v>ClickWick: Walk-in-the-Woods 3PK</v>
+            <v>Clickwick 7.5ml Single - Autumn's Glow [Bubble Bag]</v>
           </cell>
         </row>
         <row r="269">
           <cell r="F269" t="str">
-            <v>LL-11-3199</v>
+            <v>LL-11-3441</v>
           </cell>
           <cell r="G269" t="str">
-            <v>ClickWick: Herbal 3PK</v>
+            <v>Clickwick 7.5ml Single - Vanilla Plum Bliss [Bubble Bag]</v>
           </cell>
         </row>
         <row r="270">
           <cell r="F270" t="str">
-            <v>LL-11-3194</v>
+            <v>LL-11-3442</v>
           </cell>
           <cell r="G270" t="str">
-            <v>ClickWick: In Bloom 3PK</v>
+            <v>Clickwick 7.5ml Single - Pumpkin Spiced Latte [Bubble Bag]</v>
           </cell>
         </row>
         <row r="271">
           <cell r="F271" t="str">
-            <v>LL-11-3195</v>
+            <v>LL-11-3443</v>
           </cell>
           <cell r="G271" t="str">
-            <v>ClickWick: Citrus Grove 3PK</v>
+            <v>Clickwick 7.5ml Single - Fresh Picked Apples [Bubble Bag]</v>
           </cell>
         </row>
         <row r="272">
           <cell r="F272" t="str">
-            <v>LL-11-3234</v>
+            <v>LL-11-3198</v>
           </cell>
           <cell r="G272" t="str">
-            <v>ClickWick: Very Vanilla: 3PK</v>
+            <v>ClickWick: Walk-in-the-Woods 3PK</v>
           </cell>
         </row>
         <row r="273">
           <cell r="F273" t="str">
-            <v>LL-11-3235</v>
+            <v>LL-11-3199</v>
           </cell>
           <cell r="G273" t="str">
-            <v>ClickWick: Salted Coconut: 3PK</v>
+            <v>ClickWick: Herbal 3PK</v>
           </cell>
         </row>
         <row r="274">
           <cell r="F274" t="str">
-            <v>LL-11-3236</v>
+            <v>LL-11-3194</v>
           </cell>
           <cell r="G274" t="str">
-            <v>ClickWick: Peach Velvet: 3PK</v>
+            <v>ClickWick: In Bloom 3PK</v>
           </cell>
         </row>
         <row r="275">
           <cell r="F275" t="str">
-            <v>LL-11-3237</v>
+            <v>LL-11-3195</v>
           </cell>
           <cell r="G275" t="str">
-            <v>ClickWick: Spiced Rose: 3PK</v>
+            <v>ClickWick: Citrus Grove 3PK</v>
           </cell>
         </row>
         <row r="276">
           <cell r="F276" t="str">
-            <v>LL-11-3240</v>
+            <v>LL-11-3234</v>
           </cell>
           <cell r="G276" t="str">
-            <v>ClickWick: Frosted Fir: 3PK</v>
+            <v>ClickWick: Very Vanilla: 3PK</v>
           </cell>
         </row>
         <row r="277">
           <cell r="F277" t="str">
-            <v>LL-11-3241</v>
+            <v>LL-11-3235</v>
           </cell>
           <cell r="G277" t="str">
-            <v>ClickWick: Warm Mahogany: 3PK</v>
+            <v>ClickWick: Salted Coconut: 3PK</v>
           </cell>
         </row>
         <row r="278">
           <cell r="F278" t="str">
-            <v>LL-11-3306</v>
+            <v>LL-11-3236</v>
           </cell>
           <cell r="G278" t="str">
-            <v>ClickWick: Vanilla Cashmere: 3PK</v>
+            <v>ClickWick: Peach Velvet: 3PK</v>
           </cell>
         </row>
         <row r="279">
           <cell r="F279" t="str">
-            <v>LL-11-3006</v>
+            <v>LL-11-3237</v>
           </cell>
           <cell r="G279" t="str">
-            <v>Clickwick 2 Pack - Desert Canyon Air &amp; Salted Coconut (Target)</v>
+            <v>ClickWick: Spiced Rose: 3PK</v>
           </cell>
         </row>
         <row r="280">
           <cell r="F280" t="str">
-            <v>LL-11-3007</v>
+            <v>LL-11-3240</v>
           </cell>
           <cell r="G280" t="str">
-            <v>Clickwick 2 Pack - Vanilla Tangerine &amp; Peach Linen (Target)</v>
+            <v>ClickWick: Frosted Fir: 3PK</v>
           </cell>
         </row>
         <row r="281">
           <cell r="F281" t="str">
-            <v>LL-11-3008</v>
+            <v>LL-11-3241</v>
           </cell>
           <cell r="G281" t="str">
-            <v>Clickwick 4 PK - Sun-Kissed Escape ClickWick Collection</v>
+            <v>ClickWick: Warm Mahogany: 3PK</v>
           </cell>
         </row>
         <row r="282">
           <cell r="F282" t="str">
-            <v>LL-11-3064</v>
+            <v>LL-11-3306</v>
           </cell>
           <cell r="G282" t="str">
-            <v>Clickwick 4 PK - Lush Earth ClickWick Collection</v>
+            <v>ClickWick: Vanilla Cashmere: 3PK</v>
           </cell>
         </row>
         <row r="283">
           <cell r="F283" t="str">
-            <v>LL-11-3292</v>
+            <v>LL-11-3006</v>
           </cell>
           <cell r="G283" t="str">
-            <v>Fall Clickwick 4PK</v>
+            <v>Clickwick 2 Pack - Desert Canyon Air &amp; Salted Coconut (Target)</v>
           </cell>
         </row>
         <row r="284">
           <cell r="F284" t="str">
+            <v>LL-11-3007</v>
+          </cell>
+          <cell r="G284" t="str">
+            <v>Clickwick 2 Pack - Vanilla Tangerine &amp; Peach Linen (Target)</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="F285" t="str">
+            <v>LL-11-3008</v>
+          </cell>
+          <cell r="G285" t="str">
+            <v>Clickwick 4 PK - Sun-Kissed Escape ClickWick Collection</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="F286" t="str">
+            <v>LL-11-3064</v>
+          </cell>
+          <cell r="G286" t="str">
+            <v>Clickwick 4 PK - Lush Earth ClickWick Collection</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="F287" t="str">
+            <v>LL-11-3292</v>
+          </cell>
+          <cell r="G287" t="str">
+            <v>Fall Clickwick 4PK</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="F288" t="str">
             <v>LL-11-3103</v>
           </cell>
-          <cell r="G284" t="str">
+          <cell r="G288" t="str">
             <v>Winter Clickwick 4PK</v>
-          </cell>
-        </row>
-        <row r="285">
-          <cell r="F285">
-            <v>993014</v>
-          </cell>
-          <cell r="G285" t="str">
-            <v>BNC FlowArt Assorted Shipper Display (Spring 2025)</v>
-          </cell>
-        </row>
-        <row r="286">
-          <cell r="F286">
-            <v>165001</v>
-          </cell>
-          <cell r="G286" t="str">
-            <v>FlowArt: Dot-Pop, Natural Flow</v>
-          </cell>
-        </row>
-        <row r="287">
-          <cell r="F287">
-            <v>165005</v>
-          </cell>
-          <cell r="G287" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals</v>
-          </cell>
-        </row>
-        <row r="288">
-          <cell r="F288">
-            <v>165006</v>
-          </cell>
-          <cell r="G288" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
           </cell>
         </row>
         <row r="289">
           <cell r="F289">
-            <v>165007</v>
+            <v>993014</v>
           </cell>
           <cell r="G289" t="str">
-            <v>FlowArt: Pogo-Dot, Nature</v>
+            <v>BNC FlowArt Assorted Shipper Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="290">
           <cell r="F290">
-            <v>165008</v>
+            <v>165001</v>
           </cell>
           <cell r="G290" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes</v>
+            <v>FlowArt: Dot-Pop, Natural Flow</v>
           </cell>
         </row>
         <row r="291">
           <cell r="F291">
-            <v>165009</v>
+            <v>165005</v>
           </cell>
           <cell r="G291" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals</v>
           </cell>
         </row>
         <row r="292">
           <cell r="F292">
-            <v>165012</v>
+            <v>165006</v>
           </cell>
           <cell r="G292" t="str">
-            <v>FlowArt: Color-to-Reveal, Animals</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
           </cell>
         </row>
         <row r="293">
           <cell r="F293">
+            <v>165007</v>
+          </cell>
+          <cell r="G293" t="str">
+            <v>FlowArt: Pogo-Dot, Nature</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="F294">
+            <v>165008</v>
+          </cell>
+          <cell r="G294" t="str">
+            <v>FlowArt: Dot-By-Letter, Landscapes</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="F295">
+            <v>165009</v>
+          </cell>
+          <cell r="G295" t="str">
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="F296">
+            <v>165012</v>
+          </cell>
+          <cell r="G296" t="str">
+            <v>FlowArt: Color-to-Reveal, Animals</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="F297">
             <v>165014</v>
           </cell>
-          <cell r="G293" t="str">
+          <cell r="G297" t="str">
             <v>FlowArt: Stamp by Shape, Mediterranean</v>
-          </cell>
-        </row>
-        <row r="294">
-          <cell r="F294" t="str">
-            <v>LL-16-3429</v>
-          </cell>
-          <cell r="G294" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - D03</v>
-          </cell>
-        </row>
-        <row r="295">
-          <cell r="F295" t="str">
-            <v>LL-16-3430</v>
-          </cell>
-          <cell r="G295" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - D03</v>
-          </cell>
-        </row>
-        <row r="296">
-          <cell r="F296" t="str">
-            <v>LL-16-3385</v>
-          </cell>
-          <cell r="G296" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
-          </cell>
-        </row>
-        <row r="297">
-          <cell r="F297" t="str">
-            <v>LL-16-3384</v>
-          </cell>
-          <cell r="G297" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink] - D03</v>
           </cell>
         </row>
         <row r="298">
           <cell r="F298" t="str">
-            <v>LL-16-3433</v>
+            <v>LL-16-3429</v>
           </cell>
           <cell r="G298" t="str">
-            <v>FlowArt: Dot-By-Letter, Birds Song in Bloom [Metallic]</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - D03</v>
           </cell>
         </row>
         <row r="299">
           <cell r="F299" t="str">
-            <v>LL-16-3148</v>
+            <v>LL-16-3430</v>
           </cell>
           <cell r="G299" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - D03</v>
           </cell>
         </row>
         <row r="300">
           <cell r="F300" t="str">
-            <v>LL-16-3153</v>
+            <v>LL-16-3385</v>
           </cell>
           <cell r="G300" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Americana - D03</v>
           </cell>
         </row>
         <row r="301">
           <cell r="F301" t="str">
-            <v>LL-16-3148-V3</v>
+            <v>LL-16-3384</v>
           </cell>
           <cell r="G301" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink] - D03</v>
           </cell>
         </row>
         <row r="302">
           <cell r="F302" t="str">
-            <v>LL-16-3153-V3</v>
+            <v>LL-16-3433</v>
           </cell>
           <cell r="G302" t="str">
-            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Birds Song in Bloom [Metallic]</v>
           </cell>
         </row>
         <row r="303">
           <cell r="F303" t="str">
-            <v>LL-16-3149</v>
+            <v>LL-16-3148</v>
           </cell>
           <cell r="G303" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="304">
           <cell r="F304" t="str">
-            <v>LL-16-3150</v>
+            <v>LL-16-3153</v>
           </cell>
           <cell r="G304" t="str">
-            <v>FlowArt: Stamp by Shape, Secret Garden</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="305">
           <cell r="F305" t="str">
-            <v>LL-16-3151</v>
+            <v>LL-16-3148-V3</v>
           </cell>
           <cell r="G305" t="str">
-            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+            <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
           </cell>
         </row>
         <row r="306">
           <cell r="F306" t="str">
-            <v>LL-16-3152</v>
+            <v>LL-16-3153-V3</v>
           </cell>
           <cell r="G306" t="str">
-            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
+            <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
           </cell>
         </row>
         <row r="307">
           <cell r="F307" t="str">
-            <v>LL-16-3157</v>
+            <v>LL-16-3149</v>
           </cell>
           <cell r="G307" t="str">
-            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
           </cell>
         </row>
         <row r="308">
           <cell r="F308" t="str">
-            <v>LL-16-3158</v>
+            <v>LL-16-3150</v>
           </cell>
           <cell r="G308" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+            <v>FlowArt: Stamp by Shape, Secret Garden</v>
           </cell>
         </row>
         <row r="309">
           <cell r="F309" t="str">
-            <v>LL-16-3323</v>
+            <v>LL-16-3151</v>
           </cell>
           <cell r="G309" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
+            <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
           </cell>
         </row>
         <row r="310">
           <cell r="F310" t="str">
-            <v>LL-16-3159</v>
+            <v>LL-16-3152</v>
           </cell>
           <cell r="G310" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
+            <v>FlowArt: Pogo-Dot, Groovy Vibes</v>
           </cell>
         </row>
         <row r="311">
           <cell r="F311" t="str">
-            <v>LL-16-3160</v>
+            <v>LL-16-3157</v>
           </cell>
           <cell r="G311" t="str">
-            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
+            <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
           </cell>
         </row>
         <row r="312">
           <cell r="F312" t="str">
-            <v>LL-16-3290</v>
+            <v>LL-16-3158</v>
           </cell>
           <cell r="G312" t="str">
-            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
           </cell>
         </row>
         <row r="313">
           <cell r="F313" t="str">
-            <v>LL-16-3247</v>
+            <v>LL-16-3323</v>
           </cell>
           <cell r="G313" t="str">
-            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+            <v>FlowArt: Dot-By-Letter, Sweater Weather [2025 Version]</v>
           </cell>
         </row>
         <row r="314">
           <cell r="F314" t="str">
-            <v>LL-16-3248</v>
+            <v>LL-16-3159</v>
           </cell>
           <cell r="G314" t="str">
-            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+            <v>FlowArt: Illuminate &amp; Create, Frightful Fun</v>
           </cell>
         </row>
         <row r="315">
           <cell r="F315" t="str">
-            <v>LL-16-3162</v>
+            <v>LL-16-3160</v>
           </cell>
           <cell r="G315" t="str">
-            <v>FlowArt: Dot-By-Letter, Snowed In</v>
+            <v>FlowArt: Pogo-Dot, Enchanted Forest</v>
           </cell>
         </row>
         <row r="316">
           <cell r="F316" t="str">
-            <v>LL-16-3244</v>
+            <v>LL-16-3290</v>
           </cell>
           <cell r="G316" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+            <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
           </cell>
         </row>
         <row r="317">
           <cell r="F317" t="str">
-            <v>LL-16-3245</v>
+            <v>LL-16-3247</v>
           </cell>
           <cell r="G317" t="str">
-            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+            <v>FlowArt: Trace-By-Line, Fall Harvest</v>
           </cell>
         </row>
         <row r="318">
           <cell r="F318" t="str">
-            <v>LL-16-3246</v>
+            <v>LL-16-3248</v>
           </cell>
           <cell r="G318" t="str">
-            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
           </cell>
         </row>
         <row r="319">
           <cell r="F319" t="str">
-            <v>LL-16-3366</v>
+            <v>LL-16-3162</v>
           </cell>
           <cell r="G319" t="str">
-            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
+            <v>FlowArt: Dot-By-Letter, Snowed In</v>
           </cell>
         </row>
         <row r="320">
           <cell r="F320" t="str">
-            <v>LL-16-3163</v>
+            <v>LL-16-3244</v>
           </cell>
           <cell r="G320" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
+            <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
           </cell>
         </row>
         <row r="321">
           <cell r="F321" t="str">
-            <v>LL-16-3367</v>
+            <v>LL-16-3245</v>
           </cell>
           <cell r="G321" t="str">
-            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+            <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
           </cell>
         </row>
         <row r="322">
           <cell r="F322" t="str">
-            <v>LL-16-3368</v>
+            <v>LL-16-3246</v>
           </cell>
           <cell r="G322" t="str">
-            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
+            <v>FlowArt: Color-to-Reveal, Home for the Holidays [Scented]</v>
           </cell>
         </row>
         <row r="323">
           <cell r="F323" t="str">
-            <v>LL-16-3369</v>
+            <v>LL-16-3366</v>
           </cell>
           <cell r="G323" t="str">
-            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
+            <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
           </cell>
         </row>
         <row r="324">
           <cell r="F324" t="str">
-            <v>LL-16-3371</v>
+            <v>LL-16-3163</v>
           </cell>
           <cell r="G324" t="str">
-            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
+            <v>FlowArt: Illuminate &amp; Create, Winter Cheer (Typography)</v>
           </cell>
         </row>
         <row r="325">
           <cell r="F325" t="str">
-            <v>LL-16-3372</v>
+            <v>LL-16-3367</v>
           </cell>
           <cell r="G325" t="str">
-            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
+            <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
           </cell>
         </row>
         <row r="326">
           <cell r="F326" t="str">
-            <v>LL-16-3373</v>
+            <v>LL-16-3368</v>
           </cell>
           <cell r="G326" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
           </cell>
         </row>
         <row r="327">
           <cell r="F327" t="str">
-            <v>LL-16-3374</v>
+            <v>LL-16-3369</v>
           </cell>
           <cell r="G327" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Holiday Helpers</v>
           </cell>
         </row>
         <row r="328">
           <cell r="F328" t="str">
-            <v>LL-16-3352</v>
+            <v>LL-16-3371</v>
           </cell>
           <cell r="G328" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Lovestruck - TGT</v>
           </cell>
         </row>
         <row r="329">
           <cell r="F329" t="str">
-            <v>LL-16-3390</v>
+            <v>LL-16-3372</v>
           </cell>
           <cell r="G329" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Everday Inspo - TGT</v>
           </cell>
         </row>
         <row r="330">
           <cell r="F330" t="str">
-            <v>LL-16-3375</v>
+            <v>LL-16-3373</v>
           </cell>
           <cell r="G330" t="str">
-            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sweetened With Love - TGT</v>
           </cell>
         </row>
         <row r="331">
           <cell r="F331" t="str">
-            <v>LL-16-3391</v>
+            <v>LL-16-3374</v>
           </cell>
           <cell r="G331" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden - TGT</v>
           </cell>
         </row>
         <row r="332">
           <cell r="F332" t="str">
-            <v>LL-16-3376</v>
+            <v>LL-16-3352</v>
           </cell>
           <cell r="G332" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance - TGT</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine - TGT</v>
           </cell>
         </row>
         <row r="333">
           <cell r="F333" t="str">
-            <v>LL-16-3389</v>
+            <v>LL-16-3375</v>
           </cell>
           <cell r="G333" t="str">
-            <v>FlowArt: Trace-By-Line, Book Romance</v>
+            <v>FlowArt: CtR, Fragrant Blooms - TGT</v>
           </cell>
         </row>
         <row r="334">
           <cell r="F334" t="str">
-            <v>LL-16-3395</v>
+            <v>LL-16-3390</v>
           </cell>
           <cell r="G334" t="str">
-            <v>FlowArt: Trace-By-Line, Self Care Club</v>
+            <v>FlowArt: Trace-By-Line, Tied with a Bow - TGT</v>
           </cell>
         </row>
         <row r="335">
           <cell r="F335" t="str">
-            <v>LL-16-3392</v>
+            <v>LL-16-3391</v>
           </cell>
           <cell r="G335" t="str">
-            <v>FlowArt: Dot-By-Letter, Sweets</v>
+            <v>FlowArt: Trace-By-Line, A Little Me Time - TGT</v>
           </cell>
         </row>
         <row r="336">
           <cell r="F336" t="str">
-            <v>LL-16-3393</v>
+            <v>LL-16-3376</v>
           </cell>
           <cell r="G336" t="str">
-            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
+            <v>FlowArt: Trace-By-Line, Once Upon a Bookshelf - TGT</v>
           </cell>
         </row>
         <row r="337">
           <cell r="F337" t="str">
-            <v>LL-16-3394</v>
+            <v>LL-16-3389</v>
           </cell>
           <cell r="G337" t="str">
-            <v>FlowArt: Trace-By-Line, Coquette</v>
+            <v>FlowArt: Trace-By-Line, Once Upon a Bookshelf</v>
           </cell>
         </row>
         <row r="338">
           <cell r="F338" t="str">
-            <v>LL-16-3200</v>
+            <v>LL-16-3395</v>
           </cell>
           <cell r="G338" t="str">
-            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+            <v>FlowArt: Trace-By-Line, A Little Me Time</v>
           </cell>
         </row>
         <row r="339">
           <cell r="F339" t="str">
-            <v>LL-16-3201</v>
+            <v>LL-16-3392</v>
           </cell>
           <cell r="G339" t="str">
-            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
+            <v>FlowArt: Dot-By-Letter, Sweetened With Love</v>
           </cell>
         </row>
         <row r="340">
           <cell r="F340" t="str">
-            <v>LL-16-3204</v>
+            <v>LL-16-3393</v>
           </cell>
           <cell r="G340" t="str">
-            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
+            <v>FlowArt: Dot-By-Letter, Sparkle &amp; Shine</v>
           </cell>
         </row>
         <row r="341">
           <cell r="F341" t="str">
-            <v>LL-16-3205</v>
+            <v>LL-16-3394</v>
           </cell>
           <cell r="G341" t="str">
-            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+            <v>FlowArt: Trace-By-Line, Tied with a Bow</v>
           </cell>
         </row>
         <row r="342">
           <cell r="F342" t="str">
-            <v>LL-16-3206</v>
+            <v>LL-16-3200</v>
           </cell>
           <cell r="G342" t="str">
-            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+            <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
           </cell>
         </row>
         <row r="343">
           <cell r="F343" t="str">
-            <v>LL-16-3207</v>
+            <v>LL-16-3201</v>
           </cell>
           <cell r="G343" t="str">
-            <v>FlowArt: Trace Within, Peaceful Pause</v>
+            <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
           </cell>
         </row>
         <row r="344">
           <cell r="F344" t="str">
-            <v>LL-16-3249</v>
+            <v>LL-16-3204</v>
           </cell>
           <cell r="G344" t="str">
-            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+            <v>FlowArt: Trace-To-Doodle, Wild Style</v>
           </cell>
         </row>
         <row r="345">
           <cell r="F345" t="str">
-            <v>LL-16-3222</v>
+            <v>LL-16-3205</v>
           </cell>
           <cell r="G345" t="str">
-            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+            <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
           </cell>
         </row>
         <row r="346">
           <cell r="F346" t="str">
-            <v>LL-16-3223</v>
+            <v>LL-16-3206</v>
           </cell>
           <cell r="G346" t="str">
-            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+            <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
           </cell>
         </row>
         <row r="347">
           <cell r="F347" t="str">
-            <v>LL-16-3411</v>
+            <v>LL-16-3207</v>
           </cell>
           <cell r="G347" t="str">
-            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
+            <v>FlowArt: Trace Within, Peaceful Pause</v>
           </cell>
         </row>
         <row r="348">
           <cell r="F348" t="str">
-            <v>LL-16-3418</v>
+            <v>LL-16-3249</v>
           </cell>
           <cell r="G348" t="str">
-            <v>FlowArt: Trace-By-Line, Pets</v>
+            <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
           </cell>
         </row>
         <row r="349">
           <cell r="F349" t="str">
-            <v>LL-16-3420</v>
+            <v>LL-16-3222</v>
           </cell>
           <cell r="G349" t="str">
-            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing</v>
+            <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
           </cell>
         </row>
         <row r="350">
           <cell r="F350" t="str">
-            <v>LL-16-3202</v>
+            <v>LL-16-3223</v>
           </cell>
           <cell r="G350" t="str">
-            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+            <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
           </cell>
         </row>
         <row r="351">
           <cell r="F351" t="str">
-            <v>LL-16-3203</v>
+            <v>LL-16-3411</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+            <v>FlowArt: Trace-By-Line, Coastal Charm [WF Exclusive]</v>
           </cell>
         </row>
         <row r="352">
           <cell r="F352" t="str">
-            <v>LL-16-3407</v>
+            <v>LL-16-3418</v>
           </cell>
           <cell r="G352" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
+            <v>FlowArt: Trace-By-Line, Life With Pets</v>
           </cell>
         </row>
         <row r="353">
           <cell r="F353" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3420</v>
           </cell>
           <cell r="G353" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing, Beautiful Horizons</v>
           </cell>
         </row>
         <row r="354">
           <cell r="F354" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3448</v>
           </cell>
           <cell r="G354" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Trace-By-Line, Metallic #1</v>
           </cell>
         </row>
         <row r="355">
           <cell r="F355" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3449</v>
           </cell>
           <cell r="G355" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Trace-By-Line, Once Upon a Bookshelf [EVGR]</v>
           </cell>
         </row>
         <row r="356">
           <cell r="F356" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3450</v>
           </cell>
           <cell r="G356" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Trace-By-Line, A Little Me Time [EVGR]</v>
           </cell>
         </row>
         <row r="357">
           <cell r="F357" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3451</v>
           </cell>
           <cell r="G357" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Trace-By-Line, Tied with a Bow [EVGR]</v>
           </cell>
         </row>
         <row r="358">
           <cell r="F358" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3202</v>
           </cell>
           <cell r="G358" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
           </cell>
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3203</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
+            <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
           </cell>
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3447</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Premium #3 - The Great Outdoors</v>
+            <v>FlowArt: Color-to-Reveal, Glitter #1</v>
           </cell>
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Florals</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
           </cell>
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Cottage</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
         </row>
         <row r="364">
           <cell r="F364" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G364" t="str">
-            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Premium #4 - Large Dot - Floral Splendor</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
+            <v>FlowArt: Premium #5 - Large Dot - Simple Pleasures</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Dot-By-Letter, Corner Café</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Stitch-By-X, Homegrown Garden</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Stich-By-X, Cheeky Sayings</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-16-3419</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Stitch-By-X, [Nature TBD]</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: Home Sweet Home</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-16-3422</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-16-3423</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Stitch-To-Embroider: #1</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-16-3424</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Stitch-To-Quilt: #1</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Dot-By-Letter, Corner Café</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Stitch-By-X, Homegrown Garden</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Stich-By-X, Cheeky Sayings</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-16-3419</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Stitch-By-X, [Nature TBD]</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt: Stitch-By-Needlepoint: Home Sweet Home</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-16-3422</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-16-3423</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Stitch-To-Embroider: #1</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-16-3424</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Stitch-To-Quilt: #1</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="411">
           <cell r="F411" t="str">
-            <v>LL-20-3408</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowArt: Mini Single - Berry Bliss</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="412">
           <cell r="F412" t="str">
-            <v>LL-20-3409</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowArt: Mini Single - Hummingbird Haven</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="413">
           <cell r="F413" t="str">
-            <v>LL-20-3410</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowArt: Mini Single - Wildflower Woods</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="414">
           <cell r="F414" t="str">
-            <v>LL-20-3412</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowArt: Mini Single - Coastal Calm</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="415">
           <cell r="F415" t="str">
-            <v>LL-20-3413</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowArt: Mini Single - Sweet Summer</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-20-3414</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt: Mini Single - Under the Sea</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-20-3415</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-20-3434</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Botanical Bouquet]</v>
+            <v>FlowArt: Mini Single - Coastal Calm</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-20-3435</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Birds &amp; Branches]</v>
+            <v>FlowArt: Mini Single - Sweet Summer</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-20-3436</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Spring Landscape]</v>
+            <v>FlowArt: Mini Single - Under the Sea</v>
           </cell>
         </row>
         <row r="421">
           <cell r="F421" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="422">
           <cell r="F422" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3434</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt Mini Stitch-by-X: [Botanical Bouquet]</v>
           </cell>
         </row>
         <row r="423">
           <cell r="F423" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3435</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt Mini Stitch-by-X: [Birds &amp; Branches]</v>
           </cell>
         </row>
         <row r="424">
           <cell r="F424" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-20-3436</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt Mini Stitch-by-X: [Spring Landscape]</v>
           </cell>
         </row>
         <row r="425">
           <cell r="F425" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-98-3444</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt Mini - Pocket Positivity - 3Pck</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-98-3445</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini - Café Comforts - 3Pck</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-98-3446</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini - Enchanted Magic - 3Pck</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="434">
           <cell r="F434" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
-            <v>LL-30-3406</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G437" t="str">
-            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438" t="str">
-            <v>LL-30-3425</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G438" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Cozy Rooms</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="439">
           <cell r="F439" t="str">
-            <v>LL-30-3426</v>
+            <v>LL-30-3359</v>
           </cell>
           <cell r="G439" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Travel</v>
+            <v>FlowArt Mini EXPRESS, #12</v>
           </cell>
         </row>
         <row r="440">
           <cell r="F440" t="str">
-            <v>LL-30-3427</v>
+            <v>LL-30-3360</v>
           </cell>
           <cell r="G440" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Fashion</v>
+            <v>FlowArt Mini EXPRESS, #13</v>
           </cell>
         </row>
         <row r="441">
           <cell r="F441" t="str">
-            <v>LL-30-3428</v>
+            <v>LL-30-3361</v>
           </cell>
           <cell r="G441" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Fruity Tutti</v>
+            <v>FlowArt Mini EXPRESS, #14</v>
           </cell>
         </row>
         <row r="442">
-          <cell r="F442">
-            <v>167001</v>
+          <cell r="F442" t="str">
+            <v>LL-30-3362</v>
           </cell>
           <cell r="G442" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
+            <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
         <row r="443">
-          <cell r="F443">
-            <v>167002</v>
+          <cell r="F443" t="str">
+            <v>LL-30-3405</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowCrafts: Collage Art</v>
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
           </cell>
         </row>
         <row r="444">
-          <cell r="F444">
-            <v>167004</v>
+          <cell r="F444" t="str">
+            <v>LL-30-3406</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
           </cell>
         </row>
         <row r="445">
-          <cell r="F445">
-            <v>167005</v>
+          <cell r="F445" t="str">
+            <v>LL-30-3425</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Dream Spaces</v>
           </cell>
         </row>
         <row r="446">
-          <cell r="F446">
-            <v>167006</v>
+          <cell r="F446" t="str">
+            <v>LL-30-3426</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowCrafts: Decorative Tile Lamp</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Vacay Mode</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-98-3188</v>
+            <v>LL-30-3427</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - The Style Edit</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-98-3189</v>
+            <v>LL-30-3428</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Berry Cute</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-98-3190</v>
+            <v>LL-30-3456</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Stitch-by-X [Botanicals]</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-98-3191</v>
+            <v>LL-30-3457</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Stitch-by-X [Cottage Core]</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-98-3025</v>
+            <v>LL-30-3458</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowArt Mini EXPRESS, Stitch-by-X [Cozy Living]</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-98-3026</v>
+            <v>LL-30-3459</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowArt Mini EXPRESS, Stitch-by-X [Animals]</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-98-3027</v>
+            <v>LL-30-3460</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowArt Mini EXPRESS, Spring Rain</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-98-3028</v>
+            <v>LL-30-3461</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowArt Mini EXPRESS, Blossom Market</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-98-3091</v>
+            <v>LL-30-3462</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowArt Mini EXPRESS, Baby Animals</v>
           </cell>
         </row>
         <row r="456">
-          <cell r="F456" t="str">
-            <v>LL-98-3168</v>
+          <cell r="F456">
+            <v>167001</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowCrafts: Paper Flower Bouquet</v>
           </cell>
         </row>
         <row r="457">
-          <cell r="F457" t="str">
-            <v>LL-98-3169</v>
+          <cell r="F457">
+            <v>167002</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowCrafts: Collage Art</v>
           </cell>
         </row>
         <row r="458">
-          <cell r="F458" t="str">
-            <v>LL-98-3170</v>
+          <cell r="F458">
+            <v>167004</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
           </cell>
         </row>
         <row r="459">
-          <cell r="F459" t="str">
-            <v>LL-98-3307</v>
+          <cell r="F459">
+            <v>167005</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="460">
-          <cell r="F460" t="str">
-            <v>LL-98-3321</v>
+          <cell r="F460">
+            <v>167006</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowCrafts: Decorative Tile Lamp</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G461" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G462" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G463" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G464" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="465">
           <cell r="F465" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G465" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="466">
           <cell r="F466" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G466" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G467" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G468" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="469">
           <cell r="F469" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G469" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="470">
           <cell r="F470" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G470" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="471">
           <cell r="F471" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G471" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="472">
           <cell r="F472" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G472" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="473">
           <cell r="F473" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G473" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G474" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="475">
           <cell r="F475" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G475" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="476">
           <cell r="F476" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G476" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G477" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G478" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G479" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G480" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G481" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G482" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G483" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G484" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G485" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G486" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G487" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G488" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G489" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G490" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G491" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-25-3416</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G492" t="str">
-            <v>Scented Squishy Plush - Nightime</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="493">
           <cell r="F493" t="str">
-            <v>LL-25-3421</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G493" t="str">
-            <v>Scented Squishy Plush - Woodland</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="494">
           <cell r="F494" t="str">
-            <v>LL-25-3417</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G494" t="str">
-            <v>Scented Squishy Non-Plush - #2</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G495" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G496" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
           </cell>
         </row>
         <row r="497">
-          <cell r="F497">
-            <v>989514</v>
+          <cell r="F497" t="str">
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G497" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="498">
-          <cell r="F498">
-            <v>989525</v>
+          <cell r="F498" t="str">
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G498" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G499" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G500" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>11-2506-CP12</v>
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G501" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-99-3076</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G502" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-99-3077</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G503" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-99-3089</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G504" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-99-3090</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G505" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G506" t="str">
-            <v>Flameless Candle Diffuser -  Marble (HERBAL OIL)</v>
+            <v>Scented Squishy Plush - Nightime</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-12-3161</v>
+            <v>LL-25-3421</v>
           </cell>
           <cell r="G507" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Scented Squishy Plush - Woodland</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-12-3172</v>
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G508" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>Scented Squishy Non-Plush - #2</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-12-3196</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G509" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-12-3197</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G510" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="511">
-          <cell r="F511" t="str">
-            <v>LL-12-3215</v>
+          <cell r="F511">
+            <v>989514</v>
           </cell>
           <cell r="G511" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="512">
-          <cell r="F512" t="str">
-            <v>LL-12-3216</v>
+          <cell r="F512">
+            <v>989525</v>
           </cell>
           <cell r="G512" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>LL-12-3330</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>LL-12-3331</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G514" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>LL-12-3332</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G515" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-98-3221</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G516" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G517" t="str">
-            <v>Lifelines Analog Bag 2026</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G518" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G519" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G520" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>DIFFUSER, LED, Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G521" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G522" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G524" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G525" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="526">
           <cell r="F526" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G526" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="527">
           <cell r="F527" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G528" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G529" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G530" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G531" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Lifelines Digital Detox Kit - 2026</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G532" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G533" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G534" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G535" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G536" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G537" t="str">
-            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G538" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G539" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbread Shop - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G540" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G541" t="str">
-            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="542">
           <cell r="F542" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G542" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="543">
           <cell r="F543" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G543" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G544" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G545" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G546" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G547" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G548" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G549" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G550" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G551" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="552">
           <cell r="F552" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G552" t="str">
-            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="553">
           <cell r="F553" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G553" t="str">
-            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Delight - WMT</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G554" t="str">
-            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G555" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G556" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G557" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G558" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G559" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G560" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G563" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G564" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>Scented Squishy 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G565" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G566" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G567" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G568" t="str">
-            <v>Candle - Iridescent - WALMART PKG</v>
+            <v>Scented Squishy 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G569" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="570">
           <cell r="F570" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G570" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="571">
           <cell r="F571" t="str">
-            <v>99-8302</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G571" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Scented Squishy 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>99-8501</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G572" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>99-9002</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G573" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Candle - Ribbed Pink - Very Vanilla - WALMART PKG</v>
           </cell>
         </row>
         <row r="574">
-          <cell r="F574">
-            <v>999003</v>
+          <cell r="F574" t="str">
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G574" t="str">
-            <v>BNC Floor Display</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="575">
-          <cell r="F575">
-            <v>999004</v>
+          <cell r="F575" t="str">
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G575" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="576">
@@ -5329,599 +5326,788 @@
           </cell>
         </row>
         <row r="615">
-          <cell r="F615" t="str">
-            <v>LL-00-0027</v>
-          </cell>
           <cell r="G615" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>LL-99-0027</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G616" t="str">
-            <v>FlowArt Holiday Grocery Display - Empty</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G617" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>LL-99-0028</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G618" t="str">
-            <v>FlowArt Mini Grocery Display - Empty</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G619" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>LL-99-0029</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G620" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>LL-00-0037</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G621" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="622">
           <cell r="F622" t="str">
-            <v>LL-99-0037</v>
+            <v>LL-00-0040</v>
           </cell>
           <cell r="G622" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
+            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
           </cell>
         </row>
         <row r="623">
           <cell r="F623" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-99-0040</v>
           </cell>
           <cell r="G623" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #1</v>
           </cell>
         </row>
         <row r="624">
           <cell r="F624" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-00-0041</v>
           </cell>
           <cell r="G624" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>FlowArt MINI EXPRESS - WMT - 72 - #2</v>
           </cell>
         </row>
         <row r="625">
           <cell r="F625" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-99-0041</v>
           </cell>
           <cell r="G625" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #2</v>
           </cell>
         </row>
         <row r="626">
           <cell r="F626" t="str">
-            <v>LL-99-0039</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G626" t="str">
-            <v>FlowArt MINI Spring Display - Empty</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
           </cell>
         </row>
         <row r="627">
           <cell r="F627" t="str">
-            <v>LL-00-0039</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G627" t="str">
-            <v>FlowArt MINI Spring Display - 36</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
           </cell>
         </row>
         <row r="628">
           <cell r="F628" t="str">
-            <v>LL-99-0038</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G628" t="str">
-            <v>FlowArt Spring Display - Empty</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>LL-00-0038</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G629" t="str">
-            <v>FlowArt Spring Display - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>LL-99-0033</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G630" t="str">
-            <v>FlowArt Valentine Display - Empty</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-99-0039</v>
           </cell>
           <cell r="G631" t="str">
-            <v>FlowArt Valentine Display - 24</v>
+            <v>FlowArt MINI Spring Display - Empty</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-00-0039</v>
           </cell>
           <cell r="G632" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt MINI Spring Display - 36</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-99-0038</v>
           </cell>
           <cell r="G633" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Spring Display - Empty</v>
           </cell>
         </row>
         <row r="634">
           <cell r="F634" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0038</v>
           </cell>
           <cell r="G634" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Spring Display - 24</v>
           </cell>
         </row>
         <row r="635">
           <cell r="F635" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-99-0033</v>
           </cell>
           <cell r="G635" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Valentine Display - Empty</v>
           </cell>
         </row>
         <row r="636">
           <cell r="F636" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G636" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Valentine Display - 24</v>
           </cell>
         </row>
         <row r="637">
           <cell r="F637" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G637" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="638">
           <cell r="F638" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G638" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="639">
           <cell r="F639" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G639" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="640">
           <cell r="F640" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G640" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G641" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G642" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G643" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G644" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G645" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G646" t="str">
-            <v>Lifelines Tote</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>99-9101</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G647" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>99-9500</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G648" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>99-9505</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G649" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>DS01-1001</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G650" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
-            <v>DS01-1002</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G651" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="652">
           <cell r="F652" t="str">
-            <v>DS01-1003</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G652" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="653">
           <cell r="F653" t="str">
-            <v>DS01-1004</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G653" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="654">
           <cell r="F654" t="str">
-            <v>DS01-1005</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G654" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="655">
           <cell r="F655" t="str">
-            <v>DS01-1006</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G655" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="656">
           <cell r="F656" t="str">
-            <v>DS01-1007</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G656" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="657">
           <cell r="F657" t="str">
-            <v>DS01-1008</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G657" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="658">
           <cell r="F658" t="str">
-            <v>LL-16-3143</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G658" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="659">
           <cell r="F659" t="str">
-            <v>LL-12-3131</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G659" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="660">
           <cell r="F660" t="str">
-            <v>LL-16-3142</v>
+            <v>DS01-1006</v>
           </cell>
           <cell r="G660" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="661">
           <cell r="F661" t="str">
-            <v>LL-12-3135</v>
+            <v>DS01-1007</v>
           </cell>
           <cell r="G661" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="662">
           <cell r="F662" t="str">
-            <v>LL-12-3134</v>
+            <v>DS01-1008</v>
           </cell>
           <cell r="G662" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="663">
           <cell r="F663" t="str">
-            <v>LL-14-3145</v>
+            <v>99-8302</v>
           </cell>
           <cell r="G663" t="str">
-            <v>Flameless Candle Diffuser - Bubble (Cream) - WALMART PKG</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="664">
           <cell r="F664" t="str">
-            <v>LL-14-3147</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G664" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="665">
           <cell r="F665" t="str">
-            <v>LL-98-3171</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G665" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="666">
-          <cell r="F666" t="str">
-            <v>LL-11-3087</v>
+          <cell r="F666">
+            <v>999003</v>
           </cell>
           <cell r="G666" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="667">
-          <cell r="F667" t="str">
-            <v>LL-11-3088</v>
+          <cell r="F667">
+            <v>999004</v>
           </cell>
           <cell r="G667" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="668">
           <cell r="F668" t="str">
-            <v>LL-11-3089</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G668" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="669">
-          <cell r="F669">
-            <v>165002</v>
+          <cell r="F669" t="str">
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G669" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="670">
-          <cell r="F670">
-            <v>165003</v>
+          <cell r="F670" t="str">
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G670" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="671">
-          <cell r="F671">
-            <v>165004</v>
+          <cell r="F671" t="str">
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G671" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="672">
-          <cell r="F672">
-            <v>165010</v>
+          <cell r="F672" t="str">
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G672" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="673">
-          <cell r="F673">
-            <v>165011</v>
+          <cell r="F673" t="str">
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G673" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="674">
-          <cell r="F674">
-            <v>165013</v>
+          <cell r="F674" t="str">
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G674" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="675">
-          <cell r="F675">
-            <v>167003</v>
+          <cell r="F675" t="str">
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G675" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="676">
           <cell r="F676" t="str">
-            <v>11-1613</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G676" t="str">
-            <v>Flameless Candle Diffuser - Frosted Glass (Amber)</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="677">
           <cell r="F677" t="str">
-            <v>11-1614</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G677" t="str">
-            <v>Flameless Candle Diffuser - Vertical Ribbed (White)</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="678">
           <cell r="F678" t="str">
-            <v>11-1615</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G678" t="str">
-            <v>Flameless Candle Diffuser -  Two Tone</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="679">
           <cell r="F679" t="str">
-            <v>11-1610</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G679" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
         </row>
         <row r="680">
           <cell r="F680" t="str">
-            <v>16-0107</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G680" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
         </row>
         <row r="681">
           <cell r="F681" t="str">
-            <v>LL-11-2522</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G681" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
         </row>
         <row r="682">
           <cell r="F682" t="str">
-            <v>LL-11-2523</v>
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G682" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
         </row>
         <row r="683">
           <cell r="F683" t="str">
-            <v>11-0451</v>
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G683" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
         </row>
         <row r="684">
           <cell r="F684" t="str">
-            <v>99-9502</v>
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G684" t="str">
-            <v>Pen Display - Empty</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
         </row>
         <row r="685">
           <cell r="F685" t="str">
-            <v>11-0452</v>
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G685" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
         </row>
         <row r="686">
           <cell r="F686" t="str">
-            <v>112522</v>
+            <v>LL-12-3134</v>
+          </cell>
+          <cell r="G686" t="str">
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="687">
           <cell r="F687" t="str">
-            <v>99-9501</v>
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G687" t="str">
-            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+            <v>DIFFUSER, LED,Bubble (Cream) - WALMART PKG</v>
           </cell>
         </row>
         <row r="688">
           <cell r="F688" t="str">
-            <v>11-1618</v>
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G688" t="str">
-            <v>Flameless Candle Diffuser - Winter Edition (Frosted Green)</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
         </row>
         <row r="689">
           <cell r="F689" t="str">
+            <v>LL-98-3171</v>
+          </cell>
+          <cell r="G689" t="str">
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="690">
+          <cell r="F690" t="str">
+            <v>LL-11-3087</v>
+          </cell>
+          <cell r="G690" t="str">
+            <v>Clickwick 2PK - SKU 5</v>
+          </cell>
+        </row>
+        <row r="691">
+          <cell r="F691" t="str">
+            <v>LL-11-3088</v>
+          </cell>
+          <cell r="G691" t="str">
+            <v>Clickwick 2PK - SKU 6</v>
+          </cell>
+        </row>
+        <row r="692">
+          <cell r="F692" t="str">
+            <v>LL-11-3089</v>
+          </cell>
+          <cell r="G692" t="str">
+            <v>Clickwick 2PK - SKU 7</v>
+          </cell>
+        </row>
+        <row r="693">
+          <cell r="F693">
+            <v>165002</v>
+          </cell>
+          <cell r="G693" t="str">
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+          </cell>
+        </row>
+        <row r="694">
+          <cell r="F694">
+            <v>165003</v>
+          </cell>
+          <cell r="G694" t="str">
+            <v>FlowArt - Multiline art - Land</v>
+          </cell>
+        </row>
+        <row r="695">
+          <cell r="F695">
+            <v>165004</v>
+          </cell>
+          <cell r="G695" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="696">
+          <cell r="F696">
+            <v>165010</v>
+          </cell>
+          <cell r="G696" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="697">
+          <cell r="F697">
+            <v>165011</v>
+          </cell>
+          <cell r="G697" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="698">
+          <cell r="F698">
+            <v>165013</v>
+          </cell>
+          <cell r="G698" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="699">
+          <cell r="F699">
+            <v>167003</v>
+          </cell>
+          <cell r="G699" t="str">
+            <v>Decor Art - Stencil Stationery</v>
+          </cell>
+        </row>
+        <row r="700">
+          <cell r="F700" t="str">
+            <v>11-1613</v>
+          </cell>
+          <cell r="G700" t="str">
+            <v>DIFFUSER, LED,Frosted Glass (Amber)</v>
+          </cell>
+        </row>
+        <row r="701">
+          <cell r="F701" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G701" t="str">
+            <v>DIFFUSER, LED,Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="702">
+          <cell r="F702" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G702" t="str">
+            <v>DIFFUSER, LED, Two Tone</v>
+          </cell>
+        </row>
+        <row r="703">
+          <cell r="F703" t="str">
+            <v>11-1610</v>
+          </cell>
+          <cell r="G703" t="str">
+            <v>Planter Diffuser -  Octagon (Cream)</v>
+          </cell>
+        </row>
+        <row r="704">
+          <cell r="F704" t="str">
+            <v>16-0107</v>
+          </cell>
+          <cell r="G704" t="str">
+            <v>Finger Maze Sensory Journal</v>
+          </cell>
+        </row>
+        <row r="705">
+          <cell r="F705" t="str">
+            <v>LL-11-2522</v>
+          </cell>
+          <cell r="G705" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="706">
+          <cell r="F706" t="str">
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G706" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="707">
+          <cell r="F707" t="str">
+            <v>11-0451</v>
+          </cell>
+          <cell r="G707" t="str">
+            <v>Clickwick Replacement Bloom, Citrus</v>
+          </cell>
+        </row>
+        <row r="708">
+          <cell r="F708" t="str">
+            <v>99-9502</v>
+          </cell>
+          <cell r="G708" t="str">
+            <v>Pen Display - Empty</v>
+          </cell>
+        </row>
+        <row r="709">
+          <cell r="F709" t="str">
+            <v>11-0452</v>
+          </cell>
+          <cell r="G709" t="str">
+            <v>Clickwick Replacement Woods, Mountain</v>
+          </cell>
+        </row>
+        <row r="710">
+          <cell r="F710" t="str">
+            <v>112522</v>
+          </cell>
+        </row>
+        <row r="711">
+          <cell r="F711" t="str">
+            <v>99-9501</v>
+          </cell>
+          <cell r="G711" t="str">
+            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+          </cell>
+        </row>
+        <row r="712">
+          <cell r="F712" t="str">
+            <v>11-1618</v>
+          </cell>
+          <cell r="G712" t="str">
+            <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
+          </cell>
+        </row>
+        <row r="713">
+          <cell r="F713" t="str">
             <v>98-9220</v>
           </cell>
-          <cell r="G689" t="str">
+          <cell r="G713" t="str">
             <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
         </row>
@@ -5931,13 +6117,7 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="1">
-          <cell r="C1" t="str">
-            <v>LL PN (Final)</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -6098,36 +6278,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.6875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -6136,7 +6317,7 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
@@ -6156,7 +6337,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="str">
@@ -6177,7 +6358,7 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="str">
@@ -6198,7 +6379,7 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="str">
@@ -6219,7 +6400,7 @@
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="str">
@@ -6240,7 +6421,7 @@
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="str">
@@ -6261,7 +6442,7 @@
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="str">
@@ -6282,7 +6463,7 @@
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D11" s="1" t="str">
@@ -6303,7 +6484,7 @@
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="str">
@@ -6324,7 +6505,7 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="str">
@@ -6345,7 +6526,7 @@
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D14" t="str">
@@ -6366,7 +6547,7 @@
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="str">
@@ -6387,7 +6568,7 @@
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="str">
@@ -6408,7 +6589,7 @@
       <c r="B17" s="1">
         <v>6</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="1" t="str">
@@ -6429,7 +6610,7 @@
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D18" t="str">
@@ -6437,7 +6618,7 @@
         <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F18">
         <v>3.5</v>
@@ -6450,7 +6631,7 @@
       <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" t="str">
@@ -6458,7 +6639,7 @@
         <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>3.5</v>
@@ -6471,7 +6652,7 @@
       <c r="B20">
         <v>3</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="str">
@@ -6479,7 +6660,7 @@
         <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>3.5</v>
@@ -6492,7 +6673,7 @@
       <c r="B21" s="1">
         <v>4</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="1" t="str">
@@ -6513,7 +6694,7 @@
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="str">
@@ -6534,7 +6715,7 @@
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D23" t="str">
@@ -6555,7 +6736,7 @@
       <c r="B24">
         <v>3</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="str">
@@ -6576,7 +6757,7 @@
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D25" t="str">
@@ -6597,7 +6778,7 @@
       <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="str">
@@ -6618,7 +6799,7 @@
       <c r="B27">
         <v>6</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D27" t="str">
@@ -6639,7 +6820,7 @@
       <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="str">
@@ -6660,7 +6841,7 @@
       <c r="B29" s="1">
         <v>8</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D29" s="1" t="str">
@@ -6681,7 +6862,7 @@
       <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D30" t="str">
@@ -6702,7 +6883,7 @@
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D31" t="str">
@@ -6723,7 +6904,7 @@
       <c r="B32">
         <v>3</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D32" t="str">
@@ -6744,7 +6925,7 @@
       <c r="B33" s="1">
         <v>4</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D33" s="1" t="str">
@@ -6765,7 +6946,7 @@
       <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D34" t="str">
@@ -6786,7 +6967,7 @@
       <c r="B35">
         <v>2</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D35" t="str">
@@ -6807,7 +6988,7 @@
       <c r="B36">
         <v>3</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="str">
@@ -6828,7 +7009,7 @@
       <c r="B37" s="1">
         <v>4</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="1" t="str">
@@ -6849,7 +7030,7 @@
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D38" t="str">
@@ -6870,7 +7051,7 @@
       <c r="B39">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D39" t="str">
@@ -6891,7 +7072,7 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D40" t="str">
@@ -6912,7 +7093,7 @@
       <c r="B41">
         <v>4</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D41" t="str">
@@ -6933,7 +7114,7 @@
       <c r="B42">
         <v>5</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D42" t="str">
@@ -6954,7 +7135,7 @@
       <c r="B43">
         <v>6</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="str">
@@ -6975,7 +7156,7 @@
       <c r="B44" s="1">
         <v>8</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D44" s="1" t="str">
@@ -6996,7 +7177,7 @@
       <c r="B45">
         <v>1</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <v>165005</v>
       </c>
       <c r="D45" t="str">
@@ -7017,7 +7198,7 @@
       <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="2">
         <v>165008</v>
       </c>
       <c r="D46" t="str">
@@ -7038,7 +7219,7 @@
       <c r="B47">
         <v>3</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D47" t="str">
@@ -7059,7 +7240,7 @@
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D48" t="str">
@@ -7080,7 +7261,7 @@
       <c r="B49">
         <v>5</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D49" t="str">
@@ -7101,7 +7282,7 @@
       <c r="B50">
         <v>6</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D50" t="str">
@@ -7122,7 +7303,7 @@
       <c r="B51">
         <v>7</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D51" t="str">
@@ -7143,7 +7324,7 @@
       <c r="B52">
         <v>8</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D52" t="str">
@@ -7164,7 +7345,7 @@
       <c r="B53">
         <v>9</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D53" t="str">
@@ -7185,7 +7366,7 @@
       <c r="B54">
         <v>10</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="str">
@@ -7206,7 +7387,7 @@
       <c r="B55">
         <v>11</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D55" t="str">
@@ -7227,7 +7408,7 @@
       <c r="B56">
         <v>12</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D56" t="str">
@@ -7249,7 +7430,7 @@
         <f>B56+1</f>
         <v>13</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D57" t="str">
@@ -7271,7 +7452,7 @@
         <f>B57+1</f>
         <v>14</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="str">
@@ -7292,7 +7473,7 @@
       <c r="B59" s="1">
         <v>13</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D59" s="1" t="str">
@@ -7313,7 +7494,7 @@
       <c r="B60">
         <v>1</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D60" t="str">
@@ -7334,7 +7515,7 @@
       <c r="B61">
         <v>2</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D61" t="str">
@@ -7355,7 +7536,7 @@
       <c r="B62">
         <v>3</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D62" t="str">
@@ -7376,7 +7557,7 @@
       <c r="B63">
         <v>4</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D63" t="str">
@@ -7397,7 +7578,7 @@
       <c r="B64">
         <v>5</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D64" t="str">
@@ -7418,7 +7599,7 @@
       <c r="B65">
         <v>6</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D65" t="str">
@@ -7439,7 +7620,7 @@
       <c r="B66">
         <v>7</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D66" t="str">
@@ -7460,7 +7641,7 @@
       <c r="B67">
         <v>8</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D67" t="str">
@@ -7481,7 +7662,7 @@
       <c r="B68">
         <v>9</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D68" t="str">
@@ -7502,7 +7683,7 @@
       <c r="B69">
         <v>10</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D69" t="str">
@@ -7523,7 +7704,7 @@
       <c r="B70">
         <v>11</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D70" t="str">
@@ -7544,7 +7725,7 @@
       <c r="B71">
         <v>12</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D71" t="str">
@@ -7565,7 +7746,7 @@
       <c r="B72" s="1">
         <v>13</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D72" s="1" t="str">
@@ -7586,7 +7767,7 @@
       <c r="B73">
         <v>1</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D73" t="str">
@@ -7607,7 +7788,7 @@
       <c r="B74">
         <v>2</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D74" t="str">
@@ -7628,7 +7809,7 @@
       <c r="B75">
         <v>3</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D75" t="str">
@@ -7649,7 +7830,7 @@
       <c r="B76">
         <v>4</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D76" t="str">
@@ -7670,7 +7851,7 @@
       <c r="B77">
         <v>5</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D77" t="str">
@@ -7691,7 +7872,7 @@
       <c r="B78" s="1">
         <v>6</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D78" s="1" t="str">
@@ -7712,7 +7893,7 @@
       <c r="B79">
         <v>1</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="2">
         <v>165005</v>
       </c>
       <c r="D79" t="str">
@@ -7734,7 +7915,7 @@
         <f>B79+1</f>
         <v>2</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D80" t="str">
@@ -7756,7 +7937,7 @@
         <f t="shared" ref="B81:B99" si="0">B80+1</f>
         <v>3</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="2">
         <v>165008</v>
       </c>
       <c r="D81" t="str">
@@ -7778,7 +7959,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D82" t="str">
@@ -7800,7 +7981,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D83" t="str">
@@ -7822,7 +8003,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D84" t="str">
@@ -7844,7 +8025,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D85" t="str">
@@ -7866,7 +8047,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D86" t="str">
@@ -7888,7 +8069,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="str">
@@ -7910,7 +8091,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D88" t="str">
@@ -7932,7 +8113,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D89" t="str">
@@ -7954,7 +8135,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D90" t="str">
@@ -7976,7 +8157,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D91" t="str">
@@ -7998,7 +8179,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D92" t="str">
@@ -8020,7 +8201,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D93" t="str">
@@ -8042,7 +8223,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D94" t="str">
@@ -8064,7 +8245,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D95" t="str">
@@ -8086,7 +8267,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D96" t="str">
@@ -8108,7 +8289,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D97" t="str">
@@ -8130,7 +8311,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D98" t="str">
@@ -8152,7 +8333,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -8173,7 +8354,7 @@
       <c r="B100">
         <v>1</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D100" t="str">
@@ -8194,7 +8375,7 @@
       <c r="B101">
         <v>2</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D101" t="str">
@@ -8215,7 +8396,7 @@
       <c r="B102">
         <v>3</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D102" t="str">
@@ -8236,7 +8417,7 @@
       <c r="B103">
         <v>4</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="2">
         <v>165005</v>
       </c>
       <c r="D103" t="str">
@@ -8257,7 +8438,7 @@
       <c r="B104">
         <v>5</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="2">
         <v>165008</v>
       </c>
       <c r="D104" t="str">
@@ -8278,7 +8459,7 @@
       <c r="B105">
         <v>6</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D105" t="str">
@@ -8299,7 +8480,7 @@
       <c r="B106">
         <v>7</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D106" t="str">
@@ -8320,7 +8501,7 @@
       <c r="B107">
         <v>8</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D107" t="str">
@@ -8341,7 +8522,7 @@
       <c r="B108">
         <v>9</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D108" t="str">
@@ -8362,7 +8543,7 @@
       <c r="B109">
         <v>10</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D109" t="str">
@@ -8383,7 +8564,7 @@
       <c r="B110" s="1">
         <v>11</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D110" s="1" t="str">
@@ -8404,7 +8585,7 @@
       <c r="B111">
         <v>1</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D111" t="str">
@@ -8425,7 +8606,7 @@
       <c r="B112">
         <v>2</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" t="str">
@@ -8446,7 +8627,7 @@
       <c r="B113">
         <v>3</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D113" t="str">
@@ -8467,7 +8648,7 @@
       <c r="B114">
         <v>4</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D114" t="str">
@@ -8488,7 +8669,7 @@
       <c r="B115">
         <v>5</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D115" t="str">
@@ -8509,7 +8690,7 @@
       <c r="B116">
         <v>6</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D116" t="str">
@@ -8530,7 +8711,7 @@
       <c r="B117" s="1">
         <v>7</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D117" s="1" t="str">
@@ -8551,7 +8732,7 @@
       <c r="B118">
         <v>1</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D118" t="str">
@@ -8572,7 +8753,7 @@
       <c r="B119">
         <v>2</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D119" t="str">
@@ -8593,7 +8774,7 @@
       <c r="B120">
         <v>3</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D120" t="str">
@@ -8614,7 +8795,7 @@
       <c r="B121" s="1">
         <v>4</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D121" s="1" t="str">
@@ -8635,7 +8816,7 @@
       <c r="B122">
         <v>1</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D122" t="str">
@@ -8656,7 +8837,7 @@
       <c r="B123">
         <v>2</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="str">
@@ -8677,7 +8858,7 @@
       <c r="B124">
         <v>3</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D124" t="str">
@@ -8698,7 +8879,7 @@
       <c r="B125">
         <v>4</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D125" t="str">
@@ -8719,7 +8900,7 @@
       <c r="B126">
         <v>5</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D126" t="str">
@@ -8740,7 +8921,7 @@
       <c r="B127">
         <v>6</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D127" t="str">
@@ -8761,7 +8942,7 @@
       <c r="B128" s="1">
         <v>7</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D128" s="1" t="str">
@@ -8782,7 +8963,7 @@
       <c r="B129">
         <v>1</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D129" t="str">
@@ -8803,7 +8984,7 @@
       <c r="B130">
         <v>2</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D130" t="str">
@@ -8824,7 +9005,7 @@
       <c r="B131">
         <v>2</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D131" t="str">
@@ -8845,7 +9026,7 @@
       <c r="B132">
         <v>3</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D132" t="str">
@@ -8866,7 +9047,7 @@
       <c r="B133" s="1">
         <v>4</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D133" s="1" t="str">
@@ -8887,7 +9068,7 @@
       <c r="B134">
         <v>1</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D134" t="str">
@@ -8908,7 +9089,7 @@
       <c r="B135">
         <v>2</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D135" t="str">
@@ -8929,7 +9110,7 @@
       <c r="B136">
         <v>3</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D136" t="str">
@@ -8950,7 +9131,7 @@
       <c r="B137">
         <v>4</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D137" t="str">
@@ -8971,7 +9152,7 @@
       <c r="B138" s="1">
         <v>5</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D138" s="1" t="str">
@@ -8992,7 +9173,7 @@
       <c r="B139">
         <v>1</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D139" t="str">
@@ -9013,7 +9194,7 @@
       <c r="B140">
         <v>2</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D140" t="str">
@@ -9034,7 +9215,7 @@
       <c r="B141">
         <v>3</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D141" t="str">
@@ -9055,7 +9236,7 @@
       <c r="B142">
         <v>4</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D142" t="str">
@@ -9076,7 +9257,7 @@
       <c r="B143">
         <v>5</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D143" t="str">
@@ -9097,7 +9278,7 @@
       <c r="B144">
         <v>6</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="C144" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D144" t="str">
@@ -9118,7 +9299,7 @@
       <c r="B145">
         <v>7</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D145" t="str">
@@ -9139,7 +9320,7 @@
       <c r="B146">
         <v>8</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D146" t="str">
@@ -9160,7 +9341,7 @@
       <c r="B147">
         <v>1</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C147" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D147" t="str">
@@ -9181,7 +9362,7 @@
       <c r="B148">
         <v>2</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D148" t="str">
@@ -9202,7 +9383,7 @@
       <c r="B149">
         <v>3</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D149" t="str">
@@ -9223,7 +9404,7 @@
       <c r="B150">
         <v>4</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D150" t="str">
@@ -9244,7 +9425,7 @@
       <c r="B151">
         <v>5</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C151" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D151" t="str">
@@ -9265,7 +9446,7 @@
       <c r="B152">
         <v>6</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C152" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D152" t="str">
@@ -9286,7 +9467,7 @@
       <c r="B153">
         <v>7</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D153" t="str">
@@ -9307,7 +9488,7 @@
       <c r="B154">
         <v>8</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="C154" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D154" t="str">
@@ -9328,7 +9509,7 @@
       <c r="B155">
         <v>9</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D155" t="str">
@@ -9349,7 +9530,7 @@
       <c r="B156">
         <v>10</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D156" t="str">
@@ -9370,7 +9551,7 @@
       <c r="B157">
         <v>11</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D157" t="str">
@@ -9391,7 +9572,7 @@
       <c r="B158">
         <v>12</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D158" t="str">
@@ -9412,7 +9593,7 @@
       <c r="B159" s="1">
         <v>13</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D159" s="1" t="str">
@@ -9433,7 +9614,7 @@
       <c r="B160">
         <v>1</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D160" t="str">
@@ -9454,7 +9635,7 @@
       <c r="B161">
         <v>2</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D161" t="str">
@@ -9475,7 +9656,7 @@
       <c r="B162">
         <v>3</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D162" t="str">
@@ -9496,7 +9677,7 @@
       <c r="B163">
         <v>4</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D163" t="str">
@@ -9517,7 +9698,7 @@
       <c r="B164">
         <v>5</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D164" t="str">
@@ -9538,7 +9719,7 @@
       <c r="B165">
         <v>6</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D165" t="str">
@@ -9559,7 +9740,7 @@
       <c r="B166">
         <v>7</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D166" t="str">
@@ -9580,7 +9761,7 @@
       <c r="B167">
         <v>8</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D167" t="str">
@@ -9601,7 +9782,7 @@
       <c r="B168">
         <v>9</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C168" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D168" t="str">
@@ -9622,7 +9803,7 @@
       <c r="B169">
         <v>10</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D169" t="str">
@@ -9643,7 +9824,7 @@
       <c r="B170" s="1">
         <v>11</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D170" s="1" t="str">
@@ -9664,7 +9845,7 @@
       <c r="B171">
         <v>1</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D171" t="str">
@@ -9685,7 +9866,7 @@
       <c r="B172">
         <v>2</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D172" t="str">
@@ -9706,7 +9887,7 @@
       <c r="B173">
         <v>3</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D173" t="str">
@@ -9727,7 +9908,7 @@
       <c r="B174">
         <v>4</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D174" t="str">
@@ -9748,7 +9929,7 @@
       <c r="B175">
         <v>5</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D175" t="str">
@@ -9769,7 +9950,7 @@
       <c r="B176" s="1">
         <v>6</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D176" s="1" t="str">
@@ -9790,7 +9971,7 @@
       <c r="B177">
         <v>1</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="C177" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D177" t="str">
@@ -9811,7 +9992,7 @@
       <c r="B178">
         <v>2</v>
       </c>
-      <c r="C178" s="3" t="s">
+      <c r="C178" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D178" t="str">
@@ -9832,7 +10013,7 @@
       <c r="B179">
         <v>3</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="C179" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D179" t="str">
@@ -9853,7 +10034,7 @@
       <c r="B180">
         <v>4</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="C180" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D180" t="str">
@@ -9874,7 +10055,7 @@
       <c r="B181">
         <v>5</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="C181" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D181" t="str">
@@ -9895,7 +10076,7 @@
       <c r="B182">
         <v>6</v>
       </c>
-      <c r="C182" s="3" t="s">
+      <c r="C182" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D182" t="str">
@@ -9916,7 +10097,7 @@
       <c r="B183">
         <v>7</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="C183" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D183" t="str">
@@ -9937,7 +10118,7 @@
       <c r="B184">
         <v>8</v>
       </c>
-      <c r="C184" s="3" t="s">
+      <c r="C184" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D184" t="str">
@@ -9958,7 +10139,7 @@
       <c r="B185">
         <v>9</v>
       </c>
-      <c r="C185" s="3" t="s">
+      <c r="C185" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D185" t="str">
@@ -9979,7 +10160,7 @@
       <c r="B186">
         <v>10</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D186" t="str">
@@ -10000,7 +10181,7 @@
       <c r="B187">
         <v>11</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="C187" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D187" t="str">
@@ -10021,7 +10202,7 @@
       <c r="B188">
         <v>12</v>
       </c>
-      <c r="C188" s="3" t="s">
+      <c r="C188" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D188" t="str">
@@ -10042,7 +10223,7 @@
       <c r="B189">
         <v>13</v>
       </c>
-      <c r="C189" s="3" t="s">
+      <c r="C189" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D189" t="str">
@@ -10063,7 +10244,7 @@
       <c r="B190">
         <v>14</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="str">
@@ -10084,7 +10265,7 @@
       <c r="B191">
         <v>15</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D191" t="str">
@@ -10105,7 +10286,7 @@
       <c r="B192">
         <v>16</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="C192" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D192" t="str">
@@ -10126,7 +10307,7 @@
       <c r="B193">
         <v>17</v>
       </c>
-      <c r="C193" s="3" t="s">
+      <c r="C193" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D193" t="str">
@@ -10147,7 +10328,7 @@
       <c r="B194">
         <v>18</v>
       </c>
-      <c r="C194" s="3" t="s">
+      <c r="C194" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D194" t="str">
@@ -10168,7 +10349,7 @@
       <c r="B195">
         <v>19</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="C195" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D195" t="str">
@@ -10189,7 +10370,7 @@
       <c r="B196">
         <v>20</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="C196" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D196" t="str">
@@ -10210,7 +10391,7 @@
       <c r="B197">
         <v>21</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="C197" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D197" t="str">
@@ -10231,7 +10412,7 @@
       <c r="B198">
         <v>22</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="C198" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D198" t="str">
@@ -10252,7 +10433,7 @@
       <c r="B199" s="1">
         <v>23</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D199" s="1" t="str">
@@ -10273,7 +10454,7 @@
       <c r="B200">
         <v>1</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="C200" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D200" t="str">
@@ -10294,7 +10475,7 @@
       <c r="B201">
         <v>2</v>
       </c>
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D201" t="str">
@@ -10315,7 +10496,7 @@
       <c r="B202">
         <v>3</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="C202" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D202" t="str">
@@ -10336,7 +10517,7 @@
       <c r="B203">
         <v>4</v>
       </c>
-      <c r="C203" s="3" t="s">
+      <c r="C203" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D203" t="str">
@@ -10357,7 +10538,7 @@
       <c r="B204">
         <v>5</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="C204" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D204" t="str">
@@ -10378,7 +10559,7 @@
       <c r="B205">
         <v>6</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="C205" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D205" t="str">
@@ -10399,7 +10580,7 @@
       <c r="B206">
         <v>7</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="C206" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D206" t="str">
@@ -10420,7 +10601,7 @@
       <c r="B207">
         <v>8</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="C207" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D207" t="str">
@@ -10441,7 +10622,7 @@
       <c r="B208">
         <v>9</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="C208" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D208" t="str">
@@ -10462,7 +10643,7 @@
       <c r="B209">
         <v>10</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="C209" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D209" t="str">

--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toy.sharepoint.com/sites/Operations/Shared Documents/Planning/3) Planning BOM/Archive/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6CE46B8-8A67-4B67-8940-BC48F4305077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C4AD93-9EA0-481B-A797-B930415455D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$210</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="93">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -391,7 +391,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls driveId="b!HTnOnJwPMEWf4Qc1OT0tJzUXtA3JA_dFmeLcrifvRQA3dGqF56dSRIF8RuQ19ZxM" itemId="01FHB6EQ4WFPYOBAHH6NC22UE5IJXHENMZ">
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -417,6 +416,9 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
+          <cell r="A1" t="str">
+            <v>Date Created</v>
+          </cell>
           <cell r="F1" t="str">
             <v>SBOM SKU</v>
           </cell>
@@ -1601,6 +1603,7 @@
           </cell>
         </row>
         <row r="149">
+          <cell r="F149"/>
           <cell r="G149" t="str">
             <v>Lifelines Bath &amp; Shower Spa Bundle</v>
           </cell>
@@ -5326,6 +5329,7 @@
           </cell>
         </row>
         <row r="615">
+          <cell r="F615"/>
           <cell r="G615" t="str">
             <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
           </cell>
@@ -6117,7 +6121,13 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="9">
+        <row r="1">
+          <cell r="C1" t="str">
+            <v>LL PN (Final)</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -6279,7 +6289,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -7101,7 +7111,7 @@
         <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41">
         <v>6.5</v>
@@ -7115,11 +7125,11 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D42" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -7136,59 +7146,59 @@
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D43" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" s="1" customFormat="1">
-      <c r="A44" s="1" t="s">
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1">
+      <c r="A45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B45" s="1">
         <v>8</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D45" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F45" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" s="2">
-        <v>165005</v>
-      </c>
-      <c r="D45" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E45">
-        <v>4</v>
-      </c>
-      <c r="F45">
-        <v>6.5</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -7196,14 +7206,14 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>165008</v>
+        <v>165005</v>
       </c>
       <c r="D46" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -7217,17 +7227,17 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>3</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>42</v>
+        <v>2</v>
+      </c>
+      <c r="C47" s="2">
+        <v>165008</v>
       </c>
       <c r="D47" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F47">
         <v>6.5</v>
@@ -7238,14 +7248,14 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D48" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -7259,14 +7269,14 @@
         <v>46</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D49" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E49">
         <v>8</v>
@@ -7280,14 +7290,14 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D50" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E50">
         <v>8</v>
@@ -7301,17 +7311,17 @@
         <v>46</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D51" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51">
         <v>6.5</v>
@@ -7322,14 +7332,14 @@
         <v>46</v>
       </c>
       <c r="B52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D52" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -7343,17 +7353,17 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53">
         <v>6.5</v>
@@ -7364,17 +7374,17 @@
         <v>46</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D54" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E54">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54">
         <v>6.5</v>
@@ -7385,14 +7395,14 @@
         <v>46</v>
       </c>
       <c r="B55">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D55" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E55">
         <v>4</v>
@@ -7406,14 +7416,14 @@
         <v>46</v>
       </c>
       <c r="B56">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="D56" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E56">
         <v>4</v>
@@ -7427,15 +7437,14 @@
         <v>46</v>
       </c>
       <c r="B57">
-        <f>B56+1</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D57" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E57">
         <v>4</v>
@@ -7450,62 +7459,63 @@
       </c>
       <c r="B58">
         <f>B57+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D58" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59">
+        <f>B58+1</f>
+        <v>14</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
-      <c r="E58">
+      <c r="E59">
         <v>8</v>
       </c>
-      <c r="F58">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" s="1" customFormat="1">
-      <c r="A59" s="1" t="s">
+      <c r="F59">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="1" customFormat="1">
+      <c r="A60" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B60" s="1">
         <v>13</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D60" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E60" s="1">
         <v>1</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F60" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D60" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E60">
-        <v>6</v>
-      </c>
-      <c r="F60">
-        <v>6.5</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -7513,14 +7523,14 @@
         <v>51</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D61" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E61">
         <v>6</v>
@@ -7534,17 +7544,17 @@
         <v>51</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62">
         <v>6.5</v>
@@ -7555,20 +7565,20 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E63">
         <v>4</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -7576,20 +7586,20 @@
         <v>51</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E64">
         <v>4</v>
       </c>
       <c r="F64">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -7597,14 +7607,14 @@
         <v>51</v>
       </c>
       <c r="B65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -7618,20 +7628,20 @@
         <v>51</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E66">
         <v>4</v>
       </c>
       <c r="F66">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -7639,20 +7649,20 @@
         <v>51</v>
       </c>
       <c r="B67">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E67">
         <v>4</v>
       </c>
       <c r="F67">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -7660,14 +7670,14 @@
         <v>51</v>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E68">
         <v>4</v>
@@ -7681,14 +7691,14 @@
         <v>51</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -7702,17 +7712,17 @@
         <v>51</v>
       </c>
       <c r="B70">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Visual Symphony Pen, Glitter 5Pck</v>
+        <v>Scented Marker 10 Colors</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70">
         <v>6.5</v>
@@ -7723,14 +7733,14 @@
         <v>51</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Visual Symphony Pen, Swirl 5Pck</v>
+        <v>Visual Symphony Pen, Glitter 5Pck</v>
       </c>
       <c r="E71">
         <v>8</v>
@@ -7739,46 +7749,46 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="1" customFormat="1">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
         <v>51</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Visual Symphony Pen, Swirl 5Pck</v>
+      </c>
+      <c r="E72">
+        <v>8</v>
+      </c>
+      <c r="F72">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="1" customFormat="1">
+      <c r="A73" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B73" s="1">
         <v>13</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D72" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D73" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E73" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F73" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D73" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E73">
-        <v>6</v>
-      </c>
-      <c r="F73">
-        <v>6.5</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7786,14 +7796,14 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E74">
         <v>6</v>
@@ -7807,17 +7817,17 @@
         <v>62</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F75">
         <v>6.5</v>
@@ -7828,17 +7838,17 @@
         <v>62</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76">
         <v>6.5</v>
@@ -7849,14 +7859,14 @@
         <v>62</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E77">
         <v>8</v>
@@ -7865,46 +7875,46 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" s="1" customFormat="1">
-      <c r="A78" s="1" t="s">
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
         <v>62</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+      </c>
+      <c r="E78">
+        <v>8</v>
+      </c>
+      <c r="F78">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" s="1" customFormat="1">
+      <c r="A79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="1">
         <v>6</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D78" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D79" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E79" s="1">
         <v>1</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F79" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79" s="2">
-        <v>165005</v>
-      </c>
-      <c r="D79" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E79">
-        <v>8</v>
-      </c>
-      <c r="F79">
-        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -7912,18 +7922,17 @@
         <v>65</v>
       </c>
       <c r="B80">
-        <f>B79+1</f>
-        <v>2</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C80" s="2">
+        <v>165005</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E80">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80">
         <v>5</v>
@@ -7934,18 +7943,18 @@
         <v>65</v>
       </c>
       <c r="B81">
-        <f t="shared" ref="B81:B99" si="0">B80+1</f>
-        <v>3</v>
-      </c>
-      <c r="C81" s="2">
-        <v>165008</v>
+        <f>B80+1</f>
+        <v>2</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F81">
         <v>5</v>
@@ -7956,18 +7965,18 @@
         <v>65</v>
       </c>
       <c r="B82">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>24</v>
+        <f t="shared" ref="B82:B100" si="0">B81+1</f>
+        <v>3</v>
+      </c>
+      <c r="C82" s="2">
+        <v>165008</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E82">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F82">
         <v>5</v>
@@ -7979,17 +7988,17 @@
       </c>
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E83">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F83">
         <v>5</v>
@@ -8001,17 +8010,17 @@
       </c>
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E84">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F84">
         <v>5</v>
@@ -8023,17 +8032,17 @@
       </c>
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E85">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F85">
         <v>5</v>
@@ -8045,14 +8054,14 @@
       </c>
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E86">
         <v>12</v>
@@ -8067,17 +8076,17 @@
       </c>
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E87">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F87">
         <v>5</v>
@@ -8089,17 +8098,17 @@
       </c>
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F88">
         <v>5</v>
@@ -8111,17 +8120,17 @@
       </c>
       <c r="B89">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E89">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89">
         <v>5</v>
@@ -8133,17 +8142,17 @@
       </c>
       <c r="B90">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E90">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F90">
         <v>5</v>
@@ -8155,17 +8164,17 @@
       </c>
       <c r="B91">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F91">
         <v>5</v>
@@ -8177,14 +8186,14 @@
       </c>
       <c r="B92">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
       </c>
       <c r="E92">
         <v>4</v>
@@ -8199,14 +8208,14 @@
       </c>
       <c r="B93">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E93">
         <v>4</v>
@@ -8221,17 +8230,17 @@
       </c>
       <c r="B94">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E94">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F94">
         <v>5</v>
@@ -8243,17 +8252,17 @@
       </c>
       <c r="B95">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E95">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F95">
         <v>5</v>
@@ -8265,14 +8274,14 @@
       </c>
       <c r="B96">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="D96" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E96">
         <v>8</v>
@@ -8287,17 +8296,17 @@
       </c>
       <c r="B97">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E97">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F97">
         <v>5</v>
@@ -8309,63 +8318,64 @@
       </c>
       <c r="B98">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F98">
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" s="1" customFormat="1">
-      <c r="A99" s="1" t="s">
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
         <v>65</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" s="1" customFormat="1">
+      <c r="A100" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B100" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D99" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D100" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E100" s="1">
         <v>1</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F100" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" t="s">
-        <v>73</v>
-      </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D100" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E100">
-        <v>8</v>
-      </c>
-      <c r="F100">
-        <v>6.5</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -8373,14 +8383,14 @@
         <v>73</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E101">
         <v>8</v>
@@ -8394,17 +8404,17 @@
         <v>73</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E102">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102">
         <v>6.5</v>
@@ -8415,14 +8425,14 @@
         <v>73</v>
       </c>
       <c r="B103">
-        <v>4</v>
-      </c>
-      <c r="C103" s="2">
-        <v>165005</v>
+        <v>3</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -8436,14 +8446,14 @@
         <v>73</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" s="2">
-        <v>165008</v>
+        <v>165005</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -8457,14 +8467,14 @@
         <v>73</v>
       </c>
       <c r="B105">
-        <v>6</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="C105" s="2">
+        <v>165008</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E105">
         <v>4</v>
@@ -8478,14 +8488,14 @@
         <v>73</v>
       </c>
       <c r="B106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D106" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E106">
         <v>4</v>
@@ -8499,17 +8509,17 @@
         <v>73</v>
       </c>
       <c r="B107">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E107">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107">
         <v>6.5</v>
@@ -8520,14 +8530,14 @@
         <v>73</v>
       </c>
       <c r="B108">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E108">
         <v>8</v>
@@ -8541,62 +8551,62 @@
         <v>73</v>
       </c>
       <c r="B109">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D109" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F109">
         <v>6.5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" s="1" customFormat="1">
-      <c r="A110" s="1" t="s">
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
         <v>73</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110">
+        <v>10</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+      </c>
+      <c r="E110">
+        <v>4</v>
+      </c>
+      <c r="F110">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" s="1" customFormat="1">
+      <c r="A111" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B111" s="1">
         <v>11</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D110" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D111" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
-      <c r="E110" s="1">
-        <v>4</v>
-      </c>
-      <c r="F110" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" t="s">
-        <v>74</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
-      </c>
-      <c r="E111">
-        <v>6</v>
-      </c>
-      <c r="F111">
-        <v>3.5</v>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1">
+        <v>6.5</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -8604,14 +8614,14 @@
         <v>74</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E112">
         <v>6</v>
@@ -8625,14 +8635,14 @@
         <v>74</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E113">
         <v>6</v>
@@ -8646,14 +8656,14 @@
         <v>74</v>
       </c>
       <c r="B114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E114">
         <v>6</v>
@@ -8667,14 +8677,14 @@
         <v>74</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E115">
         <v>6</v>
@@ -8688,14 +8698,14 @@
         <v>74</v>
       </c>
       <c r="B116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E116">
         <v>6</v>
@@ -8704,46 +8714,46 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" s="1" customFormat="1">
-      <c r="A117" s="1" t="s">
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
         <v>74</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117">
+        <v>6</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Mini Single - Furry Friends</v>
+      </c>
+      <c r="E117">
+        <v>6</v>
+      </c>
+      <c r="F117">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" s="1" customFormat="1">
+      <c r="A118" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B118" s="1">
         <v>7</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D117" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D118" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FA Mini - Counter Display - Empty</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E118" s="1">
         <v>2</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F118" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
-        <v>75</v>
-      </c>
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D118" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
-      </c>
-      <c r="E118">
-        <v>12</v>
-      </c>
-      <c r="F118">
-        <v>3.5</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -8751,17 +8761,17 @@
         <v>75</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+        <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
       <c r="E119">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F119">
         <v>3.5</v>
@@ -8772,62 +8782,62 @@
         <v>75</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+        <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
       <c r="E120">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F120">
         <v>3.5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" s="1" customFormat="1">
-      <c r="A121" s="1" t="s">
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
         <v>75</v>
       </c>
-      <c r="B121" s="1">
-        <v>4</v>
-      </c>
-      <c r="C121" s="3" t="s">
+      <c r="B121">
+        <v>3</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+      </c>
+      <c r="E121">
+        <v>9</v>
+      </c>
+      <c r="F121">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" s="1" customFormat="1">
+      <c r="A122" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D121" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D122" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FA Holiday Mini - Counter Display - Empty</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E122" s="1">
         <v>1</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F122" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
-        <v>76</v>
-      </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E122">
-        <v>8</v>
-      </c>
-      <c r="F122">
-        <v>6.5</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -8835,17 +8845,17 @@
         <v>76</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F123">
         <v>6.5</v>
@@ -8856,17 +8866,17 @@
         <v>76</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E124">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124">
         <v>6.5</v>
@@ -8877,17 +8887,17 @@
         <v>76</v>
       </c>
       <c r="B125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D125" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E125">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125">
         <v>6.5</v>
@@ -8898,14 +8908,14 @@
         <v>76</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D126" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C126, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C126), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -8919,61 +8929,61 @@
         <v>76</v>
       </c>
       <c r="B127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D127" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C127, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C127), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E127">
+        <v>4</v>
+      </c>
+      <c r="F127">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>76</v>
+      </c>
+      <c r="B128">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D128" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
-      <c r="E127">
-        <v>4</v>
-      </c>
-      <c r="F127">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" s="1" customFormat="1">
-      <c r="A128" s="1" t="s">
+      <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="1" customFormat="1">
+      <c r="A129" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B129" s="1">
         <v>7</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D128" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C128, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C128), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D129" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
-      <c r="E128" s="1">
-        <v>4</v>
-      </c>
-      <c r="F128" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
-        <v>77</v>
-      </c>
-      <c r="B129">
-        <v>1</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C129, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C129), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
-      </c>
-      <c r="E129">
-        <v>4</v>
-      </c>
-      <c r="F129">
+      <c r="E129" s="1">
+        <v>4</v>
+      </c>
+      <c r="F129" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -8982,14 +8992,14 @@
         <v>77</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D130" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C130, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C130), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E130">
         <v>4</v>
@@ -9006,14 +9016,14 @@
         <v>2</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D131" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C131, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C131), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131">
         <v>6.5</v>
@@ -9024,61 +9034,61 @@
         <v>77</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D132" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C132, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C132), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E132">
+        <v>8</v>
+      </c>
+      <c r="F132">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>77</v>
+      </c>
+      <c r="B133">
+        <v>3</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D133" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
-      <c r="E132">
-        <v>4</v>
-      </c>
-      <c r="F132">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" s="1" customFormat="1">
-      <c r="A133" s="1" t="s">
+      <c r="E133">
+        <v>4</v>
+      </c>
+      <c r="F133">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" s="1" customFormat="1">
+      <c r="A134" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B133" s="1">
-        <v>4</v>
-      </c>
-      <c r="C133" s="3" t="s">
+      <c r="B134" s="1">
+        <v>4</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D133" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C133, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C133), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D134" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
-      <c r="E133" s="1">
-        <v>4</v>
-      </c>
-      <c r="F133" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" t="s">
-        <v>78</v>
-      </c>
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D134" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C134, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C134), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
-      </c>
-      <c r="E134">
-        <v>4</v>
-      </c>
-      <c r="F134">
+      <c r="E134" s="1">
+        <v>4</v>
+      </c>
+      <c r="F134" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -9087,14 +9097,14 @@
         <v>78</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D135" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C135, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C135), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -9108,17 +9118,17 @@
         <v>78</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D136" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C136, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C136), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E136">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F136">
         <v>6.5</v>
@@ -9129,61 +9139,61 @@
         <v>78</v>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="D137" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C137, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C137), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+      </c>
+      <c r="E137">
+        <v>8</v>
+      </c>
+      <c r="F137">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>78</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D138" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
       </c>
-      <c r="E137">
-        <v>4</v>
-      </c>
-      <c r="F137">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" s="1" customFormat="1">
-      <c r="A138" s="1" t="s">
+      <c r="E138">
+        <v>4</v>
+      </c>
+      <c r="F138">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" s="1" customFormat="1">
+      <c r="A139" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B139" s="1">
         <v>5</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C139" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D138" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C138, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C138), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D139" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
       </c>
-      <c r="E138" s="1">
-        <v>4</v>
-      </c>
-      <c r="F138" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" t="s">
-        <v>79</v>
-      </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D139" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C139, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C139), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E139">
-        <v>4</v>
-      </c>
-      <c r="F139">
+      <c r="E139" s="1">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1">
         <v>6.5</v>
       </c>
     </row>
@@ -9192,14 +9202,14 @@
         <v>79</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D140" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C140, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C140), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E140">
         <v>4</v>
@@ -9213,17 +9223,17 @@
         <v>79</v>
       </c>
       <c r="B141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D141" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C141, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C141), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E141">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F141">
         <v>6.5</v>
@@ -9234,17 +9244,17 @@
         <v>79</v>
       </c>
       <c r="B142">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D142" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C142, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C142), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F142">
         <v>6.5</v>
@@ -9255,17 +9265,17 @@
         <v>79</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D143" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C143, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C143), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E143">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143">
         <v>6.5</v>
@@ -9276,17 +9286,17 @@
         <v>79</v>
       </c>
       <c r="B144">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D144" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C144, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C144), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E144">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F144">
         <v>6.5</v>
@@ -9297,14 +9307,14 @@
         <v>79</v>
       </c>
       <c r="B145">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D145" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C145, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C145), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E145">
         <v>4</v>
@@ -9318,41 +9328,41 @@
         <v>79</v>
       </c>
       <c r="B146">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D146" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C146, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C146), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E146">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D147" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C147, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C147), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
       <c r="E147">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F147">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -9360,14 +9370,14 @@
         <v>80</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D148" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C148, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C148), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E148">
         <v>8</v>
@@ -9381,14 +9391,14 @@
         <v>80</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D149" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C149, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C149), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E149">
         <v>8</v>
@@ -9402,17 +9412,17 @@
         <v>80</v>
       </c>
       <c r="B150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D150" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C150, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C150), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Mediterranean</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E150">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F150">
         <v>6.5</v>
@@ -9423,17 +9433,17 @@
         <v>80</v>
       </c>
       <c r="B151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D151" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C151, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C151), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Stamp by Shape, Mediterranean</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151">
         <v>6.5</v>
@@ -9444,14 +9454,14 @@
         <v>80</v>
       </c>
       <c r="B152">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D152" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C152, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C152), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E152">
         <v>8</v>
@@ -9465,14 +9475,14 @@
         <v>80</v>
       </c>
       <c r="B153">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D153" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C153, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C153), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E153">
         <v>8</v>
@@ -9486,14 +9496,14 @@
         <v>80</v>
       </c>
       <c r="B154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D154" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C154, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C154), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E154">
         <v>8</v>
@@ -9507,17 +9517,17 @@
         <v>80</v>
       </c>
       <c r="B155">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D155" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C155, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C155), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155">
         <v>6.5</v>
@@ -9528,17 +9538,17 @@
         <v>80</v>
       </c>
       <c r="B156">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D156" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C156, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C156), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E156">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156">
         <v>6.5</v>
@@ -9549,17 +9559,17 @@
         <v>80</v>
       </c>
       <c r="B157">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D157" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C157, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C157), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157">
         <v>6.5</v>
@@ -9570,62 +9580,62 @@
         <v>80</v>
       </c>
       <c r="B158">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D158" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C158, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C158), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+      </c>
+      <c r="E158">
+        <v>4</v>
+      </c>
+      <c r="F158">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>80</v>
+      </c>
+      <c r="B159">
+        <v>12</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D159" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
-      <c r="E158">
-        <v>4</v>
-      </c>
-      <c r="F158">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" s="1" customFormat="1">
-      <c r="A159" s="1" t="s">
+      <c r="E159">
+        <v>4</v>
+      </c>
+      <c r="F159">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" s="1" customFormat="1">
+      <c r="A160" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B159" s="1">
+      <c r="B160" s="1">
         <v>13</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C160" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D159" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C159, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C159), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D160" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E159" s="1">
+      <c r="E160" s="1">
         <v>1</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F160" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
-        <v>81</v>
-      </c>
-      <c r="B160">
-        <v>1</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D160" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C160, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C160), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E160">
-        <v>6</v>
-      </c>
-      <c r="F160">
-        <v>6.5</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -9633,14 +9643,14 @@
         <v>81</v>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D161" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C161, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C161), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E161">
         <v>6</v>
@@ -9654,17 +9664,17 @@
         <v>81</v>
       </c>
       <c r="B162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D162" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C162, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C162), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F162">
         <v>6.5</v>
@@ -9675,20 +9685,20 @@
         <v>81</v>
       </c>
       <c r="B163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D163" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C163, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C163), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E163">
         <v>4</v>
       </c>
       <c r="F163">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -9696,20 +9706,20 @@
         <v>81</v>
       </c>
       <c r="B164">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D164" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C164, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C164), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
       </c>
       <c r="E164">
         <v>4</v>
       </c>
       <c r="F164">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -9717,14 +9727,14 @@
         <v>81</v>
       </c>
       <c r="B165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D165" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C165, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C165), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
       </c>
       <c r="E165">
         <v>4</v>
@@ -9738,20 +9748,20 @@
         <v>81</v>
       </c>
       <c r="B166">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D166" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C166, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C166), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E166">
         <v>4</v>
       </c>
       <c r="F166">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -9759,20 +9769,20 @@
         <v>81</v>
       </c>
       <c r="B167">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D167" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C167, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C167), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
       </c>
       <c r="E167">
         <v>4</v>
       </c>
       <c r="F167">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -9780,14 +9790,14 @@
         <v>81</v>
       </c>
       <c r="B168">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D168" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C168, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C168), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E168">
         <v>4</v>
@@ -9801,62 +9811,62 @@
         <v>81</v>
       </c>
       <c r="B169">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D169" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C169, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C169), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+      </c>
+      <c r="E169">
+        <v>4</v>
+      </c>
+      <c r="F169">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>81</v>
+      </c>
+      <c r="B170">
+        <v>10</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D170" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>Scented Marker 10 Colors</v>
       </c>
-      <c r="E169">
-        <v>4</v>
-      </c>
-      <c r="F169">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" s="1" customFormat="1">
-      <c r="A170" s="1" t="s">
+      <c r="E170">
+        <v>4</v>
+      </c>
+      <c r="F170">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" s="1" customFormat="1">
+      <c r="A171" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B171" s="1">
         <v>11</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="C171" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D170" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C170, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C170), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D171" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E170" s="1">
+      <c r="E171" s="1">
         <v>1</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F171" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
-        <v>82</v>
-      </c>
-      <c r="B171">
-        <v>1</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D171" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C171, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C171), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E171">
-        <v>6</v>
-      </c>
-      <c r="F171">
-        <v>6.5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -9864,14 +9874,14 @@
         <v>82</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D172" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C172, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C172), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E172">
         <v>6</v>
@@ -9885,17 +9895,17 @@
         <v>82</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D173" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C173, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C173), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F173">
         <v>6.5</v>
@@ -9906,17 +9916,17 @@
         <v>82</v>
       </c>
       <c r="B174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D174" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C174, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C174), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E174">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F174">
         <v>6.5</v>
@@ -9927,14 +9937,14 @@
         <v>82</v>
       </c>
       <c r="B175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D175" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C175, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C175), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E175">
         <v>8</v>
@@ -9943,46 +9953,46 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="176" spans="1:6" s="1" customFormat="1">
-      <c r="A176" s="1" t="s">
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
         <v>82</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176">
+        <v>5</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D176" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+      </c>
+      <c r="E176">
+        <v>8</v>
+      </c>
+      <c r="F176">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" s="1" customFormat="1">
+      <c r="A177" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B177" s="1">
         <v>6</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="C177" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D176" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C176, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C176), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D177" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
       </c>
-      <c r="E176" s="1">
+      <c r="E177" s="1">
         <v>1</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F177" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" t="s">
-        <v>83</v>
-      </c>
-      <c r="B177">
-        <v>1</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D177" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C177, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C177), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E177">
-        <v>8</v>
-      </c>
-      <c r="F177">
-        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -9990,17 +10000,17 @@
         <v>83</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D178" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C178, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C178), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E178">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178">
         <v>5</v>
@@ -10011,14 +10021,14 @@
         <v>83</v>
       </c>
       <c r="B179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D179" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C179, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C179), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Pogo-Dot, Nature</v>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
       </c>
       <c r="E179">
         <v>4</v>
@@ -10032,17 +10042,17 @@
         <v>83</v>
       </c>
       <c r="B180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D180" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C180, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C180), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Pogo-Dot, Nature</v>
       </c>
       <c r="E180">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F180">
         <v>5</v>
@@ -10053,14 +10063,14 @@
         <v>83</v>
       </c>
       <c r="B181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D181" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C181, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C181), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E181">
         <v>12</v>
@@ -10074,14 +10084,14 @@
         <v>83</v>
       </c>
       <c r="B182">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D182" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C182, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C182), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E182">
         <v>12</v>
@@ -10095,14 +10105,14 @@
         <v>83</v>
       </c>
       <c r="B183">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D183" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C183, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C183), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E183">
         <v>12</v>
@@ -10116,14 +10126,14 @@
         <v>83</v>
       </c>
       <c r="B184">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D184" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C184, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C184), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E184">
         <v>12</v>
@@ -10137,17 +10147,17 @@
         <v>83</v>
       </c>
       <c r="B185">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D185" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C185, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C185), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E185">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F185">
         <v>5</v>
@@ -10158,14 +10168,14 @@
         <v>83</v>
       </c>
       <c r="B186">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D186" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C186, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C186), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E186">
         <v>8</v>
@@ -10179,17 +10189,17 @@
         <v>83</v>
       </c>
       <c r="B187">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D187" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C187, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C187), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E187">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F187">
         <v>5</v>
@@ -10200,14 +10210,14 @@
         <v>83</v>
       </c>
       <c r="B188">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D188" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C188, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C188), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E188">
         <v>12</v>
@@ -10221,17 +10231,17 @@
         <v>83</v>
       </c>
       <c r="B189">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="D189" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C189, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C189), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E189">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F189">
         <v>5</v>
@@ -10242,14 +10252,14 @@
         <v>83</v>
       </c>
       <c r="B190">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D190" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C190, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C190), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E190">
         <v>8</v>
@@ -10263,14 +10273,14 @@
         <v>83</v>
       </c>
       <c r="B191">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D191" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C191, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C191), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E191">
         <v>8</v>
@@ -10284,14 +10294,14 @@
         <v>83</v>
       </c>
       <c r="B192">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D192" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C192, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C192), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
       <c r="E192">
         <v>8</v>
@@ -10305,17 +10315,17 @@
         <v>83</v>
       </c>
       <c r="B193">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D193" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C193, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C193), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
       </c>
       <c r="E193">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193">
         <v>5</v>
@@ -10326,14 +10336,14 @@
         <v>83</v>
       </c>
       <c r="B194">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D194" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C194, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C194), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E194">
         <v>4</v>
@@ -10347,14 +10357,14 @@
         <v>83</v>
       </c>
       <c r="B195">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D195" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C195, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C195), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E195">
         <v>4</v>
@@ -10368,14 +10378,14 @@
         <v>83</v>
       </c>
       <c r="B196">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D196" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C196, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C196), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Trace-By-Line, Woodland Whimsy</v>
       </c>
       <c r="E196">
         <v>4</v>
@@ -10389,17 +10399,17 @@
         <v>83</v>
       </c>
       <c r="B197">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D197" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C197, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C197), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace Within, Peaceful Pause</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E197">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F197">
         <v>5</v>
@@ -10410,62 +10420,62 @@
         <v>83</v>
       </c>
       <c r="B198">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D198" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C198, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C198), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Trace Within, Peaceful Pause</v>
       </c>
       <c r="E198">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F198">
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:6" s="1" customFormat="1">
-      <c r="A199" s="1" t="s">
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
         <v>83</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199">
+        <v>22</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+      </c>
+      <c r="E199">
+        <v>4</v>
+      </c>
+      <c r="F199">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" s="1" customFormat="1">
+      <c r="A200" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B200" s="1">
         <v>23</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="C200" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D199" s="1" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C199, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C199), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D200" s="1" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt - Spinner Tower - Empty</v>
       </c>
-      <c r="E199" s="1">
+      <c r="E200" s="1">
         <v>1</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F200" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" t="s">
-        <v>84</v>
-      </c>
-      <c r="B200">
-        <v>1</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D200" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C200, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C200), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E200">
-        <v>8</v>
-      </c>
-      <c r="F200">
-        <v>6.5</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -10473,14 +10483,14 @@
         <v>84</v>
       </c>
       <c r="B201">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D201" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C201, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C201), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -10494,17 +10504,17 @@
         <v>84</v>
       </c>
       <c r="B202">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D202" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C202, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C202), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E202">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F202">
         <v>6.5</v>
@@ -10515,14 +10525,14 @@
         <v>84</v>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D203" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C203, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C203), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E203">
         <v>4</v>
@@ -10536,14 +10546,14 @@
         <v>84</v>
       </c>
       <c r="B204">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D204" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C204, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C204), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E204">
         <v>4</v>
@@ -10557,14 +10567,14 @@
         <v>84</v>
       </c>
       <c r="B205">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D205" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C205, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C205), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E205">
         <v>4</v>
@@ -10578,14 +10588,14 @@
         <v>84</v>
       </c>
       <c r="B206">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D206" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C206, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C206), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E206">
         <v>4</v>
@@ -10599,14 +10609,14 @@
         <v>84</v>
       </c>
       <c r="B207">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D207" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C207, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C207), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
       </c>
       <c r="E207">
         <v>4</v>
@@ -10620,14 +10630,14 @@
         <v>84</v>
       </c>
       <c r="B208">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D208" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C208, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C208), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E208">
         <v>4</v>
@@ -10641,24 +10651,45 @@
         <v>84</v>
       </c>
       <c r="B209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D209" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C209, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C209), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E209">
+        <v>4</v>
+      </c>
+      <c r="F209">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>84</v>
+      </c>
+      <c r="B210">
+        <v>10</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D210" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C210, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C210), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Trace-To-Doodle, Style Your Space</v>
       </c>
-      <c r="E209">
-        <v>4</v>
-      </c>
-      <c r="F209">
+      <c r="E210">
+        <v>4</v>
+      </c>
+      <c r="F210">
         <v>6.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F209" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:F210" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -10668,12 +10699,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10918,20 +10951,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10956,12 +10990,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
-    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C4AD93-9EA0-481B-A797-B930415455D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2C20E7-9F4C-4CB9-9BFD-FB9F77B57A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$210</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="94">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -319,6 +319,9 @@
   <si>
     <t>LL-12-3214</t>
   </si>
+  <si>
+    <t>LL-16-3201</t>
+  </si>
 </sst>
 </file>
 
@@ -359,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -369,6 +372,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,9 +423,6 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="1">
-          <cell r="A1" t="str">
-            <v>Date Created</v>
-          </cell>
           <cell r="F1" t="str">
             <v>SBOM SKU</v>
           </cell>
@@ -1603,7 +1607,6 @@
           </cell>
         </row>
         <row r="149">
-          <cell r="F149"/>
           <cell r="G149" t="str">
             <v>Lifelines Bath &amp; Shower Spa Bundle</v>
           </cell>
@@ -2269,7 +2272,7 @@
             <v>LL-12-3242</v>
           </cell>
           <cell r="G232" t="str">
-            <v>Visual Symphony Pen, Glitter 10Pck</v>
+            <v>Scented Sparkle Pen, 10Pck</v>
           </cell>
         </row>
         <row r="233">
@@ -2277,7 +2280,7 @@
             <v>LL-12-3213</v>
           </cell>
           <cell r="G233" t="str">
-            <v>Visual Symphony Pen, Glitter 5Pck</v>
+            <v>Scented Sparkle Pen, 5Pck</v>
           </cell>
         </row>
         <row r="234">
@@ -2285,7 +2288,7 @@
             <v>LL-12-3233</v>
           </cell>
           <cell r="G234" t="str">
-            <v>Visual Symphony Pen, Glitter 2Pck (Teal / Purple)</v>
+            <v>Mindful Motion Pen, Glitter 2Pck (Teal / Purple)</v>
           </cell>
         </row>
         <row r="235">
@@ -2293,7 +2296,7 @@
             <v>LL-12-3214</v>
           </cell>
           <cell r="G235" t="str">
-            <v>Visual Symphony Pen, Swirl 5Pck</v>
+            <v>Scented Swirl Pen, 5Pck</v>
           </cell>
         </row>
         <row r="236">
@@ -2301,7 +2304,7 @@
             <v>LL-12-3238</v>
           </cell>
           <cell r="G236" t="str">
-            <v>Visual Symphony Pen, Swirl 2Pck (X / X)</v>
+            <v>Mindful Motion Pen, Swirl 2Pck (X / X)</v>
           </cell>
         </row>
         <row r="237">
@@ -3293,7 +3296,7 @@
             <v>LL-16-3447</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Color-to-Reveal, Glitter #1</v>
+            <v>FlowArt: Color-to-Reveal, Butterfly Goldfoil</v>
           </cell>
         </row>
         <row r="361">
@@ -3301,7 +3304,7 @@
             <v>LL-16-3407</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning [Pastel]</v>
           </cell>
         </row>
         <row r="362">
@@ -3330,2788 +3333,3062 @@
         </row>
         <row r="365">
           <cell r="F365" t="str">
-            <v>LL-16-3299</v>
+            <v>LL-16-3493</v>
           </cell>
           <cell r="G365" t="str">
-            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Slow Summer</v>
           </cell>
         </row>
         <row r="366">
           <cell r="F366" t="str">
-            <v>LL-16-3300</v>
+            <v>LL-16-3480</v>
           </cell>
           <cell r="G366" t="str">
-            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+            <v>FlowArt: Dot-By-Letter, Spring has Sprung [Pastel]</v>
           </cell>
         </row>
         <row r="367">
           <cell r="F367" t="str">
-            <v>LL-16-3334</v>
+            <v>LL-16-3481</v>
           </cell>
           <cell r="G367" t="str">
-            <v>FlowArt: Premium #1 - Mandalas</v>
+            <v>FlowArt: Dot-By-Letter, Let's Plant a Garden [Pastel]</v>
           </cell>
         </row>
         <row r="368">
           <cell r="F368" t="str">
-            <v>LL-16-3335</v>
+            <v>LL-16-3299</v>
           </cell>
           <cell r="G368" t="str">
-            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
+            <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
           </cell>
         </row>
         <row r="369">
           <cell r="F369" t="str">
-            <v>LL-16-3336</v>
+            <v>LL-16-3300</v>
           </cell>
           <cell r="G369" t="str">
-            <v>FlowArt: Premium #3 - The Great Outdoors</v>
+            <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
           </cell>
         </row>
         <row r="370">
           <cell r="F370" t="str">
-            <v>LL-16-3337</v>
+            <v>LL-16-3484</v>
           </cell>
           <cell r="G370" t="str">
-            <v>FlowArt: Premium #4 - Large Dot - Floral Splendor</v>
+            <v>FlowArt: Etch-by-Trace #1</v>
           </cell>
         </row>
         <row r="371">
           <cell r="F371" t="str">
-            <v>LL-16-3388</v>
+            <v>LL-16-3485</v>
           </cell>
           <cell r="G371" t="str">
-            <v>FlowArt: Premium #5 - Large Dot - Simple Pleasures</v>
+            <v>FlowArt: Etch-to-Texture #1</v>
           </cell>
         </row>
         <row r="372">
           <cell r="F372" t="str">
-            <v>LL-16-3210</v>
+            <v>LL-16-3486</v>
           </cell>
           <cell r="G372" t="str">
-            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
+            <v>FlowArt: Etch-to-Pop #1</v>
           </cell>
         </row>
         <row r="373">
           <cell r="F373" t="str">
-            <v>LL-16-3313</v>
+            <v>LL-16-3487</v>
           </cell>
           <cell r="G373" t="str">
-            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
+            <v>FlowArt: Etch-to-Reveal #1</v>
           </cell>
         </row>
         <row r="374">
           <cell r="F374" t="str">
-            <v>LL-16-3154</v>
+            <v>LL-16-3488</v>
           </cell>
           <cell r="G374" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana</v>
+            <v>FlowArt: Etch-to-Engrave #1</v>
           </cell>
         </row>
         <row r="375">
           <cell r="F375" t="str">
-            <v>LL-DB-3154</v>
+            <v>LL-16-3489</v>
           </cell>
           <cell r="G375" t="str">
-            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
+            <v>FlowArt: Etch-by-Glitter #1</v>
           </cell>
         </row>
         <row r="376">
           <cell r="F376" t="str">
-            <v>LL-16-3350</v>
+            <v>LL-16-3334</v>
           </cell>
           <cell r="G376" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
+            <v>FlowArt: Premium #1 - Mandalas</v>
           </cell>
         </row>
         <row r="377">
           <cell r="F377" t="str">
-            <v>LL-16-3351</v>
+            <v>LL-16-3335</v>
           </cell>
           <cell r="G377" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
+            <v>FlowArt: Premium #2 - Museum Masterpieces</v>
           </cell>
         </row>
         <row r="378">
           <cell r="F378" t="str">
-            <v>LL-16-3353</v>
+            <v>LL-16-3336</v>
           </cell>
           <cell r="G378" t="str">
-            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
+            <v>FlowArt: Premium #3 - The Great Outdoors</v>
           </cell>
         </row>
         <row r="379">
           <cell r="F379" t="str">
-            <v>LL-16-3341</v>
+            <v>LL-16-3337</v>
           </cell>
           <cell r="G379" t="str">
-            <v>FlowArt: Cozy Sweater - TGT</v>
+            <v>FlowArt: Premium #4 - Large Dot - Floral Splendor</v>
           </cell>
         </row>
         <row r="380">
           <cell r="F380" t="str">
-            <v>LL-16-3342</v>
+            <v>LL-16-3388</v>
           </cell>
           <cell r="G380" t="str">
-            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
+            <v>FlowArt: Premium #5 - Large Dot - Simple Pleasures</v>
           </cell>
         </row>
         <row r="381">
           <cell r="F381" t="str">
-            <v>LL-16-3343</v>
+            <v>LL-16-3210</v>
           </cell>
           <cell r="G381" t="str">
-            <v>FlowArt: Dot-By-Letter, Corner Café</v>
+            <v>FlowArt: Dot-by-Letter, Lovestruck</v>
           </cell>
         </row>
         <row r="382">
           <cell r="F382" t="str">
-            <v>LL-16-3344</v>
+            <v>LL-16-3313</v>
           </cell>
           <cell r="G382" t="str">
-            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
+            <v>FlowArt: Dot-by-Letter, Spooky Season</v>
           </cell>
         </row>
         <row r="383">
           <cell r="F383" t="str">
-            <v>LL-16-3396</v>
+            <v>LL-16-3154</v>
           </cell>
           <cell r="G383" t="str">
-            <v>FlowArt: Stitch-By-X, Homegrown Garden</v>
+            <v>FlowArt: Dot-By-Letter, Americana</v>
           </cell>
         </row>
         <row r="384">
           <cell r="F384" t="str">
-            <v>LL-16-3397</v>
+            <v>LL-DB-3154</v>
           </cell>
           <cell r="G384" t="str">
-            <v>FlowArt: Stich-By-X, Cheeky Sayings</v>
+            <v>FlowArt: Dot-By-Letter, Americana [DB Edition]</v>
           </cell>
         </row>
         <row r="385">
           <cell r="F385" t="str">
-            <v>LL-16-3419</v>
+            <v>LL-16-3350</v>
           </cell>
           <cell r="G385" t="str">
-            <v>FlowArt: Stitch-By-X, [Nature TBD]</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #1</v>
           </cell>
         </row>
         <row r="386">
           <cell r="F386" t="str">
-            <v>LL-16-3398</v>
+            <v>LL-16-3351</v>
           </cell>
           <cell r="G386" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: Home Sweet Home</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #2</v>
           </cell>
         </row>
         <row r="387">
           <cell r="F387" t="str">
-            <v>LL-16-3422</v>
+            <v>LL-16-3353</v>
           </cell>
           <cell r="G387" t="str">
-            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
+            <v>FlowArt: Dot-By-Letter, DTC [Metallic] - #4</v>
           </cell>
         </row>
         <row r="388">
           <cell r="F388" t="str">
-            <v>LL-16-3423</v>
+            <v>LL-16-3341</v>
           </cell>
           <cell r="G388" t="str">
-            <v>FlowArt: Stitch-To-Embroider: #1</v>
+            <v>FlowArt: Cozy Sweater - TGT</v>
           </cell>
         </row>
         <row r="389">
           <cell r="F389" t="str">
-            <v>LL-16-3424</v>
+            <v>LL-16-3342</v>
           </cell>
           <cell r="G389" t="str">
-            <v>FlowArt: Stitch-To-Quilt: #1</v>
+            <v>FlowArt: Dot-By-Letter, Cozy Companions</v>
           </cell>
         </row>
         <row r="390">
           <cell r="F390" t="str">
-            <v>LL-20-3311</v>
+            <v>LL-16-3343</v>
           </cell>
           <cell r="G390" t="str">
-            <v>FlowArt: Mini, 6Pck #1</v>
+            <v>FlowArt: Dot-By-Letter, Corner Café</v>
           </cell>
         </row>
         <row r="391">
           <cell r="F391" t="str">
-            <v>LL-20-3363</v>
+            <v>LL-16-3344</v>
           </cell>
           <cell r="G391" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Dot-By-Letter, Cabin Getaway</v>
           </cell>
         </row>
         <row r="392">
           <cell r="F392" t="str">
-            <v>LL-20-3364</v>
+            <v>LL-16-3396</v>
           </cell>
           <cell r="G392" t="str">
-            <v>FlowArt: Mini, 3Pck - Retail #2</v>
+            <v>FlowArt: Cross-Stitch-by-Number, Homegrown Garden</v>
           </cell>
         </row>
         <row r="393">
           <cell r="F393" t="str">
-            <v>LL-20-3208</v>
+            <v>LL-16-3397</v>
           </cell>
           <cell r="G393" t="str">
-            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
+            <v>FlowArt: Stich-By-X, Cheeky Sayings</v>
           </cell>
         </row>
         <row r="394">
           <cell r="F394" t="str">
-            <v>LL-20-3209</v>
+            <v>LL-16-3419</v>
           </cell>
           <cell r="G394" t="str">
-            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
+            <v>FlowArt: Cross-Stitch-by-Number, [Nature TBD]</v>
           </cell>
         </row>
         <row r="395">
           <cell r="F395" t="str">
-            <v>LL-20-3229</v>
+            <v>LL-16-3398</v>
           </cell>
           <cell r="G395" t="str">
-            <v>FlowArt: Mini Single - Enchanted Magic</v>
+            <v>FlowArt: Stitch-By-Needlepoint: Home Sweet Home</v>
           </cell>
         </row>
         <row r="396">
           <cell r="F396" t="str">
-            <v>LL-20-3230</v>
+            <v>LL-16-3422</v>
           </cell>
           <cell r="G396" t="str">
-            <v>FlowArt: Mini Single - Pretty Petals</v>
+            <v>FlowArt: Stitch-By-Needlepoint: #2</v>
           </cell>
         </row>
         <row r="397">
           <cell r="F397" t="str">
-            <v>LL-20-3231</v>
+            <v>LL-16-3423</v>
           </cell>
           <cell r="G397" t="str">
-            <v>FlowArt: Mini Single - Nature's Wonders</v>
+            <v>FlowArt: Stitch-To-Embroider: #1</v>
           </cell>
         </row>
         <row r="398">
           <cell r="F398" t="str">
-            <v>LL-20-3227</v>
+            <v>LL-16-3424</v>
           </cell>
           <cell r="G398" t="str">
-            <v>FlowArt: Mini Single - Pocket Positivity</v>
+            <v>FlowArt: Stitch-To-Quilt: #1</v>
           </cell>
         </row>
         <row r="399">
           <cell r="F399" t="str">
-            <v>LL-20-3228</v>
+            <v>LL-20-3311</v>
           </cell>
           <cell r="G399" t="str">
-            <v>FlowArt: Mini Single - Café Comforts</v>
+            <v>FlowArt: Mini, 6Pck #1</v>
           </cell>
         </row>
         <row r="400">
           <cell r="F400" t="str">
-            <v>LL-20-3232</v>
+            <v>LL-20-3363</v>
           </cell>
           <cell r="G400" t="str">
-            <v>FlowArt: Mini Single - Furry Friends</v>
+            <v>FlowArt: Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="401">
           <cell r="F401" t="str">
-            <v>LL-20-3312</v>
+            <v>LL-20-3364</v>
           </cell>
           <cell r="G401" t="str">
-            <v>FlowArt: Mini, 6Pck #2</v>
+            <v>FlowArt: Mini, 3Pck - Retail #2</v>
           </cell>
         </row>
         <row r="402">
           <cell r="F402" t="str">
-            <v>LL-20-3301</v>
+            <v>LL-20-3495</v>
           </cell>
           <cell r="G402" t="str">
-            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places]</v>
+            <v>FlowArt: Mini, 3Pck [Petals + NW + FF] - Retail</v>
           </cell>
         </row>
         <row r="403">
           <cell r="F403" t="str">
-            <v>LL-20-3302</v>
+            <v>LL-20-3208</v>
           </cell>
           <cell r="G403" t="str">
-            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity]</v>
+            <v>FlowArt: Mini, 3Pck #1 [Magic + Pretty P + Nature W]</v>
           </cell>
         </row>
         <row r="404">
           <cell r="F404" t="str">
-            <v>LL-20-3293</v>
+            <v>LL-20-3209</v>
           </cell>
           <cell r="G404" t="str">
-            <v>FlowArt: Mini Single - Costal Calm</v>
+            <v>FlowArt: Mini, 3Pck #2 [Pocket P + Café + Furry F]</v>
           </cell>
         </row>
         <row r="405">
           <cell r="F405" t="str">
-            <v>LL-20-3295</v>
+            <v>LL-20-3229</v>
           </cell>
           <cell r="G405" t="str">
-            <v>FlowArt: Mini Single - Cottage Garden</v>
+            <v>FlowArt: Mini Single - Enchanted Magic</v>
           </cell>
         </row>
         <row r="406">
           <cell r="F406" t="str">
-            <v>LL-20-3297</v>
+            <v>LL-20-3230</v>
           </cell>
           <cell r="G406" t="str">
-            <v>FlowArt: Mini Single - Postcard Places</v>
+            <v>FlowArt: Mini Single - Pretty Petals</v>
           </cell>
         </row>
         <row r="407">
           <cell r="F407" t="str">
-            <v>LL-20-3294</v>
+            <v>LL-20-3231</v>
           </cell>
           <cell r="G407" t="str">
-            <v>FlowArt: Mini Single - Into the Wild</v>
+            <v>FlowArt: Mini Single - Nature's Wonders</v>
           </cell>
         </row>
         <row r="408">
           <cell r="F408" t="str">
-            <v>LL-20-3296</v>
+            <v>LL-20-3227</v>
           </cell>
           <cell r="G408" t="str">
-            <v>FlowArt: Mini Single - Plant Paradise</v>
+            <v>FlowArt: Mini Single - Pocket Positivity</v>
           </cell>
         </row>
         <row r="409">
           <cell r="F409" t="str">
-            <v>LL-20-3298</v>
+            <v>LL-20-3228</v>
           </cell>
           <cell r="G409" t="str">
-            <v>FlowArt: Mini Single - Small Town Serenity</v>
+            <v>FlowArt: Mini Single - Café Comforts</v>
           </cell>
         </row>
         <row r="410">
           <cell r="F410" t="str">
-            <v>LL-20-3303</v>
+            <v>LL-20-3232</v>
           </cell>
           <cell r="G410" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #1</v>
+            <v>FlowArt: Mini Single - Furry Friends</v>
           </cell>
         </row>
         <row r="411">
           <cell r="F411" t="str">
-            <v>LL-20-3377</v>
+            <v>LL-20-3312</v>
           </cell>
           <cell r="G411" t="str">
-            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
+            <v>FlowArt: Mini, 6Pck #2</v>
           </cell>
         </row>
         <row r="412">
           <cell r="F412" t="str">
-            <v>LL-20-3250</v>
+            <v>LL-20-3494</v>
           </cell>
           <cell r="G412" t="str">
-            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
+            <v>FlowArt: Mini, 3Pck [Calm + Cottage + Paradise] - Retail</v>
           </cell>
         </row>
         <row r="413">
           <cell r="F413" t="str">
-            <v>LL-20-3251</v>
+            <v>LL-20-3301</v>
           </cell>
           <cell r="G413" t="str">
-            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
+            <v>FlowArt: Mini, 3Pck #3 [Calm + Garden + Places] - ECOMM</v>
           </cell>
         </row>
         <row r="414">
           <cell r="F414" t="str">
-            <v>LL-20-3255</v>
+            <v>LL-20-3302</v>
           </cell>
           <cell r="G414" t="str">
-            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
+            <v>FlowArt: Mini, 3Pck #4 [Wild + Plant + Serenity] - ECOMM</v>
           </cell>
         </row>
         <row r="415">
           <cell r="F415" t="str">
-            <v>LL-20-3408</v>
+            <v>LL-20-3293</v>
           </cell>
           <cell r="G415" t="str">
-            <v>FlowArt: Mini Single - Berry Bliss</v>
+            <v>FlowArt: Mini Single - Costal Calm</v>
           </cell>
         </row>
         <row r="416">
           <cell r="F416" t="str">
-            <v>LL-20-3409</v>
+            <v>LL-20-3295</v>
           </cell>
           <cell r="G416" t="str">
-            <v>FlowArt: Mini Single - Hummingbird Haven</v>
+            <v>FlowArt: Mini Single - Cottage Garden</v>
           </cell>
         </row>
         <row r="417">
           <cell r="F417" t="str">
-            <v>LL-20-3410</v>
+            <v>LL-20-3297</v>
           </cell>
           <cell r="G417" t="str">
-            <v>FlowArt: Mini Single - Wildflower Woods</v>
+            <v>FlowArt: Mini Single - Postcard Places</v>
           </cell>
         </row>
         <row r="418">
           <cell r="F418" t="str">
-            <v>LL-20-3412</v>
+            <v>LL-20-3294</v>
           </cell>
           <cell r="G418" t="str">
-            <v>FlowArt: Mini Single - Coastal Calm</v>
+            <v>FlowArt: Mini Single - Into the Wild</v>
           </cell>
         </row>
         <row r="419">
           <cell r="F419" t="str">
-            <v>LL-20-3413</v>
+            <v>LL-20-3296</v>
           </cell>
           <cell r="G419" t="str">
-            <v>FlowArt: Mini Single - Sweet Summer</v>
+            <v>FlowArt: Mini Single - Plant Paradise</v>
           </cell>
         </row>
         <row r="420">
           <cell r="F420" t="str">
-            <v>LL-20-3414</v>
+            <v>LL-20-3298</v>
           </cell>
           <cell r="G420" t="str">
-            <v>FlowArt: Mini Single - Under the Sea</v>
+            <v>FlowArt: Mini Single - Small Town Serenity</v>
           </cell>
         </row>
         <row r="421">
           <cell r="F421" t="str">
-            <v>LL-20-3415</v>
+            <v>LL-20-3303</v>
           </cell>
           <cell r="G421" t="str">
-            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
+            <v>FlowArt: Mini, Holiday 3Pck #1</v>
           </cell>
         </row>
         <row r="422">
           <cell r="F422" t="str">
-            <v>LL-20-3434</v>
+            <v>LL-20-3377</v>
           </cell>
           <cell r="G422" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Botanical Bouquet]</v>
+            <v>FlowArt: Holiday Mini, 3Pck - Retail #1</v>
           </cell>
         </row>
         <row r="423">
           <cell r="F423" t="str">
-            <v>LL-20-3435</v>
+            <v>LL-20-3250</v>
           </cell>
           <cell r="G423" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Birds &amp; Branches]</v>
+            <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
           </cell>
         </row>
         <row r="424">
           <cell r="F424" t="str">
-            <v>LL-20-3436</v>
+            <v>LL-20-3251</v>
           </cell>
           <cell r="G424" t="str">
-            <v>FlowArt Mini Stitch-by-X: [Spring Landscape]</v>
+            <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
           </cell>
         </row>
         <row r="425">
           <cell r="F425" t="str">
-            <v>LL-98-3444</v>
+            <v>LL-20-3255</v>
           </cell>
           <cell r="G425" t="str">
-            <v>FlowArt Mini - Pocket Positivity - 3Pck</v>
+            <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
           </cell>
         </row>
         <row r="426">
           <cell r="F426" t="str">
-            <v>LL-98-3445</v>
+            <v>LL-20-3408</v>
           </cell>
           <cell r="G426" t="str">
-            <v>FlowArt Mini - Café Comforts - 3Pck</v>
+            <v>FlowArt: Mini Single - Berry Bliss</v>
           </cell>
         </row>
         <row r="427">
           <cell r="F427" t="str">
-            <v>LL-98-3446</v>
+            <v>LL-20-3409</v>
           </cell>
           <cell r="G427" t="str">
-            <v>FlowArt Mini - Enchanted Magic - 3Pck</v>
+            <v>FlowArt: Mini Single - Hummingbird Haven</v>
           </cell>
         </row>
         <row r="428">
           <cell r="F428" t="str">
-            <v>LL-30-3324</v>
+            <v>LL-20-3410</v>
           </cell>
           <cell r="G428" t="str">
-            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
+            <v>FlowArt: Mini Single - Wildflower Woods</v>
           </cell>
         </row>
         <row r="429">
           <cell r="F429" t="str">
-            <v>LL-30-3325</v>
+            <v>LL-20-3412</v>
           </cell>
           <cell r="G429" t="str">
-            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
+            <v>FlowArt: Mini Single - Coastal Calm [HOLD]</v>
           </cell>
         </row>
         <row r="430">
           <cell r="F430" t="str">
-            <v>LL-30-3326</v>
+            <v>LL-20-3413</v>
           </cell>
           <cell r="G430" t="str">
-            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
+            <v>FlowArt: Mini Single - Sweet Summer [HOLD]</v>
           </cell>
         </row>
         <row r="431">
           <cell r="F431" t="str">
-            <v>LL-30-3327</v>
+            <v>LL-20-3414</v>
           </cell>
           <cell r="G431" t="str">
-            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
+            <v>FlowArt: Mini Single - Under the Sea [HOLD]</v>
           </cell>
         </row>
         <row r="432">
           <cell r="F432" t="str">
-            <v>LL-30-3328</v>
+            <v>LL-20-3415</v>
           </cell>
           <cell r="G432" t="str">
-            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
+            <v>FlowArt: Mini Single - Slow Summers [WF Exclusive]</v>
           </cell>
         </row>
         <row r="433">
           <cell r="F433" t="str">
-            <v>LL-30-3333</v>
+            <v>LL-20-3490</v>
           </cell>
           <cell r="G433" t="str">
-            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
+            <v>FlowArt Mini Cross-Stitch-by-Number: [Botanical + Birds + Spring] - Retail</v>
           </cell>
         </row>
         <row r="434">
           <cell r="F434" t="str">
-            <v>LL-30-3354</v>
+            <v>LL-20-3491</v>
           </cell>
           <cell r="G434" t="str">
-            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
+            <v>FlowArt Mini Cross-Stitch-by-Number: [Botanical + Birds + Spring] - ECOMM</v>
           </cell>
         </row>
         <row r="435">
           <cell r="F435" t="str">
-            <v>LL-30-3355</v>
+            <v>LL-20-3434</v>
           </cell>
           <cell r="G435" t="str">
-            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
+            <v>FlowArt Mini Cross-Stitch-by-Number: [Botanical Bouquet]</v>
           </cell>
         </row>
         <row r="436">
           <cell r="F436" t="str">
-            <v>LL-30-3356</v>
+            <v>LL-20-3435</v>
           </cell>
           <cell r="G436" t="str">
-            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
+            <v>FlowArt Mini Cross-Stitch-by-Number: [Birds &amp; Branches]</v>
           </cell>
         </row>
         <row r="437">
           <cell r="F437" t="str">
-            <v>LL-30-3357</v>
+            <v>LL-20-3436</v>
           </cell>
           <cell r="G437" t="str">
-            <v>FlowArt Mini EXPRESS, #10</v>
+            <v>FlowArt Mini Cross-Stitch-by-Number: [Spring Landscape]</v>
           </cell>
         </row>
         <row r="438">
           <cell r="F438" t="str">
-            <v>LL-30-3358</v>
+            <v>LL-98-3444</v>
           </cell>
           <cell r="G438" t="str">
-            <v>FlowArt Mini EXPRESS, #11</v>
+            <v>FlowArt Mini - Pocket Positivity - 3Pck</v>
           </cell>
         </row>
         <row r="439">
           <cell r="F439" t="str">
-            <v>LL-30-3359</v>
+            <v>LL-98-3445</v>
           </cell>
           <cell r="G439" t="str">
-            <v>FlowArt Mini EXPRESS, #12</v>
+            <v>FlowArt Mini - Café Comforts - 3Pck</v>
           </cell>
         </row>
         <row r="440">
           <cell r="F440" t="str">
-            <v>LL-30-3360</v>
+            <v>LL-98-3446</v>
           </cell>
           <cell r="G440" t="str">
-            <v>FlowArt Mini EXPRESS, #13</v>
+            <v>FlowArt Mini - Enchanted Magic - 3Pck</v>
           </cell>
         </row>
         <row r="441">
           <cell r="F441" t="str">
-            <v>LL-30-3361</v>
+            <v>LL-30-3324</v>
           </cell>
           <cell r="G441" t="str">
-            <v>FlowArt Mini EXPRESS, #14</v>
+            <v>FlowArt Mini EXPRESS, #1 Paws and Purs</v>
           </cell>
         </row>
         <row r="442">
           <cell r="F442" t="str">
-            <v>LL-30-3362</v>
+            <v>LL-30-3325</v>
           </cell>
           <cell r="G442" t="str">
-            <v>FlowArt Mini EXPRESS, #15</v>
+            <v>FlowArt Mini EXPRESS, #2 In Full Bloom</v>
           </cell>
         </row>
         <row r="443">
           <cell r="F443" t="str">
-            <v>LL-30-3405</v>
+            <v>LL-30-3326</v>
           </cell>
           <cell r="G443" t="str">
-            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
+            <v>FlowArt Mini EXPRESS, #3 Nature Walk</v>
           </cell>
         </row>
         <row r="444">
           <cell r="F444" t="str">
-            <v>LL-30-3406</v>
+            <v>LL-30-3327</v>
           </cell>
           <cell r="G444" t="str">
-            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
+            <v>FlowArt Mini EXPRESS, #4 Cozy comforts</v>
           </cell>
         </row>
         <row r="445">
           <cell r="F445" t="str">
-            <v>LL-30-3425</v>
+            <v>LL-30-3328</v>
           </cell>
           <cell r="G445" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Dream Spaces</v>
+            <v>FlowArt Mini EXPRESS, #5 Snow day</v>
           </cell>
         </row>
         <row r="446">
           <cell r="F446" t="str">
-            <v>LL-30-3426</v>
+            <v>LL-30-3333</v>
           </cell>
           <cell r="G446" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Vacay Mode</v>
+            <v>FlowArt Mini EXPRESS, #6 Merry Moments</v>
           </cell>
         </row>
         <row r="447">
           <cell r="F447" t="str">
-            <v>LL-30-3427</v>
+            <v>LL-30-3354</v>
           </cell>
           <cell r="G447" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - The Style Edit</v>
+            <v>FlowArt Mini EXPRESS, #7 Wings &amp; Wonder</v>
           </cell>
         </row>
         <row r="448">
           <cell r="F448" t="str">
-            <v>LL-30-3428</v>
+            <v>LL-30-3355</v>
           </cell>
           <cell r="G448" t="str">
-            <v>FlowArt Mini EXPRESS, Tween Collection - Berry Cute</v>
+            <v>FlowArt Mini EXPRESS, #8 On the Farm</v>
           </cell>
         </row>
         <row r="449">
           <cell r="F449" t="str">
-            <v>LL-30-3456</v>
+            <v>LL-30-3356</v>
           </cell>
           <cell r="G449" t="str">
-            <v>FlowArt Mini EXPRESS, Stitch-by-X [Botanicals]</v>
+            <v>FlowArt Mini EXPRESS, #9 Hometown Charm</v>
           </cell>
         </row>
         <row r="450">
           <cell r="F450" t="str">
-            <v>LL-30-3457</v>
+            <v>LL-30-3357</v>
           </cell>
           <cell r="G450" t="str">
-            <v>FlowArt Mini EXPRESS, Stitch-by-X [Cottage Core]</v>
+            <v>FlowArt Mini EXPRESS, #10</v>
           </cell>
         </row>
         <row r="451">
           <cell r="F451" t="str">
-            <v>LL-30-3458</v>
+            <v>LL-30-3358</v>
           </cell>
           <cell r="G451" t="str">
-            <v>FlowArt Mini EXPRESS, Stitch-by-X [Cozy Living]</v>
+            <v>FlowArt Mini EXPRESS, #11</v>
           </cell>
         </row>
         <row r="452">
           <cell r="F452" t="str">
-            <v>LL-30-3459</v>
+            <v>LL-30-3359</v>
           </cell>
           <cell r="G452" t="str">
-            <v>FlowArt Mini EXPRESS, Stitch-by-X [Animals]</v>
+            <v>FlowArt Mini EXPRESS, #12</v>
           </cell>
         </row>
         <row r="453">
           <cell r="F453" t="str">
-            <v>LL-30-3460</v>
+            <v>LL-30-3360</v>
           </cell>
           <cell r="G453" t="str">
-            <v>FlowArt Mini EXPRESS, Spring Rain</v>
+            <v>FlowArt Mini EXPRESS, #13</v>
           </cell>
         </row>
         <row r="454">
           <cell r="F454" t="str">
-            <v>LL-30-3461</v>
+            <v>LL-30-3361</v>
           </cell>
           <cell r="G454" t="str">
-            <v>FlowArt Mini EXPRESS, Blossom Market</v>
+            <v>FlowArt Mini EXPRESS, #14</v>
           </cell>
         </row>
         <row r="455">
           <cell r="F455" t="str">
-            <v>LL-30-3462</v>
+            <v>LL-30-3362</v>
           </cell>
           <cell r="G455" t="str">
-            <v>FlowArt Mini EXPRESS, Baby Animals</v>
+            <v>FlowArt Mini EXPRESS, #15</v>
           </cell>
         </row>
         <row r="456">
-          <cell r="F456">
-            <v>167001</v>
+          <cell r="F456" t="str">
+            <v>LL-30-3405</v>
           </cell>
           <cell r="G456" t="str">
-            <v>FlowCrafts: Paper Flower Bouquet</v>
+            <v>FlowArt Mini EXPRESS, Sweet Escapes</v>
           </cell>
         </row>
         <row r="457">
-          <cell r="F457">
-            <v>167002</v>
+          <cell r="F457" t="str">
+            <v>LL-30-3406</v>
           </cell>
           <cell r="G457" t="str">
-            <v>FlowCrafts: Collage Art</v>
+            <v>FlowArt Mini EXPRESS, Pretty Petals</v>
           </cell>
         </row>
         <row r="458">
-          <cell r="F458">
-            <v>167004</v>
+          <cell r="F458" t="str">
+            <v>LL-30-3425</v>
           </cell>
           <cell r="G458" t="str">
-            <v>FlowCrafts: Layered Wooden Wall Art</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Dream Spaces</v>
           </cell>
         </row>
         <row r="459">
-          <cell r="F459">
-            <v>167005</v>
+          <cell r="F459" t="str">
+            <v>LL-30-3426</v>
           </cell>
           <cell r="G459" t="str">
-            <v>FlowCrafts: Cord-Wrapped Planters</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Vacay Mode</v>
           </cell>
         </row>
         <row r="460">
-          <cell r="F460">
-            <v>167006</v>
+          <cell r="F460" t="str">
+            <v>LL-30-3427</v>
           </cell>
           <cell r="G460" t="str">
-            <v>FlowCrafts: Decorative Tile Lamp</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - The Style Edit</v>
           </cell>
         </row>
         <row r="461">
           <cell r="F461" t="str">
-            <v>LL-98-3188</v>
+            <v>LL-30-3428</v>
           </cell>
           <cell r="G461" t="str">
-            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Tween Collection - Berry Cute</v>
           </cell>
         </row>
         <row r="462">
           <cell r="F462" t="str">
-            <v>LL-98-3189</v>
+            <v>LL-30-3456</v>
           </cell>
           <cell r="G462" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Cross-Stitch-by-Number [Botanicals]</v>
           </cell>
         </row>
         <row r="463">
           <cell r="F463" t="str">
-            <v>LL-98-3190</v>
+            <v>LL-30-3457</v>
           </cell>
           <cell r="G463" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Cross-Stitch-by-Number [Cottage Core]</v>
           </cell>
         </row>
         <row r="464">
           <cell r="F464" t="str">
-            <v>LL-98-3191</v>
+            <v>LL-30-3458</v>
           </cell>
           <cell r="G464" t="str">
-            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
+            <v>FlowArt Mini EXPRESS, Cross-Stitch-by-Number [Cozy Living]</v>
           </cell>
         </row>
         <row r="465">
           <cell r="F465" t="str">
-            <v>LL-98-3025</v>
+            <v>LL-30-3459</v>
           </cell>
           <cell r="G465" t="str">
-            <v>FlowArt 2PK - UV (165009+165006)</v>
+            <v>FlowArt Mini EXPRESS, Cross-Stitch-by-Number [Animals]</v>
           </cell>
         </row>
         <row r="466">
           <cell r="F466" t="str">
-            <v>LL-98-3026</v>
+            <v>LL-30-3460</v>
           </cell>
           <cell r="G466" t="str">
-            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
+            <v>FlowArt Mini EXPRESS, Spring Rain</v>
           </cell>
         </row>
         <row r="467">
           <cell r="F467" t="str">
-            <v>LL-98-3027</v>
+            <v>LL-30-3461</v>
           </cell>
           <cell r="G467" t="str">
-            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
+            <v>FlowArt Mini EXPRESS, Blossom Market</v>
           </cell>
         </row>
         <row r="468">
           <cell r="F468" t="str">
-            <v>LL-98-3028</v>
+            <v>LL-30-3462</v>
           </cell>
           <cell r="G468" t="str">
-            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
+            <v>FlowArt Mini EXPRESS, Baby Animals</v>
           </cell>
         </row>
         <row r="469">
-          <cell r="F469" t="str">
-            <v>LL-98-3091</v>
+          <cell r="F469">
+            <v>167001</v>
           </cell>
           <cell r="G469" t="str">
-            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
+            <v>FlowCrafts: Paper Flower Bouquet</v>
           </cell>
         </row>
         <row r="470">
-          <cell r="F470" t="str">
-            <v>LL-98-3168</v>
+          <cell r="F470">
+            <v>167002</v>
           </cell>
           <cell r="G470" t="str">
-            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
+            <v>FlowCrafts: Collage Art</v>
           </cell>
         </row>
         <row r="471">
-          <cell r="F471" t="str">
-            <v>LL-98-3169</v>
+          <cell r="F471">
+            <v>167004</v>
           </cell>
           <cell r="G471" t="str">
-            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
+            <v>FlowCrafts: Layered Wooden Wall Art</v>
           </cell>
         </row>
         <row r="472">
-          <cell r="F472" t="str">
-            <v>LL-98-3170</v>
+          <cell r="F472">
+            <v>167005</v>
           </cell>
           <cell r="G472" t="str">
-            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
+            <v>FlowCrafts: Cord-Wrapped Planters</v>
           </cell>
         </row>
         <row r="473">
-          <cell r="F473" t="str">
-            <v>LL-98-3307</v>
+          <cell r="F473">
+            <v>167006</v>
           </cell>
           <cell r="G473" t="str">
-            <v>FlowArt 3Pck - Fall DbL [3248 + 3158 + 3157]</v>
+            <v>FlowCrafts: Decorative Tile Lamp</v>
           </cell>
         </row>
         <row r="474">
           <cell r="F474" t="str">
-            <v>LL-98-3321</v>
+            <v>LL-98-3188</v>
           </cell>
           <cell r="G474" t="str">
-            <v>FlowArt 3Pck - Fall Mixed Mode [3248 + 3290 + 3247]</v>
+            <v>FlowArt 2PK - I&amp;C (165009+165006) - with BPAD</v>
           </cell>
         </row>
         <row r="475">
           <cell r="F475" t="str">
-            <v>LL-98-3308</v>
+            <v>LL-98-3189</v>
           </cell>
           <cell r="G475" t="str">
-            <v>FlowArt 3Pck - Winter DbL [3244 + 3245 + 3162]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008) - with BPAD</v>
           </cell>
         </row>
         <row r="476">
           <cell r="F476" t="str">
-            <v>LL-98-3309</v>
+            <v>LL-98-3190</v>
           </cell>
           <cell r="G476" t="str">
-            <v>FlowArt 3Pck - Winter Mixed [3368 + 3367 + 3246]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007) - with BPAD</v>
           </cell>
         </row>
         <row r="477">
           <cell r="F477" t="str">
-            <v>LL-98-3386</v>
+            <v>LL-98-3191</v>
           </cell>
           <cell r="G477" t="str">
-            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
+            <v>FlowArt 2PK - SbS &amp; Pattern (165014+165012) - with BPAD</v>
           </cell>
         </row>
         <row r="478">
           <cell r="F478" t="str">
-            <v>LL-98-3029</v>
+            <v>LL-98-3025</v>
           </cell>
           <cell r="G478" t="str">
-            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
+            <v>FlowArt 2PK - UV (165009+165006)</v>
           </cell>
         </row>
         <row r="479">
           <cell r="F479" t="str">
-            <v>LL-98-3030</v>
+            <v>LL-98-3026</v>
           </cell>
           <cell r="G479" t="str">
-            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
+            <v>FlowArt 2PK - Dot Art (165005+165008)</v>
           </cell>
         </row>
         <row r="480">
           <cell r="F480" t="str">
-            <v>LL-98-3031</v>
+            <v>LL-98-3027</v>
           </cell>
           <cell r="G480" t="str">
-            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
+            <v>FlowArt 2PK - Pop &amp; Pogo (165001+165007)</v>
           </cell>
         </row>
         <row r="481">
           <cell r="F481" t="str">
-            <v>LL-98-3217</v>
+            <v>LL-98-3028</v>
           </cell>
           <cell r="G481" t="str">
-            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
+            <v>FlowArt 2PK - SBS &amp; HP (165014+165012)</v>
           </cell>
         </row>
         <row r="482">
           <cell r="F482" t="str">
-            <v>LL-98-3218</v>
+            <v>LL-98-3091</v>
           </cell>
           <cell r="G482" t="str">
-            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
+            <v>FlowArt 2PK - Dot Art 2 (165001+165005)</v>
           </cell>
         </row>
         <row r="483">
           <cell r="F483" t="str">
-            <v>LL-98-3219</v>
+            <v>LL-98-3168</v>
           </cell>
           <cell r="G483" t="str">
-            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
+            <v>FlowArt 2PK - Dot-by-Letter [3157 + 3158] - Fall</v>
           </cell>
         </row>
         <row r="484">
           <cell r="F484" t="str">
-            <v>LL-98-3220</v>
+            <v>LL-98-3169</v>
           </cell>
           <cell r="G484" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>FlowArt 2PK - Pogo &amp; UV [3159 + 3160] - Fall</v>
           </cell>
         </row>
         <row r="485">
           <cell r="F485" t="str">
-            <v>LL-98-3314</v>
+            <v>LL-98-3170</v>
           </cell>
           <cell r="G485" t="str">
-            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
+            <v>FlowArt 2PK - DbL &amp; UV [3162 + 3163] - Winter</v>
           </cell>
         </row>
         <row r="486">
           <cell r="F486" t="str">
-            <v>LL-98-3315</v>
+            <v>LL-98-3386</v>
           </cell>
           <cell r="G486" t="str">
-            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
+            <v>FlowArt 2PK - Cozy &amp; Inspo [ 3149 + 3224 ]</v>
           </cell>
         </row>
         <row r="487">
           <cell r="F487" t="str">
-            <v>LL-98-3316</v>
+            <v>LL-98-3029</v>
           </cell>
           <cell r="G487" t="str">
-            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
+            <v>FlowArt 2PK - DbL &amp; SbS [ 3149 + 3150 ]</v>
           </cell>
         </row>
         <row r="488">
           <cell r="F488" t="str">
-            <v>LL-98-3317</v>
+            <v>LL-98-3030</v>
           </cell>
           <cell r="G488" t="str">
-            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
+            <v>FlowArt 2PK - DbL - Metallic ink [ 3148 + 3153 ]</v>
           </cell>
         </row>
         <row r="489">
           <cell r="F489" t="str">
-            <v>LL-98-3318</v>
+            <v>LL-98-3031</v>
           </cell>
           <cell r="G489" t="str">
-            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
+            <v>FlowArt 2PK - HP &amp; PD [ 3151 + 3152 ]</v>
           </cell>
         </row>
         <row r="490">
           <cell r="F490" t="str">
-            <v>LL-98-3319</v>
+            <v>LL-98-3217</v>
           </cell>
           <cell r="G490" t="str">
-            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
+            <v>FlowArt 2Pck: In the Groove [3200 + 3201]</v>
           </cell>
         </row>
         <row r="491">
           <cell r="F491" t="str">
-            <v>LL-98-3320</v>
+            <v>LL-98-3218</v>
           </cell>
           <cell r="G491" t="str">
-            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
+            <v>FlowArt 2Pck: TbLine [3222 + 3223]</v>
           </cell>
         </row>
         <row r="492">
           <cell r="F492" t="str">
-            <v>LL-98-3258</v>
+            <v>LL-98-3219</v>
           </cell>
           <cell r="G492" t="str">
-            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
+            <v>FlowArt 2Pck: Doodle Trace [3204 + 3205]</v>
           </cell>
         </row>
         <row r="493">
           <cell r="F493" t="str">
-            <v>LL-98-3289</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G493" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
         </row>
         <row r="494">
           <cell r="F494" t="str">
-            <v>LL-98-3259</v>
+            <v>LL-98-3307</v>
           </cell>
           <cell r="G494" t="str">
-            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
+            <v>FlowArt 3Pck: Fall DbL [3248 + 3158 + 3157]</v>
           </cell>
         </row>
         <row r="495">
           <cell r="F495" t="str">
-            <v>LL-98-3257</v>
+            <v>LL-98-3321</v>
           </cell>
           <cell r="G495" t="str">
-            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
+            <v>FlowArt 3Pck: Fall Mixed Mode [3248 + 3290 + 3247]</v>
           </cell>
         </row>
         <row r="496">
           <cell r="F496" t="str">
-            <v>LL-98-3310</v>
+            <v>LL-98-3308</v>
           </cell>
           <cell r="G496" t="str">
-            <v>FlowArt 3Pck: Metallic [3299 + 3300]</v>
+            <v>FlowArt 3Pck: Winter DbL [3244 + 3245 + 3162]</v>
           </cell>
         </row>
         <row r="497">
           <cell r="F497" t="str">
-            <v>LL-98-3399</v>
+            <v>LL-98-3309</v>
           </cell>
           <cell r="G497" t="str">
-            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
+            <v>FlowArt 3Pck: Winter Mixed [3368 + 3367 + 3246]</v>
           </cell>
         </row>
         <row r="498">
           <cell r="F498" t="str">
-            <v>LL-98-3400</v>
+            <v>LL-98-3464</v>
           </cell>
           <cell r="G498" t="str">
-            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
+            <v>FlowArt 3Pck: Winter Cozy [3342 + 3343 + 3344]</v>
           </cell>
         </row>
         <row r="499">
           <cell r="F499" t="str">
-            <v>LL-98-3401</v>
+            <v>LL-98-3314</v>
           </cell>
           <cell r="G499" t="str">
-            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
+            <v>FlowArt 3Pck: DbL Classic [5005 + 5008 +3149]</v>
           </cell>
         </row>
         <row r="500">
           <cell r="F500" t="str">
-            <v>LL-98-3402</v>
+            <v>LL-98-3315</v>
           </cell>
           <cell r="G500" t="str">
-            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
+            <v>FlowArt 3Pck: Deep + Sgarden + Jungle [3153 + 3150 +3200]</v>
           </cell>
         </row>
         <row r="501">
           <cell r="F501" t="str">
-            <v>LL-98-3403</v>
+            <v>LL-98-3316</v>
           </cell>
           <cell r="G501" t="str">
-            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
+            <v>FlowArt 3Pck: Galaxy + TPara + Animals [3148 + 3222 + 5012]</v>
           </cell>
         </row>
         <row r="502">
           <cell r="F502" t="str">
-            <v>LL-98-3404</v>
+            <v>LL-98-3317</v>
           </cell>
           <cell r="G502" t="str">
-            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
+            <v>FlowArt 3Pck: TbLine Classic [3222 + 3223 + 3249]</v>
           </cell>
         </row>
         <row r="503">
           <cell r="F503" t="str">
-            <v>LL-98-3032</v>
+            <v>LL-98-3318</v>
           </cell>
           <cell r="G503" t="str">
-            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
+            <v>FlowArt 3Pck: PackBags + Wild + Foodie [3206 + 3204 + 3151]</v>
           </cell>
         </row>
         <row r="504">
           <cell r="F504" t="str">
-            <v>LL-98-3033</v>
+            <v>LL-98-3319</v>
           </cell>
           <cell r="G504" t="str">
-            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
+            <v>FlowArt 3Pck: Moonlit + Style + Cozy Cottage [3299 + 3205 + 3149]</v>
           </cell>
         </row>
         <row r="505">
           <cell r="F505" t="str">
-            <v>LL-98-3092</v>
+            <v>LL-98-3320</v>
           </cell>
           <cell r="G505" t="str">
-            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
+            <v>FlowArt 3Pck: MLand + Desert + Pause [3300 + 3201 +3207]</v>
           </cell>
         </row>
         <row r="506">
           <cell r="F506" t="str">
-            <v>LL-25-3416</v>
+            <v>LL-98-3258</v>
           </cell>
           <cell r="G506" t="str">
-            <v>Scented Squishy Plush - Nightime</v>
+            <v>FlowArt 3Pck: Blooms + Coastline + Foodie [3202 + 3203 +3151]</v>
           </cell>
         </row>
         <row r="507">
           <cell r="F507" t="str">
-            <v>LL-25-3421</v>
+            <v>LL-98-3289</v>
           </cell>
           <cell r="G507" t="str">
-            <v>Scented Squishy Plush - Woodland</v>
+            <v>FlowArt 3Pck: Beach + Americana + Deep [3243 + 3154 + 3153] - TEMP</v>
           </cell>
         </row>
         <row r="508">
           <cell r="F508" t="str">
-            <v>LL-25-3417</v>
+            <v>LL-98-3259</v>
           </cell>
           <cell r="G508" t="str">
-            <v>Scented Squishy Non-Plush - #2</v>
+            <v>FlowArt 3Pck: Beach + Americana + W&amp;W  [3243 + 3154 + 3225 ]</v>
           </cell>
         </row>
         <row r="509">
           <cell r="F509" t="str">
-            <v>LL-11-1620</v>
+            <v>LL-98-3257</v>
           </cell>
           <cell r="G509" t="str">
-            <v>Visual Plug In Diffuser - SKU 1</v>
+            <v>FlowArt 3Pck: Brunch + Inspo + Frag Blooms [3249 + 3224 + 3203]</v>
           </cell>
         </row>
         <row r="510">
           <cell r="F510" t="str">
-            <v>LL-26-3005</v>
+            <v>LL-98-3310</v>
           </cell>
           <cell r="G510" t="str">
-            <v>Visual Plug In Diffuser - SKU 2</v>
+            <v>FlowArt 3Pck: Metallic [3299 + 3300 + 3148]</v>
           </cell>
         </row>
         <row r="511">
-          <cell r="F511">
-            <v>989514</v>
+          <cell r="F511" t="str">
+            <v>LL-98-3399</v>
           </cell>
           <cell r="G511" t="str">
-            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
+            <v>FlowArt 3Pck:  Secret Garden + Jungle Oasis + Into the Deep [Metallic ink] - TEMP</v>
           </cell>
         </row>
         <row r="512">
-          <cell r="F512">
-            <v>989525</v>
+          <cell r="F512" t="str">
+            <v>LL-98-3400</v>
           </cell>
           <cell r="G512" t="str">
-            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
+            <v>FlowArt 3Pck:  Tropical Paradise + Americana + Day at the Beach - TEMP</v>
           </cell>
         </row>
         <row r="513">
           <cell r="F513" t="str">
-            <v>11-2514-CP12</v>
+            <v>LL-98-3401</v>
           </cell>
           <cell r="G513" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
+            <v>FlowArt 3Pck:  Foodie Fun + Into the Galaxy (Metallic ink] + Tropical Paradise - TEMP</v>
           </cell>
         </row>
         <row r="514">
           <cell r="F514" t="str">
-            <v>11-2521-CP12</v>
+            <v>LL-98-3402</v>
           </cell>
           <cell r="G514" t="str">
-            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+            <v>FlowArt 3Pck:  Cozy Cottage + Landscapes + Botanicals - TEMP</v>
           </cell>
         </row>
         <row r="515">
           <cell r="F515" t="str">
-            <v>11-2506-CP12</v>
+            <v>LL-98-3403</v>
           </cell>
           <cell r="G515" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
+            <v>FlowArt 3Pck:  Everyday Inspiration + Style Your Space + Lovestruck - TEMP</v>
           </cell>
         </row>
         <row r="516">
           <cell r="F516" t="str">
-            <v>LL-99-3076</v>
+            <v>LL-98-3404</v>
           </cell>
           <cell r="G516" t="str">
-            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
+            <v>FlowArt 3Pck:  Americana + Pack Your Bags + Desert Dreams - TEMP</v>
           </cell>
         </row>
         <row r="517">
           <cell r="F517" t="str">
-            <v>LL-99-3077</v>
+            <v>LL-98-3032</v>
           </cell>
           <cell r="G517" t="str">
-            <v>Meijer Fast Track Display (Spring 2025)</v>
+            <v>FlowArt 4PK - Mix A (165009+165008+165001+165014)</v>
           </cell>
         </row>
         <row r="518">
           <cell r="F518" t="str">
-            <v>LL-99-3089</v>
+            <v>LL-98-3033</v>
           </cell>
           <cell r="G518" t="str">
-            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
+            <v>FlowArt 4PK - Mix B (165006+165005+165007+165012)</v>
           </cell>
         </row>
         <row r="519">
           <cell r="F519" t="str">
-            <v>LL-99-3090</v>
+            <v>LL-98-3092</v>
           </cell>
           <cell r="G519" t="str">
-            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
+            <v>FlowArt 4PK - Mix C (165001+165014+165012+165008)</v>
           </cell>
         </row>
         <row r="520">
           <cell r="F520" t="str">
-            <v>LL-14-3088</v>
+            <v>LL-25-3416</v>
           </cell>
           <cell r="G520" t="str">
-            <v>DIFFUSER, LED, Marble (HERBAL OIL)</v>
+            <v>Scented Palm Calms Plush - Sweet Dreams</v>
           </cell>
         </row>
         <row r="521">
           <cell r="F521" t="str">
-            <v>LL-12-3161</v>
+            <v>LL-25-3421</v>
           </cell>
           <cell r="G521" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
+            <v>Scented Palm Calms Plush - Woodland Retreat</v>
           </cell>
         </row>
         <row r="522">
           <cell r="F522" t="str">
-            <v>LL-12-3172</v>
+            <v>LL-25-3463</v>
           </cell>
           <cell r="G522" t="str">
-            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
+            <v>Scented Palm Calms Plush - Rest &amp; Restore</v>
           </cell>
         </row>
         <row r="523">
           <cell r="F523" t="str">
-            <v>LL-12-3196</v>
+            <v>LL-25-3417</v>
           </cell>
           <cell r="G523" t="str">
-            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
+            <v>Scented Palm Calms Non-Plush - #2</v>
           </cell>
         </row>
         <row r="524">
           <cell r="F524" t="str">
-            <v>LL-12-3197</v>
+            <v>LL-11-1620</v>
           </cell>
           <cell r="G524" t="str">
-            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
+            <v>Visual Plug In Diffuser - SKU 1</v>
           </cell>
         </row>
         <row r="525">
           <cell r="F525" t="str">
-            <v>LL-12-3215</v>
+            <v>LL-26-3005</v>
           </cell>
           <cell r="G525" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
+            <v>Visual Plug In Diffuser - SKU 2</v>
           </cell>
         </row>
         <row r="526">
-          <cell r="F526" t="str">
-            <v>LL-12-3216</v>
+          <cell r="F526">
+            <v>989514</v>
           </cell>
           <cell r="G526" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
+            <v>Pencil 10pk + In Bloom Pen Diffuser Bundle</v>
           </cell>
         </row>
         <row r="527">
-          <cell r="F527" t="str">
-            <v>LL-12-3330</v>
+          <cell r="F527">
+            <v>989525</v>
           </cell>
           <cell r="G527" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #1</v>
+            <v>Lifelines Ocean Journal &amp; In Bloom Pen Diffuser</v>
           </cell>
         </row>
         <row r="528">
           <cell r="F528" t="str">
-            <v>LL-12-3331</v>
+            <v>11-2514-CP12</v>
           </cell>
           <cell r="G528" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #2</v>
+            <v>Pen Diffuser with Essential Oil Blends - Herbal Garden</v>
           </cell>
         </row>
         <row r="529">
           <cell r="F529" t="str">
-            <v>LL-12-3332</v>
+            <v>11-2521-CP12</v>
           </cell>
           <cell r="G529" t="str">
-            <v>Writing Bundle [2x Lava Pen / Patch ] - #3</v>
+            <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
           </cell>
         </row>
         <row r="530">
           <cell r="F530" t="str">
-            <v>LL-98-3221</v>
+            <v>11-2506-CP12</v>
           </cell>
           <cell r="G530" t="str">
-            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 20-pack (Classic)</v>
           </cell>
         </row>
         <row r="531">
           <cell r="F531" t="str">
-            <v>LL-20-3329</v>
+            <v>LL-99-3076</v>
           </cell>
           <cell r="G531" t="str">
-            <v>Lifelines Digital Detox Kit - 2026</v>
+            <v>Target Writing Sidecap Shipper (Spring 2025)</v>
           </cell>
         </row>
         <row r="532">
           <cell r="F532" t="str">
-            <v>LL-12-3212</v>
+            <v>LL-99-3077</v>
           </cell>
           <cell r="G532" t="str">
-            <v>Scented Sticky Notes</v>
+            <v>Meijer Fast Track Display (Spring 2025)</v>
           </cell>
         </row>
         <row r="533">
           <cell r="F533" t="str">
-            <v>LL-98-3167</v>
+            <v>LL-99-3089</v>
           </cell>
           <cell r="G533" t="str">
-            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
+            <v>20 Pack Pencil Tray PDQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="534">
           <cell r="F534" t="str">
-            <v>LL-99-3111</v>
+            <v>LL-99-3090</v>
           </cell>
           <cell r="G534" t="str">
-            <v>Meijer Highlighter Display Tray (Filled)</v>
+            <v>Universal Pen/Pencil PGQ (Empty tray in box)</v>
           </cell>
         </row>
         <row r="535">
           <cell r="F535" t="str">
-            <v>LL-99-3112</v>
+            <v>LL-14-3088</v>
           </cell>
           <cell r="G535" t="str">
-            <v>Meijer Lava Pen Display Tray (Filled)</v>
+            <v>DIFFUSER, LED, Marble (HERBAL OIL)</v>
           </cell>
         </row>
         <row r="536">
           <cell r="F536" t="str">
-            <v>LL-99-3113</v>
+            <v>LL-12-3161</v>
           </cell>
           <cell r="G536" t="str">
-            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Blue</v>
           </cell>
         </row>
         <row r="537">
           <cell r="F537" t="str">
-            <v>LL-99-3114</v>
+            <v>LL-12-3172</v>
           </cell>
           <cell r="G537" t="str">
-            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
+            <v>Writing Bundle [2x Lava Pen / Maze /  Highlighter] - Dusty Pink</v>
           </cell>
         </row>
         <row r="538">
           <cell r="F538" t="str">
-            <v>LL-98-3119</v>
+            <v>LL-12-3196</v>
           </cell>
           <cell r="G538" t="str">
-            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
+            <v>Writing Bundle [2x Lava Pen / Papaya /  Highlighter]</v>
           </cell>
         </row>
         <row r="539">
           <cell r="F539" t="str">
-            <v>LL-12-3132</v>
+            <v>LL-12-3197</v>
           </cell>
           <cell r="G539" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Gumball /  Highlighter]</v>
           </cell>
         </row>
         <row r="540">
           <cell r="F540" t="str">
-            <v>LL-12-3132-V2</v>
+            <v>LL-12-3215</v>
           </cell>
           <cell r="G540" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Cozy Thoughts</v>
           </cell>
         </row>
         <row r="541">
           <cell r="F541" t="str">
-            <v>LL-12-3133</v>
+            <v>LL-12-3216</v>
           </cell>
           <cell r="G541" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch /  Highlighter] - Express Yourself</v>
           </cell>
         </row>
         <row r="542">
           <cell r="F542" t="str">
-            <v>LL-12-3136</v>
+            <v>LL-12-3330</v>
           </cell>
           <cell r="G542" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - Flowers</v>
           </cell>
         </row>
         <row r="543">
           <cell r="F543" t="str">
-            <v>LL-12-3137</v>
+            <v>LL-12-3331</v>
           </cell>
           <cell r="G543" t="str">
-            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - Stacking Stones</v>
           </cell>
         </row>
         <row r="544">
           <cell r="F544" t="str">
-            <v>LL-12-3138</v>
+            <v>LL-12-3332</v>
           </cell>
           <cell r="G544" t="str">
-            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
+            <v>Writing Bundle [2x Lava Pen / Patch ] - Quilts</v>
           </cell>
         </row>
         <row r="545">
           <cell r="F545" t="str">
-            <v>LL-12-3139</v>
+            <v>LL-12-3479</v>
           </cell>
           <cell r="G545" t="str">
-            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set</v>
           </cell>
         </row>
         <row r="546">
           <cell r="F546" t="str">
-            <v>LL-16-3193</v>
+            <v>LL-98-3221</v>
           </cell>
           <cell r="G546" t="str">
-            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
+            <v>Bead Journal Bundle - Papaya &amp; Gumball - AMZ</v>
           </cell>
         </row>
         <row r="547">
           <cell r="F547" t="str">
-            <v>LL-16-3140</v>
+            <v>LL-20-3329</v>
           </cell>
           <cell r="G547" t="str">
-            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
+            <v>Lifelines Digital Detox Kit - 2026</v>
           </cell>
         </row>
         <row r="548">
           <cell r="F548" t="str">
-            <v>LL-16-3141</v>
+            <v>LL-20-3492</v>
           </cell>
           <cell r="G548" t="str">
-            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
+            <v>Lifelines Digital Detox Kit - 2026 - OP</v>
           </cell>
         </row>
         <row r="549">
           <cell r="F549" t="str">
-            <v>LL-14-3144</v>
+            <v>LL-12-3212</v>
           </cell>
           <cell r="G549" t="str">
-            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
+            <v>Scented Sticky Notes</v>
           </cell>
         </row>
         <row r="550">
           <cell r="F550" t="str">
-            <v>LL-14-3146</v>
+            <v>LL-98-3167</v>
           </cell>
           <cell r="G550" t="str">
-            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
+            <v>Tracing Art Pads (2) with Colored Pencils (14)</v>
           </cell>
         </row>
         <row r="551">
           <cell r="F551" t="str">
-            <v>LL-16-3261</v>
+            <v>LL-99-3111</v>
           </cell>
           <cell r="G551" t="str">
-            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
+            <v>Meijer Highlighter Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="552">
           <cell r="F552" t="str">
-            <v>LL-16-3281</v>
+            <v>LL-99-3112</v>
           </cell>
           <cell r="G552" t="str">
-            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
+            <v>Meijer Lava Pen Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="553">
           <cell r="F553" t="str">
-            <v>LL-16-3263</v>
+            <v>LL-99-3113</v>
           </cell>
           <cell r="G553" t="str">
-            <v>FlowArt: Trace-by-Line: Gingerbread Delight - WMT</v>
+            <v>Meijer 10PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="554">
           <cell r="F554" t="str">
-            <v>LL-16-3383</v>
+            <v>LL-99-3114</v>
           </cell>
           <cell r="G554" t="str">
-            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
+            <v>Meijer 20PK Colored Pencil Display Tray (Filled)</v>
           </cell>
         </row>
         <row r="555">
           <cell r="F555" t="str">
-            <v>LL-16-3266</v>
+            <v>LL-98-3119</v>
           </cell>
           <cell r="G555" t="str">
-            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
+            <v xml:space="preserve">2025 Writing Sidecap Shipper (Filled) </v>
           </cell>
         </row>
         <row r="556">
           <cell r="F556" t="str">
-            <v>LL-99-3370</v>
+            <v>LL-98-3465</v>
           </cell>
           <cell r="G556" t="str">
-            <v>FlowArt Minis: PDQ - WMT</v>
+            <v>Everyday Calm - Cottage Vibes - Name TBD</v>
           </cell>
         </row>
         <row r="557">
           <cell r="F557" t="str">
-            <v>LL-30-3380</v>
+            <v>LL-98-3466</v>
           </cell>
           <cell r="G557" t="str">
-            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
+            <v>Everyday Calm - Animal Lover - Name TBD</v>
           </cell>
         </row>
         <row r="558">
           <cell r="F558" t="str">
-            <v>LL-30-3381</v>
+            <v>LL-98-3467</v>
           </cell>
           <cell r="G558" t="str">
-            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
+            <v>Everyday Calm - Get Out of the Cold - Name TBD</v>
           </cell>
         </row>
         <row r="559">
           <cell r="F559" t="str">
-            <v>LL-30-3382</v>
+            <v>LL-98-3468</v>
           </cell>
           <cell r="G559" t="str">
-            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
+            <v>Mini to the Max - Name TBD</v>
           </cell>
         </row>
         <row r="560">
           <cell r="F560" t="str">
-            <v>LL-12-3271</v>
+            <v>LL-98-3469</v>
           </cell>
           <cell r="G560" t="str">
-            <v>Scented Glitter Pen 3-Pack - WMT</v>
+            <v>Calm Plus - Flower Lover - Name TBD</v>
           </cell>
         </row>
         <row r="561">
           <cell r="F561" t="str">
-            <v>LL-12-3272</v>
+            <v>LL-98-3470</v>
           </cell>
           <cell r="G561" t="str">
-            <v>Scented Lava Pen 3-Pack - WMT</v>
+            <v>Calm Plus - Natures Wonder - Name TBD</v>
           </cell>
         </row>
         <row r="562">
           <cell r="F562" t="str">
-            <v>LL-12-3273</v>
+            <v>LL-98-3471</v>
           </cell>
           <cell r="G562" t="str">
-            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
+            <v>Calm Plus - Holiday - Name TBD</v>
           </cell>
         </row>
         <row r="563">
           <cell r="F563" t="str">
-            <v>LL-12-3274</v>
+            <v>LL-98-3472</v>
           </cell>
           <cell r="G563" t="str">
-            <v>Scented Marker 10-Pack - WMT</v>
+            <v>Calm Plus - Moments of Calm - Name TBD</v>
           </cell>
         </row>
         <row r="564">
           <cell r="F564" t="str">
-            <v>LL-25-3275</v>
+            <v>LL-98-3473</v>
           </cell>
           <cell r="G564" t="str">
-            <v>Scented Squishy 1 - Zen Garden - WMT</v>
+            <v>Calm Ultra - Nature - Name TBD</v>
           </cell>
         </row>
         <row r="565">
           <cell r="F565" t="str">
-            <v>LL-25-3276</v>
+            <v>LL-98-3474</v>
           </cell>
           <cell r="G565" t="str">
-            <v>Scented Squishy 2 - Spa Serenity - WMT</v>
+            <v>Calm Ultra - Works of Art / Transporting to Magical Places - Name TBD</v>
           </cell>
         </row>
         <row r="566">
           <cell r="F566" t="str">
-            <v>LL-25-3277</v>
+            <v>LL-98-3475</v>
           </cell>
           <cell r="G566" t="str">
-            <v>Scented Squishy 3 - Mini Succulents - WMT</v>
+            <v>Best of Lifelines - Name TBD</v>
           </cell>
         </row>
         <row r="567">
           <cell r="F567" t="str">
-            <v>LL-25-3283</v>
+            <v>LL-98-3476</v>
           </cell>
           <cell r="G567" t="str">
-            <v>Scented Squishy 4 - Zen Meditation - WMT</v>
+            <v>Best of Lifelines Ultimate - Name TBD</v>
           </cell>
         </row>
         <row r="568">
           <cell r="F568" t="str">
-            <v>LL-25-3284</v>
+            <v>LL-98-3477</v>
           </cell>
           <cell r="G568" t="str">
-            <v>Scented Squishy 5 - Forest Friends - WMT</v>
+            <v>Candle Bundle - Name TBD</v>
           </cell>
         </row>
         <row r="569">
           <cell r="F569" t="str">
-            <v>LL-25-3285</v>
+            <v>LL-98-3478</v>
           </cell>
           <cell r="G569" t="str">
-            <v>Scented Squishy 6 - Animal Friends - WMT</v>
+            <v>Writing Bundle - Name TBD</v>
           </cell>
         </row>
         <row r="570">
           <cell r="F570" t="str">
-            <v>LL-25-3286</v>
+            <v>LL-12-3132</v>
           </cell>
           <cell r="G570" t="str">
-            <v>Scented Squishy 7 - Writers Desk -  WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="571">
           <cell r="F571" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-12-3132-V2</v>
           </cell>
           <cell r="G571" t="str">
-            <v>Scented Squishy 8 - Little Books -  WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Pink / Purple)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="572">
           <cell r="F572" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-12-3133</v>
           </cell>
           <cell r="G572" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Lava Pen Set - 2-pack (Blue / Green)  - WALMART PKG</v>
           </cell>
         </row>
         <row r="573">
           <cell r="F573" t="str">
-            <v>LL-14-3322</v>
+            <v>LL-12-3136</v>
           </cell>
           <cell r="G573" t="str">
-            <v>Candle - Ribbed Pink - Very Vanilla - WALMART PKG</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte - WALMART PKG</v>
           </cell>
         </row>
         <row r="574">
           <cell r="F574" t="str">
-            <v>LL-12-3279</v>
+            <v>LL-12-3137</v>
           </cell>
           <cell r="G574" t="str">
-            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
+            <v>Pen Diffuser with Essential Oil Blends - In Bloom - WALMART PKG</v>
           </cell>
         </row>
         <row r="575">
           <cell r="F575" t="str">
-            <v>LL-12-3280</v>
+            <v>LL-12-3138</v>
           </cell>
           <cell r="G575" t="str">
-            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
+            <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette) - WALMART PKG</v>
           </cell>
         </row>
         <row r="576">
           <cell r="F576" t="str">
-            <v>LL-00-0001</v>
+            <v>LL-12-3139</v>
           </cell>
           <cell r="G576" t="str">
-            <v>Empty Cardboard Shipper Base</v>
+            <v>Writing Bundle [2x Lava Pen / Journal / Highlighter] - WALMART PKG</v>
           </cell>
         </row>
         <row r="577">
           <cell r="F577" t="str">
-            <v>LL-00-0002</v>
+            <v>LL-16-3193</v>
           </cell>
           <cell r="G577" t="str">
-            <v>Empty Sidecap Shipper with Base</v>
+            <v>FlowArt: Pogo-Dot, Nature - WALMART PKG</v>
           </cell>
         </row>
         <row r="578">
           <cell r="F578" t="str">
-            <v>LL-00-0003</v>
+            <v>LL-16-3140</v>
           </cell>
           <cell r="G578" t="str">
-            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
+            <v>FlowArt: Dot-By-Letter, Landscapes - WALMART PKG</v>
           </cell>
         </row>
         <row r="579">
           <cell r="F579" t="str">
-            <v>LL-00-0005</v>
+            <v>LL-16-3141</v>
           </cell>
           <cell r="G579" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
+            <v>FlowArt: Dot-By-Letter, Botanicals - WALMART PKG</v>
           </cell>
         </row>
         <row r="580">
           <cell r="F580" t="str">
-            <v>LL-00-0006</v>
+            <v>LL-14-3144</v>
           </cell>
           <cell r="G580" t="str">
-            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
+            <v>Blush Pink Ribbed Candle - XX - WALMART PKG</v>
           </cell>
         </row>
         <row r="581">
           <cell r="F581" t="str">
-            <v>LL-00-0007</v>
+            <v>LL-14-3146</v>
           </cell>
           <cell r="G581" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
+            <v>Plant Diffuser -  Grass Plant - Bubble White  - WALMART PKG</v>
           </cell>
         </row>
         <row r="582">
           <cell r="F582" t="str">
-            <v>LL-00-0008</v>
+            <v>LL-16-3261</v>
           </cell>
           <cell r="G582" t="str">
-            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
+            <v>FlowArt Home for the Holidays Scented CtR - WMT</v>
           </cell>
         </row>
         <row r="583">
           <cell r="F583" t="str">
-            <v>LL-00-0035</v>
+            <v>LL-16-3281</v>
           </cell>
           <cell r="G583" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Full</v>
+            <v>FlowArt Dot-By-Letter Winterglow - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="584">
           <cell r="F584" t="str">
-            <v>LL-99-0035</v>
+            <v>LL-16-3263</v>
           </cell>
           <cell r="G584" t="str">
-            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
+            <v>FlowArt: Trace-by-Line: Gingerbread Delight - WMT</v>
           </cell>
         </row>
         <row r="585">
           <cell r="F585" t="str">
-            <v>LL-00-0009</v>
+            <v>LL-16-3383</v>
           </cell>
           <cell r="G585" t="str">
-            <v>Meijer - Grounding Stone Shipper</v>
+            <v>FlowArt Dot-By-Letter: The North Pole - WMT</v>
           </cell>
         </row>
         <row r="586">
           <cell r="F586" t="str">
-            <v>LL-00-0010</v>
+            <v>LL-16-3266</v>
           </cell>
           <cell r="G586" t="str">
-            <v>Target Sidecap Shipper + Base</v>
+            <v>FlowArt Dot-By-Letter: Wags &amp; Whiskers - WMT</v>
           </cell>
         </row>
         <row r="587">
           <cell r="F587" t="str">
-            <v>LL-WM-0011</v>
+            <v>LL-99-3370</v>
           </cell>
           <cell r="G587" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART</v>
+            <v>FlowArt Minis: PDQ - WMT</v>
           </cell>
         </row>
         <row r="588">
           <cell r="F588" t="str">
-            <v>LL-WM-0021</v>
+            <v>LL-30-3380</v>
           </cell>
           <cell r="G588" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
+            <v>FlowArt Minis EXPRESS: Nature Walk - WMT</v>
           </cell>
         </row>
         <row r="589">
           <cell r="F589" t="str">
-            <v>LL-WM-9921</v>
+            <v>LL-30-3381</v>
           </cell>
           <cell r="G589" t="str">
-            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
+            <v>FlowArt Minis EXPRESS: Paws and Purrs - WMT</v>
           </cell>
         </row>
         <row r="590">
           <cell r="F590" t="str">
-            <v>LL-WG-0018</v>
+            <v>LL-30-3382</v>
           </cell>
           <cell r="G590" t="str">
-            <v>Tower - FA Minis - WALGREENS - Full</v>
+            <v>FlowArt Minis EXPRESS: In Full Bloom - WMT</v>
           </cell>
         </row>
         <row r="591">
           <cell r="F591" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-12-3271</v>
           </cell>
           <cell r="G591" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>Scented Glitter Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="592">
           <cell r="F592" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-12-3272</v>
           </cell>
           <cell r="G592" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>Scented Lava Pen 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="593">
           <cell r="F593" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-12-3273</v>
           </cell>
           <cell r="G593" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>Scented Pen Discovery Set 3-Pack - WMT</v>
           </cell>
         </row>
         <row r="594">
           <cell r="F594" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-12-3274</v>
           </cell>
           <cell r="G594" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>Scented Marker 10-Pack - WMT</v>
           </cell>
         </row>
         <row r="595">
           <cell r="F595" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G595" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>Scented Palm Calms 1 - Zen Garden - WMT</v>
           </cell>
         </row>
         <row r="596">
           <cell r="F596" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G596" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>Scented Palm Calms 2 - Spa Serenity - WMT</v>
           </cell>
         </row>
         <row r="597">
           <cell r="F597" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-25-3277</v>
           </cell>
           <cell r="G597" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>Scented Palm Calms 3 - Mini Succulents - WMT</v>
           </cell>
         </row>
         <row r="598">
           <cell r="F598" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-25-3283</v>
           </cell>
           <cell r="G598" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>Scented Palm Calms 4 - Zen Meditation - WMT</v>
           </cell>
         </row>
         <row r="599">
           <cell r="F599" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-25-3284</v>
           </cell>
           <cell r="G599" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>Scented Palm Calms 5 - Forest Friends - WMT</v>
           </cell>
         </row>
         <row r="600">
           <cell r="F600" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-25-3285</v>
           </cell>
           <cell r="G600" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>Scented Palm Calms 6 - Animal Friends - WMT</v>
           </cell>
         </row>
         <row r="601">
           <cell r="F601" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-25-3286</v>
           </cell>
           <cell r="G601" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>Scented Palm Calms 7 - Writers Desk -  WMT</v>
           </cell>
         </row>
         <row r="602">
           <cell r="F602" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-25-3287</v>
           </cell>
           <cell r="G602" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>Scented Palm Calms 8 - Little Books -  WMT</v>
           </cell>
         </row>
         <row r="603">
           <cell r="F603" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-25-3278</v>
           </cell>
           <cell r="G603" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>Scented Palm Calms Discovery Set - WMT</v>
           </cell>
         </row>
         <row r="604">
           <cell r="F604" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-14-3322</v>
           </cell>
           <cell r="G604" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>Candle - Ribbed Pink - Very Vanilla - WALMART PKG</v>
           </cell>
         </row>
         <row r="605">
           <cell r="F605" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-12-3279</v>
           </cell>
           <cell r="G605" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>Ebb &amp; Flow Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="606">
           <cell r="F606" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-12-3280</v>
           </cell>
           <cell r="G606" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>Find Your Path Journal + Pen Gift Set - WMT</v>
           </cell>
         </row>
         <row r="607">
           <cell r="F607" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-00-0001</v>
           </cell>
           <cell r="G607" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>Empty Cardboard Shipper Base</v>
           </cell>
         </row>
         <row r="608">
           <cell r="F608" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-00-0002</v>
           </cell>
           <cell r="G608" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>Empty Sidecap Shipper with Base</v>
           </cell>
         </row>
         <row r="609">
           <cell r="F609" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-00-0003</v>
           </cell>
           <cell r="G609" t="str">
-            <v>FlowArt Grocery Display Evergreen - 24</v>
+            <v>Target Writing Sidecap Shipper (Summer 2025)</v>
           </cell>
         </row>
         <row r="610">
           <cell r="F610" t="str">
-            <v>LL-99-0024</v>
+            <v>LL-00-0005</v>
           </cell>
           <cell r="G610" t="str">
-            <v>FlowArt Grocery Display Evergreen - Empty</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="611">
           <cell r="F611" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-00-0006</v>
           </cell>
           <cell r="G611" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Target Writing Endcap Shipper (Fall 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="612">
           <cell r="F612" t="str">
-            <v>LL-99-0025</v>
+            <v>LL-00-0007</v>
           </cell>
           <cell r="G612" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf A</v>
           </cell>
         </row>
         <row r="613">
           <cell r="F613" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-00-0008</v>
           </cell>
           <cell r="G613" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>Target Writing Endcap Shipper (Winter 2025) - Shelf B</v>
           </cell>
         </row>
         <row r="614">
           <cell r="F614" t="str">
-            <v>LL-99-0026</v>
+            <v>LL-00-0035</v>
           </cell>
           <cell r="G614" t="str">
-            <v>FlowArt Fall Grocery Display - Empty</v>
+            <v>Holiday Sidecap - FA Express - TGT - Full</v>
           </cell>
         </row>
         <row r="615">
-          <cell r="F615"/>
+          <cell r="F615" t="str">
+            <v>LL-99-0035</v>
+          </cell>
           <cell r="G615" t="str">
-            <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
+            <v>Holiday Sidecap - FA Express - TGT - Empty</v>
           </cell>
         </row>
         <row r="616">
           <cell r="F616" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-00-0009</v>
           </cell>
           <cell r="G616" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>Meijer - Grounding Stone Shipper</v>
           </cell>
         </row>
         <row r="617">
           <cell r="F617" t="str">
-            <v>LL-99-0027</v>
+            <v>LL-00-0010</v>
           </cell>
           <cell r="G617" t="str">
-            <v>FlowArt Holiday Grocery Display - Empty</v>
+            <v>Target Sidecap Shipper + Base</v>
           </cell>
         </row>
         <row r="618">
           <cell r="F618" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-WM-0011</v>
           </cell>
           <cell r="G618" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>BTS Sidecap - FA Minis - WALMART</v>
           </cell>
         </row>
         <row r="619">
           <cell r="F619" t="str">
-            <v>LL-99-0028</v>
+            <v>LL-WM-0021</v>
           </cell>
           <cell r="G619" t="str">
-            <v>FlowArt Mini Grocery Display - Empty</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Full</v>
           </cell>
         </row>
         <row r="620">
           <cell r="F620" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-WM-9921</v>
           </cell>
           <cell r="G620" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>BTS Sidecap - FA Minis - WALMART - Empty</v>
           </cell>
         </row>
         <row r="621">
           <cell r="F621" t="str">
-            <v>LL-99-0029</v>
+            <v>LL-WG-0018</v>
           </cell>
           <cell r="G621" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
+            <v>Tower - FA Minis - WALGREENS - Full</v>
           </cell>
         </row>
         <row r="622">
           <cell r="F622" t="str">
-            <v>LL-00-0040</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G622" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
         </row>
         <row r="623">
           <cell r="F623" t="str">
-            <v>LL-99-0040</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G623" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #1</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="624">
           <cell r="F624" t="str">
-            <v>LL-00-0041</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G624" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 72 - #2</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
         </row>
         <row r="625">
           <cell r="F625" t="str">
-            <v>LL-99-0041</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G625" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #2</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
         </row>
         <row r="626">
           <cell r="F626" t="str">
-            <v>LL-00-0037</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G626" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="627">
           <cell r="F627" t="str">
-            <v>LL-99-0037</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G627" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
         </row>
         <row r="628">
           <cell r="F628" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G628" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>2026 Product Catalogue</v>
           </cell>
         </row>
         <row r="629">
           <cell r="F629" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-02-2026</v>
           </cell>
           <cell r="G629" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>2026 Product Catalogue - H2</v>
           </cell>
         </row>
         <row r="630">
           <cell r="F630" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G630" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="631">
           <cell r="F631" t="str">
-            <v>LL-99-0039</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G631" t="str">
-            <v>FlowArt MINI Spring Display - Empty</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="632">
           <cell r="F632" t="str">
-            <v>LL-00-0039</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G632" t="str">
-            <v>FlowArt MINI Spring Display - 36</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
         </row>
         <row r="633">
           <cell r="F633" t="str">
-            <v>LL-99-0038</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G633" t="str">
-            <v>FlowArt Spring Display - Empty</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
         </row>
         <row r="634">
           <cell r="F634" t="str">
-            <v>LL-00-0038</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G634" t="str">
-            <v>FlowArt Spring Display - 24</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
         </row>
         <row r="635">
           <cell r="F635" t="str">
-            <v>LL-99-0033</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G635" t="str">
-            <v>FlowArt Valentine Display - Empty</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
         </row>
         <row r="636">
           <cell r="F636" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G636" t="str">
-            <v>FlowArt Valentine Display - 24</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
         </row>
         <row r="637">
           <cell r="F637" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G637" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
         </row>
         <row r="638">
           <cell r="F638" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G638" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
         </row>
         <row r="639">
           <cell r="F639" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G639" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
         </row>
         <row r="640">
           <cell r="F640" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G640" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G641" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Grocery Display Evergreen - 24</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-99-0024</v>
           </cell>
           <cell r="G642" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FlowArt Grocery Display Evergreen - Empty</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G643" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-99-0025</v>
           </cell>
           <cell r="G644" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G645" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-99-0026</v>
           </cell>
           <cell r="G646" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>FlowArt Fall Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-00-0026-V2</v>
           </cell>
           <cell r="G647" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
           </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G648" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G649" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G650" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G651" t="str">
-            <v>Lifelines Tote</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="652">
           <cell r="F652" t="str">
-            <v>99-9101</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G652" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
         </row>
         <row r="653">
           <cell r="F653" t="str">
-            <v>99-9500</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G653" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
         </row>
         <row r="654">
           <cell r="F654" t="str">
-            <v>99-9505</v>
+            <v>LL-00-0040</v>
           </cell>
           <cell r="G654" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
           </cell>
         </row>
         <row r="655">
           <cell r="F655" t="str">
-            <v>DS01-1001</v>
+            <v>LL-99-0040</v>
           </cell>
           <cell r="G655" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #1</v>
           </cell>
         </row>
         <row r="656">
           <cell r="F656" t="str">
-            <v>DS01-1002</v>
+            <v>LL-00-0041</v>
           </cell>
           <cell r="G656" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>FlowArt MINI EXPRESS - WMT - 72 - #2</v>
           </cell>
         </row>
         <row r="657">
           <cell r="F657" t="str">
-            <v>DS01-1003</v>
+            <v>LL-99-0041</v>
           </cell>
           <cell r="G657" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #2</v>
           </cell>
         </row>
         <row r="658">
           <cell r="F658" t="str">
-            <v>DS01-1004</v>
+            <v>LL-00-0042</v>
           </cell>
           <cell r="G658" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - 72 - #1</v>
           </cell>
         </row>
         <row r="659">
           <cell r="F659" t="str">
-            <v>DS01-1005</v>
+            <v>LL-99-0042</v>
           </cell>
           <cell r="G659" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - EMPTY - #1</v>
           </cell>
         </row>
         <row r="660">
           <cell r="F660" t="str">
-            <v>DS01-1006</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G660" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
           </cell>
         </row>
         <row r="661">
           <cell r="F661" t="str">
-            <v>DS01-1007</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G661" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
           </cell>
         </row>
         <row r="662">
           <cell r="F662" t="str">
-            <v>DS01-1008</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G662" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
         </row>
         <row r="663">
           <cell r="F663" t="str">
-            <v>99-8302</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G663" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
         </row>
         <row r="664">
           <cell r="F664" t="str">
-            <v>99-8501</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G664" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
         </row>
         <row r="665">
           <cell r="F665" t="str">
-            <v>99-9002</v>
+            <v>LL-99-0039</v>
           </cell>
           <cell r="G665" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>FlowArt MINI Spring Display - Empty</v>
           </cell>
         </row>
         <row r="666">
-          <cell r="F666">
-            <v>999003</v>
+          <cell r="F666" t="str">
+            <v>LL-00-0039</v>
           </cell>
           <cell r="G666" t="str">
-            <v>BNC Floor Display</v>
+            <v>FlowArt MINI Spring Display - 36</v>
           </cell>
         </row>
         <row r="667">
-          <cell r="F667">
-            <v>999004</v>
+          <cell r="F667" t="str">
+            <v>LL-99-0038</v>
           </cell>
           <cell r="G667" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>FlowArt Spring Display - Empty</v>
           </cell>
         </row>
         <row r="668">
           <cell r="F668" t="str">
-            <v>LL-20-3304</v>
+            <v>LL-00-0038</v>
           </cell>
           <cell r="G668" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>FlowArt Spring Display - 24</v>
           </cell>
         </row>
         <row r="669">
           <cell r="F669" t="str">
-            <v>LL-20-3226</v>
+            <v>LL-99-0033</v>
           </cell>
           <cell r="G669" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>FlowArt Valentine Display - Empty</v>
           </cell>
         </row>
         <row r="670">
           <cell r="F670" t="str">
-            <v>LL-20-3252</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G670" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>FlowArt Valentine Display - 24</v>
           </cell>
         </row>
         <row r="671">
           <cell r="F671" t="str">
-            <v>LL-20-3253</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G671" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
         </row>
         <row r="672">
           <cell r="F672" t="str">
-            <v>LL-20-3254</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G672" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
         </row>
         <row r="673">
           <cell r="F673" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G673" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
         </row>
         <row r="674">
           <cell r="F674" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G674" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
         </row>
         <row r="675">
           <cell r="F675" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G675" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
         </row>
         <row r="676">
           <cell r="F676" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G676" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
         </row>
         <row r="677">
           <cell r="F677" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G677" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
         </row>
         <row r="678">
           <cell r="F678" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G678" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
         </row>
         <row r="679">
           <cell r="F679" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G679" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
         </row>
         <row r="680">
           <cell r="F680" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G680" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
         </row>
         <row r="681">
           <cell r="F681" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G681" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
         </row>
         <row r="682">
           <cell r="F682" t="str">
-            <v>LL-16-3143</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G682" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
         </row>
         <row r="683">
           <cell r="F683" t="str">
-            <v>LL-12-3131</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G683" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
         </row>
         <row r="684">
           <cell r="F684" t="str">
-            <v>LL-16-3142</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G684" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
         </row>
         <row r="685">
           <cell r="F685" t="str">
-            <v>LL-12-3135</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G685" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>Lifelines Tote</v>
           </cell>
         </row>
         <row r="686">
           <cell r="F686" t="str">
-            <v>LL-12-3134</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G686" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
         </row>
         <row r="687">
           <cell r="F687" t="str">
-            <v>LL-14-3145</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G687" t="str">
-            <v>DIFFUSER, LED,Bubble (Cream) - WALMART PKG</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
         </row>
         <row r="688">
           <cell r="F688" t="str">
-            <v>LL-14-3147</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G688" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
         </row>
         <row r="689">
           <cell r="F689" t="str">
-            <v>LL-98-3171</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G689" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="690">
           <cell r="F690" t="str">
-            <v>LL-11-3087</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G690" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
         </row>
         <row r="691">
           <cell r="F691" t="str">
-            <v>LL-11-3088</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G691" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
         </row>
         <row r="692">
           <cell r="F692" t="str">
-            <v>LL-11-3089</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G692" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
         </row>
         <row r="693">
-          <cell r="F693">
-            <v>165002</v>
+          <cell r="F693" t="str">
+            <v>DS01-1005</v>
           </cell>
           <cell r="G693" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
         </row>
         <row r="694">
-          <cell r="F694">
-            <v>165003</v>
+          <cell r="F694" t="str">
+            <v>DS01-1006</v>
           </cell>
           <cell r="G694" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
         </row>
         <row r="695">
-          <cell r="F695">
-            <v>165004</v>
+          <cell r="F695" t="str">
+            <v>DS01-1007</v>
           </cell>
           <cell r="G695" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
         </row>
         <row r="696">
-          <cell r="F696">
-            <v>165010</v>
+          <cell r="F696" t="str">
+            <v>DS01-1008</v>
           </cell>
           <cell r="G696" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
         </row>
         <row r="697">
-          <cell r="F697">
-            <v>165011</v>
+          <cell r="F697" t="str">
+            <v>99-8302</v>
           </cell>
           <cell r="G697" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
         </row>
         <row r="698">
-          <cell r="F698">
-            <v>165013</v>
+          <cell r="F698" t="str">
+            <v>99-8501</v>
           </cell>
           <cell r="G698" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
         </row>
         <row r="699">
-          <cell r="F699">
-            <v>167003</v>
+          <cell r="F699" t="str">
+            <v>99-9002</v>
           </cell>
           <cell r="G699" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
         </row>
         <row r="700">
-          <cell r="F700" t="str">
-            <v>11-1613</v>
+          <cell r="F700">
+            <v>999003</v>
           </cell>
           <cell r="G700" t="str">
-            <v>DIFFUSER, LED,Frosted Glass (Amber)</v>
+            <v>BNC Floor Display</v>
           </cell>
         </row>
         <row r="701">
-          <cell r="F701" t="str">
-            <v>11-1614</v>
+          <cell r="F701">
+            <v>999004</v>
           </cell>
           <cell r="G701" t="str">
-            <v>DIFFUSER, LED,Vertical Ribbed (White)</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
         </row>
         <row r="702">
           <cell r="F702" t="str">
-            <v>11-1615</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G702" t="str">
-            <v>DIFFUSER, LED, Two Tone</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
         </row>
         <row r="703">
           <cell r="F703" t="str">
-            <v>11-1610</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G703" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
         </row>
         <row r="704">
           <cell r="F704" t="str">
-            <v>16-0107</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G704" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
         </row>
         <row r="705">
           <cell r="F705" t="str">
-            <v>LL-11-2522</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G705" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
         </row>
         <row r="706">
           <cell r="F706" t="str">
-            <v>LL-11-2523</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G706" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
         </row>
         <row r="707">
           <cell r="F707" t="str">
-            <v>11-0451</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G707" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
         </row>
         <row r="708">
           <cell r="F708" t="str">
-            <v>99-9502</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G708" t="str">
-            <v>Pen Display - Empty</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
         </row>
         <row r="709">
           <cell r="F709" t="str">
-            <v>11-0452</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G709" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
         </row>
         <row r="710">
           <cell r="F710" t="str">
-            <v>112522</v>
+            <v>LL-16-3262</v>
+          </cell>
+          <cell r="G710" t="str">
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
         </row>
         <row r="711">
           <cell r="F711" t="str">
-            <v>99-9501</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G711" t="str">
-            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
         </row>
         <row r="712">
           <cell r="F712" t="str">
-            <v>11-1618</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G712" t="str">
-            <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
         </row>
         <row r="713">
           <cell r="F713" t="str">
+            <v>LL-16-3260</v>
+          </cell>
+          <cell r="G713" t="str">
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+          </cell>
+        </row>
+        <row r="714">
+          <cell r="F714" t="str">
+            <v>LL-16-3267</v>
+          </cell>
+          <cell r="G714" t="str">
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+          </cell>
+        </row>
+        <row r="715">
+          <cell r="F715" t="str">
+            <v>LL-16-3282</v>
+          </cell>
+          <cell r="G715" t="str">
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+          </cell>
+        </row>
+        <row r="716">
+          <cell r="F716" t="str">
+            <v>LL-16-3143</v>
+          </cell>
+          <cell r="G716" t="str">
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="717">
+          <cell r="F717" t="str">
+            <v>LL-12-3131</v>
+          </cell>
+          <cell r="G717" t="str">
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="718">
+          <cell r="F718" t="str">
+            <v>LL-16-3142</v>
+          </cell>
+          <cell r="G718" t="str">
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="719">
+          <cell r="F719" t="str">
+            <v>LL-12-3135</v>
+          </cell>
+          <cell r="G719" t="str">
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="720">
+          <cell r="F720" t="str">
+            <v>LL-12-3134</v>
+          </cell>
+          <cell r="G720" t="str">
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="721">
+          <cell r="F721" t="str">
+            <v>LL-14-3145</v>
+          </cell>
+          <cell r="G721" t="str">
+            <v>DIFFUSER, LED,Bubble (Cream) - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="722">
+          <cell r="F722" t="str">
+            <v>LL-14-3147</v>
+          </cell>
+          <cell r="G722" t="str">
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="723">
+          <cell r="F723" t="str">
+            <v>LL-98-3171</v>
+          </cell>
+          <cell r="G723" t="str">
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+          </cell>
+        </row>
+        <row r="724">
+          <cell r="F724" t="str">
+            <v>LL-11-3087</v>
+          </cell>
+          <cell r="G724" t="str">
+            <v>Clickwick 2PK - SKU 5</v>
+          </cell>
+        </row>
+        <row r="725">
+          <cell r="F725" t="str">
+            <v>LL-11-3088</v>
+          </cell>
+          <cell r="G725" t="str">
+            <v>Clickwick 2PK - SKU 6</v>
+          </cell>
+        </row>
+        <row r="726">
+          <cell r="F726" t="str">
+            <v>LL-11-3089</v>
+          </cell>
+          <cell r="G726" t="str">
+            <v>Clickwick 2PK - SKU 7</v>
+          </cell>
+        </row>
+        <row r="727">
+          <cell r="F727">
+            <v>165002</v>
+          </cell>
+          <cell r="G727" t="str">
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+          </cell>
+        </row>
+        <row r="728">
+          <cell r="F728">
+            <v>165003</v>
+          </cell>
+          <cell r="G728" t="str">
+            <v>FlowArt - Multiline art - Land</v>
+          </cell>
+        </row>
+        <row r="729">
+          <cell r="F729">
+            <v>165004</v>
+          </cell>
+          <cell r="G729" t="str">
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+          </cell>
+        </row>
+        <row r="730">
+          <cell r="F730">
+            <v>165010</v>
+          </cell>
+          <cell r="G730" t="str">
+            <v>FlowArt - Pogo-dot - In the Garden</v>
+          </cell>
+        </row>
+        <row r="731">
+          <cell r="F731">
+            <v>165011</v>
+          </cell>
+          <cell r="G731" t="str">
+            <v>FlowArt - Dot-pop - Sea</v>
+          </cell>
+        </row>
+        <row r="732">
+          <cell r="F732">
+            <v>165013</v>
+          </cell>
+          <cell r="G732" t="str">
+            <v>FlowArt - Multiline art - Sea</v>
+          </cell>
+        </row>
+        <row r="733">
+          <cell r="F733">
+            <v>167003</v>
+          </cell>
+          <cell r="G733" t="str">
+            <v>Decor Art - Stencil Stationery</v>
+          </cell>
+        </row>
+        <row r="734">
+          <cell r="F734" t="str">
+            <v>11-1613</v>
+          </cell>
+          <cell r="G734" t="str">
+            <v>DIFFUSER, LED,Frosted Glass (Amber)</v>
+          </cell>
+        </row>
+        <row r="735">
+          <cell r="F735" t="str">
+            <v>11-1614</v>
+          </cell>
+          <cell r="G735" t="str">
+            <v>DIFFUSER, LED,Vertical Ribbed (White)</v>
+          </cell>
+        </row>
+        <row r="736">
+          <cell r="F736" t="str">
+            <v>11-1615</v>
+          </cell>
+          <cell r="G736" t="str">
+            <v>DIFFUSER, LED, Two Tone</v>
+          </cell>
+        </row>
+        <row r="737">
+          <cell r="F737" t="str">
+            <v>11-1610</v>
+          </cell>
+          <cell r="G737" t="str">
+            <v>Planter Diffuser -  Octagon (Cream)</v>
+          </cell>
+        </row>
+        <row r="738">
+          <cell r="F738" t="str">
+            <v>16-0107</v>
+          </cell>
+          <cell r="G738" t="str">
+            <v>Finger Maze Sensory Journal</v>
+          </cell>
+        </row>
+        <row r="739">
+          <cell r="F739" t="str">
+            <v>LL-11-2522</v>
+          </cell>
+          <cell r="G739" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="740">
+          <cell r="F740" t="str">
+            <v>LL-11-2523</v>
+          </cell>
+          <cell r="G740" t="str">
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+          </cell>
+        </row>
+        <row r="741">
+          <cell r="F741" t="str">
+            <v>11-0451</v>
+          </cell>
+          <cell r="G741" t="str">
+            <v>Clickwick Replacement Bloom, Citrus</v>
+          </cell>
+        </row>
+        <row r="742">
+          <cell r="F742" t="str">
+            <v>99-9502</v>
+          </cell>
+          <cell r="G742" t="str">
+            <v>Pen Display - Empty</v>
+          </cell>
+        </row>
+        <row r="743">
+          <cell r="F743" t="str">
+            <v>11-0452</v>
+          </cell>
+          <cell r="G743" t="str">
+            <v>Clickwick Replacement Woods, Mountain</v>
+          </cell>
+        </row>
+        <row r="744">
+          <cell r="F744" t="str">
+            <v>112522</v>
+          </cell>
+        </row>
+        <row r="745">
+          <cell r="F745" t="str">
+            <v>99-9501</v>
+          </cell>
+          <cell r="G745" t="str">
+            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+          </cell>
+        </row>
+        <row r="746">
+          <cell r="F746" t="str">
+            <v>11-1618</v>
+          </cell>
+          <cell r="G746" t="str">
+            <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
+          </cell>
+        </row>
+        <row r="747">
+          <cell r="F747" t="str">
             <v>98-9220</v>
           </cell>
-          <cell r="G713" t="str">
+          <cell r="G747" t="str">
             <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
         </row>
@@ -6121,13 +6398,7 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="1">
-          <cell r="C1" t="str">
-            <v>LL PN (Final)</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -7327,24 +7598,24 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+    <row r="52" spans="1:6" s="5" customFormat="1">
+      <c r="A52" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>7</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D52" t="str">
+      <c r="D52" s="5" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
-      <c r="E52">
-        <v>4</v>
-      </c>
-      <c r="F52">
+      <c r="E52" s="5">
+        <v>4</v>
+      </c>
+      <c r="F52" s="5">
         <v>6.5</v>
       </c>
     </row>
@@ -7356,11 +7627,11 @@
         <v>8</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D53" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Foodie Fun</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -7740,7 +8011,7 @@
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Visual Symphony Pen, Glitter 5Pck</v>
+        <v>Scented Sparkle Pen, 5Pck</v>
       </c>
       <c r="E71">
         <v>8</v>
@@ -7761,7 +8032,7 @@
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Visual Symphony Pen, Swirl 5Pck</v>
+        <v>Scented Swirl Pen, 5Pck</v>
       </c>
       <c r="E72">
         <v>8</v>
@@ -8189,11 +8460,11 @@
         <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Letter, Pack Your Bags</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E92">
         <v>4</v>
@@ -8211,11 +8482,11 @@
         <v>14</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E93">
         <v>4</v>
@@ -8233,11 +8504,11 @@
         <v>15</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Trace-By-Groove, Desert Dreams</v>
       </c>
       <c r="E94">
         <v>4</v>
@@ -8575,11 +8846,11 @@
         <v>10</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D110" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E110">
         <v>4</v>
@@ -10710,6 +10981,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -10950,15 +11230,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
   <ds:schemaRefs>
@@ -10971,6 +11242,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10987,12 +11266,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71A164C5-E284-4D2D-9FE2-CEC8D361FB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7AC855-84D1-4B24-B394-1BAF87D5192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assortment Expansion'!$A$4:$F$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="78">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -271,6 +271,9 @@
   <si>
     <t>99-9502</t>
   </si>
+  <si>
+    <t>LL-16-3224</t>
+  </si>
 </sst>
 </file>
 
@@ -25667,7 +25670,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -27067,7 +27070,7 @@
         <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27082,12 +27085,12 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>32</v>
+      <c r="C64" s="1">
+        <v>165008</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E64">
         <v>12</v>
@@ -27106,11 +27109,11 @@
         <v>3</v>
       </c>
       <c r="C65" s="1">
-        <v>165008</v>
+        <v>165012</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E65">
         <v>8</v>
@@ -27129,18 +27132,18 @@
         <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
       </c>
       <c r="E66">
         <v>12</v>
       </c>
       <c r="F66" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -27152,11 +27155,11 @@
         <v>5</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E67">
         <v>12</v>
@@ -27175,11 +27178,11 @@
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E68">
         <v>12</v>
@@ -27198,11 +27201,11 @@
         <v>7</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -27221,11 +27224,11 @@
         <v>8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E70">
         <v>12</v>
@@ -27240,15 +27243,15 @@
         <v>51</v>
       </c>
       <c r="B71">
-        <f t="shared" ref="B71:B125" si="1">IF(A70=A71, B70+1, 1)</f>
+        <f t="shared" ref="B71:B124" si="1">IF(A70=A71, B70+1, 1)</f>
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D71" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E71">
         <v>8</v>
@@ -27267,11 +27270,11 @@
         <v>10</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E72">
         <v>4</v>
@@ -27290,11 +27293,11 @@
         <v>11</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E73">
         <v>12</v>
@@ -27309,15 +27312,15 @@
         <v>51</v>
       </c>
       <c r="B74">
-        <f t="shared" si="1"/>
+        <f>IF(A73=A74, B73+1, 1)</f>
         <v>12</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
       </c>
       <c r="E74">
         <v>12</v>
@@ -27336,18 +27339,18 @@
         <v>13</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -27359,11 +27362,11 @@
         <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E76">
         <v>12</v>
@@ -27382,11 +27385,11 @@
         <v>15</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E77">
         <v>12</v>
@@ -27404,12 +27407,12 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C78" s="1">
-        <v>165012</v>
+      <c r="C78" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D78" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E78">
         <v>8</v>
@@ -27428,11 +27431,11 @@
         <v>17</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
       </c>
       <c r="E79">
         <v>4</v>
@@ -27451,14 +27454,14 @@
         <v>18</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D80" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27467,18 +27470,18 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B81">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D81" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>Scented Stacking Highlighters - 2-pack</v>
       </c>
       <c r="E81">
         <v>4</v>
@@ -27494,14 +27497,14 @@
       </c>
       <c r="B82">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>69</v>
+        <v>2</v>
+      </c>
+      <c r="C82" s="1">
+        <v>165006</v>
       </c>
       <c r="D82" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Stacking Highlighters - 2-pack</v>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
       </c>
       <c r="E82">
         <v>4</v>
@@ -27517,14 +27520,14 @@
       </c>
       <c r="B83">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83" s="1">
-        <v>165006</v>
+        <v>165007</v>
       </c>
       <c r="D83" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
+        <v>FlowArt: Pogo-Dot, Nature</v>
       </c>
       <c r="E83">
         <v>4</v>
@@ -27540,14 +27543,14 @@
       </c>
       <c r="B84">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C84" s="1">
-        <v>165007</v>
+        <v>165008</v>
       </c>
       <c r="D84" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Pogo-Dot, Nature</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E84">
         <v>4</v>
@@ -27563,14 +27566,14 @@
       </c>
       <c r="B85">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C85" s="1">
-        <v>165008</v>
+        <v>165009</v>
       </c>
       <c r="D85" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
       </c>
       <c r="E85">
         <v>4</v>
@@ -27586,14 +27589,14 @@
       </c>
       <c r="B86">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C86" s="1">
-        <v>165009</v>
+        <v>165012</v>
       </c>
       <c r="D86" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E86">
         <v>4</v>
@@ -27609,14 +27612,14 @@
       </c>
       <c r="B87">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1">
-        <v>165012</v>
+        <v>165005</v>
       </c>
       <c r="D87" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C87, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C87), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E87">
         <v>4</v>
@@ -27632,14 +27635,14 @@
       </c>
       <c r="B88">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="C88" s="1">
-        <v>165005</v>
+        <v>8</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D88" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C88, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C88), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
       </c>
       <c r="E88">
         <v>4</v>
@@ -27655,14 +27658,14 @@
       </c>
       <c r="B89">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D89" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C89, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C89), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+        <v>Lava Pen 2 Pack - Purple/Orange</v>
       </c>
       <c r="E89">
         <v>4</v>
@@ -27678,14 +27681,14 @@
       </c>
       <c r="B90">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D90" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C90, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C90), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Lava Pen 2 Pack - Purple/Orange</v>
+        <v>Lava Pen 2 Pack - Black/Red</v>
       </c>
       <c r="E90">
         <v>4</v>
@@ -27701,14 +27704,14 @@
       </c>
       <c r="B91">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D91" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C91, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C91), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Lava Pen 2 Pack - Black/Red</v>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
       </c>
       <c r="E91">
         <v>4</v>
@@ -27720,18 +27723,18 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B92">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D92" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C92, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C92), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Red) </v>
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
       </c>
       <c r="E92">
         <v>4</v>
@@ -27747,14 +27750,14 @@
       </c>
       <c r="B93">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D93" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C93, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C93), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
       </c>
       <c r="E93">
         <v>4</v>
@@ -27770,17 +27773,17 @@
       </c>
       <c r="B94">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D94" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C94), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C94, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C94), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27793,17 +27796,17 @@
       </c>
       <c r="B95">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D95" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C95), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
       </c>
       <c r="E95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C95, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C95), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27816,14 +27819,14 @@
       </c>
       <c r="B96">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D96" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C96, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C96), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
       </c>
       <c r="E96">
         <v>4</v>
@@ -27835,21 +27838,21 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B97">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D97" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C97), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E97">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C97, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C97), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27862,17 +27865,17 @@
       </c>
       <c r="B98">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D98" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C98), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E98">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C98, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C98), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27885,14 +27888,14 @@
       </c>
       <c r="B99">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D99" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C99, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C99), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Stamp by Shape, Secret Garden</v>
       </c>
       <c r="E99">
         <v>4</v>
@@ -27908,14 +27911,14 @@
       </c>
       <c r="B100">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D100" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C100, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C100), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Stamp by Shape, Secret Garden</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E100">
         <v>4</v>
@@ -27931,14 +27934,14 @@
       </c>
       <c r="B101">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D101" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C101, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C101), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -27954,17 +27957,17 @@
       </c>
       <c r="B102">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D102" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C102), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Dot-By-Letter, Americana</v>
       </c>
       <c r="E102">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C102, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C102), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -27977,17 +27980,17 @@
       </c>
       <c r="B103">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D103" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C103), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E103">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C103, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C103), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28000,14 +28003,14 @@
       </c>
       <c r="B104">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D104" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C104, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C104), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -28019,18 +28022,18 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B105">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D105" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C105, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C105), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
       </c>
       <c r="E105">
         <v>4</v>
@@ -28046,14 +28049,14 @@
       </c>
       <c r="B106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D106" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C106, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C106), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter Wonderland</v>
+        <v>FlowArt: Dot-By-Letter, Snowed In</v>
       </c>
       <c r="E106">
         <v>4</v>
@@ -28069,17 +28072,17 @@
       </c>
       <c r="B107">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D107" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C107), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Snowed In</v>
+        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C107, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C107), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28092,17 +28095,17 @@
       </c>
       <c r="B108">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D108" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C108), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Winter's Glow [Metallic ink]</v>
+        <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
       </c>
       <c r="E108">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C108, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C108), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28115,14 +28118,14 @@
       </c>
       <c r="B109">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D109" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C109, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C109), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-To-Reveal, Snowy Village [Scented]</v>
+        <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
       </c>
       <c r="E109">
         <v>4</v>
@@ -28134,21 +28137,21 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B110">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="D110" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C110), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-by-Line, Gingerbread Delight</v>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F110" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C110, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C110), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28161,14 +28164,14 @@
       </c>
       <c r="B111">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D111" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C111, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C111), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
       </c>
       <c r="E111">
         <v>6</v>
@@ -28184,17 +28187,17 @@
       </c>
       <c r="B112">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D112" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C112), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blend- Crisp Mountain Air</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
       </c>
       <c r="E112">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F112" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C112, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C112), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28207,14 +28210,14 @@
       </c>
       <c r="B113">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D113" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C113, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C113), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
       </c>
       <c r="E113">
         <v>8</v>
@@ -28230,17 +28233,17 @@
       </c>
       <c r="B114">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D114" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C114), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake</v>
+        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
       </c>
       <c r="E114">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C114, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C114), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28253,44 +28256,44 @@
       </c>
       <c r="B115">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D115" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C115), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Cotton Candy</v>
+        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C115, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C115), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B116">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="D116" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C116), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Universal Tabletop Display - Empty </v>
+        <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F116" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C116, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C116), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -28299,14 +28302,14 @@
       </c>
       <c r="B117">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D117" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C117, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C117), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pocket Positivity</v>
+        <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
       <c r="E117">
         <v>6</v>
@@ -28322,14 +28325,14 @@
       </c>
       <c r="B118">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D118" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C118, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C118), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Café Comforts</v>
+        <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
       <c r="E118">
         <v>6</v>
@@ -28345,17 +28348,17 @@
       </c>
       <c r="B119">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D119" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C119), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Enchanted Magic</v>
+        <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
       <c r="E119">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F119" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C119, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C119), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
@@ -28368,14 +28371,14 @@
       </c>
       <c r="B120">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C120, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C120), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Nature's Wonders</v>
+        <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
       <c r="E120">
         <v>12</v>
@@ -28391,14 +28394,14 @@
       </c>
       <c r="B121">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D121" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C121, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C121), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Pretty Petals</v>
+        <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
       <c r="E121">
         <v>12</v>
@@ -28410,25 +28413,25 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B122">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C122), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Mini Single - Furry Friends</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E122">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F122" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C122, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C122), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -28437,14 +28440,14 @@
       </c>
       <c r="B123">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="C123" s="1">
+        <v>165005</v>
       </c>
       <c r="D123" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C123, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C123), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -28460,43 +28463,20 @@
       </c>
       <c r="B124">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="C124" s="1">
-        <v>165005</v>
+        <v>3</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D124" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C124), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E124">
         <v>1</v>
       </c>
       <c r="F124" s="2">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C124, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C124), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
-        <v>66</v>
-      </c>
-      <c r="B125">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D125" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C125), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E125">
-        <v>1</v>
-      </c>
-      <c r="F125" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C125, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C125), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
         <v>6.5</v>
       </c>
     </row>
@@ -28510,12 +28490,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28760,20 +28742,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0db41735-03c9-45f7-99e2-dcae27ef4500" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="856a7437-a7e7-4452-817c-46e435f59c4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
+    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -28798,12 +28781,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0db41735-03c9-45f7-99e2-dcae27ef4500"/>
-    <ds:schemaRef ds:uri="856a7437-a7e7-4452-817c-46e435f59c4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7AC855-84D1-4B24-B394-1BAF87D5192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD2768D8-BB86-44B0-988D-A4068932372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11064,7 +11064,7 @@
             <v>LL-16-3368</v>
           </cell>
           <cell r="G323" t="str">
-            <v>FlowArt: Dot-By-Letter, Frosty Fun</v>
+            <v>FlowArt: Dot-By-Letter, The North Pole</v>
           </cell>
           <cell r="H323" t="str">
             <v>Y</v>
@@ -12044,7 +12044,7 @@
             <v>LL-16-3420</v>
           </cell>
           <cell r="G351" t="str">
-            <v>FlowArt: Trace-By-Line, Dimensional Line Tracing, Beautiful Horizons</v>
+            <v>FlowArt: Trace-By-Line, Dimensional, Beautiful Horizons</v>
           </cell>
           <cell r="H351" t="str">
             <v>Y</v>
@@ -12321,25 +12321,25 @@
         </row>
         <row r="359">
           <cell r="F359" t="str">
-            <v>LL-16-3407</v>
+            <v>LL-16-3224</v>
           </cell>
           <cell r="G359" t="str">
-            <v>FlowArt: Dot-By-Letter, Farmers Market Morning [Pastel]</v>
+            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
           </cell>
           <cell r="H359" t="str">
             <v>Y</v>
           </cell>
           <cell r="I359" t="str">
-            <v>607</v>
+            <v>396</v>
           </cell>
           <cell r="J359">
-            <v>810076216072</v>
+            <v>810076213965</v>
           </cell>
           <cell r="K359">
-            <v>50810076216077</v>
+            <v>50810076213960</v>
           </cell>
           <cell r="L359">
-            <v>30810076216073</v>
+            <v>30810076213966</v>
           </cell>
           <cell r="M359">
             <v>4</v>
@@ -12356,25 +12356,25 @@
         </row>
         <row r="360">
           <cell r="F360" t="str">
-            <v>LL-16-3224</v>
+            <v>LL-16-3225</v>
           </cell>
           <cell r="G360" t="str">
-            <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
           </cell>
           <cell r="H360" t="str">
             <v>Y</v>
           </cell>
           <cell r="I360" t="str">
-            <v>396</v>
+            <v>397</v>
           </cell>
           <cell r="J360">
-            <v>810076213965</v>
+            <v>810076213972</v>
           </cell>
           <cell r="K360">
-            <v>50810076213960</v>
+            <v>50810076213977</v>
           </cell>
           <cell r="L360">
-            <v>30810076213966</v>
+            <v>30810076213973</v>
           </cell>
           <cell r="M360">
             <v>4</v>
@@ -12391,25 +12391,25 @@
         </row>
         <row r="361">
           <cell r="F361" t="str">
-            <v>LL-16-3225</v>
+            <v>LL-16-3243</v>
           </cell>
           <cell r="G361" t="str">
-            <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
           </cell>
           <cell r="H361" t="str">
             <v>Y</v>
           </cell>
           <cell r="I361" t="str">
-            <v>397</v>
+            <v>417</v>
           </cell>
           <cell r="J361">
-            <v>810076213972</v>
+            <v>810076214177</v>
           </cell>
           <cell r="K361">
-            <v>50810076213977</v>
+            <v>50810076214172</v>
           </cell>
           <cell r="L361">
-            <v>30810076213973</v>
+            <v>30810076214178</v>
           </cell>
           <cell r="M361">
             <v>4</v>
@@ -12426,25 +12426,25 @@
         </row>
         <row r="362">
           <cell r="F362" t="str">
-            <v>LL-16-3243</v>
+            <v>LL-16-3493</v>
           </cell>
           <cell r="G362" t="str">
-            <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+            <v>FlowArt: Dot-By-Letter, Slow Summer</v>
           </cell>
           <cell r="H362" t="str">
             <v>Y</v>
           </cell>
           <cell r="I362" t="str">
-            <v>417</v>
+            <v>676</v>
           </cell>
           <cell r="J362">
-            <v>810076214177</v>
+            <v>810076216768</v>
           </cell>
           <cell r="K362">
-            <v>50810076214172</v>
+            <v>50810076216763</v>
           </cell>
           <cell r="L362">
-            <v>30810076214178</v>
+            <v>30810076216769</v>
           </cell>
           <cell r="M362">
             <v>4</v>
@@ -12461,25 +12461,25 @@
         </row>
         <row r="363">
           <cell r="F363" t="str">
-            <v>LL-16-3493</v>
+            <v>LL-16-3407</v>
           </cell>
           <cell r="G363" t="str">
-            <v>FlowArt: Dot-By-Letter, Slow Summer</v>
+            <v>FlowArt: Dot-By-Letter, Farmers Market Morning [Pastel]</v>
           </cell>
           <cell r="H363" t="str">
             <v>Y</v>
           </cell>
           <cell r="I363" t="str">
-            <v>676</v>
+            <v>607</v>
           </cell>
           <cell r="J363">
-            <v>810076216768</v>
+            <v>810076216072</v>
           </cell>
           <cell r="K363">
-            <v>50810076216763</v>
+            <v>50810076216077</v>
           </cell>
           <cell r="L363">
-            <v>30810076216769</v>
+            <v>30810076216073</v>
           </cell>
           <cell r="M363">
             <v>4</v>
@@ -17395,7 +17395,7 @@
             <v>FlowArt 3Pck: Lovestruck + Sweetened + Inspo</v>
           </cell>
           <cell r="H508" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I508" t="str">
             <v>714</v>
@@ -17427,7 +17427,7 @@
             <v>FlowArt 3Pck: Birdsong + Sparkle + Deep</v>
           </cell>
           <cell r="H509" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I509" t="str">
             <v>715</v>
@@ -17459,7 +17459,7 @@
             <v>FlowArt 3Pck: Blooms + Coastline + Animals</v>
           </cell>
           <cell r="H510" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I510" t="str">
             <v>716</v>
@@ -17491,7 +17491,7 @@
             <v>FlowArt 3Pck: Pets + Horizons + TPara</v>
           </cell>
           <cell r="H511" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I511" t="str">
             <v>717</v>
@@ -17523,7 +17523,7 @@
             <v>FlowArt 3Pck: Pets + Horizons + Botanicals</v>
           </cell>
           <cell r="H512" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I512" t="str">
             <v>718</v>
@@ -17555,7 +17555,7 @@
             <v>FlowArt 3Pck: Me Time + Bow + Bookshelf</v>
           </cell>
           <cell r="H513" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I513" t="str">
             <v>719</v>
@@ -17587,7 +17587,7 @@
             <v>FlowArt 3Pck: Jungle + Desert + TPara</v>
           </cell>
           <cell r="H514" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I514" t="str">
             <v>720</v>
@@ -17619,7 +17619,7 @@
             <v>FlowArt 3Pck: Homegrown + Cheeky + Home Sweet Home</v>
           </cell>
           <cell r="H515" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I515" t="str">
             <v>721</v>
@@ -17651,7 +17651,7 @@
             <v>FlowArt 3Pck: Homegrown + Cheeky + Tranquil Waters</v>
           </cell>
           <cell r="H516" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I516" t="str">
             <v>722</v>
@@ -17683,7 +17683,7 @@
             <v>FlowArt 3Pck: Stitch Line 1 + Stitch Line 2 + Embroidery</v>
           </cell>
           <cell r="H517" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I517" t="str">
             <v>723</v>
@@ -17715,7 +17715,7 @@
             <v>FlowArt 3Pck: Lace + Quilting + Homegrown</v>
           </cell>
           <cell r="H518" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I518" t="str">
             <v>724</v>
@@ -17747,7 +17747,7 @@
             <v>FlowArt 3Pck: Butterfly + Botanicals + Birdsong [Metallic]</v>
           </cell>
           <cell r="H519" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I519" t="str">
             <v>725</v>
@@ -21604,25 +21604,16 @@
         </row>
         <row r="640">
           <cell r="F640" t="str">
-            <v>LL-WM-0005</v>
+            <v>LL-WM-9950</v>
           </cell>
           <cell r="G640" t="str">
-            <v>May26 Sidekick - FA - WALMART - 12</v>
+            <v>FY27Q1 Endcap - FA - WMT - EMPTY</v>
           </cell>
           <cell r="H640" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I640" t="str">
-            <v>511</v>
-          </cell>
-          <cell r="J640">
-            <v>810076215112</v>
-          </cell>
-          <cell r="K640">
-            <v>50810076215117</v>
-          </cell>
-          <cell r="L640">
-            <v>30810076215113</v>
+            <v/>
           </cell>
           <cell r="M640">
             <v>0</v>
@@ -21630,22 +21621,28 @@
           <cell r="N640">
             <v>1</v>
           </cell>
-          <cell r="P640">
-            <v>60</v>
-          </cell>
         </row>
         <row r="641">
           <cell r="F641" t="str">
-            <v>LL-WM-9905</v>
+            <v>LL-WM-0045</v>
           </cell>
           <cell r="G641" t="str">
-            <v>May26 Sidekick - FA - WALMART - Empty</v>
+            <v>FY27Q1 Endcap - FA - WMT - 9 - SHELF #1</v>
           </cell>
           <cell r="H641" t="str">
             <v>N</v>
           </cell>
           <cell r="I641" t="str">
-            <v/>
+            <v>726</v>
+          </cell>
+          <cell r="J641">
+            <v>810076217260</v>
+          </cell>
+          <cell r="K641">
+            <v>50810076217265</v>
+          </cell>
+          <cell r="L641">
+            <v>30810076217261</v>
           </cell>
           <cell r="M641">
             <v>0</v>
@@ -21654,24 +21651,30 @@
             <v>1</v>
           </cell>
           <cell r="P641">
-            <v>0</v>
+            <v>45</v>
           </cell>
         </row>
         <row r="642">
           <cell r="F642" t="str">
-            <v>LL-WM-0006</v>
+            <v>LL-WM-0046</v>
           </cell>
           <cell r="G642" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - 16</v>
+            <v>FY27Q1 Endcap - FA - WMT - 9 - SHELF #2</v>
           </cell>
           <cell r="H642" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I642" t="str">
-            <v>559</v>
+            <v>727</v>
           </cell>
           <cell r="J642">
-            <v>810076215594</v>
+            <v>810076217277</v>
+          </cell>
+          <cell r="K642">
+            <v>50810076217272</v>
+          </cell>
+          <cell r="L642">
+            <v>30810076217278</v>
           </cell>
           <cell r="M642">
             <v>0</v>
@@ -21680,21 +21683,30 @@
             <v>1</v>
           </cell>
           <cell r="P642">
-            <v>80</v>
+            <v>45</v>
           </cell>
         </row>
         <row r="643">
           <cell r="F643" t="str">
-            <v>LL-WM-9906</v>
+            <v>LL-WM-0047</v>
           </cell>
           <cell r="G643" t="str">
-            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
+            <v>FY27Q1 Endcap - FA - WMT - 9 - SHELF #3</v>
           </cell>
           <cell r="H643" t="str">
             <v>N</v>
           </cell>
           <cell r="I643" t="str">
-            <v/>
+            <v>728</v>
+          </cell>
+          <cell r="J643">
+            <v>810076217284</v>
+          </cell>
+          <cell r="K643">
+            <v>50810076217289</v>
+          </cell>
+          <cell r="L643">
+            <v>30810076217285</v>
           </cell>
           <cell r="M643">
             <v>0</v>
@@ -21703,30 +21715,30 @@
             <v>1</v>
           </cell>
           <cell r="P643">
-            <v>0</v>
+            <v>45</v>
           </cell>
         </row>
         <row r="644">
           <cell r="F644" t="str">
-            <v>LL-00-0011</v>
+            <v>LL-WM-0048</v>
           </cell>
           <cell r="G644" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>FY27Q1 Endcap - FA - WMT - 9 - SHELF #4</v>
           </cell>
           <cell r="H644" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I644" t="str">
-            <v>405</v>
+            <v>729</v>
           </cell>
           <cell r="J644">
-            <v>810076214054</v>
+            <v>810076217291</v>
           </cell>
           <cell r="K644">
-            <v>50810076214059</v>
+            <v>50810076217296</v>
           </cell>
           <cell r="L644">
-            <v>30810076214055</v>
+            <v>30810076217292</v>
           </cell>
           <cell r="M644">
             <v>0</v>
@@ -21735,30 +21747,30 @@
             <v>1</v>
           </cell>
           <cell r="P644">
-            <v>252</v>
+            <v>45</v>
           </cell>
         </row>
         <row r="645">
           <cell r="F645" t="str">
-            <v>LL-99-0011</v>
+            <v>LL-WM-0049</v>
           </cell>
           <cell r="G645" t="str">
-            <v>BTS FA Mini Empty</v>
+            <v>FY27Q1 Endcap - FA - WMT - 9 - SHELF #5</v>
           </cell>
           <cell r="H645" t="str">
             <v>N</v>
           </cell>
           <cell r="I645" t="str">
-            <v>406</v>
+            <v>730</v>
           </cell>
           <cell r="J645">
-            <v>810076214061</v>
+            <v>810076217307</v>
           </cell>
           <cell r="K645">
-            <v>50810076214066</v>
+            <v>50810076217302</v>
           </cell>
           <cell r="L645">
-            <v>30810076214062</v>
+            <v>30810076217308</v>
           </cell>
           <cell r="M645">
             <v>0</v>
@@ -21766,28 +21778,31 @@
           <cell r="N645">
             <v>1</v>
           </cell>
+          <cell r="P645">
+            <v>45</v>
+          </cell>
         </row>
         <row r="646">
           <cell r="F646" t="str">
-            <v>LL-01-2026</v>
+            <v>LL-WM-0005</v>
           </cell>
           <cell r="G646" t="str">
-            <v>2026 Product Catalogue</v>
+            <v>May26 Sidekick - FA - WALMART - 12</v>
           </cell>
           <cell r="H646" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I646" t="str">
-            <v>413</v>
+            <v>511</v>
           </cell>
           <cell r="J646">
-            <v>810076214139</v>
+            <v>810076215112</v>
           </cell>
           <cell r="K646">
-            <v>50810076214134</v>
+            <v>50810076215117</v>
           </cell>
           <cell r="L646">
-            <v>30810076214130</v>
+            <v>30810076215113</v>
           </cell>
           <cell r="M646">
             <v>0</v>
@@ -21795,13 +21810,16 @@
           <cell r="N646">
             <v>1</v>
           </cell>
+          <cell r="P646">
+            <v>60</v>
+          </cell>
         </row>
         <row r="647">
           <cell r="F647" t="str">
-            <v>LL-02-2026</v>
+            <v>LL-WM-9905</v>
           </cell>
           <cell r="G647" t="str">
-            <v>2026 Product Catalogue - H2</v>
+            <v>May26 Sidekick - FA - WALMART - Empty</v>
           </cell>
           <cell r="H647" t="str">
             <v>N</v>
@@ -21815,28 +21833,25 @@
           <cell r="N647">
             <v>1</v>
           </cell>
+          <cell r="P647">
+            <v>0</v>
+          </cell>
         </row>
         <row r="648">
           <cell r="F648" t="str">
-            <v>LL-00-0014</v>
+            <v>LL-WM-0006</v>
           </cell>
           <cell r="G648" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>Oct26 Sidekick - FA - WALMART - 16</v>
           </cell>
           <cell r="H648" t="str">
             <v>Y</v>
           </cell>
           <cell r="I648" t="str">
-            <v>437</v>
+            <v>559</v>
           </cell>
           <cell r="J648">
-            <v>810076214375</v>
-          </cell>
-          <cell r="K648">
-            <v>50810076214370</v>
-          </cell>
-          <cell r="L648">
-            <v>30810076214376</v>
+            <v>810076215594</v>
           </cell>
           <cell r="M648">
             <v>0</v>
@@ -21845,30 +21860,21 @@
             <v>1</v>
           </cell>
           <cell r="P648">
-            <v>126</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="649">
           <cell r="F649" t="str">
-            <v>LL-99-0014</v>
+            <v>LL-WM-9906</v>
           </cell>
           <cell r="G649" t="str">
-            <v>FA Mini - Counter Display - Empty</v>
+            <v>Oct26 Sidekick - FA - WALMART - Empty</v>
           </cell>
           <cell r="H649" t="str">
             <v>N</v>
           </cell>
           <cell r="I649" t="str">
-            <v>619</v>
-          </cell>
-          <cell r="J649">
-            <v>810076216195</v>
-          </cell>
-          <cell r="K649">
-            <v>50810076216190</v>
-          </cell>
-          <cell r="L649">
-            <v>30810076216196</v>
+            <v/>
           </cell>
           <cell r="M649">
             <v>0</v>
@@ -21876,28 +21882,31 @@
           <cell r="N649">
             <v>1</v>
           </cell>
+          <cell r="P649">
+            <v>0</v>
+          </cell>
         </row>
         <row r="650">
           <cell r="F650" t="str">
-            <v>LL-00-0032</v>
+            <v>LL-00-0011</v>
           </cell>
           <cell r="G650" t="str">
-            <v>FA Mini - PDQ Display - Full - 6</v>
+            <v>BTS Sidecap - FA Minis</v>
           </cell>
           <cell r="H650" t="str">
             <v>Y</v>
           </cell>
           <cell r="I650" t="str">
-            <v>562</v>
+            <v>405</v>
           </cell>
           <cell r="J650">
-            <v>810076215624</v>
+            <v>810076214054</v>
           </cell>
           <cell r="K650">
-            <v>50810076215629</v>
+            <v>50810076214059</v>
           </cell>
           <cell r="L650">
-            <v>30810076215625</v>
+            <v>30810076214055</v>
           </cell>
           <cell r="M650">
             <v>0</v>
@@ -21906,21 +21915,30 @@
             <v>1</v>
           </cell>
           <cell r="P650">
-            <v>21</v>
+            <v>252</v>
           </cell>
         </row>
         <row r="651">
           <cell r="F651" t="str">
-            <v>LL-99-0032</v>
+            <v>LL-99-0011</v>
           </cell>
           <cell r="G651" t="str">
-            <v>FA Mini - PDQ Display - Empty</v>
+            <v>BTS FA Mini Empty</v>
           </cell>
           <cell r="H651" t="str">
             <v>N</v>
           </cell>
           <cell r="I651" t="str">
-            <v/>
+            <v>406</v>
+          </cell>
+          <cell r="J651">
+            <v>810076214061</v>
+          </cell>
+          <cell r="K651">
+            <v>50810076214066</v>
+          </cell>
+          <cell r="L651">
+            <v>30810076214062</v>
           </cell>
           <cell r="M651">
             <v>0</v>
@@ -21931,25 +21949,25 @@
         </row>
         <row r="652">
           <cell r="F652" t="str">
-            <v>LL-00-0034</v>
+            <v>LL-01-2026</v>
           </cell>
           <cell r="G652" t="str">
-            <v>FA Mini - Stew Leonard - 36</v>
+            <v>2026 Product Catalogue</v>
           </cell>
           <cell r="H652" t="str">
             <v>N</v>
           </cell>
           <cell r="I652" t="str">
-            <v>577</v>
+            <v>413</v>
           </cell>
           <cell r="J652">
-            <v>810076215778</v>
+            <v>810076214139</v>
           </cell>
           <cell r="K652">
-            <v>50810076215773</v>
+            <v>50810076214134</v>
           </cell>
           <cell r="L652">
-            <v>30810076215779</v>
+            <v>30810076214130</v>
           </cell>
           <cell r="M652">
             <v>0</v>
@@ -21957,31 +21975,19 @@
           <cell r="N652">
             <v>1</v>
           </cell>
-          <cell r="P652">
-            <v>21</v>
-          </cell>
         </row>
         <row r="653">
           <cell r="F653" t="str">
-            <v>LL-00-0015</v>
+            <v>LL-02-2026</v>
           </cell>
           <cell r="G653" t="str">
-            <v>FA Holiday Mini - Counter Display - Full</v>
+            <v>2026 Product Catalogue - H2</v>
           </cell>
           <cell r="H653" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I653" t="str">
-            <v>438</v>
-          </cell>
-          <cell r="J653">
-            <v>810076214382</v>
-          </cell>
-          <cell r="K653">
-            <v>50810076214387</v>
-          </cell>
-          <cell r="L653">
-            <v>30810076214383</v>
+            <v/>
           </cell>
           <cell r="M653">
             <v>0</v>
@@ -21989,22 +21995,28 @@
           <cell r="N653">
             <v>1</v>
           </cell>
-          <cell r="P653">
-            <v>126</v>
-          </cell>
         </row>
         <row r="654">
           <cell r="F654" t="str">
-            <v>LL-99-0015</v>
+            <v>LL-00-0014</v>
           </cell>
           <cell r="G654" t="str">
-            <v>FA Holiday Mini - Counter Display - Empty</v>
+            <v>FA Mini - Counter Display - Full</v>
           </cell>
           <cell r="H654" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I654" t="str">
-            <v/>
+            <v>437</v>
+          </cell>
+          <cell r="J654">
+            <v>810076214375</v>
+          </cell>
+          <cell r="K654">
+            <v>50810076214370</v>
+          </cell>
+          <cell r="L654">
+            <v>30810076214376</v>
           </cell>
           <cell r="M654">
             <v>0</v>
@@ -22012,57 +22024,60 @@
           <cell r="N654">
             <v>1</v>
           </cell>
+          <cell r="P654">
+            <v>126</v>
+          </cell>
         </row>
         <row r="655">
           <cell r="F655" t="str">
-            <v>LL-99-3087</v>
+            <v>LL-99-0014</v>
           </cell>
           <cell r="G655" t="str">
-            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+            <v>FA Mini - Counter Display - Empty</v>
           </cell>
           <cell r="H655" t="str">
             <v>N</v>
           </cell>
           <cell r="I655" t="str">
-            <v>214</v>
+            <v>619</v>
           </cell>
           <cell r="J655">
-            <v>810076212142</v>
+            <v>810076216195</v>
           </cell>
           <cell r="K655">
-            <v>50810076212147</v>
+            <v>50810076216190</v>
           </cell>
           <cell r="L655">
-            <v>30810076212143</v>
-          </cell>
-          <cell r="O655">
+            <v>30810076216196</v>
+          </cell>
+          <cell r="M655">
             <v>0</v>
           </cell>
-          <cell r="P655">
-            <v>0</v>
+          <cell r="N655">
+            <v>1</v>
           </cell>
         </row>
         <row r="656">
           <cell r="F656" t="str">
-            <v>LL-00-0017</v>
+            <v>LL-00-0032</v>
           </cell>
           <cell r="G656" t="str">
-            <v>Writing - Counter Display - Full</v>
+            <v>FA Mini - PDQ Display - Full - 6</v>
           </cell>
           <cell r="H656" t="str">
             <v>Y</v>
           </cell>
           <cell r="I656" t="str">
-            <v>440</v>
+            <v>562</v>
           </cell>
           <cell r="J656">
-            <v>810076214405</v>
+            <v>810076215624</v>
           </cell>
           <cell r="K656">
-            <v>50810076214400</v>
+            <v>50810076215629</v>
           </cell>
           <cell r="L656">
-            <v>30810076214406</v>
+            <v>30810076215625</v>
           </cell>
           <cell r="M656">
             <v>0</v>
@@ -22070,28 +22085,22 @@
           <cell r="N656">
             <v>1</v>
           </cell>
+          <cell r="P656">
+            <v>21</v>
+          </cell>
         </row>
         <row r="657">
           <cell r="F657" t="str">
-            <v>LL-00-0012</v>
+            <v>LL-99-0032</v>
           </cell>
           <cell r="G657" t="str">
-            <v>Holiday Sidecap - FA Minis</v>
+            <v>FA Mini - PDQ Display - Empty</v>
           </cell>
           <cell r="H657" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I657" t="str">
-            <v>430</v>
-          </cell>
-          <cell r="J657">
-            <v>810076214306</v>
-          </cell>
-          <cell r="K657">
-            <v>50810076214301</v>
-          </cell>
-          <cell r="L657">
-            <v>30810076214307</v>
+            <v/>
           </cell>
           <cell r="M657">
             <v>0</v>
@@ -22102,25 +22111,25 @@
         </row>
         <row r="658">
           <cell r="F658" t="str">
-            <v>LL-99-0012</v>
+            <v>LL-00-0034</v>
           </cell>
           <cell r="G658" t="str">
-            <v>Holiday FA Mini Empty</v>
+            <v>FA Mini - Stew Leonard - 36</v>
           </cell>
           <cell r="H658" t="str">
             <v>N</v>
           </cell>
           <cell r="I658" t="str">
-            <v>431</v>
+            <v>577</v>
           </cell>
           <cell r="J658">
-            <v>810076214313</v>
+            <v>810076215778</v>
           </cell>
           <cell r="K658">
-            <v>50810076214318</v>
+            <v>50810076215773</v>
           </cell>
           <cell r="L658">
-            <v>30810076214314</v>
+            <v>30810076215779</v>
           </cell>
           <cell r="M658">
             <v>0</v>
@@ -22129,30 +22138,30 @@
             <v>1</v>
           </cell>
           <cell r="P658">
-            <v>252</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="659">
           <cell r="F659" t="str">
-            <v>LL-00-0024</v>
+            <v>LL-00-0015</v>
           </cell>
           <cell r="G659" t="str">
-            <v>FlowArt Grocery Display Evergreen - 24</v>
+            <v>FA Holiday Mini - Counter Display - Full</v>
           </cell>
           <cell r="H659" t="str">
             <v>Y</v>
           </cell>
           <cell r="I659" t="str">
-            <v>517</v>
+            <v>438</v>
           </cell>
           <cell r="J659">
-            <v>810076215174</v>
+            <v>810076214382</v>
           </cell>
           <cell r="K659">
-            <v>50810076215179</v>
+            <v>50810076214387</v>
           </cell>
           <cell r="L659">
-            <v>30810076215175</v>
+            <v>30810076214383</v>
           </cell>
           <cell r="M659">
             <v>0</v>
@@ -22160,19 +22169,16 @@
           <cell r="N659">
             <v>1</v>
           </cell>
-          <cell r="O659">
-            <v>159.84</v>
-          </cell>
           <cell r="P659">
-            <v>120</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="660">
           <cell r="F660" t="str">
-            <v>LL-99-0024</v>
+            <v>LL-99-0015</v>
           </cell>
           <cell r="G660" t="str">
-            <v>FlowArt Grocery Display Evergreen - Empty</v>
+            <v>FA Holiday Mini - Counter Display - Empty</v>
           </cell>
           <cell r="H660" t="str">
             <v>N</v>
@@ -22189,51 +22195,54 @@
         </row>
         <row r="661">
           <cell r="F661" t="str">
-            <v>LL-00-0025</v>
+            <v>LL-99-3087</v>
           </cell>
           <cell r="G661" t="str">
-            <v>FlowArt Summer Grocery Display - 24</v>
+            <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
           </cell>
           <cell r="H661" t="str">
             <v>N</v>
           </cell>
           <cell r="I661" t="str">
-            <v>518</v>
+            <v>214</v>
           </cell>
           <cell r="J661">
-            <v>810076215181</v>
+            <v>810076212142</v>
           </cell>
           <cell r="K661">
-            <v>50810076215186</v>
+            <v>50810076212147</v>
           </cell>
           <cell r="L661">
-            <v>30810076215182</v>
-          </cell>
-          <cell r="M661">
+            <v>30810076212143</v>
+          </cell>
+          <cell r="O661">
             <v>0</v>
           </cell>
-          <cell r="N661">
-            <v>1</v>
-          </cell>
-          <cell r="O661">
-            <v>159.84</v>
-          </cell>
           <cell r="P661">
-            <v>120</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="662">
           <cell r="F662" t="str">
-            <v>LL-99-0025</v>
+            <v>LL-00-0017</v>
           </cell>
           <cell r="G662" t="str">
-            <v>FlowArt Summer Grocery Display - Empty</v>
+            <v>Writing - Counter Display - Full</v>
           </cell>
           <cell r="H662" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I662" t="str">
-            <v/>
+            <v>440</v>
+          </cell>
+          <cell r="J662">
+            <v>810076214405</v>
+          </cell>
+          <cell r="K662">
+            <v>50810076214400</v>
+          </cell>
+          <cell r="L662">
+            <v>30810076214406</v>
           </cell>
           <cell r="M662">
             <v>0</v>
@@ -22244,25 +22253,25 @@
         </row>
         <row r="663">
           <cell r="F663" t="str">
-            <v>LL-00-0026</v>
+            <v>LL-00-0012</v>
           </cell>
           <cell r="G663" t="str">
-            <v>FlowArt Fall Grocery Display - 24</v>
+            <v>Holiday Sidecap - FA Minis</v>
           </cell>
           <cell r="H663" t="str">
             <v>Y</v>
           </cell>
           <cell r="I663" t="str">
-            <v>519</v>
+            <v>430</v>
           </cell>
           <cell r="J663">
-            <v>810076215198</v>
+            <v>810076214306</v>
           </cell>
           <cell r="K663">
-            <v>50810076215193</v>
+            <v>50810076214301</v>
           </cell>
           <cell r="L663">
-            <v>30810076215199</v>
+            <v>30810076214307</v>
           </cell>
           <cell r="M663">
             <v>0</v>
@@ -22270,25 +22279,28 @@
           <cell r="N663">
             <v>1</v>
           </cell>
-          <cell r="O663">
-            <v>159.84</v>
-          </cell>
-          <cell r="P663">
-            <v>120</v>
-          </cell>
         </row>
         <row r="664">
           <cell r="F664" t="str">
-            <v>LL-99-0026</v>
+            <v>LL-99-0012</v>
           </cell>
           <cell r="G664" t="str">
-            <v>FlowArt Fall Grocery Display - Empty</v>
+            <v>Holiday FA Mini Empty</v>
           </cell>
           <cell r="H664" t="str">
             <v>N</v>
           </cell>
           <cell r="I664" t="str">
-            <v/>
+            <v>431</v>
+          </cell>
+          <cell r="J664">
+            <v>810076214313</v>
+          </cell>
+          <cell r="K664">
+            <v>50810076214318</v>
+          </cell>
+          <cell r="L664">
+            <v>30810076214314</v>
           </cell>
           <cell r="M664">
             <v>0</v>
@@ -22296,19 +22308,31 @@
           <cell r="N664">
             <v>1</v>
           </cell>
+          <cell r="P664">
+            <v>252</v>
+          </cell>
         </row>
         <row r="665">
           <cell r="F665" t="str">
-            <v>LL-00-0026-V2</v>
+            <v>LL-00-0024</v>
           </cell>
           <cell r="G665" t="str">
-            <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
+            <v>FlowArt Grocery Display Evergreen - 24</v>
           </cell>
           <cell r="H665" t="str">
             <v>Y</v>
           </cell>
           <cell r="I665" t="str">
-            <v/>
+            <v>517</v>
+          </cell>
+          <cell r="J665">
+            <v>810076215174</v>
+          </cell>
+          <cell r="K665">
+            <v>50810076215179</v>
+          </cell>
+          <cell r="L665">
+            <v>30810076215175</v>
           </cell>
           <cell r="M665">
             <v>0</v>
@@ -22320,30 +22344,21 @@
             <v>159.84</v>
           </cell>
           <cell r="P665">
-            <v>80</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="666">
           <cell r="F666" t="str">
-            <v>LL-00-0027</v>
+            <v>LL-99-0024</v>
           </cell>
           <cell r="G666" t="str">
-            <v>FlowArt Holiday Grocery Display - 24</v>
+            <v>FlowArt Grocery Display Evergreen - Empty</v>
           </cell>
           <cell r="H666" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I666" t="str">
-            <v>520</v>
-          </cell>
-          <cell r="J666">
-            <v>810076215204</v>
-          </cell>
-          <cell r="K666">
-            <v>50810076215209</v>
-          </cell>
-          <cell r="L666">
-            <v>30810076215205</v>
+            <v/>
           </cell>
           <cell r="M666">
             <v>0</v>
@@ -22351,25 +22366,28 @@
           <cell r="N666">
             <v>1</v>
           </cell>
-          <cell r="O666">
-            <v>239.76</v>
-          </cell>
-          <cell r="P666">
-            <v>120</v>
-          </cell>
         </row>
         <row r="667">
           <cell r="F667" t="str">
-            <v>LL-99-0027</v>
+            <v>LL-00-0025</v>
           </cell>
           <cell r="G667" t="str">
-            <v>FlowArt Holiday Grocery Display - Empty</v>
+            <v>FlowArt Summer Grocery Display - 24</v>
           </cell>
           <cell r="H667" t="str">
             <v>N</v>
           </cell>
           <cell r="I667" t="str">
-            <v/>
+            <v>518</v>
+          </cell>
+          <cell r="J667">
+            <v>810076215181</v>
+          </cell>
+          <cell r="K667">
+            <v>50810076215186</v>
+          </cell>
+          <cell r="L667">
+            <v>30810076215182</v>
           </cell>
           <cell r="M667">
             <v>0</v>
@@ -22378,7 +22396,7 @@
             <v>1</v>
           </cell>
           <cell r="O667">
-            <v>239.76</v>
+            <v>159.84</v>
           </cell>
           <cell r="P667">
             <v>120</v>
@@ -22386,25 +22404,16 @@
         </row>
         <row r="668">
           <cell r="F668" t="str">
-            <v>LL-00-0028</v>
+            <v>LL-99-0025</v>
           </cell>
           <cell r="G668" t="str">
-            <v>FlowArt Mini Grocery Display - 36</v>
+            <v>FlowArt Summer Grocery Display - Empty</v>
           </cell>
           <cell r="H668" t="str">
             <v>N</v>
           </cell>
           <cell r="I668" t="str">
-            <v>521</v>
-          </cell>
-          <cell r="J668">
-            <v>810076215211</v>
-          </cell>
-          <cell r="K668">
-            <v>50810076215216</v>
-          </cell>
-          <cell r="L668">
-            <v>30810076215212</v>
+            <v/>
           </cell>
           <cell r="M668">
             <v>0</v>
@@ -22412,25 +22421,28 @@
           <cell r="N668">
             <v>1</v>
           </cell>
-          <cell r="O668">
-            <v>251.64000000000001</v>
-          </cell>
-          <cell r="P668">
-            <v>126</v>
-          </cell>
         </row>
         <row r="669">
           <cell r="F669" t="str">
-            <v>LL-99-0028</v>
+            <v>LL-00-0026</v>
           </cell>
           <cell r="G669" t="str">
-            <v>FlowArt Mini Grocery Display - Empty</v>
+            <v>FlowArt Fall Grocery Display - 24</v>
           </cell>
           <cell r="H669" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I669" t="str">
-            <v/>
+            <v>519</v>
+          </cell>
+          <cell r="J669">
+            <v>810076215198</v>
+          </cell>
+          <cell r="K669">
+            <v>50810076215193</v>
+          </cell>
+          <cell r="L669">
+            <v>30810076215199</v>
           </cell>
           <cell r="M669">
             <v>0</v>
@@ -22439,33 +22451,24 @@
             <v>1</v>
           </cell>
           <cell r="O669">
-            <v>251.64000000000001</v>
+            <v>159.84</v>
           </cell>
           <cell r="P669">
-            <v>126</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="670">
           <cell r="F670" t="str">
-            <v>LL-00-0029</v>
+            <v>LL-99-0026</v>
           </cell>
           <cell r="G670" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - 36</v>
+            <v>FlowArt Fall Grocery Display - Empty</v>
           </cell>
           <cell r="H670" t="str">
             <v>N</v>
           </cell>
           <cell r="I670" t="str">
-            <v>522</v>
-          </cell>
-          <cell r="J670">
-            <v>810076215228</v>
-          </cell>
-          <cell r="K670">
-            <v>50810076215223</v>
-          </cell>
-          <cell r="L670">
-            <v>30810076215229</v>
+            <v/>
           </cell>
           <cell r="M670">
             <v>0</v>
@@ -22473,22 +22476,16 @@
           <cell r="N670">
             <v>1</v>
           </cell>
-          <cell r="O670">
-            <v>251.64000000000001</v>
-          </cell>
-          <cell r="P670">
-            <v>126</v>
-          </cell>
         </row>
         <row r="671">
           <cell r="F671" t="str">
-            <v>LL-99-0029</v>
+            <v>LL-00-0026-V2</v>
           </cell>
           <cell r="G671" t="str">
-            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
+            <v>FlowArt Fall Grocery Display - 24 - Version 2</v>
           </cell>
           <cell r="H671" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I671" t="str">
             <v/>
@@ -22500,24 +22497,33 @@
             <v>1</v>
           </cell>
           <cell r="O671">
-            <v>251.64000000000001</v>
+            <v>159.84</v>
           </cell>
           <cell r="P671">
-            <v>126</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="672">
           <cell r="F672" t="str">
-            <v>LL-00-0040</v>
+            <v>LL-00-0027</v>
           </cell>
           <cell r="G672" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
+            <v>FlowArt Holiday Grocery Display - 24</v>
           </cell>
           <cell r="H672" t="str">
             <v>Y</v>
           </cell>
           <cell r="I672" t="str">
-            <v/>
+            <v>520</v>
+          </cell>
+          <cell r="J672">
+            <v>810076215204</v>
+          </cell>
+          <cell r="K672">
+            <v>50810076215209</v>
+          </cell>
+          <cell r="L672">
+            <v>30810076215205</v>
           </cell>
           <cell r="M672">
             <v>0</v>
@@ -22526,18 +22532,18 @@
             <v>1</v>
           </cell>
           <cell r="O672">
-            <v>251.64000000000001</v>
+            <v>239.76</v>
           </cell>
           <cell r="P672">
-            <v>126</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="673">
           <cell r="F673" t="str">
-            <v>LL-99-0040</v>
+            <v>LL-99-0027</v>
           </cell>
           <cell r="G673" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #1</v>
+            <v>FlowArt Holiday Grocery Display - Empty</v>
           </cell>
           <cell r="H673" t="str">
             <v>N</v>
@@ -22552,24 +22558,33 @@
             <v>1</v>
           </cell>
           <cell r="O673">
-            <v>251.64000000000001</v>
+            <v>239.76</v>
           </cell>
           <cell r="P673">
-            <v>126</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="674">
           <cell r="F674" t="str">
-            <v>LL-00-0041</v>
+            <v>LL-00-0028</v>
           </cell>
           <cell r="G674" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 72 - #2</v>
+            <v>FlowArt Mini Grocery Display - 36</v>
           </cell>
           <cell r="H674" t="str">
             <v>N</v>
           </cell>
           <cell r="I674" t="str">
-            <v/>
+            <v>521</v>
+          </cell>
+          <cell r="J674">
+            <v>810076215211</v>
+          </cell>
+          <cell r="K674">
+            <v>50810076215216</v>
+          </cell>
+          <cell r="L674">
+            <v>30810076215212</v>
           </cell>
           <cell r="M674">
             <v>0</v>
@@ -22586,10 +22601,10 @@
         </row>
         <row r="675">
           <cell r="F675" t="str">
-            <v>LL-99-0041</v>
+            <v>LL-99-0028</v>
           </cell>
           <cell r="G675" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #2</v>
+            <v>FlowArt Mini Grocery Display - Empty</v>
           </cell>
           <cell r="H675" t="str">
             <v>N</v>
@@ -22612,25 +22627,25 @@
         </row>
         <row r="676">
           <cell r="F676" t="str">
-            <v>LL-00-0042</v>
+            <v>LL-00-0029</v>
           </cell>
           <cell r="G676" t="str">
-            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - 72 - #1</v>
+            <v>FlowArt Mini Holiday Grocery Display - 36</v>
           </cell>
           <cell r="H676" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I676" t="str">
-            <v>664</v>
+            <v>522</v>
           </cell>
           <cell r="J676">
-            <v>810076216645</v>
+            <v>810076215228</v>
           </cell>
           <cell r="K676">
-            <v>50810076216640</v>
+            <v>50810076215223</v>
           </cell>
           <cell r="L676">
-            <v>30810076216646</v>
+            <v>30810076215229</v>
           </cell>
           <cell r="M676">
             <v>0</v>
@@ -22647,10 +22662,10 @@
         </row>
         <row r="677">
           <cell r="F677" t="str">
-            <v>LL-99-0042</v>
+            <v>LL-99-0029</v>
           </cell>
           <cell r="G677" t="str">
-            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - EMPTY - #1</v>
+            <v>FlowArt Mini Holiday Grocery Display - Empty</v>
           </cell>
           <cell r="H677" t="str">
             <v>N</v>
@@ -22673,25 +22688,16 @@
         </row>
         <row r="678">
           <cell r="F678" t="str">
-            <v>LL-00-0037</v>
+            <v>LL-00-0040</v>
           </cell>
           <cell r="G678" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
+            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
           </cell>
           <cell r="H678" t="str">
             <v>Y</v>
           </cell>
           <cell r="I678" t="str">
-            <v>647</v>
-          </cell>
-          <cell r="J678">
-            <v>810076216478</v>
-          </cell>
-          <cell r="K678">
-            <v>50810076216473</v>
-          </cell>
-          <cell r="L678">
-            <v>30810076216479</v>
+            <v/>
           </cell>
           <cell r="M678">
             <v>0</v>
@@ -22708,10 +22714,10 @@
         </row>
         <row r="679">
           <cell r="F679" t="str">
-            <v>LL-99-0037</v>
+            <v>LL-99-0040</v>
           </cell>
           <cell r="G679" t="str">
-            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #1</v>
           </cell>
           <cell r="H679" t="str">
             <v>N</v>
@@ -22734,10 +22740,10 @@
         </row>
         <row r="680">
           <cell r="F680" t="str">
-            <v>LL-DG-9930</v>
+            <v>LL-00-0041</v>
           </cell>
           <cell r="G680" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
+            <v>FlowArt MINI EXPRESS - WMT - 60 - #2</v>
           </cell>
           <cell r="H680" t="str">
             <v>N</v>
@@ -22751,28 +22757,25 @@
           <cell r="N680">
             <v>1</v>
           </cell>
+          <cell r="O680">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P680">
+            <v>126</v>
+          </cell>
         </row>
         <row r="681">
           <cell r="F681" t="str">
-            <v>LL-DG-0030</v>
+            <v>LL-99-0041</v>
           </cell>
           <cell r="G681" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
+            <v>FlowArt MINI EXPRESS - WMT - EMPTY- #2</v>
           </cell>
           <cell r="H681" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I681" t="str">
-            <v>557</v>
-          </cell>
-          <cell r="J681">
-            <v>810076215570</v>
-          </cell>
-          <cell r="K681">
-            <v>50810076215575</v>
-          </cell>
-          <cell r="L681">
-            <v>30810076215571</v>
+            <v/>
           </cell>
           <cell r="M681">
             <v>0</v>
@@ -22781,33 +22784,33 @@
             <v>1</v>
           </cell>
           <cell r="O681">
-            <v>179.64000000000001</v>
+            <v>251.64000000000001</v>
           </cell>
           <cell r="P681">
-            <v>80.28</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="682">
           <cell r="F682" t="str">
-            <v>LL-DG-0031</v>
+            <v>LL-00-0042</v>
           </cell>
           <cell r="G682" t="str">
-            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
+            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - 72 - #1</v>
           </cell>
           <cell r="H682" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I682" t="str">
-            <v>558</v>
+            <v>664</v>
           </cell>
           <cell r="J682">
-            <v>810076215587</v>
+            <v>810076216645</v>
           </cell>
           <cell r="K682">
-            <v>50810076215582</v>
+            <v>50810076216640</v>
           </cell>
           <cell r="L682">
-            <v>30810076215588</v>
+            <v>30810076216646</v>
           </cell>
           <cell r="M682">
             <v>0</v>
@@ -22816,18 +22819,18 @@
             <v>1</v>
           </cell>
           <cell r="O682">
-            <v>179.64000000000001</v>
+            <v>251.64000000000001</v>
           </cell>
           <cell r="P682">
-            <v>80.28</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="683">
           <cell r="F683" t="str">
-            <v>LL-99-0039</v>
+            <v>LL-99-0042</v>
           </cell>
           <cell r="G683" t="str">
-            <v>FlowArt MINI Spring Display - Empty</v>
+            <v>FlowArt MINI EXPRESS - TGT Cross-Stitch - EMPTY - #1</v>
           </cell>
           <cell r="H683" t="str">
             <v>N</v>
@@ -22841,28 +22844,34 @@
           <cell r="N683">
             <v>1</v>
           </cell>
+          <cell r="O683">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P683">
+            <v>126</v>
+          </cell>
         </row>
         <row r="684">
           <cell r="F684" t="str">
-            <v>LL-00-0039</v>
+            <v>LL-00-0037</v>
           </cell>
           <cell r="G684" t="str">
-            <v>FlowArt MINI Spring Display - 36</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - 40</v>
           </cell>
           <cell r="H684" t="str">
             <v>Y</v>
           </cell>
           <cell r="I684" t="str">
-            <v>634</v>
+            <v>647</v>
           </cell>
           <cell r="J684">
-            <v>810076216348</v>
+            <v>810076216478</v>
           </cell>
           <cell r="K684">
-            <v>50810076216343</v>
+            <v>50810076216473</v>
           </cell>
           <cell r="L684">
-            <v>30810076216349</v>
+            <v>30810076216479</v>
           </cell>
           <cell r="M684">
             <v>0</v>
@@ -22871,18 +22880,18 @@
             <v>1</v>
           </cell>
           <cell r="O684">
-            <v>143.76</v>
+            <v>251.64000000000001</v>
           </cell>
           <cell r="P684">
-            <v>120</v>
+            <v>126</v>
           </cell>
         </row>
         <row r="685">
           <cell r="F685" t="str">
-            <v>LL-99-0038</v>
+            <v>LL-99-0037</v>
           </cell>
           <cell r="G685" t="str">
-            <v>FlowArt Spring Display - Empty</v>
+            <v>FlowArt Mini Holiday Pharmacy Display - Empty</v>
           </cell>
           <cell r="H685" t="str">
             <v>N</v>
@@ -22896,28 +22905,25 @@
           <cell r="N685">
             <v>1</v>
           </cell>
+          <cell r="O685">
+            <v>251.64000000000001</v>
+          </cell>
+          <cell r="P685">
+            <v>126</v>
+          </cell>
         </row>
         <row r="686">
           <cell r="F686" t="str">
-            <v>LL-00-0038</v>
+            <v>LL-DG-9930</v>
           </cell>
           <cell r="G686" t="str">
-            <v>FlowArt Spring Display - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - EMPTY</v>
           </cell>
           <cell r="H686" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I686" t="str">
-            <v>632</v>
-          </cell>
-          <cell r="J686">
-            <v>810076216324</v>
-          </cell>
-          <cell r="K686">
-            <v>50810076216329</v>
-          </cell>
-          <cell r="L686">
-            <v>30810076216325</v>
+            <v/>
           </cell>
           <cell r="M686">
             <v>0</v>
@@ -22925,25 +22931,28 @@
           <cell r="N686">
             <v>1</v>
           </cell>
-          <cell r="O686">
-            <v>239.76</v>
-          </cell>
-          <cell r="P686">
-            <v>120</v>
-          </cell>
         </row>
         <row r="687">
           <cell r="F687" t="str">
-            <v>LL-99-0033</v>
+            <v>LL-DG-0030</v>
           </cell>
           <cell r="G687" t="str">
-            <v>FlowArt Valentine Display - Empty</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 1 - 36</v>
           </cell>
           <cell r="H687" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I687" t="str">
-            <v/>
+            <v>557</v>
+          </cell>
+          <cell r="J687">
+            <v>810076215570</v>
+          </cell>
+          <cell r="K687">
+            <v>50810076215575</v>
+          </cell>
+          <cell r="L687">
+            <v>30810076215571</v>
           </cell>
           <cell r="M687">
             <v>0</v>
@@ -22951,28 +22960,34 @@
           <cell r="N687">
             <v>1</v>
           </cell>
+          <cell r="O687">
+            <v>179.64000000000001</v>
+          </cell>
+          <cell r="P687">
+            <v>80.28</v>
+          </cell>
         </row>
         <row r="688">
           <cell r="F688" t="str">
-            <v>LL-00-0033</v>
+            <v>LL-DG-0031</v>
           </cell>
           <cell r="G688" t="str">
-            <v>FlowArt Valentine Display - 24</v>
+            <v>FlowArt Mini EXPRESS - DISPLAY 2 - 36</v>
           </cell>
           <cell r="H688" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I688" t="str">
-            <v>576</v>
+            <v>558</v>
           </cell>
           <cell r="J688">
-            <v>810076215761</v>
+            <v>810076215587</v>
           </cell>
           <cell r="K688">
-            <v>50810076215766</v>
+            <v>50810076215582</v>
           </cell>
           <cell r="L688">
-            <v>30810076215762</v>
+            <v>30810076215588</v>
           </cell>
           <cell r="M688">
             <v>0</v>
@@ -22981,33 +22996,24 @@
             <v>1</v>
           </cell>
           <cell r="O688">
-            <v>239.76</v>
+            <v>179.64000000000001</v>
           </cell>
           <cell r="P688">
-            <v>120</v>
+            <v>80.28</v>
           </cell>
         </row>
         <row r="689">
           <cell r="F689" t="str">
-            <v>LL-00-0043</v>
+            <v>LL-99-0039</v>
           </cell>
           <cell r="G689" t="str">
-            <v>FA Mini - Fixed Assortment - 6</v>
+            <v>FlowArt MINI Spring Display - Empty</v>
           </cell>
           <cell r="H689" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I689" t="str">
-            <v>678</v>
-          </cell>
-          <cell r="J689">
-            <v>810076216782</v>
-          </cell>
-          <cell r="K689">
-            <v>50810076216787</v>
-          </cell>
-          <cell r="L689">
-            <v>30810076216783</v>
+            <v/>
           </cell>
           <cell r="M689">
             <v>0</v>
@@ -23018,25 +23024,25 @@
         </row>
         <row r="690">
           <cell r="F690" t="str">
-            <v>LL-DISP-FA-SP26</v>
+            <v>LL-00-0039</v>
           </cell>
           <cell r="G690" t="str">
-            <v>MT 2026 - FA Spring / Summer - 36</v>
+            <v>FlowArt MINI Spring Display - 36</v>
           </cell>
           <cell r="H690" t="str">
             <v>Y</v>
           </cell>
           <cell r="I690" t="str">
-            <v>473</v>
+            <v>634</v>
           </cell>
           <cell r="J690">
-            <v>810076214733</v>
+            <v>810076216348</v>
           </cell>
           <cell r="K690">
-            <v>50810076214738</v>
+            <v>50810076216343</v>
           </cell>
           <cell r="L690">
-            <v>30810076214734</v>
+            <v>30810076216349</v>
           </cell>
           <cell r="M690">
             <v>0</v>
@@ -23044,28 +23050,25 @@
           <cell r="N690">
             <v>1</v>
           </cell>
+          <cell r="O690">
+            <v>143.76</v>
+          </cell>
+          <cell r="P690">
+            <v>120</v>
+          </cell>
         </row>
         <row r="691">
           <cell r="F691" t="str">
-            <v>LL-DISP-FA-FA26</v>
+            <v>LL-99-0038</v>
           </cell>
           <cell r="G691" t="str">
-            <v>MT 2026 - FA Fall - 24</v>
+            <v>FlowArt Spring Display - Empty</v>
           </cell>
           <cell r="H691" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I691" t="str">
-            <v>474</v>
-          </cell>
-          <cell r="J691">
-            <v>810076214740</v>
-          </cell>
-          <cell r="K691">
-            <v>50810076214745</v>
-          </cell>
-          <cell r="L691">
-            <v>30810076214741</v>
+            <v/>
           </cell>
           <cell r="M691">
             <v>0</v>
@@ -23076,25 +23079,25 @@
         </row>
         <row r="692">
           <cell r="F692" t="str">
-            <v>LL-DISP-FA-WN26</v>
+            <v>LL-00-0038</v>
           </cell>
           <cell r="G692" t="str">
-            <v>MT 2026 - FA Winter - 24</v>
+            <v>FlowArt Spring Display - 24</v>
           </cell>
           <cell r="H692" t="str">
             <v>Y</v>
           </cell>
           <cell r="I692" t="str">
-            <v>475</v>
+            <v>632</v>
           </cell>
           <cell r="J692">
-            <v>810076214757</v>
+            <v>810076216324</v>
           </cell>
           <cell r="K692">
-            <v>50810076214752</v>
+            <v>50810076216329</v>
           </cell>
           <cell r="L692">
-            <v>30810076214758</v>
+            <v>30810076216325</v>
           </cell>
           <cell r="M692">
             <v>0</v>
@@ -23102,16 +23105,22 @@
           <cell r="N692">
             <v>1</v>
           </cell>
+          <cell r="O692">
+            <v>239.76</v>
+          </cell>
+          <cell r="P692">
+            <v>120</v>
+          </cell>
         </row>
         <row r="693">
           <cell r="F693" t="str">
-            <v>LL-DISP-WR2</v>
+            <v>LL-99-0033</v>
           </cell>
           <cell r="G693" t="str">
-            <v>MT 2026 - Writing Display - 32</v>
+            <v>FlowArt Valentine Display - Empty</v>
           </cell>
           <cell r="H693" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I693" t="str">
             <v/>
@@ -23125,16 +23134,25 @@
         </row>
         <row r="694">
           <cell r="F694" t="str">
-            <v>LL-DISP-WR1</v>
+            <v>LL-00-0033</v>
           </cell>
           <cell r="G694" t="str">
-            <v>MT 2026 - Writing Display - 46</v>
+            <v>FlowArt Valentine Display - 24</v>
           </cell>
           <cell r="H694" t="str">
             <v>Y</v>
           </cell>
           <cell r="I694" t="str">
-            <v/>
+            <v>576</v>
+          </cell>
+          <cell r="J694">
+            <v>810076215761</v>
+          </cell>
+          <cell r="K694">
+            <v>50810076215766</v>
+          </cell>
+          <cell r="L694">
+            <v>30810076215762</v>
           </cell>
           <cell r="M694">
             <v>0</v>
@@ -23142,19 +23160,34 @@
           <cell r="N694">
             <v>1</v>
           </cell>
+          <cell r="O694">
+            <v>239.76</v>
+          </cell>
+          <cell r="P694">
+            <v>120</v>
+          </cell>
         </row>
         <row r="695">
           <cell r="F695" t="str">
-            <v>LL-RO-FA48</v>
+            <v>LL-00-0043</v>
           </cell>
           <cell r="G695" t="str">
-            <v>MT 2026 - FA REORDER - 48</v>
+            <v>FA Mini - Fixed Assortment - 6</v>
           </cell>
           <cell r="H695" t="str">
             <v>Y</v>
           </cell>
           <cell r="I695" t="str">
-            <v/>
+            <v>678</v>
+          </cell>
+          <cell r="J695">
+            <v>810076216782</v>
+          </cell>
+          <cell r="K695">
+            <v>50810076216787</v>
+          </cell>
+          <cell r="L695">
+            <v>30810076216783</v>
           </cell>
           <cell r="M695">
             <v>0</v>
@@ -23165,16 +23198,25 @@
         </row>
         <row r="696">
           <cell r="F696" t="str">
-            <v>LL-TWR-FA160</v>
+            <v>LL-DISP-FA-SP26</v>
           </cell>
           <cell r="G696" t="str">
-            <v>MT 2026 - FA Tower - 160</v>
+            <v>MT 2026 - FA Spring / Summer - 36</v>
           </cell>
           <cell r="H696" t="str">
             <v>Y</v>
           </cell>
           <cell r="I696" t="str">
-            <v/>
+            <v>473</v>
+          </cell>
+          <cell r="J696">
+            <v>810076214733</v>
+          </cell>
+          <cell r="K696">
+            <v>50810076214738</v>
+          </cell>
+          <cell r="L696">
+            <v>30810076214734</v>
           </cell>
           <cell r="M696">
             <v>0</v>
@@ -23185,16 +23227,25 @@
         </row>
         <row r="697">
           <cell r="F697" t="str">
-            <v>LL-DISP-FA2</v>
+            <v>LL-DISP-FA-FA26</v>
           </cell>
           <cell r="G697" t="str">
-            <v>MT 2026 - FA Display - 36</v>
+            <v>MT 2026 - FA Fall - 24</v>
           </cell>
           <cell r="H697" t="str">
             <v>Y</v>
           </cell>
           <cell r="I697" t="str">
-            <v/>
+            <v>474</v>
+          </cell>
+          <cell r="J697">
+            <v>810076214740</v>
+          </cell>
+          <cell r="K697">
+            <v>50810076214745</v>
+          </cell>
+          <cell r="L697">
+            <v>30810076214741</v>
           </cell>
           <cell r="M697">
             <v>0</v>
@@ -23205,25 +23256,25 @@
         </row>
         <row r="698">
           <cell r="F698" t="str">
-            <v>LL-00-0016</v>
+            <v>LL-DISP-FA-WN26</v>
           </cell>
           <cell r="G698" t="str">
-            <v>FA - Counter Display - Full - 36</v>
+            <v>MT 2026 - FA Winter - 24</v>
           </cell>
           <cell r="H698" t="str">
             <v>Y</v>
           </cell>
           <cell r="I698" t="str">
-            <v>439</v>
+            <v>475</v>
           </cell>
           <cell r="J698">
-            <v>810076214399</v>
+            <v>810076214757</v>
           </cell>
           <cell r="K698">
-            <v>50810076214394</v>
+            <v>50810076214752</v>
           </cell>
           <cell r="L698">
-            <v>30810076214390</v>
+            <v>30810076214758</v>
           </cell>
           <cell r="M698">
             <v>0</v>
@@ -23231,16 +23282,13 @@
           <cell r="N698">
             <v>1</v>
           </cell>
-          <cell r="P698">
-            <v>180</v>
-          </cell>
         </row>
         <row r="699">
           <cell r="F699" t="str">
-            <v>LL-DISP-FA1</v>
+            <v>LL-DISP-WR2</v>
           </cell>
           <cell r="G699" t="str">
-            <v>MT 2026 - FA Display - 80</v>
+            <v>MT 2026 - Writing Display - 32</v>
           </cell>
           <cell r="H699" t="str">
             <v>Y</v>
@@ -23257,25 +23305,16 @@
         </row>
         <row r="700">
           <cell r="F700" t="str">
-            <v>LL-00-0004</v>
+            <v>LL-DISP-WR1</v>
           </cell>
           <cell r="G700" t="str">
-            <v>FlowArt - Spinner Tower - Empty</v>
+            <v>MT 2026 - Writing Display - 46</v>
           </cell>
           <cell r="H700" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I700" t="str">
-            <v>317</v>
-          </cell>
-          <cell r="J700">
-            <v>810076213170</v>
-          </cell>
-          <cell r="K700">
-            <v>50810076213175</v>
-          </cell>
-          <cell r="L700">
-            <v>30810076213171</v>
+            <v/>
           </cell>
           <cell r="M700">
             <v>0</v>
@@ -23286,25 +23325,16 @@
         </row>
         <row r="701">
           <cell r="F701" t="str">
-            <v>LL-00-0018</v>
+            <v>LL-RO-FA48</v>
           </cell>
           <cell r="G701" t="str">
-            <v>FlowArt - Spinner Tower - Full - 80</v>
+            <v>MT 2026 - FA REORDER - 48</v>
           </cell>
           <cell r="H701" t="str">
             <v>Y</v>
           </cell>
           <cell r="I701" t="str">
-            <v>441</v>
-          </cell>
-          <cell r="J701">
-            <v>810076214412</v>
-          </cell>
-          <cell r="K701">
-            <v>50810076214417</v>
-          </cell>
-          <cell r="L701">
-            <v>30810076214413</v>
+            <v/>
           </cell>
           <cell r="M701">
             <v>0</v>
@@ -23312,31 +23342,19 @@
           <cell r="N701">
             <v>1</v>
           </cell>
-          <cell r="P701">
-            <v>400</v>
-          </cell>
         </row>
         <row r="702">
           <cell r="F702" t="str">
-            <v>LL-00-0036</v>
+            <v>LL-TWR-FA160</v>
           </cell>
           <cell r="G702" t="str">
-            <v>FlowArt - DBL - Full - 4</v>
+            <v>MT 2026 - FA Tower - 160</v>
           </cell>
           <cell r="H702" t="str">
             <v>Y</v>
           </cell>
           <cell r="I702" t="str">
-            <v>611</v>
-          </cell>
-          <cell r="J702">
-            <v>810076216119</v>
-          </cell>
-          <cell r="K702">
-            <v>50810076216114</v>
-          </cell>
-          <cell r="L702">
-            <v>30810076216110</v>
+            <v/>
           </cell>
           <cell r="M702">
             <v>0</v>
@@ -23347,25 +23365,16 @@
         </row>
         <row r="703">
           <cell r="F703" t="str">
-            <v>LL-99-0036</v>
+            <v>LL-DISP-FA2</v>
           </cell>
           <cell r="G703" t="str">
-            <v>FlowArt - DBL - Empty - 4</v>
+            <v>MT 2026 - FA Display - 36</v>
           </cell>
           <cell r="H703" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I703" t="str">
-            <v>612</v>
-          </cell>
-          <cell r="J703">
-            <v>810076216126</v>
-          </cell>
-          <cell r="K703">
-            <v>50810076216121</v>
-          </cell>
-          <cell r="L703">
-            <v>30810076216127</v>
+            <v/>
           </cell>
           <cell r="M703">
             <v>0</v>
@@ -23376,145 +23385,181 @@
         </row>
         <row r="704">
           <cell r="F704" t="str">
-            <v>LL-TOTE-BAG1</v>
+            <v>LL-00-0016</v>
           </cell>
           <cell r="G704" t="str">
-            <v>Lifelines Tote</v>
+            <v>FA - Counter Display - Full - 36</v>
           </cell>
           <cell r="H704" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I704" t="str">
-            <v/>
+            <v>439</v>
+          </cell>
+          <cell r="J704">
+            <v>810076214399</v>
+          </cell>
+          <cell r="K704">
+            <v>50810076214394</v>
+          </cell>
+          <cell r="L704">
+            <v>30810076214390</v>
           </cell>
           <cell r="M704">
             <v>0</v>
           </cell>
           <cell r="N704">
-            <v>100</v>
+            <v>1</v>
+          </cell>
+          <cell r="P704">
+            <v>180</v>
           </cell>
         </row>
         <row r="705">
           <cell r="F705" t="str">
-            <v>99-9101</v>
+            <v>LL-DISP-FA1</v>
           </cell>
           <cell r="G705" t="str">
-            <v>Assortment, PDQ - Oil Blends</v>
+            <v>MT 2026 - FA Display - 80</v>
           </cell>
           <cell r="H705" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I705" t="str">
             <v/>
           </cell>
-          <cell r="J705" t="str">
-            <v/>
-          </cell>
-          <cell r="K705" t="str">
-            <v/>
-          </cell>
-          <cell r="L705" t="str">
-            <v/>
+          <cell r="M705">
+            <v>0</v>
+          </cell>
+          <cell r="N705">
+            <v>1</v>
           </cell>
         </row>
         <row r="706">
           <cell r="F706" t="str">
-            <v>99-9500</v>
+            <v>LL-00-0004</v>
           </cell>
           <cell r="G706" t="str">
-            <v>Assortment, PDQ - Scented Writing Essentials</v>
+            <v>FlowArt - Spinner Tower - Empty</v>
           </cell>
           <cell r="H706" t="str">
             <v>N</v>
           </cell>
           <cell r="I706" t="str">
-            <v/>
-          </cell>
-          <cell r="J706" t="str">
-            <v/>
-          </cell>
-          <cell r="K706" t="str">
-            <v/>
-          </cell>
-          <cell r="L706" t="str">
-            <v/>
+            <v>317</v>
+          </cell>
+          <cell r="J706">
+            <v>810076213170</v>
+          </cell>
+          <cell r="K706">
+            <v>50810076213175</v>
+          </cell>
+          <cell r="L706">
+            <v>30810076213171</v>
+          </cell>
+          <cell r="M706">
+            <v>0</v>
+          </cell>
+          <cell r="N706">
+            <v>1</v>
           </cell>
         </row>
         <row r="707">
           <cell r="F707" t="str">
-            <v>99-9505</v>
+            <v>LL-00-0018</v>
           </cell>
           <cell r="G707" t="str">
-            <v>Tabletop Writing Display - Assortment</v>
+            <v>FlowArt - Spinner Tower - Full - 80</v>
           </cell>
           <cell r="H707" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I707" t="str">
-            <v/>
-          </cell>
-          <cell r="J707" t="str">
-            <v/>
-          </cell>
-          <cell r="K707" t="str">
-            <v/>
-          </cell>
-          <cell r="L707" t="str">
-            <v/>
+            <v>441</v>
+          </cell>
+          <cell r="J707">
+            <v>810076214412</v>
+          </cell>
+          <cell r="K707">
+            <v>50810076214417</v>
+          </cell>
+          <cell r="L707">
+            <v>30810076214413</v>
+          </cell>
+          <cell r="M707">
+            <v>0</v>
+          </cell>
+          <cell r="N707">
+            <v>1</v>
+          </cell>
+          <cell r="P707">
+            <v>400</v>
           </cell>
         </row>
         <row r="708">
           <cell r="F708" t="str">
-            <v>DS01-1001</v>
+            <v>LL-00-0036</v>
           </cell>
           <cell r="G708" t="str">
-            <v>TYT Journal + CMA Pen + Pencils</v>
+            <v>FlowArt - DBL - Full - 4</v>
           </cell>
           <cell r="H708" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I708" t="str">
-            <v/>
-          </cell>
-          <cell r="J708" t="str">
-            <v/>
-          </cell>
-          <cell r="K708" t="str">
-            <v/>
-          </cell>
-          <cell r="L708" t="str">
-            <v/>
+            <v>611</v>
+          </cell>
+          <cell r="J708">
+            <v>810076216119</v>
+          </cell>
+          <cell r="K708">
+            <v>50810076216114</v>
+          </cell>
+          <cell r="L708">
+            <v>30810076216110</v>
+          </cell>
+          <cell r="M708">
+            <v>0</v>
+          </cell>
+          <cell r="N708">
+            <v>1</v>
           </cell>
         </row>
         <row r="709">
           <cell r="F709" t="str">
-            <v>DS01-1002</v>
+            <v>LL-99-0036</v>
           </cell>
           <cell r="G709" t="str">
-            <v>SIU BG + CMA Pen + Pencils</v>
+            <v>FlowArt - DBL - Empty - 4</v>
           </cell>
           <cell r="H709" t="str">
             <v>N</v>
           </cell>
           <cell r="I709" t="str">
-            <v/>
-          </cell>
-          <cell r="J709" t="str">
-            <v/>
-          </cell>
-          <cell r="K709" t="str">
-            <v/>
-          </cell>
-          <cell r="L709" t="str">
-            <v/>
+            <v>612</v>
+          </cell>
+          <cell r="J709">
+            <v>810076216126</v>
+          </cell>
+          <cell r="K709">
+            <v>50810076216121</v>
+          </cell>
+          <cell r="L709">
+            <v>30810076216127</v>
+          </cell>
+          <cell r="M709">
+            <v>0</v>
+          </cell>
+          <cell r="N709">
+            <v>1</v>
           </cell>
         </row>
         <row r="710">
           <cell r="F710" t="str">
-            <v>DS01-1003</v>
+            <v>LL-TOTE-BAG1</v>
           </cell>
           <cell r="G710" t="str">
-            <v>Everyday Diffuser + Discovery</v>
+            <v>Lifelines Tote</v>
           </cell>
           <cell r="H710" t="str">
             <v>N</v>
@@ -23522,22 +23567,19 @@
           <cell r="I710" t="str">
             <v/>
           </cell>
-          <cell r="J710" t="str">
-            <v/>
-          </cell>
-          <cell r="K710" t="str">
-            <v/>
-          </cell>
-          <cell r="L710" t="str">
-            <v/>
+          <cell r="M710">
+            <v>0</v>
+          </cell>
+          <cell r="N710">
+            <v>100</v>
           </cell>
         </row>
         <row r="711">
           <cell r="F711" t="str">
-            <v>DS01-1004</v>
+            <v>99-9101</v>
           </cell>
           <cell r="G711" t="str">
-            <v>Waves + CMA 4Pck</v>
+            <v>Assortment, PDQ - Oil Blends</v>
           </cell>
           <cell r="H711" t="str">
             <v>N</v>
@@ -23557,10 +23599,10 @@
         </row>
         <row r="712">
           <cell r="F712" t="str">
-            <v>DS01-1005</v>
+            <v>99-9500</v>
           </cell>
           <cell r="G712" t="str">
-            <v>Motion Fidget + Discovery</v>
+            <v>Assortment, PDQ - Scented Writing Essentials</v>
           </cell>
           <cell r="H712" t="str">
             <v>N</v>
@@ -23580,10 +23622,10 @@
         </row>
         <row r="713">
           <cell r="F713" t="str">
-            <v>DS01-1006</v>
+            <v>99-9505</v>
           </cell>
           <cell r="G713" t="str">
-            <v>Meditative Fidget + Discovery</v>
+            <v>Tabletop Writing Display - Assortment</v>
           </cell>
           <cell r="H713" t="str">
             <v>N</v>
@@ -23603,10 +23645,10 @@
         </row>
         <row r="714">
           <cell r="F714" t="str">
-            <v>DS01-1007</v>
+            <v>DS01-1001</v>
           </cell>
           <cell r="G714" t="str">
-            <v>Gift Set + CMA Pen + Workbook</v>
+            <v>TYT Journal + CMA Pen + Pencils</v>
           </cell>
           <cell r="H714" t="str">
             <v>N</v>
@@ -23626,10 +23668,10 @@
         </row>
         <row r="715">
           <cell r="F715" t="str">
-            <v>DS01-1008</v>
+            <v>DS01-1002</v>
           </cell>
           <cell r="G715" t="str">
-            <v>Lifelines Bath and Shower Diffuser Set</v>
+            <v>SIU BG + CMA Pen + Pencils</v>
           </cell>
           <cell r="H715" t="str">
             <v>N</v>
@@ -23649,10 +23691,10 @@
         </row>
         <row r="716">
           <cell r="F716" t="str">
-            <v>99-8302</v>
+            <v>DS01-1003</v>
           </cell>
           <cell r="G716" t="str">
-            <v>2024 BNC Spring Shipper Replen</v>
+            <v>Everyday Diffuser + Discovery</v>
           </cell>
           <cell r="H716" t="str">
             <v>N</v>
@@ -23672,13 +23714,13 @@
         </row>
         <row r="717">
           <cell r="F717" t="str">
-            <v>99-8501</v>
+            <v>DS01-1004</v>
           </cell>
           <cell r="G717" t="str">
-            <v>BNC Writing Counter Display</v>
+            <v>Waves + CMA 4Pck</v>
           </cell>
           <cell r="H717" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I717" t="str">
             <v/>
@@ -23695,10 +23737,10 @@
         </row>
         <row r="718">
           <cell r="F718" t="str">
-            <v>99-9002</v>
+            <v>DS01-1005</v>
           </cell>
           <cell r="G718" t="str">
-            <v>Assortment, PDQ - Aroma Introduction</v>
+            <v>Motion Fidget + Discovery</v>
           </cell>
           <cell r="H718" t="str">
             <v>N</v>
@@ -23717,11 +23759,11 @@
           </cell>
         </row>
         <row r="719">
-          <cell r="F719">
-            <v>999003</v>
+          <cell r="F719" t="str">
+            <v>DS01-1006</v>
           </cell>
           <cell r="G719" t="str">
-            <v>BNC Floor Display</v>
+            <v>Meditative Fidget + Discovery</v>
           </cell>
           <cell r="H719" t="str">
             <v>N</v>
@@ -23738,19 +23780,13 @@
           <cell r="L719" t="str">
             <v/>
           </cell>
-          <cell r="M719" t="str">
-            <v/>
-          </cell>
-          <cell r="N719" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="720">
-          <cell r="F720">
-            <v>999004</v>
+          <cell r="F720" t="str">
+            <v>DS01-1007</v>
           </cell>
           <cell r="G720" t="str">
-            <v>Empty BNC Floor Display</v>
+            <v>Gift Set + CMA Pen + Workbook</v>
           </cell>
           <cell r="H720" t="str">
             <v>N</v>
@@ -23767,334 +23803,268 @@
           <cell r="L720" t="str">
             <v/>
           </cell>
-          <cell r="M720" t="str">
-            <v/>
-          </cell>
-          <cell r="N720" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="721">
           <cell r="F721" t="str">
-            <v>LL-98-3220</v>
+            <v>DS01-1008</v>
           </cell>
           <cell r="G721" t="str">
-            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
+            <v>Lifelines Bath and Shower Diffuser Set</v>
           </cell>
           <cell r="H721" t="str">
             <v>N</v>
           </cell>
           <cell r="I721" t="str">
-            <v>392</v>
-          </cell>
-          <cell r="J721">
-            <v>810076213927</v>
-          </cell>
-          <cell r="K721">
-            <v>50810076213922</v>
-          </cell>
-          <cell r="L721">
-            <v>30810076213928</v>
-          </cell>
-          <cell r="N721">
-            <v>20</v>
-          </cell>
-          <cell r="O721">
-            <v>29.99</v>
-          </cell>
-          <cell r="P721">
-            <v>14.994999999999999</v>
+            <v/>
+          </cell>
+          <cell r="J721" t="str">
+            <v/>
+          </cell>
+          <cell r="K721" t="str">
+            <v/>
+          </cell>
+          <cell r="L721" t="str">
+            <v/>
           </cell>
         </row>
         <row r="722">
           <cell r="F722" t="str">
-            <v>LL-20-3304</v>
+            <v>99-8302</v>
           </cell>
           <cell r="G722" t="str">
-            <v>FlowArt: Mini, Holiday 3Pck #2</v>
+            <v>2024 BNC Spring Shipper Replen</v>
           </cell>
           <cell r="H722" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I722" t="str">
-            <v>491</v>
-          </cell>
-          <cell r="J722">
-            <v>810076214917</v>
-          </cell>
-          <cell r="K722">
-            <v>50810076214912</v>
-          </cell>
-          <cell r="L722">
-            <v>30810076214918</v>
+            <v/>
+          </cell>
+          <cell r="J722" t="str">
+            <v/>
+          </cell>
+          <cell r="K722" t="str">
+            <v/>
+          </cell>
+          <cell r="L722" t="str">
+            <v/>
           </cell>
         </row>
         <row r="723">
           <cell r="F723" t="str">
-            <v>LL-20-3226</v>
+            <v>99-8501</v>
           </cell>
           <cell r="G723" t="str">
-            <v>FlowArt: Mini, 3Pck #3</v>
+            <v>BNC Writing Counter Display</v>
           </cell>
           <cell r="H723" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I723" t="str">
-            <v>398</v>
-          </cell>
-          <cell r="J723">
-            <v>810076213989</v>
-          </cell>
-          <cell r="K723">
-            <v>50810076213984</v>
-          </cell>
-          <cell r="L723">
-            <v>30810076213980</v>
-          </cell>
-          <cell r="M723">
-            <v>4</v>
-          </cell>
-          <cell r="N723">
-            <v>12</v>
-          </cell>
-          <cell r="O723">
-            <v>19.989999999999998</v>
-          </cell>
-          <cell r="P723">
-            <v>9.9949999999999992</v>
+            <v/>
+          </cell>
+          <cell r="J723" t="str">
+            <v/>
+          </cell>
+          <cell r="K723" t="str">
+            <v/>
+          </cell>
+          <cell r="L723" t="str">
+            <v/>
           </cell>
         </row>
         <row r="724">
           <cell r="F724" t="str">
-            <v>LL-20-3252</v>
+            <v>99-9002</v>
           </cell>
           <cell r="G724" t="str">
-            <v>FlowArt: Mini Single - Holiday Cheer</v>
+            <v>Assortment, PDQ - Aroma Introduction</v>
           </cell>
           <cell r="H724" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I724" t="str">
-            <v>426</v>
-          </cell>
-          <cell r="J724">
-            <v>810076214269</v>
-          </cell>
-          <cell r="K724">
-            <v>50810076214264</v>
-          </cell>
-          <cell r="L724">
-            <v>30810076214260</v>
-          </cell>
-          <cell r="M724">
-            <v>6</v>
-          </cell>
-          <cell r="N724">
-            <v>24</v>
-          </cell>
-          <cell r="O724">
-            <v>6.99</v>
-          </cell>
-          <cell r="P724">
-            <v>3.4950000000000001</v>
+            <v/>
+          </cell>
+          <cell r="J724" t="str">
+            <v/>
+          </cell>
+          <cell r="K724" t="str">
+            <v/>
+          </cell>
+          <cell r="L724" t="str">
+            <v/>
           </cell>
         </row>
         <row r="725">
-          <cell r="F725" t="str">
-            <v>LL-20-3253</v>
+          <cell r="F725">
+            <v>999003</v>
           </cell>
           <cell r="G725" t="str">
-            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
+            <v>BNC Floor Display</v>
           </cell>
           <cell r="H725" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I725" t="str">
-            <v>427</v>
-          </cell>
-          <cell r="J725">
-            <v>810076214276</v>
-          </cell>
-          <cell r="K725">
-            <v>50810076214271</v>
-          </cell>
-          <cell r="L725">
-            <v>30810076214277</v>
-          </cell>
-          <cell r="M725">
-            <v>6</v>
-          </cell>
-          <cell r="N725">
-            <v>24</v>
-          </cell>
-          <cell r="O725">
-            <v>6.99</v>
-          </cell>
-          <cell r="P725">
-            <v>3.4950000000000001</v>
+            <v/>
+          </cell>
+          <cell r="J725" t="str">
+            <v/>
+          </cell>
+          <cell r="K725" t="str">
+            <v/>
+          </cell>
+          <cell r="L725" t="str">
+            <v/>
+          </cell>
+          <cell r="M725" t="str">
+            <v/>
+          </cell>
+          <cell r="N725" t="str">
+            <v/>
           </cell>
         </row>
         <row r="726">
-          <cell r="F726" t="str">
-            <v>LL-20-3254</v>
+          <cell r="F726">
+            <v>999004</v>
           </cell>
           <cell r="G726" t="str">
-            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
+            <v>Empty BNC Floor Display</v>
           </cell>
           <cell r="H726" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I726" t="str">
-            <v>428</v>
-          </cell>
-          <cell r="J726">
-            <v>810076214283</v>
-          </cell>
-          <cell r="K726">
-            <v>50810076214288</v>
-          </cell>
-          <cell r="L726">
-            <v>30810076214284</v>
-          </cell>
-          <cell r="M726">
-            <v>6</v>
-          </cell>
-          <cell r="N726">
-            <v>24</v>
-          </cell>
-          <cell r="O726">
-            <v>6.99</v>
-          </cell>
-          <cell r="P726">
-            <v>3.4950000000000001</v>
+            <v/>
+          </cell>
+          <cell r="J726" t="str">
+            <v/>
+          </cell>
+          <cell r="K726" t="str">
+            <v/>
+          </cell>
+          <cell r="L726" t="str">
+            <v/>
+          </cell>
+          <cell r="M726" t="str">
+            <v/>
+          </cell>
+          <cell r="N726" t="str">
+            <v/>
           </cell>
         </row>
         <row r="727">
           <cell r="F727" t="str">
-            <v>LL-20-3268</v>
+            <v>LL-98-3220</v>
           </cell>
           <cell r="G727" t="str">
-            <v>FlowArt Minis: Nature's Wonder - WMT</v>
+            <v>FlowArt 2Pck:TbLetter + Within [3206 + 3207]</v>
           </cell>
           <cell r="H727" t="str">
             <v>N</v>
           </cell>
           <cell r="I727" t="str">
-            <v>450</v>
+            <v>392</v>
           </cell>
           <cell r="J727">
-            <v>810076214504</v>
+            <v>810076213927</v>
           </cell>
           <cell r="K727">
-            <v>50810076214509</v>
+            <v>50810076213922</v>
           </cell>
           <cell r="L727">
-            <v>30810076214505</v>
-          </cell>
-          <cell r="M727">
-            <v>6</v>
+            <v>30810076213928</v>
           </cell>
           <cell r="N727">
-            <v>24</v>
+            <v>20</v>
           </cell>
           <cell r="O727">
-            <v>6.99</v>
+            <v>29.99</v>
           </cell>
           <cell r="P727">
-            <v>3.4950000000000001</v>
+            <v>14.994999999999999</v>
           </cell>
         </row>
         <row r="728">
           <cell r="F728" t="str">
-            <v>LL-20-3269</v>
+            <v>LL-20-3304</v>
           </cell>
           <cell r="G728" t="str">
-            <v>FlowArt Minis: Furry Friends - WMT</v>
+            <v>FlowArt: Mini, Holiday 3Pck #2</v>
           </cell>
           <cell r="H728" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I728" t="str">
-            <v>451</v>
+            <v>491</v>
           </cell>
           <cell r="J728">
-            <v>810076214511</v>
+            <v>810076214917</v>
           </cell>
           <cell r="K728">
-            <v>50810076214516</v>
+            <v>50810076214912</v>
           </cell>
           <cell r="L728">
-            <v>30810076214512</v>
-          </cell>
-          <cell r="M728">
-            <v>6</v>
-          </cell>
-          <cell r="N728">
-            <v>24</v>
-          </cell>
-          <cell r="O728">
-            <v>6.99</v>
-          </cell>
-          <cell r="P728">
-            <v>3.4950000000000001</v>
+            <v>30810076214918</v>
           </cell>
         </row>
         <row r="729">
           <cell r="F729" t="str">
-            <v>LL-20-3270</v>
+            <v>LL-20-3226</v>
           </cell>
           <cell r="G729" t="str">
-            <v>FlowArt Minis: Pretty Petals - WMT</v>
+            <v>FlowArt: Mini, 3Pck #3</v>
           </cell>
           <cell r="H729" t="str">
             <v>N</v>
           </cell>
           <cell r="I729" t="str">
-            <v>452</v>
+            <v>398</v>
           </cell>
           <cell r="J729">
-            <v>810076214528</v>
+            <v>810076213989</v>
           </cell>
           <cell r="K729">
-            <v>50810076214523</v>
+            <v>50810076213984</v>
           </cell>
           <cell r="L729">
-            <v>30810076214529</v>
+            <v>30810076213980</v>
           </cell>
           <cell r="M729">
-            <v>6</v>
+            <v>4</v>
           </cell>
           <cell r="N729">
-            <v>24</v>
+            <v>12</v>
           </cell>
           <cell r="O729">
-            <v>6.99</v>
+            <v>19.989999999999998</v>
           </cell>
           <cell r="P729">
-            <v>3.4950000000000001</v>
+            <v>9.9949999999999992</v>
           </cell>
         </row>
         <row r="730">
           <cell r="F730" t="str">
-            <v>LL-16-3262</v>
+            <v>LL-20-3252</v>
           </cell>
           <cell r="G730" t="str">
-            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
+            <v>FlowArt: Mini Single - Holiday Cheer</v>
           </cell>
           <cell r="H730" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I730" t="str">
-            <v>444</v>
+            <v>426</v>
           </cell>
           <cell r="J730">
-            <v>810076214443</v>
+            <v>810076214269</v>
           </cell>
           <cell r="K730">
-            <v>50810076214448</v>
+            <v>50810076214264</v>
           </cell>
           <cell r="L730">
-            <v>30810076214444</v>
+            <v>30810076214260</v>
           </cell>
           <cell r="M730">
             <v>6</v>
@@ -24103,33 +24073,33 @@
             <v>24</v>
           </cell>
           <cell r="O730">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P730">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="731">
           <cell r="F731" t="str">
-            <v>LL-16-3264</v>
+            <v>LL-20-3253</v>
           </cell>
           <cell r="G731" t="str">
-            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
+            <v>FlowArt: Mini Single - Sugar &amp; Spice</v>
           </cell>
           <cell r="H731" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I731" t="str">
-            <v>446</v>
+            <v>427</v>
           </cell>
           <cell r="J731">
-            <v>810076214467</v>
+            <v>810076214276</v>
           </cell>
           <cell r="K731">
-            <v>50810076214462</v>
+            <v>50810076214271</v>
           </cell>
           <cell r="L731">
-            <v>30810076214468</v>
+            <v>30810076214277</v>
           </cell>
           <cell r="M731">
             <v>6</v>
@@ -24138,33 +24108,33 @@
             <v>24</v>
           </cell>
           <cell r="O731">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P731">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="732">
           <cell r="F732" t="str">
-            <v>LL-16-3265</v>
+            <v>LL-20-3254</v>
           </cell>
           <cell r="G732" t="str">
-            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
+            <v>FlowArt: Mini Single - Merry &amp; Bright</v>
           </cell>
           <cell r="H732" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I732" t="str">
-            <v>447</v>
+            <v>428</v>
           </cell>
           <cell r="J732">
-            <v>810076214474</v>
+            <v>810076214283</v>
           </cell>
           <cell r="K732">
-            <v>50810076214479</v>
+            <v>50810076214288</v>
           </cell>
           <cell r="L732">
-            <v>30810076214475</v>
+            <v>30810076214284</v>
           </cell>
           <cell r="M732">
             <v>6</v>
@@ -24173,33 +24143,33 @@
             <v>24</v>
           </cell>
           <cell r="O732">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P732">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="733">
           <cell r="F733" t="str">
-            <v>LL-16-3260</v>
+            <v>LL-20-3268</v>
           </cell>
           <cell r="G733" t="str">
-            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
+            <v>FlowArt Minis: Nature's Wonder - WMT</v>
           </cell>
           <cell r="H733" t="str">
             <v>N</v>
           </cell>
           <cell r="I733" t="str">
-            <v>442</v>
+            <v>450</v>
           </cell>
           <cell r="J733">
-            <v>810076214429</v>
+            <v>810076214504</v>
           </cell>
           <cell r="K733">
-            <v>50810076214424</v>
+            <v>50810076214509</v>
           </cell>
           <cell r="L733">
-            <v>30810076214420</v>
+            <v>30810076214505</v>
           </cell>
           <cell r="M733">
             <v>6</v>
@@ -24208,33 +24178,33 @@
             <v>24</v>
           </cell>
           <cell r="O733">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P733">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="734">
           <cell r="F734" t="str">
-            <v>LL-16-3267</v>
+            <v>LL-20-3269</v>
           </cell>
           <cell r="G734" t="str">
-            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
+            <v>FlowArt Minis: Furry Friends - WMT</v>
           </cell>
           <cell r="H734" t="str">
             <v>N</v>
           </cell>
           <cell r="I734" t="str">
-            <v>449</v>
+            <v>451</v>
           </cell>
           <cell r="J734">
-            <v>810076214498</v>
+            <v>810076214511</v>
           </cell>
           <cell r="K734">
-            <v>50810076214493</v>
+            <v>50810076214516</v>
           </cell>
           <cell r="L734">
-            <v>30810076214499</v>
+            <v>30810076214512</v>
           </cell>
           <cell r="M734">
             <v>6</v>
@@ -24243,33 +24213,33 @@
             <v>24</v>
           </cell>
           <cell r="O734">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P734">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="735">
           <cell r="F735" t="str">
-            <v>LL-16-3282</v>
+            <v>LL-20-3270</v>
           </cell>
           <cell r="G735" t="str">
-            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
+            <v>FlowArt Minis: Pretty Petals - WMT</v>
           </cell>
           <cell r="H735" t="str">
             <v>N</v>
           </cell>
           <cell r="I735" t="str">
-            <v>469</v>
+            <v>452</v>
           </cell>
           <cell r="J735">
-            <v>810076214696</v>
+            <v>810076214528</v>
           </cell>
           <cell r="K735">
-            <v>50810076214691</v>
+            <v>50810076214523</v>
           </cell>
           <cell r="L735">
-            <v>30810076214697</v>
+            <v>30810076214529</v>
           </cell>
           <cell r="M735">
             <v>6</v>
@@ -24278,472 +24248,508 @@
             <v>24</v>
           </cell>
           <cell r="O735">
-            <v>10</v>
+            <v>6.99</v>
           </cell>
           <cell r="P735">
-            <v>5</v>
+            <v>3.4950000000000001</v>
           </cell>
         </row>
         <row r="736">
           <cell r="F736" t="str">
-            <v>LL-16-3143</v>
+            <v>LL-16-3262</v>
           </cell>
           <cell r="G736" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
+            <v>FlowArt Trace By Line: Holiday Icons  - WMT</v>
           </cell>
           <cell r="H736" t="str">
             <v>N</v>
           </cell>
           <cell r="I736" t="str">
-            <v>286</v>
+            <v>444</v>
           </cell>
           <cell r="J736">
-            <v>810076212869</v>
+            <v>810076214443</v>
           </cell>
           <cell r="K736">
-            <v>50810076212864</v>
+            <v>50810076214448</v>
           </cell>
           <cell r="L736">
-            <v>30810076212860</v>
+            <v>30810076214444</v>
+          </cell>
+          <cell r="M736">
+            <v>6</v>
+          </cell>
+          <cell r="N736">
+            <v>24</v>
+          </cell>
+          <cell r="O736">
+            <v>10</v>
+          </cell>
+          <cell r="P736">
+            <v>5</v>
           </cell>
         </row>
         <row r="737">
           <cell r="F737" t="str">
-            <v>LL-12-3131</v>
+            <v>LL-16-3264</v>
           </cell>
           <cell r="G737" t="str">
-            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
+            <v>FlowArt Dot-By-Letter: Woodland Wonders - WMT</v>
           </cell>
           <cell r="H737" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I737" t="str">
-            <v>274</v>
+            <v>446</v>
           </cell>
           <cell r="J737">
-            <v>810076212746</v>
+            <v>810076214467</v>
           </cell>
           <cell r="K737">
-            <v>50810076212741</v>
+            <v>50810076214462</v>
           </cell>
           <cell r="L737">
-            <v>30810076212747</v>
+            <v>30810076214468</v>
+          </cell>
+          <cell r="M737">
+            <v>6</v>
+          </cell>
+          <cell r="N737">
+            <v>24</v>
+          </cell>
+          <cell r="O737">
+            <v>10</v>
+          </cell>
+          <cell r="P737">
+            <v>5</v>
           </cell>
         </row>
         <row r="738">
           <cell r="F738" t="str">
-            <v>LL-16-3142</v>
+            <v>LL-16-3265</v>
           </cell>
           <cell r="G738" t="str">
-            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
+            <v>FlowArt Dot-By Letter: Majestic Earth - WMT [Metallic]</v>
           </cell>
           <cell r="H738" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I738" t="str">
-            <v>285</v>
+            <v>447</v>
           </cell>
           <cell r="J738">
-            <v>810076212852</v>
+            <v>810076214474</v>
           </cell>
           <cell r="K738">
-            <v>50810076212857</v>
+            <v>50810076214479</v>
           </cell>
           <cell r="L738">
-            <v>30810076212853</v>
+            <v>30810076214475</v>
+          </cell>
+          <cell r="M738">
+            <v>6</v>
+          </cell>
+          <cell r="N738">
+            <v>24</v>
+          </cell>
+          <cell r="O738">
+            <v>10</v>
+          </cell>
+          <cell r="P738">
+            <v>5</v>
           </cell>
         </row>
         <row r="739">
           <cell r="F739" t="str">
-            <v>LL-12-3135</v>
+            <v>LL-16-3260</v>
           </cell>
           <cell r="G739" t="str">
-            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
+            <v>FlowArt Dot-By-Letter: Holiday Classic  - WMT</v>
           </cell>
           <cell r="H739" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I739" t="str">
-            <v>278</v>
+            <v>442</v>
           </cell>
           <cell r="J739">
-            <v>810076212784</v>
+            <v>810076214429</v>
           </cell>
           <cell r="K739">
-            <v>50810076212789</v>
+            <v>50810076214424</v>
           </cell>
           <cell r="L739">
-            <v>30810076212785</v>
+            <v>30810076214420</v>
+          </cell>
+          <cell r="M739">
+            <v>6</v>
+          </cell>
+          <cell r="N739">
+            <v>24</v>
+          </cell>
+          <cell r="O739">
+            <v>10</v>
+          </cell>
+          <cell r="P739">
+            <v>5</v>
           </cell>
         </row>
         <row r="740">
           <cell r="F740" t="str">
-            <v>LL-12-3134</v>
+            <v>LL-16-3267</v>
           </cell>
           <cell r="G740" t="str">
-            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
+            <v>FlowArt Trace By Line: Sea Life Wonders - WMT</v>
           </cell>
           <cell r="H740" t="str">
             <v>N</v>
           </cell>
           <cell r="I740" t="str">
-            <v>277</v>
+            <v>449</v>
           </cell>
           <cell r="J740">
-            <v>810076212777</v>
+            <v>810076214498</v>
           </cell>
           <cell r="K740">
-            <v>50810076212772</v>
+            <v>50810076214493</v>
           </cell>
           <cell r="L740">
-            <v>30810076212778</v>
+            <v>30810076214499</v>
+          </cell>
+          <cell r="M740">
+            <v>6</v>
+          </cell>
+          <cell r="N740">
+            <v>24</v>
+          </cell>
+          <cell r="O740">
+            <v>10</v>
+          </cell>
+          <cell r="P740">
+            <v>5</v>
           </cell>
         </row>
         <row r="741">
           <cell r="F741" t="str">
-            <v>LL-14-3145</v>
+            <v>LL-16-3282</v>
           </cell>
           <cell r="G741" t="str">
-            <v>DIFFUSER, LED,Bubble (Cream) - WALMART PKG</v>
+            <v>FlowArt Dot-By-Letter Metallic Theme TBD 2 - WMT</v>
           </cell>
           <cell r="H741" t="str">
             <v>N</v>
           </cell>
           <cell r="I741" t="str">
-            <v>288</v>
+            <v>469</v>
           </cell>
           <cell r="J741">
-            <v>810076212883</v>
+            <v>810076214696</v>
           </cell>
           <cell r="K741">
-            <v>50810076212888</v>
+            <v>50810076214691</v>
           </cell>
           <cell r="L741">
-            <v>30810076212884</v>
+            <v>30810076214697</v>
+          </cell>
+          <cell r="M741">
+            <v>6</v>
+          </cell>
+          <cell r="N741">
+            <v>24</v>
+          </cell>
+          <cell r="O741">
+            <v>10</v>
+          </cell>
+          <cell r="P741">
+            <v>5</v>
           </cell>
         </row>
         <row r="742">
           <cell r="F742" t="str">
-            <v>LL-14-3147</v>
+            <v>LL-16-3143</v>
           </cell>
           <cell r="G742" t="str">
-            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
+            <v>FlowArt: Illuminate &amp; Create, Wildlife - WALMART PKG</v>
           </cell>
           <cell r="H742" t="str">
             <v>N</v>
           </cell>
           <cell r="I742" t="str">
-            <v>290</v>
+            <v>286</v>
           </cell>
           <cell r="J742">
-            <v>810076212906</v>
+            <v>810076212869</v>
           </cell>
           <cell r="K742">
-            <v>50810076212901</v>
+            <v>50810076212864</v>
           </cell>
           <cell r="L742">
-            <v>30810076212907</v>
+            <v>30810076212860</v>
           </cell>
         </row>
         <row r="743">
           <cell r="F743" t="str">
-            <v>LL-98-3171</v>
+            <v>LL-12-3131</v>
           </cell>
           <cell r="G743" t="str">
-            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
+            <v>Scented Lava Pen Set- 5-pack  - WALMART PKG</v>
           </cell>
           <cell r="H743" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I743" t="str">
-            <v>315</v>
+            <v>274</v>
           </cell>
           <cell r="J743">
-            <v>810076213156</v>
+            <v>810076212746</v>
           </cell>
           <cell r="K743">
-            <v>50810076213151</v>
+            <v>50810076212741</v>
           </cell>
           <cell r="L743">
-            <v>30810076213157</v>
+            <v>30810076212747</v>
           </cell>
         </row>
         <row r="744">
           <cell r="F744" t="str">
-            <v>LL-11-3087</v>
+            <v>LL-16-3142</v>
           </cell>
           <cell r="G744" t="str">
-            <v>Clickwick 2PK - SKU 5</v>
+            <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers - WALMART PKG</v>
           </cell>
           <cell r="H744" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I744" t="str">
-            <v>215</v>
+            <v>285</v>
           </cell>
           <cell r="J744">
-            <v>810076212159</v>
+            <v>810076212852</v>
           </cell>
           <cell r="K744">
-            <v>50810076212154</v>
+            <v>50810076212857</v>
           </cell>
           <cell r="L744">
-            <v>30810076212150</v>
-          </cell>
-          <cell r="O744">
-            <v>26.99</v>
-          </cell>
-          <cell r="P744">
-            <v>13.494999999999999</v>
+            <v>30810076212853</v>
           </cell>
         </row>
         <row r="745">
           <cell r="F745" t="str">
-            <v>LL-11-3088</v>
+            <v>LL-12-3135</v>
           </cell>
           <cell r="G745" t="str">
-            <v>Clickwick 2PK - SKU 6</v>
+            <v>Pen Diffuser with Essential Oil Blends -  Strawberry Milkshake - WALMART PKG</v>
           </cell>
           <cell r="H745" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I745" t="str">
-            <v>216</v>
+            <v>278</v>
           </cell>
           <cell r="J745">
-            <v>810076212166</v>
+            <v>810076212784</v>
           </cell>
           <cell r="K745">
-            <v>50810076212161</v>
+            <v>50810076212789</v>
           </cell>
           <cell r="L745">
-            <v>30810076212167</v>
-          </cell>
-          <cell r="O745">
-            <v>14.99</v>
-          </cell>
-          <cell r="P745">
-            <v>7.4950000000000001</v>
+            <v>30810076212785</v>
           </cell>
         </row>
         <row r="746">
           <cell r="F746" t="str">
-            <v>LL-11-3089</v>
+            <v>LL-12-3134</v>
           </cell>
           <cell r="G746" t="str">
-            <v>Clickwick 2PK - SKU 7</v>
+            <v>Scented Lava Pen Set - 2-pack (Lime Green / Violet)  - WALMART PKG</v>
           </cell>
           <cell r="H746" t="str">
             <v>N</v>
           </cell>
           <cell r="I746" t="str">
-            <v>217</v>
+            <v>277</v>
           </cell>
           <cell r="J746">
-            <v>810076212173</v>
+            <v>810076212777</v>
           </cell>
           <cell r="K746">
-            <v>50810076212178</v>
+            <v>50810076212772</v>
           </cell>
           <cell r="L746">
-            <v>30810076212174</v>
-          </cell>
-          <cell r="O746">
-            <v>14.99</v>
-          </cell>
-          <cell r="P746">
-            <v>7.4950000000000001</v>
+            <v>30810076212778</v>
           </cell>
         </row>
         <row r="747">
-          <cell r="F747">
-            <v>165002</v>
+          <cell r="F747" t="str">
+            <v>LL-14-3145</v>
           </cell>
           <cell r="G747" t="str">
-            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
+            <v>DIFFUSER, LED,Bubble (Cream) - WALMART PKG</v>
           </cell>
           <cell r="H747" t="str">
             <v>N</v>
           </cell>
           <cell r="I747" t="str">
-            <v>147</v>
+            <v>288</v>
           </cell>
           <cell r="J747">
-            <v>810076211473</v>
-          </cell>
-          <cell r="K747" t="str">
-            <v/>
-          </cell>
-          <cell r="L747" t="str">
-            <v/>
-          </cell>
-          <cell r="M747" t="str">
-            <v/>
-          </cell>
-          <cell r="N747" t="str">
-            <v/>
+            <v>810076212883</v>
+          </cell>
+          <cell r="K747">
+            <v>50810076212888</v>
+          </cell>
+          <cell r="L747">
+            <v>30810076212884</v>
           </cell>
         </row>
         <row r="748">
-          <cell r="F748">
-            <v>165003</v>
+          <cell r="F748" t="str">
+            <v>LL-14-3147</v>
           </cell>
           <cell r="G748" t="str">
-            <v>FlowArt - Multiline art - Land</v>
+            <v>Plant Diffuser - Succulent - Two Toned - WALMART PKG</v>
           </cell>
           <cell r="H748" t="str">
             <v>N</v>
           </cell>
           <cell r="I748" t="str">
-            <v>148</v>
+            <v>290</v>
           </cell>
           <cell r="J748">
-            <v>810076211480</v>
-          </cell>
-          <cell r="K748" t="str">
-            <v/>
-          </cell>
-          <cell r="L748" t="str">
-            <v/>
-          </cell>
-          <cell r="M748" t="str">
-            <v/>
-          </cell>
-          <cell r="N748" t="str">
-            <v/>
+            <v>810076212906</v>
+          </cell>
+          <cell r="K748">
+            <v>50810076212901</v>
+          </cell>
+          <cell r="L748">
+            <v>30810076212907</v>
           </cell>
         </row>
         <row r="749">
-          <cell r="F749">
-            <v>165004</v>
+          <cell r="F749" t="str">
+            <v>LL-98-3171</v>
           </cell>
           <cell r="G749" t="str">
-            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
+            <v>Ultimate Essential Oil Gift Set with EDPD - WALMART PKG</v>
           </cell>
           <cell r="H749" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I749" t="str">
-            <v>149</v>
+            <v>315</v>
           </cell>
           <cell r="J749">
-            <v>810076211497</v>
-          </cell>
-          <cell r="K749" t="str">
-            <v/>
-          </cell>
-          <cell r="L749" t="str">
-            <v/>
-          </cell>
-          <cell r="M749" t="str">
-            <v/>
-          </cell>
-          <cell r="N749" t="str">
-            <v/>
+            <v>810076213156</v>
+          </cell>
+          <cell r="K749">
+            <v>50810076213151</v>
+          </cell>
+          <cell r="L749">
+            <v>30810076213157</v>
           </cell>
         </row>
         <row r="750">
-          <cell r="F750">
-            <v>165010</v>
+          <cell r="F750" t="str">
+            <v>LL-11-3087</v>
           </cell>
           <cell r="G750" t="str">
-            <v>FlowArt - Pogo-dot - In the Garden</v>
+            <v>Clickwick 2PK - SKU 5</v>
           </cell>
           <cell r="H750" t="str">
             <v>N</v>
           </cell>
           <cell r="I750" t="str">
-            <v>155</v>
+            <v>215</v>
           </cell>
           <cell r="J750">
-            <v>810076211558</v>
-          </cell>
-          <cell r="K750" t="str">
-            <v/>
-          </cell>
-          <cell r="L750" t="str">
-            <v/>
-          </cell>
-          <cell r="M750" t="str">
-            <v/>
-          </cell>
-          <cell r="N750" t="str">
-            <v/>
+            <v>810076212159</v>
+          </cell>
+          <cell r="K750">
+            <v>50810076212154</v>
+          </cell>
+          <cell r="L750">
+            <v>30810076212150</v>
+          </cell>
+          <cell r="O750">
+            <v>26.99</v>
+          </cell>
+          <cell r="P750">
+            <v>13.494999999999999</v>
           </cell>
         </row>
         <row r="751">
-          <cell r="F751">
-            <v>165011</v>
+          <cell r="F751" t="str">
+            <v>LL-11-3088</v>
           </cell>
           <cell r="G751" t="str">
-            <v>FlowArt - Dot-pop - Sea</v>
+            <v>Clickwick 2PK - SKU 6</v>
           </cell>
           <cell r="H751" t="str">
             <v>N</v>
           </cell>
           <cell r="I751" t="str">
-            <v>156</v>
+            <v>216</v>
           </cell>
           <cell r="J751">
-            <v>810076211565</v>
-          </cell>
-          <cell r="K751" t="str">
-            <v/>
-          </cell>
-          <cell r="L751" t="str">
-            <v/>
-          </cell>
-          <cell r="M751" t="str">
-            <v/>
-          </cell>
-          <cell r="N751" t="str">
-            <v/>
+            <v>810076212166</v>
+          </cell>
+          <cell r="K751">
+            <v>50810076212161</v>
+          </cell>
+          <cell r="L751">
+            <v>30810076212167</v>
+          </cell>
+          <cell r="O751">
+            <v>14.99</v>
+          </cell>
+          <cell r="P751">
+            <v>7.4950000000000001</v>
           </cell>
         </row>
         <row r="752">
-          <cell r="F752">
-            <v>165013</v>
+          <cell r="F752" t="str">
+            <v>LL-11-3089</v>
           </cell>
           <cell r="G752" t="str">
-            <v>FlowArt - Multiline art - Sea</v>
+            <v>Clickwick 2PK - SKU 7</v>
           </cell>
           <cell r="H752" t="str">
             <v>N</v>
           </cell>
           <cell r="I752" t="str">
-            <v>158</v>
+            <v>217</v>
           </cell>
           <cell r="J752">
-            <v>810076211589</v>
-          </cell>
-          <cell r="K752" t="str">
-            <v/>
-          </cell>
-          <cell r="L752" t="str">
-            <v/>
-          </cell>
-          <cell r="M752" t="str">
-            <v/>
-          </cell>
-          <cell r="N752" t="str">
-            <v/>
+            <v>810076212173</v>
+          </cell>
+          <cell r="K752">
+            <v>50810076212178</v>
+          </cell>
+          <cell r="L752">
+            <v>30810076212174</v>
+          </cell>
+          <cell r="O752">
+            <v>14.99</v>
+          </cell>
+          <cell r="P752">
+            <v>7.4950000000000001</v>
           </cell>
         </row>
         <row r="753">
           <cell r="F753">
-            <v>167003</v>
+            <v>165002</v>
           </cell>
           <cell r="G753" t="str">
-            <v>Decor Art - Stencil Stationery</v>
+            <v>FlowArt - Pattern art - Fur &amp; feathers</v>
           </cell>
           <cell r="H753" t="str">
             <v>N</v>
           </cell>
           <cell r="I753" t="str">
-            <v>162</v>
+            <v>147</v>
           </cell>
           <cell r="J753">
-            <v>810076211626</v>
+            <v>810076211473</v>
           </cell>
           <cell r="K753" t="str">
             <v/>
@@ -24759,20 +24765,20 @@
           </cell>
         </row>
         <row r="754">
-          <cell r="F754" t="str">
-            <v>11-1613</v>
+          <cell r="F754">
+            <v>165003</v>
           </cell>
           <cell r="G754" t="str">
-            <v>DIFFUSER, LED,Frosted Glass (Amber)</v>
+            <v>FlowArt - Multiline art - Land</v>
           </cell>
           <cell r="H754" t="str">
             <v>N</v>
           </cell>
           <cell r="I754" t="str">
-            <v>088</v>
+            <v>148</v>
           </cell>
           <cell r="J754">
-            <v>810076210889</v>
+            <v>810076211480</v>
           </cell>
           <cell r="K754" t="str">
             <v/>
@@ -24780,22 +24786,28 @@
           <cell r="L754" t="str">
             <v/>
           </cell>
+          <cell r="M754" t="str">
+            <v/>
+          </cell>
+          <cell r="N754" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="755">
-          <cell r="F755" t="str">
-            <v>11-1614</v>
+          <cell r="F755">
+            <v>165004</v>
           </cell>
           <cell r="G755" t="str">
-            <v>DIFFUSER, LED,Vertical Ribbed (White)</v>
+            <v>FlowArt - Mosaic art - Flora &amp; Fauna</v>
           </cell>
           <cell r="H755" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I755" t="str">
-            <v>089</v>
+            <v>149</v>
           </cell>
           <cell r="J755">
-            <v>810076210896</v>
+            <v>810076211497</v>
           </cell>
           <cell r="K755" t="str">
             <v/>
@@ -24803,22 +24815,28 @@
           <cell r="L755" t="str">
             <v/>
           </cell>
+          <cell r="M755" t="str">
+            <v/>
+          </cell>
+          <cell r="N755" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="756">
-          <cell r="F756" t="str">
-            <v>11-1615</v>
+          <cell r="F756">
+            <v>165010</v>
           </cell>
           <cell r="G756" t="str">
-            <v>DIFFUSER, LED, Two Tone</v>
+            <v>FlowArt - Pogo-dot - In the Garden</v>
           </cell>
           <cell r="H756" t="str">
             <v>N</v>
           </cell>
           <cell r="I756" t="str">
-            <v>090</v>
+            <v>155</v>
           </cell>
           <cell r="J756">
-            <v>810076210902</v>
+            <v>810076211558</v>
           </cell>
           <cell r="K756" t="str">
             <v/>
@@ -24826,22 +24844,28 @@
           <cell r="L756" t="str">
             <v/>
           </cell>
+          <cell r="M756" t="str">
+            <v/>
+          </cell>
+          <cell r="N756" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="757">
-          <cell r="F757" t="str">
-            <v>11-1610</v>
+          <cell r="F757">
+            <v>165011</v>
           </cell>
           <cell r="G757" t="str">
-            <v>Planter Diffuser -  Octagon (Cream)</v>
+            <v>FlowArt - Dot-pop - Sea</v>
           </cell>
           <cell r="H757" t="str">
             <v>N</v>
           </cell>
           <cell r="I757" t="str">
-            <v>095</v>
+            <v>156</v>
           </cell>
           <cell r="J757">
-            <v>810076210957</v>
+            <v>810076211565</v>
           </cell>
           <cell r="K757" t="str">
             <v/>
@@ -24849,22 +24873,28 @@
           <cell r="L757" t="str">
             <v/>
           </cell>
+          <cell r="M757" t="str">
+            <v/>
+          </cell>
+          <cell r="N757" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="758">
-          <cell r="F758" t="str">
-            <v>16-0107</v>
+          <cell r="F758">
+            <v>165013</v>
           </cell>
           <cell r="G758" t="str">
-            <v>Finger Maze Sensory Journal</v>
+            <v>FlowArt - Multiline art - Sea</v>
           </cell>
           <cell r="H758" t="str">
             <v>N</v>
           </cell>
           <cell r="I758" t="str">
-            <v>100</v>
+            <v>158</v>
           </cell>
           <cell r="J758">
-            <v>810076211008</v>
+            <v>810076211589</v>
           </cell>
           <cell r="K758" t="str">
             <v/>
@@ -24872,115 +24902,103 @@
           <cell r="L758" t="str">
             <v/>
           </cell>
+          <cell r="M758" t="str">
+            <v/>
+          </cell>
+          <cell r="N758" t="str">
+            <v/>
+          </cell>
         </row>
         <row r="759">
-          <cell r="F759" t="str">
-            <v>LL-11-2522</v>
+          <cell r="F759">
+            <v>167003</v>
           </cell>
           <cell r="G759" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
+            <v>Decor Art - Stencil Stationery</v>
           </cell>
           <cell r="H759" t="str">
             <v>N</v>
           </cell>
           <cell r="I759" t="str">
-            <v>225</v>
+            <v>162</v>
           </cell>
           <cell r="J759">
-            <v>810076212258</v>
-          </cell>
-          <cell r="K759">
-            <v>50810076212253</v>
-          </cell>
-          <cell r="L759">
-            <v>30810076212259</v>
-          </cell>
-          <cell r="O759">
-            <v>39.99</v>
-          </cell>
-          <cell r="P759">
-            <v>19.995000000000001</v>
+            <v>810076211626</v>
+          </cell>
+          <cell r="K759" t="str">
+            <v/>
+          </cell>
+          <cell r="L759" t="str">
+            <v/>
+          </cell>
+          <cell r="M759" t="str">
+            <v/>
+          </cell>
+          <cell r="N759" t="str">
+            <v/>
           </cell>
         </row>
         <row r="760">
           <cell r="F760" t="str">
-            <v>LL-11-2523</v>
+            <v>11-1613</v>
           </cell>
           <cell r="G760" t="str">
-            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
+            <v>DIFFUSER, LED,Frosted Glass (Amber)</v>
           </cell>
           <cell r="H760" t="str">
             <v>N</v>
           </cell>
           <cell r="I760" t="str">
-            <v>226</v>
+            <v>088</v>
           </cell>
           <cell r="J760">
-            <v>810076212265</v>
-          </cell>
-          <cell r="K760">
-            <v>50810076212260</v>
-          </cell>
-          <cell r="L760">
-            <v>30810076212266</v>
-          </cell>
-          <cell r="O760">
-            <v>39.99</v>
-          </cell>
-          <cell r="P760">
-            <v>19.995000000000001</v>
+            <v>810076210889</v>
+          </cell>
+          <cell r="K760" t="str">
+            <v/>
+          </cell>
+          <cell r="L760" t="str">
+            <v/>
           </cell>
         </row>
         <row r="761">
           <cell r="F761" t="str">
-            <v>LL-12-3238</v>
+            <v>11-1614</v>
           </cell>
           <cell r="G761" t="str">
-            <v>Mindful Motion Pen, Swirl 2Pck (X / X)</v>
+            <v>DIFFUSER, LED,Vertical Ribbed (White)</v>
           </cell>
           <cell r="H761" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I761" t="str">
-            <v>412</v>
+            <v>089</v>
           </cell>
           <cell r="J761">
-            <v>810076214122</v>
-          </cell>
-          <cell r="K761">
-            <v>50810076214127</v>
-          </cell>
-          <cell r="L761">
-            <v>30810076214123</v>
-          </cell>
-          <cell r="M761">
-            <v>4</v>
-          </cell>
-          <cell r="N761">
-            <v>12</v>
-          </cell>
-          <cell r="O761">
-            <v>12.99</v>
-          </cell>
-          <cell r="P761">
-            <v>6.4950000000000001</v>
+            <v>810076210896</v>
+          </cell>
+          <cell r="K761" t="str">
+            <v/>
+          </cell>
+          <cell r="L761" t="str">
+            <v/>
           </cell>
         </row>
         <row r="762">
-          <cell r="F762">
-            <v>989518</v>
+          <cell r="F762" t="str">
+            <v>11-1615</v>
           </cell>
           <cell r="G762" t="str">
-            <v>Lifelines Frosted Cream Candle with Clickwick (11-1603 &amp; 110455 Woodsy)</v>
+            <v>DIFFUSER, LED, Two Tone</v>
           </cell>
           <cell r="H762" t="str">
             <v>N</v>
           </cell>
           <cell r="I762" t="str">
-            <v>139</v>
+            <v>090</v>
           </cell>
           <cell r="J762">
-            <v>810076211398</v>
+            <v>810076210902</v>
           </cell>
           <cell r="K762" t="str">
             <v/>
@@ -24988,28 +25006,22 @@
           <cell r="L762" t="str">
             <v/>
           </cell>
-          <cell r="O762">
-            <v>41.98</v>
-          </cell>
-          <cell r="P762">
-            <v>20.99</v>
-          </cell>
         </row>
         <row r="763">
-          <cell r="F763">
-            <v>989519</v>
+          <cell r="F763" t="str">
+            <v>11-1610</v>
           </cell>
           <cell r="G763" t="str">
-            <v>Lifelines Frosted Charcoal Candle with Clickwick (11-1612 &amp; 110454 Citrus/Bloom)</v>
+            <v>Planter Diffuser -  Octagon (Cream)</v>
           </cell>
           <cell r="H763" t="str">
             <v>N</v>
           </cell>
           <cell r="I763" t="str">
-            <v>140</v>
+            <v>095</v>
           </cell>
           <cell r="J763">
-            <v>810076211404</v>
+            <v>810076210957</v>
           </cell>
           <cell r="K763" t="str">
             <v/>
@@ -25017,135 +25029,138 @@
           <cell r="L763" t="str">
             <v/>
           </cell>
-          <cell r="O763">
-            <v>41.98</v>
-          </cell>
-          <cell r="P763">
-            <v>20.99</v>
-          </cell>
         </row>
         <row r="764">
-          <cell r="F764">
-            <v>989520</v>
+          <cell r="F764" t="str">
+            <v>16-0107</v>
           </cell>
           <cell r="G764" t="str">
-            <v>Lifelines Grass Planter with Clickwick (11-1608 &amp; 110454 citrus)</v>
+            <v>Finger Maze Sensory Journal</v>
           </cell>
           <cell r="H764" t="str">
             <v>N</v>
           </cell>
           <cell r="I764" t="str">
-            <v>141</v>
+            <v>100</v>
           </cell>
           <cell r="J764">
-            <v>810076211411</v>
+            <v>810076211008</v>
           </cell>
           <cell r="K764" t="str">
             <v/>
           </cell>
           <cell r="L764" t="str">
             <v/>
-          </cell>
-          <cell r="O764">
-            <v>41.98</v>
-          </cell>
-          <cell r="P764">
-            <v>20.99</v>
           </cell>
         </row>
         <row r="765">
           <cell r="F765" t="str">
-            <v>11-0451</v>
+            <v>LL-11-2522</v>
           </cell>
           <cell r="G765" t="str">
-            <v>Clickwick Replacement Bloom, Citrus</v>
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Diner (UO exclusive)</v>
           </cell>
           <cell r="H765" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I765" t="str">
-            <v>047</v>
+            <v>225</v>
           </cell>
           <cell r="J765">
-            <v>810076210476</v>
-          </cell>
-          <cell r="K765" t="str">
-            <v/>
-          </cell>
-          <cell r="L765" t="str">
-            <v/>
+            <v>810076212258</v>
+          </cell>
+          <cell r="K765">
+            <v>50810076212253</v>
+          </cell>
+          <cell r="L765">
+            <v>30810076212259</v>
           </cell>
           <cell r="O765">
-            <v>11.99</v>
+            <v>39.99</v>
           </cell>
           <cell r="P765">
-            <v>5.9950000000000001</v>
+            <v>19.995000000000001</v>
           </cell>
         </row>
         <row r="766">
           <cell r="F766" t="str">
-            <v>99-9502</v>
+            <v>LL-11-2523</v>
           </cell>
           <cell r="G766" t="str">
-            <v>Pen Display - Empty</v>
+            <v>Lifelines Pen Diffuser with Essential Oil Blends -Café  (UO exclusive)</v>
           </cell>
           <cell r="H766" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="I766" t="str">
-            <v/>
-          </cell>
-          <cell r="L766" t="str">
-            <v/>
+            <v>226</v>
+          </cell>
+          <cell r="J766">
+            <v>810076212265</v>
+          </cell>
+          <cell r="K766">
+            <v>50810076212260</v>
+          </cell>
+          <cell r="L766">
+            <v>30810076212266</v>
           </cell>
           <cell r="O766">
-            <v>11.99</v>
+            <v>39.99</v>
           </cell>
           <cell r="P766">
-            <v>5.9950000000000001</v>
+            <v>19.995000000000001</v>
           </cell>
         </row>
         <row r="767">
           <cell r="F767" t="str">
-            <v>11-0452</v>
+            <v>LL-12-3238</v>
           </cell>
           <cell r="G767" t="str">
-            <v>Clickwick Replacement Woods, Mountain</v>
+            <v>Mindful Motion Pen, Swirl 2Pck (X / X)</v>
           </cell>
           <cell r="H767" t="str">
             <v>Y</v>
           </cell>
           <cell r="I767" t="str">
-            <v>048</v>
+            <v>412</v>
           </cell>
           <cell r="J767">
-            <v>810076210483</v>
-          </cell>
-          <cell r="K767" t="str">
-            <v/>
-          </cell>
-          <cell r="L767" t="str">
-            <v/>
+            <v>810076214122</v>
+          </cell>
+          <cell r="K767">
+            <v>50810076214127</v>
+          </cell>
+          <cell r="L767">
+            <v>30810076214123</v>
+          </cell>
+          <cell r="M767">
+            <v>4</v>
+          </cell>
+          <cell r="N767">
+            <v>12</v>
           </cell>
           <cell r="O767">
-            <v>11.99</v>
+            <v>12.99</v>
           </cell>
           <cell r="P767">
-            <v>5.9950000000000001</v>
+            <v>6.4950000000000001</v>
           </cell>
         </row>
         <row r="768">
-          <cell r="F768" t="str">
-            <v>112522</v>
+          <cell r="F768">
+            <v>989518</v>
+          </cell>
+          <cell r="G768" t="str">
+            <v>Lifelines Frosted Cream Candle with Clickwick (11-1603 &amp; 110455 Woodsy)</v>
           </cell>
           <cell r="H768" t="str">
             <v>N</v>
           </cell>
           <cell r="I768" t="str">
-            <v>193</v>
+            <v>139</v>
           </cell>
           <cell r="J768">
-            <v>810076211930</v>
+            <v>810076211398</v>
           </cell>
           <cell r="K768" t="str">
             <v/>
@@ -25153,34 +25168,28 @@
           <cell r="L768" t="str">
             <v/>
           </cell>
-          <cell r="M768" t="str">
-            <v/>
-          </cell>
-          <cell r="N768" t="str">
-            <v/>
-          </cell>
           <cell r="O768">
-            <v>9.99</v>
+            <v>41.98</v>
           </cell>
           <cell r="P768">
-            <v>4.9950000000000001</v>
+            <v>20.99</v>
           </cell>
         </row>
         <row r="769">
-          <cell r="F769" t="str">
-            <v>99-9501</v>
+          <cell r="F769">
+            <v>989519</v>
           </cell>
           <cell r="G769" t="str">
-            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
+            <v>Lifelines Frosted Charcoal Candle with Clickwick (11-1612 &amp; 110454 Citrus/Bloom)</v>
           </cell>
           <cell r="H769" t="str">
             <v>N</v>
           </cell>
           <cell r="I769" t="str">
-            <v>077</v>
+            <v>140</v>
           </cell>
           <cell r="J769">
-            <v>810076210773</v>
+            <v>810076211404</v>
           </cell>
           <cell r="K769" t="str">
             <v/>
@@ -25188,266 +25197,227 @@
           <cell r="L769" t="str">
             <v/>
           </cell>
-          <cell r="M769">
-            <v>0</v>
-          </cell>
-          <cell r="N769">
-            <v>1</v>
-          </cell>
           <cell r="O769">
-            <v>300</v>
+            <v>41.98</v>
           </cell>
           <cell r="P769">
-            <v>150</v>
+            <v>20.99</v>
           </cell>
         </row>
         <row r="770">
-          <cell r="F770" t="str">
-            <v>11-1618</v>
+          <cell r="F770">
+            <v>989520</v>
           </cell>
           <cell r="G770" t="str">
-            <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
+            <v>Lifelines Grass Planter with Clickwick (11-1608 &amp; 110454 citrus)</v>
+          </cell>
+          <cell r="H770" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I770" t="str">
+            <v>141</v>
+          </cell>
+          <cell r="J770">
+            <v>810076211411</v>
+          </cell>
+          <cell r="K770" t="str">
+            <v/>
+          </cell>
+          <cell r="L770" t="str">
+            <v/>
+          </cell>
+          <cell r="O770">
+            <v>41.98</v>
+          </cell>
+          <cell r="P770">
+            <v>20.99</v>
           </cell>
         </row>
         <row r="771">
           <cell r="F771" t="str">
-            <v>98-9220</v>
+            <v>11-0451</v>
           </cell>
           <cell r="G771" t="str">
-            <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
+            <v>Clickwick Replacement Bloom, Citrus</v>
+          </cell>
+          <cell r="H771" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="I771" t="str">
+            <v>047</v>
+          </cell>
+          <cell r="J771">
+            <v>810076210476</v>
+          </cell>
+          <cell r="K771" t="str">
+            <v/>
+          </cell>
+          <cell r="L771" t="str">
+            <v/>
+          </cell>
+          <cell r="O771">
+            <v>11.99</v>
+          </cell>
+          <cell r="P771">
+            <v>5.9950000000000001</v>
           </cell>
         </row>
         <row r="772">
           <cell r="F772" t="str">
-            <v>LL-25-3275</v>
+            <v>99-9502</v>
           </cell>
           <cell r="G772" t="str">
-            <v>Scented Palm Calms 1 - Zen Garden - WMT</v>
+            <v>Pen Display - Empty</v>
           </cell>
           <cell r="H772" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I772" t="str">
-            <v>457</v>
-          </cell>
-          <cell r="J772">
-            <v>810076214573</v>
-          </cell>
-          <cell r="K772">
-            <v>50810076214578</v>
-          </cell>
-          <cell r="L772">
-            <v>30810076214574</v>
-          </cell>
-          <cell r="M772">
-            <v>4</v>
-          </cell>
-          <cell r="N772">
-            <v>12</v>
+            <v/>
+          </cell>
+          <cell r="L772" t="str">
+            <v/>
           </cell>
           <cell r="O772">
-            <v>15</v>
+            <v>11.99</v>
           </cell>
           <cell r="P772">
-            <v>7.5</v>
+            <v>5.9950000000000001</v>
           </cell>
         </row>
         <row r="773">
           <cell r="F773" t="str">
-            <v>LL-25-3276</v>
+            <v>11-0452</v>
           </cell>
           <cell r="G773" t="str">
-            <v>Scented Palm Calms 2 - Spa Serenity - WMT</v>
+            <v>Clickwick Replacement Woods, Mountain</v>
           </cell>
           <cell r="H773" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="I773" t="str">
-            <v>458</v>
+            <v>048</v>
           </cell>
           <cell r="J773">
-            <v>810076214580</v>
-          </cell>
-          <cell r="K773">
-            <v>50810076214585</v>
-          </cell>
-          <cell r="L773">
-            <v>30810076214581</v>
-          </cell>
-          <cell r="M773">
-            <v>4</v>
-          </cell>
-          <cell r="N773">
-            <v>12</v>
+            <v>810076210483</v>
+          </cell>
+          <cell r="K773" t="str">
+            <v/>
+          </cell>
+          <cell r="L773" t="str">
+            <v/>
           </cell>
           <cell r="O773">
-            <v>15</v>
+            <v>11.99</v>
           </cell>
           <cell r="P773">
-            <v>7.5</v>
+            <v>5.9950000000000001</v>
           </cell>
         </row>
         <row r="774">
           <cell r="F774" t="str">
-            <v>LL-25-3283</v>
-          </cell>
-          <cell r="G774" t="str">
-            <v>Scented Palm Calms 4 - Zen Meditation - WMT</v>
+            <v>112522</v>
           </cell>
           <cell r="H774" t="str">
             <v>N</v>
           </cell>
           <cell r="I774" t="str">
-            <v>463</v>
+            <v>193</v>
           </cell>
           <cell r="J774">
-            <v>810076214634</v>
-          </cell>
-          <cell r="K774">
-            <v>50810076214639</v>
-          </cell>
-          <cell r="L774">
-            <v>30810076214635</v>
-          </cell>
-          <cell r="M774">
-            <v>4</v>
-          </cell>
-          <cell r="N774">
-            <v>12</v>
+            <v>810076211930</v>
+          </cell>
+          <cell r="K774" t="str">
+            <v/>
+          </cell>
+          <cell r="L774" t="str">
+            <v/>
+          </cell>
+          <cell r="M774" t="str">
+            <v/>
+          </cell>
+          <cell r="N774" t="str">
+            <v/>
           </cell>
           <cell r="O774">
-            <v>15</v>
+            <v>9.99</v>
           </cell>
           <cell r="P774">
-            <v>7.5</v>
+            <v>4.9950000000000001</v>
           </cell>
         </row>
         <row r="775">
           <cell r="F775" t="str">
-            <v>LL-25-3284</v>
+            <v>99-9501</v>
           </cell>
           <cell r="G775" t="str">
-            <v>Scented Palm Calms 5 - Forest Friends - WMT</v>
+            <v xml:space="preserve">Pen Diffuser Assortment - 30 ct </v>
           </cell>
           <cell r="H775" t="str">
             <v>N</v>
           </cell>
           <cell r="I775" t="str">
-            <v>464</v>
+            <v>077</v>
           </cell>
           <cell r="J775">
-            <v>810076214641</v>
-          </cell>
-          <cell r="K775">
-            <v>50810076214646</v>
-          </cell>
-          <cell r="L775">
-            <v>30810076214642</v>
+            <v>810076210773</v>
+          </cell>
+          <cell r="K775" t="str">
+            <v/>
+          </cell>
+          <cell r="L775" t="str">
+            <v/>
           </cell>
           <cell r="M775">
-            <v>4</v>
+            <v>0</v>
           </cell>
           <cell r="N775">
-            <v>12</v>
+            <v>1</v>
           </cell>
           <cell r="O775">
-            <v>15</v>
+            <v>300</v>
           </cell>
           <cell r="P775">
-            <v>7.5</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="776">
           <cell r="F776" t="str">
-            <v>LL-25-3285</v>
+            <v>11-1618</v>
           </cell>
           <cell r="G776" t="str">
-            <v>Scented Palm Calms 6 - Animal Friends - WMT</v>
-          </cell>
-          <cell r="H776" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="I776" t="str">
-            <v>465</v>
-          </cell>
-          <cell r="J776">
-            <v>810076214658</v>
-          </cell>
-          <cell r="K776">
-            <v>50810076214653</v>
-          </cell>
-          <cell r="L776">
-            <v>30810076214659</v>
-          </cell>
-          <cell r="M776">
-            <v>4</v>
-          </cell>
-          <cell r="N776">
-            <v>12</v>
-          </cell>
-          <cell r="O776">
-            <v>15</v>
-          </cell>
-          <cell r="P776">
-            <v>7.5</v>
+            <v>DIFFUSER, LED,Winter Edition (Frosted Green)</v>
           </cell>
         </row>
         <row r="777">
           <cell r="F777" t="str">
-            <v>LL-25-3286</v>
+            <v>98-9220</v>
           </cell>
           <cell r="G777" t="str">
-            <v>Scented Palm Calms 7 - Writers Desk -  WMT</v>
-          </cell>
-          <cell r="H777" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="I777" t="str">
-            <v>466</v>
-          </cell>
-          <cell r="J777">
-            <v>810076214665</v>
-          </cell>
-          <cell r="K777">
-            <v>50810076214660</v>
-          </cell>
-          <cell r="L777">
-            <v>30810076214666</v>
-          </cell>
-          <cell r="M777">
-            <v>4</v>
-          </cell>
-          <cell r="N777">
-            <v>12</v>
-          </cell>
-          <cell r="O777">
-            <v>15</v>
-          </cell>
-          <cell r="P777">
-            <v>7.5</v>
+            <v>Candle + Oil  BOX Set  (4 oils) - Frosted Cream Candle</v>
           </cell>
         </row>
         <row r="778">
           <cell r="F778" t="str">
-            <v>LL-25-3287</v>
+            <v>LL-25-3275</v>
           </cell>
           <cell r="G778" t="str">
-            <v>Scented Palm Calms 8 - Little Books -  WMT</v>
+            <v>Scented Palm Calms 1 - Zen Garden - WMT</v>
           </cell>
           <cell r="H778" t="str">
             <v>N</v>
           </cell>
           <cell r="I778" t="str">
-            <v>467</v>
+            <v>457</v>
           </cell>
           <cell r="J778">
-            <v>810076214672</v>
+            <v>810076214573</v>
           </cell>
           <cell r="K778">
-            <v>50810076214677</v>
+            <v>50810076214578</v>
           </cell>
           <cell r="L778">
-            <v>30810076214673</v>
+            <v>30810076214574</v>
           </cell>
           <cell r="M778">
             <v>4</v>
@@ -25464,25 +25434,25 @@
         </row>
         <row r="779">
           <cell r="F779" t="str">
-            <v>LL-25-3278</v>
+            <v>LL-25-3276</v>
           </cell>
           <cell r="G779" t="str">
-            <v>Scented Palm Calms Discovery Set - WMT</v>
+            <v>Scented Palm Calms 2 - Spa Serenity - WMT</v>
           </cell>
           <cell r="H779" t="str">
             <v>N</v>
           </cell>
           <cell r="I779" t="str">
-            <v>460</v>
+            <v>458</v>
           </cell>
           <cell r="J779">
-            <v>810076214603</v>
+            <v>810076214580</v>
           </cell>
           <cell r="K779">
-            <v>50810076214608</v>
+            <v>50810076214585</v>
           </cell>
           <cell r="L779">
-            <v>30810076214604</v>
+            <v>30810076214581</v>
           </cell>
           <cell r="M779">
             <v>4</v>
@@ -25491,14 +25461,224 @@
             <v>12</v>
           </cell>
           <cell r="O779">
+            <v>15</v>
+          </cell>
+          <cell r="P779">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="780">
+          <cell r="F780" t="str">
+            <v>LL-25-3283</v>
+          </cell>
+          <cell r="G780" t="str">
+            <v>Scented Palm Calms 4 - Zen Meditation - WMT</v>
+          </cell>
+          <cell r="H780" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I780" t="str">
+            <v>463</v>
+          </cell>
+          <cell r="J780">
+            <v>810076214634</v>
+          </cell>
+          <cell r="K780">
+            <v>50810076214639</v>
+          </cell>
+          <cell r="L780">
+            <v>30810076214635</v>
+          </cell>
+          <cell r="M780">
+            <v>4</v>
+          </cell>
+          <cell r="N780">
+            <v>12</v>
+          </cell>
+          <cell r="O780">
+            <v>15</v>
+          </cell>
+          <cell r="P780">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="781">
+          <cell r="F781" t="str">
+            <v>LL-25-3284</v>
+          </cell>
+          <cell r="G781" t="str">
+            <v>Scented Palm Calms 5 - Forest Friends - WMT</v>
+          </cell>
+          <cell r="H781" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I781" t="str">
+            <v>464</v>
+          </cell>
+          <cell r="J781">
+            <v>810076214641</v>
+          </cell>
+          <cell r="K781">
+            <v>50810076214646</v>
+          </cell>
+          <cell r="L781">
+            <v>30810076214642</v>
+          </cell>
+          <cell r="M781">
+            <v>4</v>
+          </cell>
+          <cell r="N781">
+            <v>12</v>
+          </cell>
+          <cell r="O781">
+            <v>15</v>
+          </cell>
+          <cell r="P781">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="782">
+          <cell r="F782" t="str">
+            <v>LL-25-3285</v>
+          </cell>
+          <cell r="G782" t="str">
+            <v>Scented Palm Calms 6 - Animal Friends - WMT</v>
+          </cell>
+          <cell r="H782" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I782" t="str">
+            <v>465</v>
+          </cell>
+          <cell r="J782">
+            <v>810076214658</v>
+          </cell>
+          <cell r="K782">
+            <v>50810076214653</v>
+          </cell>
+          <cell r="L782">
+            <v>30810076214659</v>
+          </cell>
+          <cell r="M782">
+            <v>4</v>
+          </cell>
+          <cell r="N782">
+            <v>12</v>
+          </cell>
+          <cell r="O782">
+            <v>15</v>
+          </cell>
+          <cell r="P782">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="783">
+          <cell r="F783" t="str">
+            <v>LL-25-3286</v>
+          </cell>
+          <cell r="G783" t="str">
+            <v>Scented Palm Calms 7 - Writers Desk -  WMT</v>
+          </cell>
+          <cell r="H783" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I783" t="str">
+            <v>466</v>
+          </cell>
+          <cell r="J783">
+            <v>810076214665</v>
+          </cell>
+          <cell r="K783">
+            <v>50810076214660</v>
+          </cell>
+          <cell r="L783">
+            <v>30810076214666</v>
+          </cell>
+          <cell r="M783">
+            <v>4</v>
+          </cell>
+          <cell r="N783">
+            <v>12</v>
+          </cell>
+          <cell r="O783">
+            <v>15</v>
+          </cell>
+          <cell r="P783">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="784">
+          <cell r="F784" t="str">
+            <v>LL-25-3287</v>
+          </cell>
+          <cell r="G784" t="str">
+            <v>Scented Palm Calms 8 - Little Books -  WMT</v>
+          </cell>
+          <cell r="H784" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I784" t="str">
+            <v>467</v>
+          </cell>
+          <cell r="J784">
+            <v>810076214672</v>
+          </cell>
+          <cell r="K784">
+            <v>50810076214677</v>
+          </cell>
+          <cell r="L784">
+            <v>30810076214673</v>
+          </cell>
+          <cell r="M784">
+            <v>4</v>
+          </cell>
+          <cell r="N784">
+            <v>12</v>
+          </cell>
+          <cell r="O784">
+            <v>15</v>
+          </cell>
+          <cell r="P784">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="785">
+          <cell r="F785" t="str">
+            <v>LL-25-3278</v>
+          </cell>
+          <cell r="G785" t="str">
+            <v>Scented Palm Calms Discovery Set - WMT</v>
+          </cell>
+          <cell r="H785" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="I785" t="str">
+            <v>460</v>
+          </cell>
+          <cell r="J785">
+            <v>810076214603</v>
+          </cell>
+          <cell r="K785">
+            <v>50810076214608</v>
+          </cell>
+          <cell r="L785">
+            <v>30810076214604</v>
+          </cell>
+          <cell r="M785">
+            <v>4</v>
+          </cell>
+          <cell r="N785">
+            <v>12</v>
+          </cell>
+          <cell r="O785">
             <v>10</v>
           </cell>
-          <cell r="P779">
+          <cell r="P785">
             <v>5</v>
           </cell>
         </row>
-        <row r="1479">
-          <cell r="F1479" t="str">
+        <row r="1485">
+          <cell r="F1485" t="str">
             <v>=IF(RC5=RC1, "", VLOOKUP(RC5, SBOM!C6:C7, 2, FALSE))</v>
           </cell>
         </row>
@@ -27073,8 +27253,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -27096,8 +27275,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -27119,8 +27297,7 @@
         <v>8</v>
       </c>
       <c r="F65" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -27165,8 +27342,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -27188,8 +27364,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -27211,8 +27386,7 @@
         <v>4</v>
       </c>
       <c r="F69" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -27234,8 +27408,7 @@
         <v>12</v>
       </c>
       <c r="F70" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -27257,8 +27430,7 @@
         <v>8</v>
       </c>
       <c r="F71" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -27280,8 +27452,7 @@
         <v>4</v>
       </c>
       <c r="F72" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -27303,8 +27474,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C73), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -27326,8 +27496,7 @@
         <v>12</v>
       </c>
       <c r="F74" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C74), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -27349,8 +27518,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -27372,8 +27540,7 @@
         <v>12</v>
       </c>
       <c r="F76" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C76), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -27395,8 +27562,7 @@
         <v>12</v>
       </c>
       <c r="F77" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -27418,8 +27584,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -27441,8 +27606,7 @@
         <v>4</v>
       </c>
       <c r="F79" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -27464,8 +27628,7 @@
         <v>8</v>
       </c>
       <c r="F80" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -28501,6 +28664,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -28741,15 +28913,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
   <ds:schemaRefs>
@@ -28762,6 +28925,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28778,12 +28949,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD2768D8-BB86-44B0-988D-A4068932372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5859D1CF-EA07-45F7-B5F4-FD8F2F663595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="81">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -274,6 +274,15 @@
   <si>
     <t>LL-16-3224</t>
   </si>
+  <si>
+    <t>165005</t>
+  </si>
+  <si>
+    <t>165008</t>
+  </si>
+  <si>
+    <t>165012</t>
+  </si>
 </sst>
 </file>
 
@@ -304,7 +313,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -312,11 +321,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -325,6 +343,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5599,7 +5622,7 @@
             <v>LL-14-3173</v>
           </cell>
           <cell r="G160" t="str">
-            <v>DIFFUSER, LED, FROSTED CREAM - AMZ - Vanilla Tangerine</v>
+            <v>DIFFUSER, LED, FROSTED CREAM - 2x CW - Vanilla Tangerine</v>
           </cell>
           <cell r="H160" t="str">
             <v>Y</v>
@@ -5634,7 +5657,7 @@
             <v>LL-14-3177</v>
           </cell>
           <cell r="G161" t="str">
-            <v>DIFFUSER, LED, FROSTED CHARCOAL - AMZ - Desert Winds</v>
+            <v>DIFFUSER, LED, FROSTED CHARCOAL - 2x CW - Desert Winds</v>
           </cell>
           <cell r="H161" t="str">
             <v>Y</v>
@@ -5669,7 +5692,7 @@
             <v>LL-14-3178</v>
           </cell>
           <cell r="G162" t="str">
-            <v>DIFFUSER, LED, MARBLE - AMZ - Desert Winds</v>
+            <v>DIFFUSER, LED, MARBLE - 2x CW - Desert Winds</v>
           </cell>
           <cell r="H162" t="str">
             <v>Y</v>
@@ -5704,7 +5727,7 @@
             <v>LL-14-3179</v>
           </cell>
           <cell r="G163" t="str">
-            <v>DIFFUSER, LED, BUBBLE CREAM - AMZ - Coconut Hisbiscus</v>
+            <v>DIFFUSER, LED, BUBBLE CREAM - 2x CW - Coconut Hisbiscus</v>
           </cell>
           <cell r="H163" t="str">
             <v>Y</v>
@@ -5739,7 +5762,7 @@
             <v>LL-14-3256</v>
           </cell>
           <cell r="G164" t="str">
-            <v>DIFFUSER, LED, BUBBLE BLUE - AMZ - Salted Coconut</v>
+            <v>DIFFUSER, LED, BUBBLE BLUE - 2x CW - Salted Coconut</v>
           </cell>
           <cell r="H164" t="str">
             <v>Y</v>
@@ -5774,7 +5797,7 @@
             <v>LL-14-3180</v>
           </cell>
           <cell r="G165" t="str">
-            <v>DIFFUSER, LED, BUBBLE GREEN - AMZ - Peach Velvet</v>
+            <v>DIFFUSER, LED, BUBBLE GREEN - 2x CW - Peach Velvet</v>
           </cell>
           <cell r="H165" t="str">
             <v>Y</v>
@@ -5809,7 +5832,7 @@
             <v>LL-14-3181</v>
           </cell>
           <cell r="G166" t="str">
-            <v>DIFFUSER, LED, RIBBED PINK - AMZ - Peach Velvet</v>
+            <v>DIFFUSER, LED, RIBBED PINK - 2x CW - Peach Velvet</v>
           </cell>
           <cell r="H166" t="str">
             <v>Y</v>
@@ -5844,7 +5867,7 @@
             <v>LL-14-3182</v>
           </cell>
           <cell r="G167" t="str">
-            <v>DIFFUSER, LED, RIBBED OLIVE - AMZ - Coconut Hisbiscus</v>
+            <v>DIFFUSER, LED, RIBBED OLIVE - 2x CW - Coconut Hisbiscus</v>
           </cell>
           <cell r="H167" t="str">
             <v>Y</v>
@@ -21891,7 +21914,7 @@
             <v>LL-00-0011</v>
           </cell>
           <cell r="G650" t="str">
-            <v>BTS Sidecap - FA Minis</v>
+            <v>May26 Sidecap - FA Minis - 72</v>
           </cell>
           <cell r="H650" t="str">
             <v>Y</v>
@@ -22001,7 +22024,7 @@
             <v>LL-00-0014</v>
           </cell>
           <cell r="G654" t="str">
-            <v>FA Mini - Counter Display - Full</v>
+            <v>FA Mini - Counter Display - 36</v>
           </cell>
           <cell r="H654" t="str">
             <v>Y</v>
@@ -27211,25 +27234,25 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+    <row r="62" spans="1:6" s="6" customFormat="1">
+      <c r="A62" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D62" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="6">
         <v>4</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="8">
         <f>ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
         <v>6.5</v>
       </c>
@@ -27242,8 +27265,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C63" s="1">
-        <v>165005</v>
+      <c r="C63" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="D63" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
@@ -27264,12 +27287,12 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C64" s="1">
-        <v>165008</v>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D64" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E64">
         <v>12</v>
@@ -27286,12 +27309,12 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C65" s="1">
-        <v>165012</v>
+      <c r="C65" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D65" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
       </c>
       <c r="E65">
         <v>8</v>
@@ -27309,18 +27332,17 @@
         <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D66" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
       <c r="E66">
         <v>12</v>
       </c>
       <c r="F66" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -27332,11 +27354,11 @@
         <v>5</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D67" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
       <c r="E67">
         <v>12</v>
@@ -27354,14 +27376,14 @@
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D68" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
       </c>
       <c r="E68">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F68" s="2">
         <v>5</v>
@@ -27376,14 +27398,14 @@
         <v>7</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D69" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F69" s="2">
         <v>5</v>
@@ -27398,14 +27420,14 @@
         <v>8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D70" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
       </c>
       <c r="E70">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F70" s="2">
         <v>5</v>
@@ -27427,7 +27449,7 @@
         <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2">
         <v>5</v>
@@ -27442,14 +27464,14 @@
         <v>10</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D72" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2">
         <v>5</v>
@@ -27464,11 +27486,11 @@
         <v>11</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D73" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
       <c r="E73">
         <v>12</v>
@@ -27486,17 +27508,17 @@
         <v>12</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="D74" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>FlowArt - Spinner Tower - Empty</v>
       </c>
       <c r="E74">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -27508,14 +27530,14 @@
         <v>13</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D75" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F75" s="2">
         <v>5</v>
@@ -27530,11 +27552,11 @@
         <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D76" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
       </c>
       <c r="E76">
         <v>12</v>
@@ -27552,14 +27574,14 @@
         <v>15</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D77" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
       </c>
       <c r="E77">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F77" s="2">
         <v>5</v>
@@ -27596,38 +27618,38 @@
         <v>17</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D79" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+    <row r="80" spans="1:6" s="6" customFormat="1">
+      <c r="A80" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="6">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D80" t="str">
+      <c r="C80" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D80" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
-      </c>
-      <c r="E80">
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E80" s="6">
         <v>8</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="8">
         <v>5</v>
       </c>
     </row>
@@ -28644,6 +28666,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -28664,15 +28687,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B10405EB6D76C04A99D739F71CB1C882" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="588855ac044783769b53e0cfeb370d1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="856a7437-a7e7-4452-817c-46e435f59c4c" xmlns:ns3="0db41735-03c9-45f7-99e2-dcae27ef4500" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f4c0eefc11dc6e5e719c9a8931b7f89" ns2:_="" ns3:_="">
     <xsd:import namespace="856a7437-a7e7-4452-817c-46e435f59c4c"/>
@@ -28913,6 +28927,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366D689B-EA99-40CD-8C29-C46E1E100306}">
   <ds:schemaRefs>
@@ -28925,14 +28948,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54E2E001-0CF6-4D1A-BD8C-B56D3CAC6266}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28949,4 +28964,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34DF14EF-9695-4C1E-AA3D-1898563EEFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assortment-expansion.xlsx
+++ b/assortment-expansion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PaulKirchner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5859D1CF-EA07-45F7-B5F4-FD8F2F663595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A79E6BC-FF47-4F9F-8F32-1F29CBB5506E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="84">
   <si>
     <t>Assortment Expansion</t>
   </si>
@@ -269,9 +269,6 @@
     <t>LL-16-3300</t>
   </si>
   <si>
-    <t>99-9502</t>
-  </si>
-  <si>
     <t>LL-16-3224</t>
   </si>
   <si>
@@ -282,6 +279,18 @@
   </si>
   <si>
     <t>165012</t>
+  </si>
+  <si>
+    <t>NEEDTOCOMEUPWITHONE</t>
+  </si>
+  <si>
+    <t>165006</t>
+  </si>
+  <si>
+    <t>165007</t>
+  </si>
+  <si>
+    <t>165009</t>
   </si>
 </sst>
 </file>
@@ -313,21 +322,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -343,16 +343,46 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -486,6 +516,8 @@
           <cell r="L3">
             <v>30810076213720</v>
           </cell>
+          <cell r="M3"/>
+          <cell r="N3"/>
           <cell r="O3">
             <v>25.98</v>
           </cell>
@@ -515,6 +547,8 @@
           <cell r="L4">
             <v>30810076210293</v>
           </cell>
+          <cell r="M4"/>
+          <cell r="N4"/>
           <cell r="O4">
             <v>19.989999999999998</v>
           </cell>
@@ -2054,6 +2088,7 @@
           <cell r="L49">
             <v>30810076210446</v>
           </cell>
+          <cell r="M49"/>
           <cell r="N49">
             <v>6</v>
           </cell>
@@ -2331,6 +2366,8 @@
           <cell r="L57">
             <v>30810076213096</v>
           </cell>
+          <cell r="M57"/>
+          <cell r="N57"/>
           <cell r="O57">
             <v>14.99</v>
           </cell>
@@ -2360,6 +2397,8 @@
           <cell r="L58">
             <v>30810076213102</v>
           </cell>
+          <cell r="M58"/>
+          <cell r="N58"/>
           <cell r="O58">
             <v>14.99</v>
           </cell>
@@ -2389,6 +2428,8 @@
           <cell r="L59">
             <v>30810076213119</v>
           </cell>
+          <cell r="M59"/>
+          <cell r="N59"/>
           <cell r="O59">
             <v>14.99</v>
           </cell>
@@ -2727,6 +2768,8 @@
           <cell r="L69" t="str">
             <v/>
           </cell>
+          <cell r="M69"/>
+          <cell r="N69"/>
           <cell r="O69">
             <v>12.99</v>
           </cell>
@@ -3164,6 +3207,7 @@
           <cell r="N82">
             <v>36</v>
           </cell>
+          <cell r="P82"/>
         </row>
         <row r="83">
           <cell r="F83" t="str">
@@ -3193,6 +3237,7 @@
           <cell r="N83">
             <v>36</v>
           </cell>
+          <cell r="P83"/>
         </row>
         <row r="84">
           <cell r="F84" t="str">
@@ -3222,6 +3267,7 @@
           <cell r="N84">
             <v>36</v>
           </cell>
+          <cell r="P84"/>
         </row>
         <row r="85">
           <cell r="F85" t="str">
@@ -3449,6 +3495,7 @@
           <cell r="L91">
             <v>30810076212709</v>
           </cell>
+          <cell r="M91"/>
           <cell r="N91">
             <v>72</v>
           </cell>
@@ -3755,6 +3802,8 @@
           <cell r="L100">
             <v>30810076211238</v>
           </cell>
+          <cell r="M100"/>
+          <cell r="N100"/>
           <cell r="O100" t="str">
             <v>-</v>
           </cell>
@@ -4131,6 +4180,7 @@
           <cell r="L111">
             <v>30810076210705</v>
           </cell>
+          <cell r="M111"/>
           <cell r="N111">
             <v>24</v>
           </cell>
@@ -4268,6 +4318,7 @@
           <cell r="L115">
             <v>30810076210651</v>
           </cell>
+          <cell r="M115"/>
           <cell r="N115">
             <v>24</v>
           </cell>
@@ -4300,6 +4351,7 @@
           <cell r="L116">
             <v>30810076210644</v>
           </cell>
+          <cell r="M116"/>
           <cell r="N116">
             <v>24</v>
           </cell>
@@ -4332,6 +4384,7 @@
           <cell r="L117">
             <v>30810076210637</v>
           </cell>
+          <cell r="M117"/>
           <cell r="N117">
             <v>24</v>
           </cell>
@@ -4364,6 +4417,8 @@
           <cell r="L118">
             <v>30810076210538</v>
           </cell>
+          <cell r="M118"/>
+          <cell r="N118"/>
           <cell r="O118">
             <v>11.99</v>
           </cell>
@@ -4393,6 +4448,8 @@
           <cell r="L119">
             <v>30810076210545</v>
           </cell>
+          <cell r="M119"/>
+          <cell r="N119"/>
           <cell r="O119">
             <v>11.99</v>
           </cell>
@@ -4422,6 +4479,8 @@
           <cell r="L120">
             <v>30810076210552</v>
           </cell>
+          <cell r="M120"/>
+          <cell r="N120"/>
           <cell r="O120">
             <v>11.99</v>
           </cell>
@@ -4451,6 +4510,8 @@
           <cell r="L121">
             <v>30810076210569</v>
           </cell>
+          <cell r="M121"/>
+          <cell r="N121"/>
           <cell r="O121">
             <v>11.99</v>
           </cell>
@@ -4480,6 +4541,8 @@
           <cell r="L122">
             <v>30810076210576</v>
           </cell>
+          <cell r="M122"/>
+          <cell r="N122"/>
           <cell r="O122">
             <v>11.99</v>
           </cell>
@@ -4509,6 +4572,8 @@
           <cell r="L123">
             <v>30810076210583</v>
           </cell>
+          <cell r="M123"/>
+          <cell r="N123"/>
           <cell r="O123">
             <v>11.99</v>
           </cell>
@@ -4538,6 +4603,8 @@
           <cell r="L124">
             <v>30810076210590</v>
           </cell>
+          <cell r="M124"/>
+          <cell r="N124"/>
           <cell r="O124">
             <v>11.99</v>
           </cell>
@@ -4567,6 +4634,8 @@
           <cell r="L125">
             <v>30810076210606</v>
           </cell>
+          <cell r="M125"/>
+          <cell r="N125"/>
           <cell r="O125">
             <v>11.99</v>
           </cell>
@@ -4596,6 +4665,8 @@
           <cell r="L126">
             <v>30810076210613</v>
           </cell>
+          <cell r="M126"/>
+          <cell r="N126"/>
           <cell r="O126">
             <v>11.99</v>
           </cell>
@@ -4625,6 +4696,8 @@
           <cell r="L127">
             <v>30810076210620</v>
           </cell>
+          <cell r="M127"/>
+          <cell r="N127"/>
           <cell r="O127">
             <v>11.99</v>
           </cell>
@@ -4654,6 +4727,7 @@
           <cell r="L128">
             <v>30810076211177</v>
           </cell>
+          <cell r="M128"/>
           <cell r="N128">
             <v>10</v>
           </cell>
@@ -4686,6 +4760,8 @@
           <cell r="L129">
             <v>30810076210675</v>
           </cell>
+          <cell r="M129"/>
+          <cell r="N129"/>
           <cell r="O129">
             <v>19.989999999999998</v>
           </cell>
@@ -4715,6 +4791,8 @@
           <cell r="L130">
             <v>30810076210682</v>
           </cell>
+          <cell r="M130"/>
+          <cell r="N130"/>
           <cell r="O130">
             <v>19.989999999999998</v>
           </cell>
@@ -4744,6 +4822,8 @@
           <cell r="L131">
             <v>30810076210699</v>
           </cell>
+          <cell r="M131"/>
+          <cell r="N131"/>
           <cell r="O131">
             <v>19.989999999999998</v>
           </cell>
@@ -4773,6 +4853,7 @@
           <cell r="L132">
             <v>30810076210668</v>
           </cell>
+          <cell r="M132"/>
           <cell r="N132">
             <v>24</v>
           </cell>
@@ -4805,6 +4886,8 @@
           <cell r="L133">
             <v>30810076211115</v>
           </cell>
+          <cell r="M133"/>
+          <cell r="N133"/>
           <cell r="O133">
             <v>18.989999999999998</v>
           </cell>
@@ -4834,6 +4917,7 @@
           <cell r="L134">
             <v>30810076210804</v>
           </cell>
+          <cell r="M134"/>
           <cell r="N134">
             <v>24</v>
           </cell>
@@ -4866,6 +4950,7 @@
           <cell r="L135">
             <v>30810076210811</v>
           </cell>
+          <cell r="M135"/>
           <cell r="N135">
             <v>24</v>
           </cell>
@@ -4898,6 +4983,8 @@
           <cell r="L136">
             <v>30810076211146</v>
           </cell>
+          <cell r="M136"/>
+          <cell r="N136"/>
           <cell r="O136">
             <v>19.989999999999998</v>
           </cell>
@@ -4927,6 +5014,8 @@
           <cell r="L137">
             <v>30810076211122</v>
           </cell>
+          <cell r="M137"/>
+          <cell r="N137"/>
           <cell r="O137">
             <v>19.989999999999998</v>
           </cell>
@@ -4956,6 +5045,8 @@
           <cell r="L138">
             <v>30810076211139</v>
           </cell>
+          <cell r="M138"/>
+          <cell r="N138"/>
           <cell r="O138">
             <v>19.989999999999998</v>
           </cell>
@@ -4985,6 +5076,8 @@
           <cell r="L139">
             <v>30810076212563</v>
           </cell>
+          <cell r="M139"/>
+          <cell r="N139"/>
           <cell r="O139">
             <v>19.989999999999998</v>
           </cell>
@@ -5014,6 +5107,8 @@
           <cell r="L140">
             <v>30810076212570</v>
           </cell>
+          <cell r="M140"/>
+          <cell r="N140"/>
           <cell r="O140">
             <v>19.989999999999998</v>
           </cell>
@@ -5043,6 +5138,8 @@
           <cell r="L141">
             <v>30810076212587</v>
           </cell>
+          <cell r="M141"/>
+          <cell r="N141"/>
           <cell r="O141">
             <v>19.989999999999998</v>
           </cell>
@@ -5072,6 +5169,8 @@
           <cell r="L142">
             <v>30810076212716</v>
           </cell>
+          <cell r="M142"/>
+          <cell r="N142"/>
         </row>
         <row r="143">
           <cell r="F143" t="str">
@@ -5095,6 +5194,8 @@
           <cell r="L143">
             <v>30810076212723</v>
           </cell>
+          <cell r="M143"/>
+          <cell r="N143"/>
         </row>
         <row r="144">
           <cell r="F144" t="str">
@@ -5118,6 +5219,8 @@
           <cell r="L144">
             <v>30810076212730</v>
           </cell>
+          <cell r="M144"/>
+          <cell r="N144"/>
         </row>
         <row r="145">
           <cell r="F145" t="str">
@@ -5141,6 +5244,7 @@
           <cell r="L145">
             <v>30810076211245</v>
           </cell>
+          <cell r="M145"/>
           <cell r="N145">
             <v>24</v>
           </cell>
@@ -5173,6 +5277,7 @@
           <cell r="L146">
             <v>30810076211252</v>
           </cell>
+          <cell r="M146"/>
           <cell r="N146">
             <v>24</v>
           </cell>
@@ -5205,6 +5310,8 @@
           <cell r="L147">
             <v>30810076210798</v>
           </cell>
+          <cell r="M147"/>
+          <cell r="N147"/>
           <cell r="O147">
             <v>49.99</v>
           </cell>
@@ -5248,6 +5355,7 @@
           </cell>
         </row>
         <row r="149">
+          <cell r="F149"/>
           <cell r="G149" t="str">
             <v>Lifelines Bath &amp; Shower Spa Bundle</v>
           </cell>
@@ -5336,6 +5444,8 @@
           <cell r="L151" t="str">
             <v/>
           </cell>
+          <cell r="M151"/>
+          <cell r="N151"/>
           <cell r="O151">
             <v>42.98</v>
           </cell>
@@ -5365,6 +5475,8 @@
           <cell r="L152">
             <v>30810076210217</v>
           </cell>
+          <cell r="M152"/>
+          <cell r="N152"/>
           <cell r="O152">
             <v>29.99</v>
           </cell>
@@ -6234,6 +6346,8 @@
           <cell r="L177">
             <v>30810076210910</v>
           </cell>
+          <cell r="M177"/>
+          <cell r="N177"/>
           <cell r="O177">
             <v>29.99</v>
           </cell>
@@ -7243,6 +7357,8 @@
           <cell r="L206" t="str">
             <v/>
           </cell>
+          <cell r="M206"/>
+          <cell r="N206"/>
           <cell r="O206">
             <v>19.989999999999998</v>
           </cell>
@@ -7272,6 +7388,8 @@
           <cell r="L207" t="str">
             <v/>
           </cell>
+          <cell r="M207"/>
+          <cell r="N207"/>
           <cell r="O207">
             <v>19.989999999999998</v>
           </cell>
@@ -7336,6 +7454,8 @@
           <cell r="L209">
             <v>30810076212433</v>
           </cell>
+          <cell r="M209"/>
+          <cell r="N209"/>
           <cell r="O209">
             <v>19.989999999999998</v>
           </cell>
@@ -7814,6 +7934,8 @@
           <cell r="L223">
             <v>30810076212990</v>
           </cell>
+          <cell r="M223"/>
+          <cell r="N223"/>
           <cell r="O223">
             <v>12.99</v>
           </cell>
@@ -7948,6 +8070,8 @@
           <cell r="L227">
             <v>30810076212440</v>
           </cell>
+          <cell r="M227"/>
+          <cell r="N227"/>
           <cell r="O227">
             <v>12.99</v>
           </cell>
@@ -7977,6 +8101,8 @@
           <cell r="L228">
             <v>30810076212457</v>
           </cell>
+          <cell r="M228"/>
+          <cell r="N228"/>
           <cell r="O228">
             <v>12.99</v>
           </cell>
@@ -8006,6 +8132,8 @@
           <cell r="L229">
             <v>30810076212464</v>
           </cell>
+          <cell r="M229"/>
+          <cell r="N229"/>
           <cell r="O229">
             <v>12.99</v>
           </cell>
@@ -8035,6 +8163,8 @@
           <cell r="L230">
             <v>30810076212471</v>
           </cell>
+          <cell r="M230"/>
+          <cell r="N230"/>
           <cell r="O230">
             <v>12.99</v>
           </cell>
@@ -8475,6 +8605,7 @@
           <cell r="I243" t="str">
             <v/>
           </cell>
+          <cell r="J243"/>
           <cell r="K243" t="str">
             <v/>
           </cell>
@@ -8761,6 +8892,7 @@
           <cell r="L251">
             <v>30810076212297</v>
           </cell>
+          <cell r="M251"/>
           <cell r="N251">
             <v>60</v>
           </cell>
@@ -8793,6 +8925,7 @@
           <cell r="L252">
             <v>30810076212303</v>
           </cell>
+          <cell r="M252"/>
           <cell r="N252">
             <v>60</v>
           </cell>
@@ -8895,6 +9028,7 @@
           <cell r="L255">
             <v>30810076212334</v>
           </cell>
+          <cell r="M255"/>
           <cell r="N255">
             <v>60</v>
           </cell>
@@ -8962,6 +9096,7 @@
           <cell r="L257">
             <v>30810076212358</v>
           </cell>
+          <cell r="M257"/>
           <cell r="N257">
             <v>60</v>
           </cell>
@@ -9029,6 +9164,7 @@
           <cell r="L259">
             <v>30810076215397</v>
           </cell>
+          <cell r="M259"/>
           <cell r="N259">
             <v>60</v>
           </cell>
@@ -9061,6 +9197,7 @@
           <cell r="L260">
             <v>30810076215403</v>
           </cell>
+          <cell r="M260"/>
           <cell r="N260">
             <v>60</v>
           </cell>
@@ -9093,6 +9230,7 @@
           <cell r="L261">
             <v>30810076215410</v>
           </cell>
+          <cell r="M261"/>
           <cell r="N261">
             <v>60</v>
           </cell>
@@ -9125,6 +9263,7 @@
           <cell r="L262">
             <v>30810076215427</v>
           </cell>
+          <cell r="M262"/>
           <cell r="N262">
             <v>60</v>
           </cell>
@@ -9157,6 +9296,7 @@
           <cell r="L263">
             <v>30810076215434</v>
           </cell>
+          <cell r="M263"/>
           <cell r="N263">
             <v>60</v>
           </cell>
@@ -9189,6 +9329,7 @@
           <cell r="L264">
             <v>30810076214772</v>
           </cell>
+          <cell r="M264"/>
           <cell r="N264">
             <v>60</v>
           </cell>
@@ -9212,6 +9353,7 @@
           <cell r="I265" t="str">
             <v/>
           </cell>
+          <cell r="M265"/>
           <cell r="N265">
             <v>60</v>
           </cell>
@@ -9235,6 +9377,7 @@
           <cell r="I266" t="str">
             <v/>
           </cell>
+          <cell r="M266"/>
           <cell r="N266">
             <v>60</v>
           </cell>
@@ -9258,6 +9401,7 @@
           <cell r="I267" t="str">
             <v/>
           </cell>
+          <cell r="M267"/>
           <cell r="N267">
             <v>60</v>
           </cell>
@@ -9281,6 +9425,7 @@
           <cell r="I268" t="str">
             <v/>
           </cell>
+          <cell r="M268"/>
           <cell r="N268">
             <v>60</v>
           </cell>
@@ -9313,6 +9458,8 @@
           <cell r="L269">
             <v>30810076213683</v>
           </cell>
+          <cell r="M269"/>
+          <cell r="N269"/>
           <cell r="O269">
             <v>22.99</v>
           </cell>
@@ -9342,6 +9489,8 @@
           <cell r="L270">
             <v>30810076213690</v>
           </cell>
+          <cell r="M270"/>
+          <cell r="N270"/>
           <cell r="O270">
             <v>22.99</v>
           </cell>
@@ -9371,6 +9520,8 @@
           <cell r="L271">
             <v>30810076213607</v>
           </cell>
+          <cell r="M271"/>
+          <cell r="N271"/>
           <cell r="O271">
             <v>22.99</v>
           </cell>
@@ -9400,6 +9551,8 @@
           <cell r="L272">
             <v>30810076213614</v>
           </cell>
+          <cell r="M272"/>
+          <cell r="N272"/>
           <cell r="O272">
             <v>22.99</v>
           </cell>
@@ -9429,6 +9582,8 @@
           <cell r="L273">
             <v>30810076214086</v>
           </cell>
+          <cell r="M273"/>
+          <cell r="N273"/>
           <cell r="O273">
             <v>22.99</v>
           </cell>
@@ -9458,6 +9613,8 @@
           <cell r="L274">
             <v>30810076214093</v>
           </cell>
+          <cell r="M274"/>
+          <cell r="N274"/>
           <cell r="O274">
             <v>22.99</v>
           </cell>
@@ -9487,6 +9644,8 @@
           <cell r="L275">
             <v>30810076214109</v>
           </cell>
+          <cell r="M275"/>
+          <cell r="N275"/>
           <cell r="O275">
             <v>22.99</v>
           </cell>
@@ -9516,6 +9675,8 @@
           <cell r="L276">
             <v>30810076214116</v>
           </cell>
+          <cell r="M276"/>
+          <cell r="N276"/>
           <cell r="O276">
             <v>22.99</v>
           </cell>
@@ -9545,6 +9706,8 @@
           <cell r="L277">
             <v>30810076214147</v>
           </cell>
+          <cell r="M277"/>
+          <cell r="N277"/>
           <cell r="O277">
             <v>22.99</v>
           </cell>
@@ -9574,6 +9737,8 @@
           <cell r="L278">
             <v>30810076214154</v>
           </cell>
+          <cell r="M278"/>
+          <cell r="N278"/>
           <cell r="O278">
             <v>22.99</v>
           </cell>
@@ -9603,6 +9768,8 @@
           <cell r="L279">
             <v>30810076214932</v>
           </cell>
+          <cell r="M279"/>
+          <cell r="N279"/>
           <cell r="O279">
             <v>22.99</v>
           </cell>
@@ -9842,6 +10009,8 @@
           <cell r="L286">
             <v>30810076212136</v>
           </cell>
+          <cell r="M286"/>
+          <cell r="N286"/>
           <cell r="O286">
             <v>179.98</v>
           </cell>
@@ -10387,6 +10556,9 @@
           <cell r="I302" t="str">
             <v/>
           </cell>
+          <cell r="J302"/>
+          <cell r="K302"/>
+          <cell r="L302"/>
           <cell r="M302">
             <v>4</v>
           </cell>
@@ -10413,6 +10585,9 @@
           <cell r="I303" t="str">
             <v/>
           </cell>
+          <cell r="J303"/>
+          <cell r="K303"/>
+          <cell r="L303"/>
           <cell r="M303">
             <v>4</v>
           </cell>
@@ -13694,6 +13869,8 @@
           <cell r="L397">
             <v>30810076214994</v>
           </cell>
+          <cell r="M397"/>
+          <cell r="N397"/>
           <cell r="O397">
             <v>37.99</v>
           </cell>
@@ -14108,6 +14285,8 @@
           <cell r="L409">
             <v>30810076215007</v>
           </cell>
+          <cell r="M409"/>
+          <cell r="N409"/>
           <cell r="O409">
             <v>37.99</v>
           </cell>
@@ -15047,6 +15226,8 @@
           <cell r="L436">
             <v>30810076216424</v>
           </cell>
+          <cell r="M436"/>
+          <cell r="N436"/>
           <cell r="O436">
             <v>22.99</v>
           </cell>
@@ -15076,6 +15257,8 @@
           <cell r="L437">
             <v>30810076216431</v>
           </cell>
+          <cell r="M437"/>
+          <cell r="N437"/>
           <cell r="O437">
             <v>22.99</v>
           </cell>
@@ -15105,6 +15288,8 @@
           <cell r="L438">
             <v>30810076216448</v>
           </cell>
+          <cell r="M438"/>
+          <cell r="N438"/>
           <cell r="O438">
             <v>22.99</v>
           </cell>
@@ -16289,6 +16474,7 @@
           <cell r="L472">
             <v>30810076213355</v>
           </cell>
+          <cell r="M472"/>
           <cell r="N472">
             <v>20</v>
           </cell>
@@ -16321,6 +16507,7 @@
           <cell r="L473">
             <v>30810076213362</v>
           </cell>
+          <cell r="M473"/>
           <cell r="N473">
             <v>20</v>
           </cell>
@@ -16353,6 +16540,7 @@
           <cell r="L474">
             <v>30810076213379</v>
           </cell>
+          <cell r="M474"/>
           <cell r="N474">
             <v>20</v>
           </cell>
@@ -16385,6 +16573,7 @@
           <cell r="L475">
             <v>30810076213386</v>
           </cell>
+          <cell r="M475"/>
           <cell r="N475">
             <v>20</v>
           </cell>
@@ -16417,6 +16606,7 @@
           <cell r="L476">
             <v>30810076211832</v>
           </cell>
+          <cell r="M476"/>
           <cell r="N476">
             <v>20</v>
           </cell>
@@ -16449,6 +16639,7 @@
           <cell r="L477">
             <v>30810076211849</v>
           </cell>
+          <cell r="M477"/>
           <cell r="N477">
             <v>20</v>
           </cell>
@@ -16481,6 +16672,7 @@
           <cell r="L478">
             <v>30810076211856</v>
           </cell>
+          <cell r="M478"/>
           <cell r="N478">
             <v>20</v>
           </cell>
@@ -16513,6 +16705,7 @@
           <cell r="L479">
             <v>30810076211863</v>
           </cell>
+          <cell r="M479"/>
           <cell r="N479">
             <v>20</v>
           </cell>
@@ -16545,6 +16738,7 @@
           <cell r="L480">
             <v>30810076212235</v>
           </cell>
+          <cell r="M480"/>
           <cell r="N480">
             <v>20</v>
           </cell>
@@ -16577,6 +16771,7 @@
           <cell r="L481">
             <v>30810076213126</v>
           </cell>
+          <cell r="M481"/>
           <cell r="N481">
             <v>20</v>
           </cell>
@@ -16609,6 +16804,7 @@
           <cell r="L482">
             <v>30810076213133</v>
           </cell>
+          <cell r="M482"/>
           <cell r="N482">
             <v>20</v>
           </cell>
@@ -16641,6 +16837,7 @@
           <cell r="L483">
             <v>30810076213140</v>
           </cell>
+          <cell r="M483"/>
           <cell r="N483">
             <v>20</v>
           </cell>
@@ -16673,6 +16870,7 @@
           <cell r="L484">
             <v>30810076215878</v>
           </cell>
+          <cell r="M484"/>
           <cell r="N484">
             <v>20</v>
           </cell>
@@ -16705,6 +16903,7 @@
           <cell r="L485">
             <v>30810076211870</v>
           </cell>
+          <cell r="M485"/>
           <cell r="N485">
             <v>20</v>
           </cell>
@@ -16737,6 +16936,7 @@
           <cell r="L486">
             <v>30810076211887</v>
           </cell>
+          <cell r="M486"/>
           <cell r="N486">
             <v>20</v>
           </cell>
@@ -16769,6 +16969,7 @@
           <cell r="L487">
             <v>30810076211894</v>
           </cell>
+          <cell r="M487"/>
           <cell r="N487">
             <v>20</v>
           </cell>
@@ -16801,6 +17002,7 @@
           <cell r="L488">
             <v>30810076213898</v>
           </cell>
+          <cell r="M488"/>
           <cell r="N488">
             <v>12</v>
           </cell>
@@ -16833,6 +17035,7 @@
           <cell r="L489">
             <v>30810076213904</v>
           </cell>
+          <cell r="M489"/>
           <cell r="N489">
             <v>20</v>
           </cell>
@@ -16865,6 +17068,7 @@
           <cell r="L490">
             <v>30810076213911</v>
           </cell>
+          <cell r="M490"/>
           <cell r="N490">
             <v>18</v>
           </cell>
@@ -16897,6 +17101,7 @@
           <cell r="L491">
             <v>30810076214949</v>
           </cell>
+          <cell r="M491"/>
           <cell r="N491">
             <v>20</v>
           </cell>
@@ -16929,6 +17134,7 @@
           <cell r="L492">
             <v>30810076215090</v>
           </cell>
+          <cell r="M492"/>
           <cell r="N492">
             <v>20</v>
           </cell>
@@ -16961,6 +17167,7 @@
           <cell r="L493">
             <v>30810076214956</v>
           </cell>
+          <cell r="M493"/>
           <cell r="N493">
             <v>20</v>
           </cell>
@@ -16993,6 +17200,7 @@
           <cell r="L494">
             <v>30810076214963</v>
           </cell>
+          <cell r="M494"/>
           <cell r="N494">
             <v>20</v>
           </cell>
@@ -17016,6 +17224,10 @@
           <cell r="I495" t="str">
             <v/>
           </cell>
+          <cell r="J495"/>
+          <cell r="K495"/>
+          <cell r="L495"/>
+          <cell r="M495"/>
           <cell r="N495">
             <v>20</v>
           </cell>
@@ -17048,6 +17260,7 @@
           <cell r="L496">
             <v>30810076215021</v>
           </cell>
+          <cell r="M496"/>
           <cell r="N496">
             <v>14</v>
           </cell>
@@ -17080,6 +17293,7 @@
           <cell r="L497">
             <v>30810076215038</v>
           </cell>
+          <cell r="M497"/>
           <cell r="N497">
             <v>14</v>
           </cell>
@@ -17112,6 +17326,7 @@
           <cell r="L498">
             <v>30810076215045</v>
           </cell>
+          <cell r="M498"/>
           <cell r="N498">
             <v>14</v>
           </cell>
@@ -17144,6 +17359,7 @@
           <cell r="L499">
             <v>30810076215052</v>
           </cell>
+          <cell r="M499"/>
           <cell r="N499">
             <v>14</v>
           </cell>
@@ -17176,6 +17392,7 @@
           <cell r="L500">
             <v>30810076215069</v>
           </cell>
+          <cell r="M500"/>
           <cell r="N500">
             <v>14</v>
           </cell>
@@ -17208,6 +17425,7 @@
           <cell r="L501">
             <v>30810076215076</v>
           </cell>
+          <cell r="M501"/>
           <cell r="N501">
             <v>14</v>
           </cell>
@@ -17240,6 +17458,7 @@
           <cell r="L502">
             <v>30810076215083</v>
           </cell>
+          <cell r="M502"/>
           <cell r="N502">
             <v>14</v>
           </cell>
@@ -17272,6 +17491,7 @@
           <cell r="L503">
             <v>30810076214352</v>
           </cell>
+          <cell r="M503"/>
           <cell r="N503">
             <v>14</v>
           </cell>
@@ -17304,6 +17524,7 @@
           <cell r="L504">
             <v>30810076214369</v>
           </cell>
+          <cell r="M504"/>
           <cell r="N504">
             <v>14</v>
           </cell>
@@ -17336,6 +17557,7 @@
           <cell r="L505">
             <v>30810076214345</v>
           </cell>
+          <cell r="M505"/>
           <cell r="N505">
             <v>14</v>
           </cell>
@@ -17368,6 +17590,7 @@
           <cell r="L506">
             <v>30810076214970</v>
           </cell>
+          <cell r="M506"/>
           <cell r="N506">
             <v>14</v>
           </cell>
@@ -17400,6 +17623,7 @@
           <cell r="L507">
             <v>30810076216837</v>
           </cell>
+          <cell r="M507"/>
           <cell r="N507">
             <v>14</v>
           </cell>
@@ -17432,6 +17656,7 @@
           <cell r="L508">
             <v>30810076217148</v>
           </cell>
+          <cell r="M508"/>
           <cell r="N508">
             <v>14</v>
           </cell>
@@ -17464,6 +17689,7 @@
           <cell r="L509">
             <v>30810076217155</v>
           </cell>
+          <cell r="M509"/>
           <cell r="N509">
             <v>14</v>
           </cell>
@@ -17496,6 +17722,7 @@
           <cell r="L510">
             <v>30810076217162</v>
           </cell>
+          <cell r="M510"/>
           <cell r="N510">
             <v>14</v>
           </cell>
@@ -17528,6 +17755,7 @@
           <cell r="L511">
             <v>30810076217179</v>
           </cell>
+          <cell r="M511"/>
           <cell r="N511">
             <v>14</v>
           </cell>
@@ -17560,6 +17788,7 @@
           <cell r="L512">
             <v>30810076217186</v>
           </cell>
+          <cell r="M512"/>
           <cell r="N512">
             <v>14</v>
           </cell>
@@ -17592,6 +17821,7 @@
           <cell r="L513">
             <v>30810076217193</v>
           </cell>
+          <cell r="M513"/>
           <cell r="N513">
             <v>14</v>
           </cell>
@@ -17624,6 +17854,7 @@
           <cell r="L514">
             <v>30810076217209</v>
           </cell>
+          <cell r="M514"/>
           <cell r="N514">
             <v>14</v>
           </cell>
@@ -17656,6 +17887,7 @@
           <cell r="L515">
             <v>30810076217216</v>
           </cell>
+          <cell r="M515"/>
           <cell r="N515">
             <v>14</v>
           </cell>
@@ -17688,6 +17920,7 @@
           <cell r="L516">
             <v>30810076217223</v>
           </cell>
+          <cell r="M516"/>
           <cell r="N516">
             <v>14</v>
           </cell>
@@ -17720,6 +17953,7 @@
           <cell r="L517">
             <v>30810076217230</v>
           </cell>
+          <cell r="M517"/>
           <cell r="N517">
             <v>14</v>
           </cell>
@@ -17752,6 +17986,7 @@
           <cell r="L518">
             <v>30810076217247</v>
           </cell>
+          <cell r="M518"/>
           <cell r="N518">
             <v>14</v>
           </cell>
@@ -17784,6 +18019,7 @@
           <cell r="L519">
             <v>30810076217254</v>
           </cell>
+          <cell r="M519"/>
           <cell r="N519">
             <v>14</v>
           </cell>
@@ -17816,6 +18052,7 @@
           <cell r="L520">
             <v>30810076214710</v>
           </cell>
+          <cell r="M520"/>
           <cell r="N520">
             <v>14</v>
           </cell>
@@ -17848,6 +18085,7 @@
           <cell r="L521">
             <v>30810076216011</v>
           </cell>
+          <cell r="M521"/>
           <cell r="N521">
             <v>14</v>
           </cell>
@@ -17880,6 +18118,7 @@
           <cell r="L522">
             <v>30810076216028</v>
           </cell>
+          <cell r="M522"/>
           <cell r="N522">
             <v>14</v>
           </cell>
@@ -17912,6 +18151,7 @@
           <cell r="L523">
             <v>30810076216035</v>
           </cell>
+          <cell r="M523"/>
           <cell r="N523">
             <v>14</v>
           </cell>
@@ -17944,6 +18184,7 @@
           <cell r="L524">
             <v>30810076216042</v>
           </cell>
+          <cell r="M524"/>
           <cell r="N524">
             <v>14</v>
           </cell>
@@ -17976,6 +18217,7 @@
           <cell r="L525">
             <v>30810076216059</v>
           </cell>
+          <cell r="M525"/>
           <cell r="N525">
             <v>14</v>
           </cell>
@@ -18008,6 +18250,7 @@
           <cell r="L526">
             <v>30810076216066</v>
           </cell>
+          <cell r="M526"/>
           <cell r="N526">
             <v>14</v>
           </cell>
@@ -18040,6 +18283,7 @@
           <cell r="L527">
             <v>30810076216806</v>
           </cell>
+          <cell r="M527"/>
           <cell r="N527">
             <v>14</v>
           </cell>
@@ -18072,6 +18316,7 @@
           <cell r="L528">
             <v>30810076216813</v>
           </cell>
+          <cell r="M528"/>
           <cell r="N528">
             <v>14</v>
           </cell>
@@ -18104,6 +18349,7 @@
           <cell r="L529">
             <v>30810076216820</v>
           </cell>
+          <cell r="M529"/>
           <cell r="N529">
             <v>14</v>
           </cell>
@@ -18136,6 +18382,7 @@
           <cell r="L530">
             <v>30810076211900</v>
           </cell>
+          <cell r="M530"/>
           <cell r="N530">
             <v>12</v>
           </cell>
@@ -18168,6 +18415,7 @@
           <cell r="L531">
             <v>30810076211917</v>
           </cell>
+          <cell r="M531"/>
           <cell r="N531">
             <v>12</v>
           </cell>
@@ -18200,6 +18448,7 @@
           <cell r="L532">
             <v>30810076212242</v>
           </cell>
+          <cell r="M532"/>
           <cell r="N532">
             <v>12</v>
           </cell>
@@ -18827,6 +19076,8 @@
           <cell r="L550" t="str">
             <v/>
           </cell>
+          <cell r="M550"/>
+          <cell r="N550"/>
           <cell r="O550">
             <v>24.99</v>
           </cell>
@@ -18856,6 +19107,8 @@
           <cell r="L551" t="str">
             <v/>
           </cell>
+          <cell r="M551"/>
+          <cell r="N551"/>
           <cell r="O551">
             <v>24.99</v>
           </cell>
@@ -19057,6 +19310,8 @@
           <cell r="L557">
             <v>30810076211993</v>
           </cell>
+          <cell r="M557"/>
+          <cell r="N557"/>
         </row>
         <row r="558">
           <cell r="F558" t="str">
@@ -19080,6 +19335,8 @@
           <cell r="L558">
             <v>30810076212006</v>
           </cell>
+          <cell r="M558"/>
+          <cell r="N558"/>
           <cell r="O558">
             <v>0</v>
           </cell>
@@ -19109,6 +19366,8 @@
           <cell r="L559">
             <v>30810076212211</v>
           </cell>
+          <cell r="M559"/>
+          <cell r="N559"/>
           <cell r="O559">
             <v>0</v>
           </cell>
@@ -19138,6 +19397,8 @@
           <cell r="L560">
             <v>30810076212228</v>
           </cell>
+          <cell r="M560"/>
+          <cell r="N560"/>
           <cell r="O560">
             <v>0</v>
           </cell>
@@ -19721,6 +19982,8 @@
           <cell r="L577">
             <v>30810076212518</v>
           </cell>
+          <cell r="M577"/>
+          <cell r="N577"/>
           <cell r="O577">
             <v>79.989999999999995</v>
           </cell>
@@ -19750,6 +20013,8 @@
           <cell r="L578">
             <v>30810076212525</v>
           </cell>
+          <cell r="M578"/>
+          <cell r="N578"/>
           <cell r="O578">
             <v>79.989999999999995</v>
           </cell>
@@ -19779,6 +20044,8 @@
           <cell r="L579">
             <v>30810076212532</v>
           </cell>
+          <cell r="M579"/>
+          <cell r="N579"/>
           <cell r="O579">
             <v>79.989999999999995</v>
           </cell>
@@ -19808,6 +20075,8 @@
           <cell r="L580">
             <v>30810076212549</v>
           </cell>
+          <cell r="M580"/>
+          <cell r="N580"/>
           <cell r="O580">
             <v>199.99</v>
           </cell>
@@ -19837,6 +20106,8 @@
           <cell r="L581" t="str">
             <v/>
           </cell>
+          <cell r="M581"/>
+          <cell r="N581"/>
           <cell r="O581">
             <v>429.99</v>
           </cell>
@@ -19866,9 +20137,12 @@
           <cell r="L582">
             <v>30810076216844</v>
           </cell>
+          <cell r="M582"/>
+          <cell r="N582"/>
           <cell r="O582">
             <v>29.99</v>
           </cell>
+          <cell r="P582"/>
         </row>
         <row r="583">
           <cell r="F583" t="str">
@@ -19892,9 +20166,12 @@
           <cell r="L583">
             <v>30810076216851</v>
           </cell>
+          <cell r="M583"/>
+          <cell r="N583"/>
           <cell r="O583">
             <v>29.99</v>
           </cell>
+          <cell r="P583"/>
         </row>
         <row r="584">
           <cell r="F584" t="str">
@@ -19918,9 +20195,12 @@
           <cell r="L584">
             <v>30810076216868</v>
           </cell>
+          <cell r="M584"/>
+          <cell r="N584"/>
           <cell r="O584">
             <v>29.99</v>
           </cell>
+          <cell r="P584"/>
         </row>
         <row r="585">
           <cell r="F585" t="str">
@@ -19944,9 +20224,12 @@
           <cell r="L585">
             <v>30810076216875</v>
           </cell>
+          <cell r="M585"/>
+          <cell r="N585"/>
           <cell r="O585">
             <v>29.99</v>
           </cell>
+          <cell r="P585"/>
         </row>
         <row r="586">
           <cell r="F586" t="str">
@@ -19970,9 +20253,12 @@
           <cell r="L586">
             <v>30810076216882</v>
           </cell>
+          <cell r="M586"/>
+          <cell r="N586"/>
           <cell r="O586">
             <v>39.99</v>
           </cell>
+          <cell r="P586"/>
         </row>
         <row r="587">
           <cell r="F587" t="str">
@@ -19996,9 +20282,12 @@
           <cell r="L587">
             <v>30810076216899</v>
           </cell>
+          <cell r="M587"/>
+          <cell r="N587"/>
           <cell r="O587">
             <v>39.99</v>
           </cell>
+          <cell r="P587"/>
         </row>
         <row r="588">
           <cell r="F588" t="str">
@@ -20022,9 +20311,12 @@
           <cell r="L588">
             <v>30810076216905</v>
           </cell>
+          <cell r="M588"/>
+          <cell r="N588"/>
           <cell r="O588">
             <v>39.99</v>
           </cell>
+          <cell r="P588"/>
         </row>
         <row r="589">
           <cell r="F589" t="str">
@@ -20048,9 +20340,12 @@
           <cell r="L589">
             <v>30810076216912</v>
           </cell>
+          <cell r="M589"/>
+          <cell r="N589"/>
           <cell r="O589">
             <v>39.99</v>
           </cell>
+          <cell r="P589"/>
         </row>
         <row r="590">
           <cell r="F590" t="str">
@@ -20074,9 +20369,12 @@
           <cell r="L590">
             <v>30810076216929</v>
           </cell>
+          <cell r="M590"/>
+          <cell r="N590"/>
           <cell r="O590">
             <v>49.99</v>
           </cell>
+          <cell r="P590"/>
         </row>
         <row r="591">
           <cell r="F591" t="str">
@@ -20100,9 +20398,12 @@
           <cell r="L591">
             <v>30810076216936</v>
           </cell>
+          <cell r="M591"/>
+          <cell r="N591"/>
           <cell r="O591">
             <v>49.99</v>
           </cell>
+          <cell r="P591"/>
         </row>
         <row r="592">
           <cell r="F592" t="str">
@@ -20126,6 +20427,8 @@
           <cell r="L592">
             <v>30810076216943</v>
           </cell>
+          <cell r="M592"/>
+          <cell r="N592"/>
           <cell r="O592">
             <v>79.989999999999995</v>
           </cell>
@@ -20152,6 +20455,8 @@
           <cell r="L593">
             <v>30810076216950</v>
           </cell>
+          <cell r="M593"/>
+          <cell r="N593"/>
           <cell r="O593">
             <v>99.99</v>
           </cell>
@@ -20178,9 +20483,12 @@
           <cell r="L594">
             <v>30810076216967</v>
           </cell>
+          <cell r="M594"/>
+          <cell r="N594"/>
           <cell r="O594">
             <v>79.989999999999995</v>
           </cell>
+          <cell r="P594"/>
         </row>
         <row r="595">
           <cell r="F595" t="str">
@@ -20204,9 +20512,12 @@
           <cell r="L595">
             <v>30810076216974</v>
           </cell>
+          <cell r="M595"/>
+          <cell r="N595"/>
           <cell r="O595">
             <v>99.99</v>
           </cell>
+          <cell r="P595"/>
         </row>
         <row r="596">
           <cell r="F596" t="str">
@@ -21505,12 +21816,17 @@
           <cell r="I635" t="str">
             <v/>
           </cell>
+          <cell r="J635"/>
+          <cell r="K635"/>
+          <cell r="L635"/>
           <cell r="M635">
             <v>0</v>
           </cell>
           <cell r="N635">
             <v>1</v>
           </cell>
+          <cell r="O635"/>
+          <cell r="P635"/>
         </row>
         <row r="636">
           <cell r="F636" t="str">
@@ -21586,12 +21902,17 @@
           <cell r="I638" t="str">
             <v/>
           </cell>
+          <cell r="J638"/>
+          <cell r="K638"/>
+          <cell r="L638"/>
           <cell r="M638">
             <v>0</v>
           </cell>
           <cell r="N638">
             <v>1</v>
           </cell>
+          <cell r="O638"/>
+          <cell r="P638"/>
         </row>
         <row r="639">
           <cell r="F639" t="str">
@@ -21638,12 +21959,17 @@
           <cell r="I640" t="str">
             <v/>
           </cell>
+          <cell r="J640"/>
+          <cell r="K640"/>
+          <cell r="L640"/>
           <cell r="M640">
             <v>0</v>
           </cell>
           <cell r="N640">
             <v>1</v>
           </cell>
+          <cell r="O640"/>
+          <cell r="P640"/>
         </row>
         <row r="641">
           <cell r="F641" t="str">
@@ -21673,6 +21999,7 @@
           <cell r="N641">
             <v>1</v>
           </cell>
+          <cell r="O641"/>
           <cell r="P641">
             <v>45</v>
           </cell>
@@ -21833,6 +22160,7 @@
           <cell r="N646">
             <v>1</v>
           </cell>
+          <cell r="O646"/>
           <cell r="P646">
             <v>60</v>
           </cell>
@@ -21899,12 +22227,16 @@
           <cell r="I649" t="str">
             <v/>
           </cell>
+          <cell r="J649"/>
+          <cell r="K649"/>
+          <cell r="L649"/>
           <cell r="M649">
             <v>0</v>
           </cell>
           <cell r="N649">
             <v>1</v>
           </cell>
+          <cell r="O649"/>
           <cell r="P649">
             <v>0</v>
           </cell>
@@ -22238,6 +22570,8 @@
           <cell r="L661">
             <v>30810076212143</v>
           </cell>
+          <cell r="M661"/>
+          <cell r="N661"/>
           <cell r="O661">
             <v>0</v>
           </cell>
@@ -22331,6 +22665,7 @@
           <cell r="N664">
             <v>1</v>
           </cell>
+          <cell r="O664"/>
           <cell r="P664">
             <v>252</v>
           </cell>
@@ -22696,6 +23031,9 @@
           <cell r="I677" t="str">
             <v/>
           </cell>
+          <cell r="J677"/>
+          <cell r="K677"/>
+          <cell r="L677"/>
           <cell r="M677">
             <v>0</v>
           </cell>
@@ -22714,7 +23052,7 @@
             <v>LL-00-0040</v>
           </cell>
           <cell r="G678" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 72 - #1</v>
+            <v>FlowArt MINI EXPRESS - WMT - 70 - #1</v>
           </cell>
           <cell r="H678" t="str">
             <v>Y</v>
@@ -22722,6 +23060,9 @@
           <cell r="I678" t="str">
             <v/>
           </cell>
+          <cell r="J678"/>
+          <cell r="K678"/>
+          <cell r="L678"/>
           <cell r="M678">
             <v>0</v>
           </cell>
@@ -22748,6 +23089,9 @@
           <cell r="I679" t="str">
             <v/>
           </cell>
+          <cell r="J679"/>
+          <cell r="K679"/>
+          <cell r="L679"/>
           <cell r="M679">
             <v>0</v>
           </cell>
@@ -22766,7 +23110,7 @@
             <v>LL-00-0041</v>
           </cell>
           <cell r="G680" t="str">
-            <v>FlowArt MINI EXPRESS - WMT - 60 - #2</v>
+            <v>FlowArt MINI EXPRESS - WMT - 70 - #2</v>
           </cell>
           <cell r="H680" t="str">
             <v>N</v>
@@ -22774,6 +23118,9 @@
           <cell r="I680" t="str">
             <v/>
           </cell>
+          <cell r="J680"/>
+          <cell r="K680"/>
+          <cell r="L680"/>
           <cell r="M680">
             <v>0</v>
           </cell>
@@ -22800,6 +23147,9 @@
           <cell r="I681" t="str">
             <v/>
           </cell>
+          <cell r="J681"/>
+          <cell r="K681"/>
+          <cell r="L681"/>
           <cell r="M681">
             <v>0</v>
           </cell>
@@ -22861,6 +23211,9 @@
           <cell r="I683" t="str">
             <v/>
           </cell>
+          <cell r="J683"/>
+          <cell r="K683"/>
+          <cell r="L683"/>
           <cell r="M683">
             <v>0</v>
           </cell>
@@ -22922,6 +23275,9 @@
           <cell r="I685" t="str">
             <v/>
           </cell>
+          <cell r="J685"/>
+          <cell r="K685"/>
+          <cell r="L685"/>
           <cell r="M685">
             <v>0</v>
           </cell>
@@ -23218,6 +23574,8 @@
           <cell r="N695">
             <v>1</v>
           </cell>
+          <cell r="O695"/>
+          <cell r="P695"/>
         </row>
         <row r="696">
           <cell r="F696" t="str">
@@ -23305,6 +23663,8 @@
           <cell r="N698">
             <v>1</v>
           </cell>
+          <cell r="O698"/>
+          <cell r="P698"/>
         </row>
         <row r="699">
           <cell r="F699" t="str">
@@ -23515,6 +23875,7 @@
           <cell r="N707">
             <v>1</v>
           </cell>
+          <cell r="O707"/>
           <cell r="P707">
             <v>400</v>
           </cell>
@@ -23576,6 +23937,8 @@
           <cell r="N709">
             <v>1</v>
           </cell>
+          <cell r="O709"/>
+          <cell r="P709"/>
         </row>
         <row r="710">
           <cell r="F710" t="str">
@@ -23590,12 +23953,17 @@
           <cell r="I710" t="str">
             <v/>
           </cell>
+          <cell r="J710"/>
+          <cell r="K710"/>
+          <cell r="L710"/>
           <cell r="M710">
             <v>0</v>
           </cell>
           <cell r="N710">
             <v>100</v>
           </cell>
+          <cell r="O710"/>
+          <cell r="P710"/>
         </row>
         <row r="711">
           <cell r="F711" t="str">
@@ -23849,6 +24217,10 @@
           <cell r="L721" t="str">
             <v/>
           </cell>
+          <cell r="M721"/>
+          <cell r="N721"/>
+          <cell r="O721"/>
+          <cell r="P721"/>
         </row>
         <row r="722">
           <cell r="F722" t="str">
@@ -23976,6 +24348,8 @@
           <cell r="N726" t="str">
             <v/>
           </cell>
+          <cell r="O726"/>
+          <cell r="P726"/>
         </row>
         <row r="727">
           <cell r="F727" t="str">
@@ -23999,6 +24373,7 @@
           <cell r="L727">
             <v>30810076213928</v>
           </cell>
+          <cell r="M727"/>
           <cell r="N727">
             <v>20</v>
           </cell>
@@ -24031,6 +24406,8 @@
           <cell r="L728">
             <v>30810076214918</v>
           </cell>
+          <cell r="M728"/>
+          <cell r="N728"/>
         </row>
         <row r="729">
           <cell r="F729" t="str">
@@ -24670,6 +25047,10 @@
           <cell r="L749">
             <v>30810076213157</v>
           </cell>
+          <cell r="M749"/>
+          <cell r="N749"/>
+          <cell r="O749"/>
+          <cell r="P749"/>
         </row>
         <row r="750">
           <cell r="F750" t="str">
@@ -24693,6 +25074,8 @@
           <cell r="L750">
             <v>30810076212150</v>
           </cell>
+          <cell r="M750"/>
+          <cell r="N750"/>
           <cell r="O750">
             <v>26.99</v>
           </cell>
@@ -24722,6 +25105,8 @@
           <cell r="L751">
             <v>30810076212167</v>
           </cell>
+          <cell r="M751"/>
+          <cell r="N751"/>
           <cell r="O751">
             <v>14.99</v>
           </cell>
@@ -24751,6 +25136,8 @@
           <cell r="L752">
             <v>30810076212174</v>
           </cell>
+          <cell r="M752"/>
+          <cell r="N752"/>
           <cell r="O752">
             <v>14.99</v>
           </cell>
@@ -25098,6 +25485,8 @@
           <cell r="L765">
             <v>30810076212259</v>
           </cell>
+          <cell r="M765"/>
+          <cell r="N765"/>
           <cell r="O765">
             <v>39.99</v>
           </cell>
@@ -25127,6 +25516,8 @@
           <cell r="L766">
             <v>30810076212266</v>
           </cell>
+          <cell r="M766"/>
+          <cell r="N766"/>
           <cell r="O766">
             <v>39.99</v>
           </cell>
@@ -25191,6 +25582,8 @@
           <cell r="L768" t="str">
             <v/>
           </cell>
+          <cell r="M768"/>
+          <cell r="N768"/>
           <cell r="O768">
             <v>41.98</v>
           </cell>
@@ -25220,6 +25613,8 @@
           <cell r="L769" t="str">
             <v/>
           </cell>
+          <cell r="M769"/>
+          <cell r="N769"/>
           <cell r="O769">
             <v>41.98</v>
           </cell>
@@ -25249,6 +25644,8 @@
           <cell r="L770" t="str">
             <v/>
           </cell>
+          <cell r="M770"/>
+          <cell r="N770"/>
           <cell r="O770">
             <v>41.98</v>
           </cell>
@@ -25870,10 +26267,35 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="700" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{4EE3999C-3B52-43F2-8FD6-E6B658D34512}">
+  <we:reference id="wa200003784" version="1.2.0.2" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003784" version="1.2.0.2" store="WA200003784" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.9375" bestFit="1" customWidth="1"/>
@@ -25924,2744 +26346,3104 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" s="6" customFormat="1">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C5), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Café Comforts</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="6">
         <v>6</v>
       </c>
-      <c r="F5" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C5), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F5" s="8">
+        <f>IF(IF(RIGHT($A5,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C5), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C5), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A5,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C5), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C5, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C5), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+    <row r="6" spans="1:6" s="6" customFormat="1">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <f>IF(A5=A6, B5+1, 1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C6), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Enchanted Magic</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>6</v>
       </c>
-      <c r="F6" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C6), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F6" s="8">
+        <f>IF(IF(RIGHT($A6,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C6), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C6), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A6,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C6), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C6, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C6), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+    <row r="7" spans="1:6" s="6" customFormat="1">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <f t="shared" ref="B7:B70" si="0">IF(A6=A7, B6+1, 1)</f>
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C7), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Pretty Petals</v>
       </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C7), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="E7" s="6">
+        <v>12</v>
+      </c>
+      <c r="F7" s="8">
+        <f>IF(IF(RIGHT($A7,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C7), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C7), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A7,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C7), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C7, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C7), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+    <row r="8" spans="1:6" s="6" customFormat="1">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C8), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Furry Friends</v>
       </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C8), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="E8" s="6">
+        <v>12</v>
+      </c>
+      <c r="F8" s="8">
+        <f>IF(IF(RIGHT($A8,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C8), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C8), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A8,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C8), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C8, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C8), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" s="6" customFormat="1">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C9), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Nature's Wonders</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <v>6</v>
       </c>
-      <c r="F9" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C9), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F9" s="8">
+        <f>IF(IF(RIGHT($A9,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C9), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C9), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A9,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C9), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C9, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C9), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" s="6" customFormat="1">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C10), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Pocket Positivity</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="6">
         <v>6</v>
       </c>
-      <c r="F10" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C10), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F10" s="8">
+        <f>IF(IF(RIGHT($A10,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C10), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C10), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A10,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C10), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C10, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C10), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+    <row r="11" spans="1:6" s="6" customFormat="1">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C11), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Snowflake Serenity [Metallic]</v>
       </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C11), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="E11" s="6">
+        <v>9</v>
+      </c>
+      <c r="F11" s="8">
+        <f>IF(IF(RIGHT($A11,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C11), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C11), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A11,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C11), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C11, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C11), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+    <row r="12" spans="1:6" s="6" customFormat="1">
+      <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C12), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Frosted Village [Metallic]</v>
       </c>
-      <c r="E12">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C12), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="E12" s="6">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8">
+        <f>IF(IF(RIGHT($A12,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C12), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C12), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A12,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C12), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C12, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C12), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" s="6" customFormat="1">
+      <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C13), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Mini Single - Deck the Halls [Metallic]</v>
       </c>
-      <c r="E13">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C13), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="E13" s="6">
+        <v>18</v>
+      </c>
+      <c r="F13" s="8">
+        <f>IF(IF(RIGHT($A13,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C13), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C13), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A13,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C13), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C13, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C13), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+    <row r="14" spans="1:6" s="6" customFormat="1">
+      <c r="A14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="str">
+      <c r="C14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C14), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Display - Empty</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6</v>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <f>IF(IF(RIGHT($A14,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A14,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C14, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C14), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+    <row r="15" spans="1:6" s="6" customFormat="1">
+      <c r="A15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D15" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C15), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="6">
         <v>8</v>
       </c>
-      <c r="F15" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C15), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F15" s="8">
+        <f>IF(IF(RIGHT($A15,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C15), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C15), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A15,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C15), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C15, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C15), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+    <row r="16" spans="1:6" s="6" customFormat="1">
+      <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D16" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C16), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="6">
         <v>8</v>
       </c>
-      <c r="F16" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C16), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F16" s="8">
+        <f>IF(IF(RIGHT($A16,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C16), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C16), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A16,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C16), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C16, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C16), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+    <row r="17" spans="1:6" s="6" customFormat="1">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D17" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C17), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="6">
         <v>4</v>
       </c>
-      <c r="F17" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C17), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F17" s="8">
+        <f>IF(IF(RIGHT($A17,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C17), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C17), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A17,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C17), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C17, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C17), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+    <row r="18" spans="1:6" s="6" customFormat="1">
+      <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D18" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C18), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="6">
         <v>4</v>
       </c>
-      <c r="F18" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C18), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F18" s="8">
+        <f>IF(IF(RIGHT($A18,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C18), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C18), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A18,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C18), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C18, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C18), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+    <row r="19" spans="1:6" s="6" customFormat="1">
+      <c r="A19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D19" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C19), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="6">
         <v>4</v>
       </c>
-      <c r="F19" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C19), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F19" s="8">
+        <f>IF(IF(RIGHT($A19,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C19), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C19), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A19,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C19), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C19, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C19), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+    <row r="20" spans="1:6" s="6" customFormat="1">
+      <c r="A20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="str">
+      <c r="C20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C20), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
-      </c>
-      <c r="E20">
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+      </c>
+      <c r="E20" s="6">
         <v>4</v>
       </c>
-      <c r="F20" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F20" s="8">
+        <f>IF(IF(RIGHT($A20,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A20,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C20, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C20), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+    <row r="21" spans="1:6" s="6" customFormat="1">
+      <c r="A21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" t="str">
+      <c r="C21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C21), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
-      </c>
-      <c r="E21">
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E21" s="6">
         <v>4</v>
       </c>
-      <c r="F21" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C21), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F21" s="8">
+        <f>IF(IF(RIGHT($A21,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C21), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C21), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A21,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C21), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C21, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C21), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+    <row r="22" spans="1:6" s="6" customFormat="1">
+      <c r="A22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="str">
+      <c r="C22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C22), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C22), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+      </c>
+      <c r="E22" s="6">
+        <v>8</v>
+      </c>
+      <c r="F22" s="8">
+        <f>IF(IF(RIGHT($A22,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C22), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C22), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A22,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C22), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C22, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C22), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" s="6" customFormat="1">
+      <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="str">
+      <c r="C23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C23), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
-      </c>
-      <c r="E23">
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E23" s="6">
         <v>4</v>
       </c>
-      <c r="F23" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C23), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F23" s="8">
+        <f>IF(IF(RIGHT($A23,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C23), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C23), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A23,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C23), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C23, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C23), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24">
+    <row r="24" spans="1:6" s="6" customFormat="1">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
+      </c>
+      <c r="E24" s="6">
+        <v>6</v>
+      </c>
+      <c r="F24" s="8">
+        <f>IF(IF(RIGHT($A24,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C24), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C24), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A24,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C24), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C24), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="6" customFormat="1">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
+      </c>
+      <c r="E25" s="6">
+        <v>6</v>
+      </c>
+      <c r="F25" s="8">
+        <f>IF(IF(RIGHT($A25,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C25), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C25), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A25,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C25), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C25), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="6" customFormat="1">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
+      </c>
+      <c r="E26" s="6">
+        <v>4</v>
+      </c>
+      <c r="F26" s="8">
+        <f>IF(IF(RIGHT($A26,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A26,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="6" customFormat="1">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4</v>
+      </c>
+      <c r="F27" s="8">
+        <f>IF(IF(RIGHT($A27,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A27,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="6" customFormat="1">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
+      </c>
+      <c r="E28" s="6">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8">
+        <f>IF(IF(RIGHT($A28,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A28,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="6" customFormat="1">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4</v>
+      </c>
+      <c r="F29" s="8">
+        <f>IF(IF(RIGHT($A29,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A29,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="6" customFormat="1">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
+      </c>
+      <c r="E30" s="6">
+        <v>4</v>
+      </c>
+      <c r="F30" s="8">
+        <f>IF(IF(RIGHT($A30,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C30), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C30), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A30,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C30), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C30), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="6" customFormat="1">
+      <c r="A31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="6">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
+      </c>
+      <c r="E31" s="6">
+        <v>4</v>
+      </c>
+      <c r="F31" s="8">
+        <f>IF(IF(RIGHT($A31,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A31,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="6" customFormat="1">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Scented Marker 10 Colors</v>
+      </c>
+      <c r="E32" s="6">
+        <v>4</v>
+      </c>
+      <c r="F32" s="8">
+        <f>IF(IF(RIGHT($A32,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A32,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="6" customFormat="1">
+      <c r="A33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8">
+        <f>IF(IF(RIGHT($A33,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C33), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C33), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A33,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C33), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C33), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="6" customFormat="1">
+      <c r="A34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C24), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
-      </c>
-      <c r="E24">
+      <c r="C34" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Scented Sparkle Pen, 5Pck</v>
+      </c>
+      <c r="E34" s="6">
+        <v>8</v>
+      </c>
+      <c r="F34" s="8">
+        <f>IF(IF(RIGHT($A34,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A34,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="6" customFormat="1">
+      <c r="A35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="6">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Scented Swirl Pen, 5Pck</v>
+      </c>
+      <c r="E35" s="6">
+        <v>8</v>
+      </c>
+      <c r="F35" s="8">
+        <f>IF(IF(RIGHT($A35,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A35,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="6" customFormat="1">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>Scented Stacking Highlighters - 2-pack</v>
+      </c>
+      <c r="E36" s="6">
         <v>4</v>
       </c>
-      <c r="F24" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C24, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C24), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F36" s="8">
+        <f>IF(IF(RIGHT($A36,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A36,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25">
+    <row r="37" spans="1:6" s="6" customFormat="1">
+      <c r="A37" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C25), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends - In Bloom</v>
-      </c>
-      <c r="E25">
-        <v>6</v>
-      </c>
-      <c r="F25" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C25, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C25), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E37" s="6">
+        <v>4</v>
+      </c>
+      <c r="F37" s="8">
+        <f>IF(IF(RIGHT($A37,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A37,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
+    <row r="38" spans="1:6" s="6" customFormat="1">
+      <c r="A38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C26), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with  Essential Oil Blends - Citrus Grove</v>
-      </c>
-      <c r="E26">
-        <v>6</v>
-      </c>
-      <c r="F26" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C26, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C26), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C38" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+      </c>
+      <c r="E38" s="6">
+        <v>4</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IF(IF(RIGHT($A38,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A38,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27">
+    <row r="39" spans="1:6" s="6" customFormat="1">
+      <c r="A39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C27), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Blue / Green) </v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C27, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C27), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+      <c r="C39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8">
+        <f>IF(IF(RIGHT($A39,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A39,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28">
+    <row r="40" spans="1:6" s="6" customFormat="1">
+      <c r="A40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C28), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Lava Pen Set- 5-pack (Brights)</v>
-      </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C28, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C28), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>10</v>
+      <c r="C40" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+      </c>
+      <c r="E40" s="6">
+        <v>8</v>
+      </c>
+      <c r="F40" s="8">
+        <f>IF(IF(RIGHT($A40,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C40), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C40), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A40,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C40), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C40), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29">
+    <row r="41" spans="1:6" s="6" customFormat="1">
+      <c r="A41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C29), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Rub &amp; Sniff™ Scented Colored Pencils - 10-pack (Classic Palette)</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C29, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C29), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C41" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+      </c>
+      <c r="E41" s="6">
+        <v>8</v>
+      </c>
+      <c r="F41" s="8">
+        <f>IF(IF(RIGHT($A41,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C41), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C41), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A41,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C41), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C41), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30">
+    <row r="42" spans="1:6" s="6" customFormat="1">
+      <c r="A42" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C30), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Pen Diffuser with Essential Oil Blends -  Spiced Chai Latte</v>
-      </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C30, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C30), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E42" s="6">
+        <v>8</v>
+      </c>
+      <c r="F42" s="8">
+        <f>IF(IF(RIGHT($A42,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C42), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C42), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A42,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C42), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C42), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31">
+    <row r="43" spans="1:6" s="6" customFormat="1">
+      <c r="A43" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C31), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set- 5-pack </v>
-      </c>
-      <c r="E31">
+      <c r="C43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E43" s="6">
         <v>4</v>
       </c>
-      <c r="F31" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C31, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C31), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>10</v>
+      <c r="F43" s="8">
+        <f>IF(IF(RIGHT($A43,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C43), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C43), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A43,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C43), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C43), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32">
+    <row r="44" spans="1:6" s="6" customFormat="1">
+      <c r="A44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C32), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v xml:space="preserve">Scented Lava Pen Set - 2-pack (Pink / Purple) </v>
-      </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C32, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C32), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C44" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+      </c>
+      <c r="E44" s="6">
+        <v>8</v>
+      </c>
+      <c r="F44" s="8">
+        <f>IF(IF(RIGHT($A44,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C44), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C44), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A44,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C44), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C44), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33">
+    <row r="45" spans="1:6" s="6" customFormat="1">
+      <c r="A45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C33), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Marker 10 Colors</v>
-      </c>
-      <c r="E33">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C33, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C33), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C45" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
+      </c>
+      <c r="E45" s="6">
+        <v>8</v>
+      </c>
+      <c r="F45" s="8">
+        <f>IF(IF(RIGHT($A45,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C45), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C45), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A45,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C45), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C45), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34">
+    <row r="46" spans="1:6" s="6" customFormat="1">
+      <c r="A46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C34), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>UNIVERSAL COUNTER DISPLAY - EMPTY</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C34, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C34), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>0</v>
+      <c r="C46" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+      </c>
+      <c r="E46" s="6">
+        <v>8</v>
+      </c>
+      <c r="F46" s="8">
+        <f>IF(IF(RIGHT($A46,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C46), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C46), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A46,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C46), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C46), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
+    <row r="47" spans="1:6" s="6" customFormat="1">
+      <c r="A47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C35), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Sparkle Pen, 5Pck</v>
-      </c>
-      <c r="E35">
-        <v>8</v>
-      </c>
-      <c r="F35" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C35, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C35), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>10</v>
+      <c r="C47" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+      </c>
+      <c r="E47" s="6">
+        <v>4</v>
+      </c>
+      <c r="F47" s="8">
+        <f>IF(IF(RIGHT($A47,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C47), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C47), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A47,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C47), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C47), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
+    <row r="48" spans="1:6" s="6" customFormat="1">
+      <c r="A48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C36), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Swirl Pen, 5Pck</v>
-      </c>
-      <c r="E36">
+      <c r="C48" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
+      </c>
+      <c r="E48" s="6">
         <v>8</v>
       </c>
-      <c r="F36" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C36, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C36), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>10</v>
+      <c r="F48" s="8">
+        <f>IF(IF(RIGHT($A48,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C48), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C48), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A48,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C48), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C48), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
+    <row r="49" spans="1:6" s="6" customFormat="1">
+      <c r="A49" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="6">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C37), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>Scented Stacking Highlighters - 2-pack</v>
-      </c>
-      <c r="E37">
+      <c r="C49" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+      </c>
+      <c r="E49" s="6">
         <v>4</v>
       </c>
-      <c r="F37" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C37, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C37), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F49" s="8">
+        <f>IF(IF(RIGHT($A49,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A49,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+    <row r="50" spans="1:6" s="6" customFormat="1">
+      <c r="A50" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B50" s="6">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+      </c>
+      <c r="E50" s="6">
+        <v>4</v>
+      </c>
+      <c r="F50" s="8">
+        <f>IF(IF(RIGHT($A50,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A50,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="6" customFormat="1">
+      <c r="A51" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C38" s="1">
-        <v>165005</v>
-      </c>
-      <c r="D38" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C38), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E38">
-        <v>4</v>
-      </c>
-      <c r="F38" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C38, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C38), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C51" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
+      </c>
+      <c r="E51" s="6">
+        <v>8</v>
+      </c>
+      <c r="F51" s="8">
+        <f>IF(IF(RIGHT($A51,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A51,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39">
+    <row r="52" spans="1:6" s="6" customFormat="1">
+      <c r="A52" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C39" s="1">
-        <v>165008</v>
-      </c>
-      <c r="D39" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C39), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E39">
-        <v>4</v>
-      </c>
-      <c r="F39" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C39, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C39), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E52" s="6">
+        <v>8</v>
+      </c>
+      <c r="F52" s="8">
+        <f>IF(IF(RIGHT($A52,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C52), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C52), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A52,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C52), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C52), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40">
+    <row r="53" spans="1:6" s="6" customFormat="1">
+      <c r="A53" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C40), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C40, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C40), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>0</v>
+      <c r="C53" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+      </c>
+      <c r="E53" s="6">
+        <v>4</v>
+      </c>
+      <c r="F53" s="8">
+        <f>IF(IF(RIGHT($A53,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A53,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41">
+    <row r="54" spans="1:6" s="6" customFormat="1">
+      <c r="A54" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C41), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E41">
-        <v>8</v>
-      </c>
-      <c r="F41" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C41, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C41), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C54" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E54" s="6">
+        <v>4</v>
+      </c>
+      <c r="F54" s="8">
+        <f>IF(IF(RIGHT($A54,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C54), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C54), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A54,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C54), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C54), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42">
+    <row r="55" spans="1:6" s="6" customFormat="1">
+      <c r="A55" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C42), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E42">
-        <v>8</v>
-      </c>
-      <c r="F42" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C42, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C42), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C55" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D55" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+      </c>
+      <c r="E55" s="6">
+        <v>4</v>
+      </c>
+      <c r="F55" s="8">
+        <f>IF(IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A55,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43">
+    <row r="56" spans="1:6" s="6" customFormat="1">
+      <c r="A56" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C43), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E43">
-        <v>8</v>
-      </c>
-      <c r="F43" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C43, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C43), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E56" s="6">
+        <v>4</v>
+      </c>
+      <c r="F56" s="8">
+        <f>IF(IF(RIGHT($A56,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A56,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44">
+    <row r="57" spans="1:6" s="6" customFormat="1">
+      <c r="A57" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C44), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
-      </c>
-      <c r="E44">
-        <v>4</v>
-      </c>
-      <c r="F44" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C44, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C44), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C57" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+      </c>
+      <c r="E57" s="6">
+        <v>8</v>
+      </c>
+      <c r="F57" s="8">
+        <f>IF(IF(RIGHT($A57,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A57,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45">
+    <row r="58" spans="1:6" s="6" customFormat="1">
+      <c r="A58" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C58" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D45" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C45), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+      <c r="D58" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
         <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
       </c>
-      <c r="E45">
+      <c r="E58" s="6">
         <v>8</v>
       </c>
-      <c r="F45" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C45, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C45), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F58" s="8">
+        <f>IF(IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A58,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46">
+    <row r="59" spans="1:6" s="6" customFormat="1">
+      <c r="A59" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C46), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
-      </c>
-      <c r="E46">
-        <v>8</v>
-      </c>
-      <c r="F46" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C46, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C46), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C59" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+      </c>
+      <c r="E59" s="6">
+        <v>4</v>
+      </c>
+      <c r="F59" s="8">
+        <f>IF(IF(RIGHT($A59,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A59,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47">
+    <row r="60" spans="1:6" s="6" customFormat="1">
+      <c r="A60" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C47), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
-      </c>
-      <c r="E47">
-        <v>8</v>
-      </c>
-      <c r="F47" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C47, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C47), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="C60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E60" s="6">
+        <v>4</v>
+      </c>
+      <c r="F60" s="8">
+        <f>IF(IF(RIGHT($A60,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A60,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48">
+    <row r="61" spans="1:6" s="6" customFormat="1">
+      <c r="A61" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C48), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
-      </c>
-      <c r="E48">
+      <c r="C61" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+      </c>
+      <c r="E61" s="6">
         <v>4</v>
       </c>
-      <c r="F48" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C48, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C48), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C49), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Tropical Paradise</v>
-      </c>
-      <c r="E49">
-        <v>8</v>
-      </c>
-      <c r="F49" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C49, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C49), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C50), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
-      </c>
-      <c r="E50">
-        <v>4</v>
-      </c>
-      <c r="F50" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C50, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C50), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B51">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C51), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
-      </c>
-      <c r="E51">
-        <v>4</v>
-      </c>
-      <c r="F51" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C51, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C51), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C52), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E52">
-        <v>8</v>
-      </c>
-      <c r="F52" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C52, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C52), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C53), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E53">
-        <v>8</v>
-      </c>
-      <c r="F53" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C53, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C53), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C54), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E54">
-        <v>4</v>
-      </c>
-      <c r="F54" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C54, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C54), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C55" s="1">
-        <v>165005</v>
-      </c>
-      <c r="D55" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C55), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C55, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C55), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C56" s="1">
-        <v>165008</v>
-      </c>
-      <c r="D56" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C56), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E56">
-        <v>4</v>
-      </c>
-      <c r="F56" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C56, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C56), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C57), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
-      </c>
-      <c r="E57">
-        <v>4</v>
-      </c>
-      <c r="F57" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C57, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C57), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C58), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Americana</v>
-      </c>
-      <c r="E58">
-        <v>4</v>
-      </c>
-      <c r="F58" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C58, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C58), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C59), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
-      </c>
-      <c r="E59">
-        <v>8</v>
-      </c>
-      <c r="F59" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C59, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C59), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D60" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C60), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
-      </c>
-      <c r="E60">
-        <v>8</v>
-      </c>
-      <c r="F60" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C60, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C60), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C61), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
-      </c>
-      <c r="E61">
-        <v>4</v>
-      </c>
-      <c r="F61" s="2">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
+      <c r="F61" s="8">
+        <f>IF(IF(RIGHT($A61,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A61,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C61, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C61), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>6.5</v>
       </c>
     </row>
     <row r="62" spans="1:6" s="6" customFormat="1">
       <c r="A62" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B62" s="6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D62" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C62), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
       </c>
       <c r="E62" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F62" s="8">
-        <f>ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)</f>
-        <v>6.5</v>
+        <f>IF(IF(RIGHT($A62,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A62,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C62, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C62), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
+    <row r="63" spans="1:6" s="6" customFormat="1">
+      <c r="A63" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D63" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Botanicals</v>
-      </c>
-      <c r="E63">
-        <v>8</v>
-      </c>
-      <c r="F63" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
-        <v>51</v>
-      </c>
-      <c r="B64">
+      <c r="B63" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Galaxy [Metallic ink]</v>
-      </c>
-      <c r="E64">
+      <c r="C63" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C63), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
+      </c>
+      <c r="E63" s="6">
         <v>12</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F63" s="8">
+        <f>IF(IF(RIGHT($A63,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A63,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C63, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C63), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+    <row r="64" spans="1:6" s="6" customFormat="1">
+      <c r="A64" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B65">
+      <c r="B64" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D65" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Landscapes</v>
-      </c>
-      <c r="E65">
-        <v>8</v>
-      </c>
-      <c r="F65" s="2">
+      <c r="C64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C64), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
+      </c>
+      <c r="E64" s="6">
+        <v>12</v>
+      </c>
+      <c r="F64" s="8">
+        <f>IF(IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A64,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C64, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C64), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+    <row r="65" spans="1:6" s="6" customFormat="1">
+      <c r="A65" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B66">
+      <c r="B65" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Wags &amp; Whiskers</v>
-      </c>
-      <c r="E66">
-        <v>12</v>
-      </c>
-      <c r="F66" s="2">
+      <c r="C65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C65), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
+      </c>
+      <c r="E65" s="6">
+        <v>4</v>
+      </c>
+      <c r="F65" s="8">
+        <f>IF(IF(RIGHT($A65,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A65,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C65, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C65), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+    <row r="66" spans="1:6" s="6" customFormat="1">
+      <c r="A66" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B67">
+      <c r="B66" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Into the Deep [Metallic ink]</v>
-      </c>
-      <c r="E67">
+      <c r="C66" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C66), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
+      </c>
+      <c r="E66" s="6">
         <v>12</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F66" s="8">
+        <f>IF(IF(RIGHT($A66,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A66,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C66, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C66), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
+    <row r="67" spans="1:6" s="6" customFormat="1">
+      <c r="A67" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B68">
+      <c r="B67" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fragrant Blooms</v>
-      </c>
-      <c r="E68">
+      <c r="C67" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C67), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
+      </c>
+      <c r="E67" s="6">
         <v>4</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F67" s="8">
+        <f>IF(IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A67,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C67, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C67), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+    <row r="68" spans="1:6" s="6" customFormat="1">
+      <c r="A68" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B69">
+      <c r="B68" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D69" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Day at the Beach</v>
-      </c>
-      <c r="E69">
-        <v>12</v>
-      </c>
-      <c r="F69" s="2">
+      <c r="C68" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C68), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
+      </c>
+      <c r="E68" s="6">
+        <v>8</v>
+      </c>
+      <c r="F68" s="8">
+        <f>IF(IF(RIGHT($A68,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A68,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C68, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C68), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+    <row r="69" spans="1:6" s="6" customFormat="1">
+      <c r="A69" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B70">
+      <c r="B69" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D70" t="str">
+      <c r="C69" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C69), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
+      </c>
+      <c r="E69" s="6">
+        <v>12</v>
+      </c>
+      <c r="F69" s="8">
+        <f>IF(IF(RIGHT($A69,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A69,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C69, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C69), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" s="6" customFormat="1">
+      <c r="A70" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C70), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Citrus Coastlines</v>
-      </c>
-      <c r="E70">
-        <v>8</v>
-      </c>
-      <c r="F70" s="2">
+        <v>FlowArt - Spinner Tower - Empty</v>
+      </c>
+      <c r="E70" s="6">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8">
+        <f>IF(IF(RIGHT($A70,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A70,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C70, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C70), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" s="6" customFormat="1">
+      <c r="A71" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" s="6">
+        <f t="shared" ref="B71:B124" si="1">IF(A70=A71, B70+1, 1)</f>
+        <v>10</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
+      </c>
+      <c r="E71" s="6">
+        <v>12</v>
+      </c>
+      <c r="F71" s="8">
+        <f>IF(IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A71,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C71), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+    <row r="72" spans="1:6" s="6" customFormat="1">
+      <c r="A72" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B71">
-        <f t="shared" ref="B71:B124" si="1">IF(A70=A71, B70+1, 1)</f>
-        <v>9</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D71" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C71, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C71), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Groove, Jungle Oasis</v>
-      </c>
-      <c r="E71">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D72" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Trace-By-Line, Brunch in Bloom</v>
-      </c>
-      <c r="E72">
-        <v>12</v>
-      </c>
-      <c r="F72" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>51</v>
-      </c>
-      <c r="B73">
+      <c r="B72" s="6">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" t="str">
+      <c r="C72" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D72" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C72), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
+      </c>
+      <c r="E72" s="6">
+        <v>12</v>
+      </c>
+      <c r="F72" s="8">
+        <f>IF(IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A72,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C72, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C72), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="6" customFormat="1">
+      <c r="A73" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B73" s="6">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C73), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Cozy Cottage</v>
-      </c>
-      <c r="E73">
-        <v>12</v>
-      </c>
-      <c r="F73" s="2">
+        <v>FlowArt: Color-to-Reveal, Animals</v>
+      </c>
+      <c r="E73" s="6">
+        <v>4</v>
+      </c>
+      <c r="F73" s="8">
+        <f>IF(IF(RIGHT($A73,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C73), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C73), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A73,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C73), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C73, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C73), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+    <row r="74" spans="1:6" s="6" customFormat="1">
+      <c r="A74" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="6">
         <f>IF(A73=A74, B73+1, 1)</f>
-        <v>12</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D74" t="str">
+        <v>13</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D74" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C74), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt - Spinner Tower - Empty</v>
-      </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74" s="2">
-        <v>0</v>
+        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
+      </c>
+      <c r="E74" s="6">
+        <v>8</v>
+      </c>
+      <c r="F74" s="8">
+        <f>IF(IF(RIGHT($A74,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C74), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C74), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A74,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C74), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C74, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C74), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+    <row r="75" spans="1:6" s="6" customFormat="1">
+      <c r="A75" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B75">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D75" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Majestic Earth [Metallic ink]</v>
-      </c>
-      <c r="E75">
-        <v>12</v>
-      </c>
-      <c r="F75" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
-        <v>51</v>
-      </c>
-      <c r="B76">
+      <c r="B75" s="6">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D76" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Moonlit Garden [Metallic ink]</v>
-      </c>
-      <c r="E76">
+      <c r="C75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C75), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
+      </c>
+      <c r="E75" s="6">
         <v>12</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F75" s="8">
+        <f>IF(IF(RIGHT($A75,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A75,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C75, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C75), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+    <row r="76" spans="1:6" s="6" customFormat="1">
+      <c r="A76" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B77">
+      <c r="B76" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Animals</v>
-      </c>
-      <c r="E77">
-        <v>8</v>
-      </c>
-      <c r="F77" s="2">
+      <c r="C76" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C76), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+      </c>
+      <c r="E76" s="6">
+        <v>12</v>
+      </c>
+      <c r="F76" s="8">
+        <f>IF(IF(RIGHT($A76,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C76), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C76), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A76,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C76), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C76, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C76), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+    <row r="77" spans="1:6" s="6" customFormat="1">
+      <c r="A77" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B78">
+      <c r="B77" s="6">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D78" t="str">
-        <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Color-to-Reveal, Fall is in the Air [Scented]</v>
-      </c>
-      <c r="E78">
-        <v>8</v>
-      </c>
-      <c r="F78" s="2">
+      <c r="C77" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C77), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Trace-By-Line, Fall Harvest</v>
+      </c>
+      <c r="E77" s="6">
+        <v>16</v>
+      </c>
+      <c r="F77" s="8">
+        <f>IF(IF(RIGHT($A77,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A77,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C77, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C77), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+    <row r="78" spans="1:6" s="6" customFormat="1">
+      <c r="A78" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B79">
+      <c r="B78" s="6">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" t="str">
+      <c r="C78" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C78), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Pumpkins &amp; Pastures</v>
+      </c>
+      <c r="E78" s="6">
+        <v>4</v>
+      </c>
+      <c r="F78" s="8">
+        <f>IF(IF(RIGHT($A78,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A78,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C78, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C78), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" s="6" customFormat="1">
+      <c r="A79" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B79" s="6">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C79), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Sweater Weather [2026]</v>
-      </c>
-      <c r="E79">
-        <v>8</v>
-      </c>
-      <c r="F79" s="2">
+        <v>FlowArt: Dot-By-Letter, Strolling through Fall</v>
+      </c>
+      <c r="E79" s="6">
+        <v>4</v>
+      </c>
+      <c r="F79" s="8">
+        <f>IF(IF(RIGHT($A79,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A79,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C79, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C79), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" s="6" customFormat="1">
       <c r="A80" s="6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B80" s="6">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D80" s="6" t="str">
         <f>IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C80), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
-        <v>FlowArt: Dot-By-Letter, Everyday Inspiration</v>
+        <v>Scented Stacking Highlighters - 2-pack</v>
       </c>
       <c r="E80" s="6">
+        <v>4</v>
+      </c>
+      <c r="F80" s="8">
+        <f>IF(IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A80,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C80, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C80), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" s="6" customFormat="1">
+      <c r="A81" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="6">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C81), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Illuminate &amp; Create, Wildlife</v>
+      </c>
+      <c r="E81" s="6">
+        <v>4</v>
+      </c>
+      <c r="F81" s="8">
+        <f>IF(IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A81,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C81, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C81), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" s="6" customFormat="1">
+      <c r="A82" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C82), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Pogo-Dot, Nature</v>
+      </c>
+      <c r="E82" s="6">
+        <v>4</v>
+      </c>
+      <c r="F82" s="8">
+        <f>IF(IF(RIGHT($A82,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A82,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C82, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C82), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" s="6" customFormat="1">
+      <c r="A83" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C83), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Landscapes</v>
+      </c>
+      <c r="E83" s="6">
+        <v>4</v>
+      </c>
+      <c r="F83" s="8">
+        <f>IF(IF(RIGHT($A83,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A83,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C83, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C83), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" s="6" customFormat="1">
+      <c r="A84" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" s="6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D84" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C84), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Illuminate &amp; Create, Foliage and Flowers</v>
+      </c>
+      <c r="E84" s="6">
+        <v>4</v>
+      </c>
+      <c r="F84" s="8">
+        <f>IF(IF(RIGHT($A84,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A84,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C84, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C84), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" s="6" customFormat="1">
+      <c r="A85" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C85), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Color-to-Reveal, Animals</v>
+      </c>
+      <c r="E85" s="6">
+        <v>4</v>
+      </c>
+      <c r="F85" s="8">
+        <f>IF(IF(RIGHT($A85,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A85,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C85, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C85), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" s="6" customFormat="1">
+      <c r="A86" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="6" t="str">
+        <f>IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$G, 2, FALSE), VLOOKUP(VALUE($C86), [1]SBOM!$F:$G, 2, FALSE)), "")</f>
+        <v>FlowArt: Dot-By-Letter, Botanicals</v>
+      </c>
+      <c r="E86" s="6">
+        <v>4</v>
+      </c>
+      <c r="F86" s="8">
+        <f>IF(IF(RIGHT($A86,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C86), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C86), [1]SBOM!$F:$P, 11, FALSE)), 0), 2))&lt;0, 0, IF(RIGHT($A86,5)="FA160", ROUND(IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C86), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)-1.5, ROUND(IFERROR(IFERROR(VLOOKUP($C86, [1]SBOM!$F:$P, 11, FALSE),VLOOKUP(VALUE($C86), [1]SBOM!$F:$P, 11, FALSE)), 0), 2)))</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" s="6" customFormat="1">
+      <c r="A87" s="6" t="s">
+        <v>65</v>
+      </c>
+  